--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9D6D7D-B030-41B2-8C4D-75902328779C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC68309-215F-42BA-9488-DE35265B5F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danske backdrops" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="796">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -40,15 +40,18 @@
     <t>Note</t>
   </si>
   <si>
+    <t>1 døgn, 2 hold, 3 dyr</t>
+  </si>
+  <si>
+    <t>Åbn backdrop</t>
+  </si>
+  <si>
     <t>1000 års kunsthistorie</t>
   </si>
   <si>
     <t>1000 Års Kunsthistorie</t>
   </si>
   <si>
-    <t>Åbn backdrop</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -142,12 +145,24 @@
     <t>Alvin Og De Frække Jordegern</t>
   </si>
   <si>
+    <t>alvinnn!!! og de frække jordegern</t>
+  </si>
+  <si>
+    <t>ALVINNN!!! Og de frække jordegern</t>
+  </si>
+  <si>
     <t>alvinnn!!! og gjengen</t>
   </si>
   <si>
     <t>Alvinnn!!! Og Gjengen</t>
   </si>
   <si>
+    <t>ambulancen - liv eller død</t>
+  </si>
+  <si>
+    <t>Ambulancen - liv eller død</t>
+  </si>
+  <si>
     <t>andre rieu: welcome to my world</t>
   </si>
   <si>
@@ -172,12 +187,24 @@
     <t>Arn - Tempelridderen</t>
   </si>
   <si>
+    <t>asterix &amp; obelix i dragens rige</t>
+  </si>
+  <si>
+    <t>Asterix &amp; Obelix i dragens rige</t>
+  </si>
+  <si>
     <t>asterix: sejren over cæsar</t>
   </si>
   <si>
     <t>Asterix: Sejren over Cæsar</t>
   </si>
   <si>
+    <t>astérix &amp; obélix: l'empire du milieu</t>
+  </si>
+  <si>
+    <t>Astérix &amp; Obélix: L'empire du milieu</t>
+  </si>
+  <si>
     <t>bag stjernerne</t>
   </si>
   <si>
@@ -226,6 +253,12 @@
     <t>Beliggenhed, Beliggenhed, Beliggenhed - Sommerhuse</t>
   </si>
   <si>
+    <t>bennys badekar</t>
+  </si>
+  <si>
+    <t>Bennys badekar</t>
+  </si>
+  <si>
     <t>bering sea gold</t>
   </si>
   <si>
@@ -298,6 +331,12 @@
     <t>Charterfeber Danmark</t>
   </si>
   <si>
+    <t>cirkus summarum</t>
+  </si>
+  <si>
+    <t>Cirkus Summarum</t>
+  </si>
+  <si>
     <t>cirkusrevyen 2024</t>
   </si>
   <si>
@@ -316,6 +355,12 @@
     <t>Conquistadorernes Storhed Og Fald</t>
   </si>
   <si>
+    <t>dag og nat</t>
+  </si>
+  <si>
+    <t>Dag og nat</t>
+  </si>
+  <si>
     <t>dage i haven</t>
   </si>
   <si>
@@ -394,6 +439,18 @@
     <t>Den Utrolige Dr. Pol</t>
   </si>
   <si>
+    <t>den utrolige historie om den kæmpestore pære</t>
+  </si>
+  <si>
+    <t>Den utrolige historie om den kæmpestore pære</t>
+  </si>
+  <si>
+    <t>den utrolige historien om den kjempestore pæra</t>
+  </si>
+  <si>
+    <t>Den utrolige historien om den kjempestore pæra</t>
+  </si>
+  <si>
     <t>der er et yndigt land</t>
   </si>
   <si>
@@ -430,6 +487,18 @@
     <t>Dexter: Resurrection</t>
   </si>
   <si>
+    <t>dicte</t>
+  </si>
+  <si>
+    <t>Dicte</t>
+  </si>
+  <si>
+    <t>doktor mcstuffins</t>
+  </si>
+  <si>
+    <t>Doktor McStuffins</t>
+  </si>
+  <si>
     <t>drabschef wisting</t>
   </si>
   <si>
@@ -526,6 +595,12 @@
     <t>Ekstreme Samlere</t>
   </si>
   <si>
+    <t>et hus af ler</t>
+  </si>
+  <si>
+    <t>Et hus af ler</t>
+  </si>
+  <si>
     <t>et råb om håb</t>
   </si>
   <si>
@@ -550,6 +625,12 @@
     <t>Fabeldyr: Grindelwalds Forbrytelser</t>
   </si>
   <si>
+    <t>fabeldyr: humlesnurrs hemmeligheter</t>
+  </si>
+  <si>
+    <t>Fabeldyr: Humlesnurrs hemmeligheter</t>
+  </si>
+  <si>
     <t>familien addams</t>
   </si>
   <si>
@@ -574,6 +655,12 @@
     <t>Familien Hardacre</t>
   </si>
   <si>
+    <t>familien thunderman</t>
+  </si>
+  <si>
+    <t>Familien Thunderman</t>
+  </si>
+  <si>
     <t>fanget på politiets kamera</t>
   </si>
   <si>
@@ -598,6 +685,12 @@
     <t>Fantastiske Skabninger Og Hvor De Findes</t>
   </si>
   <si>
+    <t>fantastiske skabninger: dumbledores hemmeligheder</t>
+  </si>
+  <si>
+    <t>Fantastiske skabninger: Dumbledores hemmeligheder</t>
+  </si>
+  <si>
     <t>fantastiske skabninger: grindelwalds forbrydelser</t>
   </si>
   <si>
@@ -622,12 +715,24 @@
     <t>Far Til Fire - På Japansk</t>
   </si>
   <si>
+    <t>far til fire - på toppen</t>
+  </si>
+  <si>
+    <t>Far til fire - på toppen</t>
+  </si>
+  <si>
     <t>far til fire på landet</t>
   </si>
   <si>
     <t>Far Til Fire På Landet</t>
   </si>
   <si>
+    <t>far til fire på toppen</t>
+  </si>
+  <si>
+    <t>Far til fire på toppen</t>
+  </si>
+  <si>
     <t>faraoer i krig</t>
   </si>
   <si>
@@ -664,6 +769,12 @@
     <t>Flådens Historie</t>
   </si>
   <si>
+    <t>for lækker til love</t>
+  </si>
+  <si>
+    <t>For lækker til love</t>
+  </si>
+  <si>
     <t>formel 1</t>
   </si>
   <si>
@@ -694,6 +805,12 @@
     <t>Forsvundne Arvinger</t>
   </si>
   <si>
+    <t>fortidens fantastiske ingeniørkunst</t>
+  </si>
+  <si>
+    <t>Fortidens fantastiske ingeniørkunst</t>
+  </si>
+  <si>
     <t>fra 1-værelses til strandvejsvilla</t>
   </si>
   <si>
@@ -718,6 +835,12 @@
     <t>Frank &amp; Kastaniegaarden</t>
   </si>
   <si>
+    <t>frank hvam - nobody</t>
+  </si>
+  <si>
+    <t>Frank Hvam - Nobody</t>
+  </si>
+  <si>
     <t>franske drømmeslotte</t>
   </si>
   <si>
@@ -826,6 +949,12 @@
     <t>Hamster Og Grete</t>
   </si>
   <si>
+    <t>han, hun og drømmeslottet</t>
+  </si>
+  <si>
+    <t>Han, hun og drømmeslottet</t>
+  </si>
+  <si>
     <t>han, hun og drømmeslottet - på tur</t>
   </si>
   <si>
@@ -856,6 +985,12 @@
     <t>Helt Sort</t>
   </si>
   <si>
+    <t>helt super</t>
+  </si>
+  <si>
+    <t>Helt super</t>
+  </si>
+  <si>
     <t>hercule poirot</t>
   </si>
   <si>
@@ -880,12 +1015,30 @@
     <t>Hjørnebjørne</t>
   </si>
   <si>
+    <t>hotel romantik sverige</t>
+  </si>
+  <si>
+    <t>Hotel Romantik Sverige</t>
+  </si>
+  <si>
+    <t>hotell romantik</t>
+  </si>
+  <si>
+    <t>Hotell Romantik</t>
+  </si>
+  <si>
     <t>hunden ib</t>
   </si>
   <si>
     <t>Hunden Ib</t>
   </si>
   <si>
+    <t>huse med hemmeligheder</t>
+  </si>
+  <si>
+    <t>Huse med hemmeligheder</t>
+  </si>
+  <si>
     <t>huset på christianshavn</t>
   </si>
   <si>
@@ -898,6 +1051,12 @@
     <t>Huset På Prærien</t>
   </si>
   <si>
+    <t>husmorens storhed og fald</t>
+  </si>
+  <si>
+    <t>Husmorens storhed og fald</t>
+  </si>
+  <si>
     <t>hvem byder bedst</t>
   </si>
   <si>
@@ -910,18 +1069,36 @@
     <t>Hvem Byder Bedst?</t>
   </si>
   <si>
+    <t>hvem passer på grisene?</t>
+  </si>
+  <si>
+    <t>Hvem passer på grisene?</t>
+  </si>
+  <si>
     <t>hvem sjikanerer tove?</t>
   </si>
   <si>
     <t>Hvem Sjikanerer Tove?</t>
   </si>
   <si>
+    <t>hvem vil være millionær</t>
+  </si>
+  <si>
+    <t>Hvem vil være millionær</t>
+  </si>
+  <si>
     <t>hvem vil være millionær?</t>
   </si>
   <si>
     <t>Hvem Vil Være Millionær?</t>
   </si>
   <si>
+    <t>hvor er kylling</t>
+  </si>
+  <si>
+    <t>Hvor er Kylling</t>
+  </si>
+  <si>
     <t>hvor er kylling?</t>
   </si>
   <si>
@@ -946,6 +1123,12 @@
     <t>I En Klasse For Sig</t>
   </si>
   <si>
+    <t>i seriemördarens samling</t>
+  </si>
+  <si>
+    <t>I seriemördarens samling</t>
+  </si>
+  <si>
     <t>idas fristelser</t>
   </si>
   <si>
@@ -970,6 +1153,12 @@
     <t>Ingemann, Fyn &amp; Lolland-Falster</t>
   </si>
   <si>
+    <t>ja for fanø</t>
+  </si>
+  <si>
+    <t>Ja for Fanø</t>
+  </si>
+  <si>
     <t>ja for fanø!</t>
   </si>
   <si>
@@ -1000,6 +1189,18 @@
     <t>Jordemoderen</t>
   </si>
   <si>
+    <t>josef: drømmenes konge</t>
+  </si>
+  <si>
+    <t>Josef: Drømmenes konge</t>
+  </si>
+  <si>
+    <t>kald mig far</t>
+  </si>
+  <si>
+    <t>Kald mig far</t>
+  </si>
+  <si>
     <t>kasper og sofie</t>
   </si>
   <si>
@@ -1036,6 +1237,12 @@
     <t>Klovn</t>
   </si>
   <si>
+    <t>ko-bakken på sporet</t>
+  </si>
+  <si>
+    <t>Ko-bakken på sporet</t>
+  </si>
+  <si>
     <t>koch'en på toppen</t>
   </si>
   <si>
@@ -1066,6 +1273,12 @@
     <t>Kurs Mod Fjerne Kyster</t>
   </si>
   <si>
+    <t>kurs mod nord</t>
+  </si>
+  <si>
+    <t>Kurs mod nord</t>
+  </si>
+  <si>
     <t>kæledyrenes hemmelige liv 2</t>
   </si>
   <si>
@@ -1138,6 +1351,18 @@
     <t>Leonardo Da Vinci - Renæssancemenneske</t>
   </si>
   <si>
+    <t>leonardo da vinci - renæssancemenneske (3:4)</t>
+  </si>
+  <si>
+    <t>Leonardo da Vinci - Renæssancemenneske (3:4)</t>
+  </si>
+  <si>
+    <t>leonardo da vinci - renæssancemenneske (4:4)</t>
+  </si>
+  <si>
+    <t>Leonardo da Vinci - Renæssancemenneske (4:4)</t>
+  </si>
+  <si>
     <t>lille nørd</t>
   </si>
   <si>
@@ -1150,6 +1375,18 @@
     <t>Lille Prinsesse</t>
   </si>
   <si>
+    <t>lille virgil og orla frøsnapper</t>
+  </si>
+  <si>
+    <t>Lille Virgil og Orla Frøsnapper</t>
+  </si>
+  <si>
+    <t>linde på langeland</t>
+  </si>
+  <si>
+    <t>Linde på Langeland</t>
+  </si>
+  <si>
     <t>loppe deluxe</t>
   </si>
   <si>
@@ -1186,6 +1423,12 @@
     <t>Lykkehjulet</t>
   </si>
   <si>
+    <t>madagascar 3: efterlyst i hele europa</t>
+  </si>
+  <si>
+    <t>Madagascar 3: Efterlyst i hele Europa</t>
+  </si>
+  <si>
     <t>madde + truls</t>
   </si>
   <si>
@@ -1270,6 +1513,12 @@
     <t>Mille Og Dyrenes Planet</t>
   </si>
   <si>
+    <t>min kones ferie</t>
+  </si>
+  <si>
+    <t>Min kones ferie</t>
+  </si>
+  <si>
     <t>min søsters børn i afrika</t>
   </si>
   <si>
@@ -1396,6 +1645,12 @@
     <t>Nul Stjerner - Filler</t>
   </si>
   <si>
+    <t>nybyggerne</t>
+  </si>
+  <si>
+    <t>Nybyggerne</t>
+  </si>
+  <si>
     <t>når livet tager en drejning</t>
   </si>
   <si>
@@ -1432,6 +1687,12 @@
     <t>Oxen</t>
   </si>
   <si>
+    <t>paddington i peru</t>
+  </si>
+  <si>
+    <t>Paddington i Peru</t>
+  </si>
+  <si>
     <t>panda &amp; vennerne - lama alarm!</t>
   </si>
   <si>
@@ -1510,6 +1771,12 @@
     <t>Pippi Langstrømpe</t>
   </si>
   <si>
+    <t>podcast-mordet, der rystede verden</t>
+  </si>
+  <si>
+    <t>Podcast-mordet, der rystede verden</t>
+  </si>
+  <si>
     <t>poirot</t>
   </si>
   <si>
@@ -1540,6 +1807,18 @@
     <t>Pyjamasheltene V</t>
   </si>
   <si>
+    <t>ramses den store - kongen af egypten</t>
+  </si>
+  <si>
+    <t>Ramses den Store - Kongen af Egypten</t>
+  </si>
+  <si>
+    <t>ramses: egyptens store konge</t>
+  </si>
+  <si>
+    <t>Ramses: Egyptens store konge</t>
+  </si>
+  <si>
     <t>rasmus klump</t>
   </si>
   <si>
@@ -1570,6 +1849,12 @@
     <t>Renovating Mississippi</t>
   </si>
   <si>
+    <t>rig på sex</t>
+  </si>
+  <si>
+    <t>Rig på sex</t>
+  </si>
+  <si>
     <t>rip, rap og rup på eventyr</t>
   </si>
   <si>
@@ -1588,6 +1873,18 @@
     <t>Romerrigets Forsvundne Skatte</t>
   </si>
   <si>
+    <t>ronja räubertochter</t>
+  </si>
+  <si>
+    <t>Ronja Räubertochter</t>
+  </si>
+  <si>
+    <t>ronja røverdatter</t>
+  </si>
+  <si>
+    <t>Ronja Røverdatter</t>
+  </si>
+  <si>
     <t>rosa fra rouladegade</t>
   </si>
   <si>
@@ -1630,6 +1927,12 @@
     <t>Råttatouille</t>
   </si>
   <si>
+    <t>shaolin</t>
+  </si>
+  <si>
+    <t>Shaolin</t>
+  </si>
+  <si>
     <t>shetland</t>
   </si>
   <si>
@@ -1666,6 +1969,12 @@
     <t>Skjelvet</t>
   </si>
   <si>
+    <t>skyllet væk</t>
+  </si>
+  <si>
+    <t>Skyllet væk</t>
+  </si>
+  <si>
     <t>skæg med tal</t>
   </si>
   <si>
@@ -1684,6 +1993,12 @@
     <t>Snurre Snups Byggevenner</t>
   </si>
   <si>
+    <t>snydt til at smugle i dubai</t>
+  </si>
+  <si>
+    <t>Snydt til at smugle i Dubai</t>
+  </si>
+  <si>
     <t>som sunket i jorden</t>
   </si>
   <si>
@@ -1696,6 +2011,12 @@
     <t>Sommer I Magaluf</t>
   </si>
   <si>
+    <t>sommer til salg</t>
+  </si>
+  <si>
+    <t>Sommer til salg</t>
+  </si>
+  <si>
     <t>sommerdahl</t>
   </si>
   <si>
@@ -1726,18 +2047,42 @@
     <t>Spidey Og Hans Fantastiske Venner</t>
   </si>
   <si>
+    <t>spirit - en fri sjæl</t>
+  </si>
+  <si>
+    <t>Spirit - En fri sjæl</t>
+  </si>
+  <si>
     <t>sprinter galore</t>
   </si>
   <si>
     <t>Sprinter Galore</t>
   </si>
   <si>
+    <t>stikkeren</t>
+  </si>
+  <si>
+    <t>Stikkeren</t>
+  </si>
+  <si>
+    <t>stoltenberg</t>
+  </si>
+  <si>
+    <t>Stoltenberg</t>
+  </si>
+  <si>
     <t>store danskere</t>
   </si>
   <si>
     <t>Store danskere</t>
   </si>
   <si>
+    <t>store kanoner</t>
+  </si>
+  <si>
+    <t>Store kanoner</t>
+  </si>
+  <si>
     <t>store lars</t>
   </si>
   <si>
@@ -1750,6 +2095,12 @@
     <t>Stormester</t>
   </si>
   <si>
+    <t>stormester - en chance til</t>
+  </si>
+  <si>
+    <t>Stormester - en chance til</t>
+  </si>
+  <si>
     <t>stormester - vindernes vinder</t>
   </si>
   <si>
@@ -1768,6 +2119,12 @@
     <t>Superhelten Sprinter Galore</t>
   </si>
   <si>
+    <t>superhelteskolen</t>
+  </si>
+  <si>
+    <t>Superhelteskolen</t>
+  </si>
+  <si>
     <t>superhjälteskolan</t>
   </si>
   <si>
@@ -1810,6 +2167,12 @@
     <t>Svenske Krimsaker</t>
   </si>
   <si>
+    <t>sygeplejeskolen</t>
+  </si>
+  <si>
+    <t>Sygeplejeskolen</t>
+  </si>
+  <si>
     <t>syng 2</t>
   </si>
   <si>
@@ -1840,6 +2203,12 @@
     <t>The Mentalist</t>
   </si>
   <si>
+    <t>to på flugt</t>
+  </si>
+  <si>
+    <t>To på flugt</t>
+  </si>
+  <si>
     <t>toppen af toppen</t>
   </si>
   <si>
@@ -1870,6 +2239,12 @@
     <t>Universets Hemmeligheder</t>
   </si>
   <si>
+    <t>ups, vi er voksne</t>
+  </si>
+  <si>
+    <t>Ups, vi er voksne</t>
+  </si>
+  <si>
     <t>vegg vegg vegg</t>
   </si>
   <si>
@@ -1924,6 +2299,12 @@
     <t>Verdensmænd</t>
   </si>
   <si>
+    <t>verdensmænd - bobos surprise</t>
+  </si>
+  <si>
+    <t>Verdensmænd - Bobos surprise</t>
+  </si>
+  <si>
     <t>vestens vildeste hamster</t>
   </si>
   <si>
@@ -1972,10 +2353,22 @@
     <t>Vilde Kræ</t>
   </si>
   <si>
+    <t>vilde kræ i</t>
+  </si>
+  <si>
+    <t>Vilde Kræ I</t>
+  </si>
+  <si>
     <t>vilde vidunderlige danmark</t>
   </si>
   <si>
     <t>Vilde Vidunderlige Danmark</t>
+  </si>
+  <si>
+    <t>vintervejens helte</t>
+  </si>
+  <si>
+    <t>Vintervejens Helte</t>
   </si>
   <si>
     <t>voksne mennesker</t>
@@ -2381,8 +2774,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E330"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E396"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -2391,7 +2784,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2408,4166 +2801,5384 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>37</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>39</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>41</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>45</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>47</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>49</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>51</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>53</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>57</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>59</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>61</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>63</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>65</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>67</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>69</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>71</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>73</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>75</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>77</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>79</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>81</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>83</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>85</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>87</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>89</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>91</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>93</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>95</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>97</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>99</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>101</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>102</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>103</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>105</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>107</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>108</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>109</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>110</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>111</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>113</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>114</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>115</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>116</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>117</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>119</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>121</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>122</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>123</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>124</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>125</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>126</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>127</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>128</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>129</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>130</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>131</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>132</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>133</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>134</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>135</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>136</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>137</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>138</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>139</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>140</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>141</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>143</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>144</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>145</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>146</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>147</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>149</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>150</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>151</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>152</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>153</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>154</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>155</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>156</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>157</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>158</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>159</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>160</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>161</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>162</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>163</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>164</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>165</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>166</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>167</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>168</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>169</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>170</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>171</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>172</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
         <v>173</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>174</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
         <v>175</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>176</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
         <v>177</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>178</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
         <v>179</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="B89" t="s">
         <v>181</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>182</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>183</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>184</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B91" t="s">
         <v>185</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>186</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
         <v>187</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>188</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="B93" t="s">
         <v>189</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>190</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="B94" t="s">
         <v>191</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>192</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="B95" t="s">
         <v>193</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>194</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="B96" t="s">
         <v>195</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
         <v>196</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="B97" t="s">
         <v>197</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
         <v>198</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="B98" t="s">
         <v>199</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>200</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="B99" t="s">
         <v>201</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>202</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D99" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="B100" t="s">
         <v>203</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>204</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="B101" t="s">
         <v>205</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>206</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="B102" t="s">
         <v>207</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>208</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D102" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="B103" t="s">
         <v>209</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
         <v>210</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="B104" t="s">
         <v>211</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>212</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="B105" t="s">
         <v>213</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
         <v>214</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="B106" t="s">
         <v>215</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
         <v>216</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="B107" t="s">
         <v>217</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
         <v>218</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="B108" t="s">
         <v>219</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>220</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="B109" t="s">
         <v>221</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>222</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D109" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B110" t="s">
         <v>223</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>224</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B111" t="s">
         <v>225</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>226</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D111" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
         <v>227</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
         <v>228</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D112" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
         <v>229</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
         <v>230</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D113" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="B114" t="s">
         <v>231</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>232</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="B115" t="s">
         <v>233</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>234</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="B116" t="s">
         <v>235</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>236</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D116" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="B117" t="s">
         <v>237</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
         <v>238</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D117" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="B118" t="s">
         <v>239</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>240</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D118" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="B119" t="s">
         <v>241</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
         <v>242</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="B120" t="s">
         <v>243</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
         <v>244</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="B121" t="s">
         <v>245</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>246</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D121" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="B122" t="s">
         <v>247</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
         <v>248</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="B123" t="s">
         <v>249</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
         <v>250</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D123" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="B124" t="s">
         <v>251</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
         <v>252</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D124" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="B125" t="s">
         <v>253</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>254</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D125" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="B126" t="s">
         <v>255</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
         <v>256</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="B127" t="s">
         <v>257</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>258</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="B128" t="s">
         <v>259</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>260</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D128" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="B129" t="s">
         <v>261</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D129" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="B130" t="s">
         <v>263</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D130" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="B131" t="s">
         <v>265</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
         <v>266</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D131" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="B132" t="s">
         <v>267</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
         <v>268</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D132" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="B133" t="s">
         <v>269</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
         <v>270</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D133" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="B134" t="s">
         <v>271</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
         <v>272</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="B135" t="s">
         <v>273</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
         <v>274</v>
       </c>
-      <c r="C135" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="B136" t="s">
         <v>275</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
         <v>276</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="B137" t="s">
         <v>277</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
         <v>278</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D137" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="B138" t="s">
         <v>279</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
         <v>280</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="B139" t="s">
         <v>281</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
         <v>282</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="B140" t="s">
         <v>283</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
         <v>284</v>
       </c>
-      <c r="C140" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D140" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="B141" t="s">
         <v>285</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
         <v>286</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D141" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="B142" t="s">
         <v>287</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
         <v>288</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="B143" t="s">
         <v>289</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
         <v>290</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="B144" t="s">
         <v>291</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
         <v>292</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="B145" t="s">
         <v>293</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
         <v>294</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="B146" t="s">
         <v>295</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>296</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D146" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="B147" t="s">
         <v>297</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
         <v>298</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="B148" t="s">
         <v>299</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>300</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D148" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="B149" t="s">
         <v>301</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D149" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
         <v>302</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D149" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="B150" t="s">
         <v>303</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
         <v>304</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D150" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="B151" t="s">
         <v>305</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D151" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
         <v>306</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D151" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="B152" t="s">
         <v>307</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
         <v>308</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D152" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="B153" t="s">
         <v>309</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
         <v>310</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="B154" t="s">
         <v>311</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D154" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
         <v>312</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="B155" t="s">
         <v>313</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D155" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
         <v>314</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="B156" t="s">
         <v>315</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D156" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
         <v>316</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D156" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="B157" t="s">
         <v>317</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D157" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
         <v>318</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="B158" t="s">
         <v>319</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
         <v>320</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D158" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="B159" t="s">
         <v>321</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D159" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
         <v>322</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D159" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="B160" t="s">
         <v>323</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D160" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
         <v>324</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D160" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="B161" t="s">
         <v>325</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D161" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
         <v>326</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D161" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="B162" t="s">
         <v>327</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
         <v>328</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D162" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="B163" t="s">
         <v>329</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D163" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
         <v>330</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D163" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="B164" t="s">
         <v>331</v>
       </c>
-      <c r="B164" t="s">
+      <c r="C164" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
         <v>332</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D164" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="B165" t="s">
         <v>333</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C165" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D165" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
         <v>334</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D165" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="B166" t="s">
         <v>335</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D166" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
         <v>336</v>
       </c>
-      <c r="C166" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="B167" t="s">
         <v>337</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D167" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
         <v>338</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="B168" t="s">
         <v>339</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
         <v>340</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D168" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="B169" t="s">
         <v>341</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D169" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
         <v>342</v>
       </c>
-      <c r="C169" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="B170" t="s">
         <v>343</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
         <v>344</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D170" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="B171" t="s">
         <v>345</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
         <v>346</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="B172" t="s">
         <v>347</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
         <v>348</v>
       </c>
-      <c r="C172" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="B173" t="s">
         <v>349</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D173" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
         <v>350</v>
       </c>
-      <c r="C173" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="B174" t="s">
         <v>351</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D174" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
         <v>352</v>
       </c>
-      <c r="C174" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="B175" t="s">
         <v>353</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
         <v>354</v>
       </c>
-      <c r="C175" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="B176" t="s">
         <v>355</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
         <v>356</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="B177" t="s">
         <v>357</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D177" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
         <v>358</v>
       </c>
-      <c r="C177" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="B178" t="s">
         <v>359</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
         <v>360</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="B179" t="s">
         <v>361</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D179" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
         <v>362</v>
       </c>
-      <c r="C179" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="B180" t="s">
         <v>363</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D180" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
         <v>364</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="B181" t="s">
         <v>365</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D181" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
         <v>366</v>
       </c>
-      <c r="C181" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="B182" t="s">
         <v>367</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
         <v>368</v>
       </c>
-      <c r="C182" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="B183" t="s">
         <v>369</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D183" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
         <v>370</v>
       </c>
-      <c r="C183" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="B184" t="s">
         <v>371</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D184" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
         <v>372</v>
       </c>
-      <c r="C184" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="B185" t="s">
         <v>373</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D185" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
         <v>374</v>
       </c>
-      <c r="C185" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="B186" t="s">
         <v>375</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D186" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
         <v>376</v>
       </c>
-      <c r="C186" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="B187" t="s">
         <v>377</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
         <v>378</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="B188" t="s">
         <v>379</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
         <v>380</v>
       </c>
-      <c r="C188" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="B189" t="s">
         <v>381</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
         <v>382</v>
       </c>
-      <c r="C189" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="B190" t="s">
         <v>383</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
         <v>384</v>
       </c>
-      <c r="C190" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+      <c r="B191" t="s">
         <v>385</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
         <v>386</v>
       </c>
-      <c r="C191" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+      <c r="B192" t="s">
         <v>387</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C192" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
         <v>388</v>
       </c>
-      <c r="C192" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="B193" t="s">
         <v>389</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
         <v>390</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="B194" t="s">
         <v>391</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
         <v>392</v>
       </c>
-      <c r="C194" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="B195" t="s">
         <v>393</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
         <v>394</v>
       </c>
-      <c r="C195" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+      <c r="B196" t="s">
         <v>395</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
         <v>396</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+      <c r="B197" t="s">
         <v>397</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
         <v>398</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+      <c r="B198" t="s">
         <v>399</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D198" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
         <v>400</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+      <c r="B199" t="s">
         <v>401</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C199" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
         <v>402</v>
       </c>
-      <c r="C199" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="B200" t="s">
         <v>403</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
         <v>404</v>
       </c>
-      <c r="C200" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D200" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+      <c r="B201" t="s">
         <v>405</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D201" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
         <v>406</v>
       </c>
-      <c r="C201" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
+      <c r="B202" t="s">
         <v>407</v>
       </c>
-      <c r="B202" t="s">
+      <c r="C202" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D202" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
         <v>408</v>
       </c>
-      <c r="C202" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
+      <c r="B203" t="s">
         <v>409</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
         <v>410</v>
       </c>
-      <c r="C203" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
+      <c r="B204" t="s">
         <v>411</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C204" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
         <v>412</v>
       </c>
-      <c r="C204" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
+      <c r="B205" t="s">
         <v>413</v>
       </c>
-      <c r="B205" t="s">
+      <c r="C205" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D205" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
         <v>414</v>
       </c>
-      <c r="C205" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
+      <c r="B206" t="s">
         <v>415</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D206" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
         <v>416</v>
       </c>
-      <c r="C206" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
+      <c r="B207" t="s">
         <v>417</v>
       </c>
-      <c r="B207" t="s">
+      <c r="C207" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D207" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
         <v>418</v>
       </c>
-      <c r="C207" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
+      <c r="B208" t="s">
         <v>419</v>
       </c>
-      <c r="B208" t="s">
+      <c r="C208" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D208" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
         <v>420</v>
       </c>
-      <c r="C208" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
+      <c r="B209" t="s">
         <v>421</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
         <v>422</v>
       </c>
-      <c r="C209" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
+      <c r="B210" t="s">
         <v>423</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
         <v>424</v>
       </c>
-      <c r="C210" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
+      <c r="B211" t="s">
         <v>425</v>
       </c>
-      <c r="B211" t="s">
+      <c r="C211" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
         <v>426</v>
       </c>
-      <c r="C211" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
+      <c r="B212" t="s">
         <v>427</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
         <v>428</v>
       </c>
-      <c r="C212" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
+      <c r="B213" t="s">
         <v>429</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D213" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
         <v>430</v>
       </c>
-      <c r="C213" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
+      <c r="B214" t="s">
         <v>431</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
         <v>432</v>
       </c>
-      <c r="C214" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
+      <c r="B215" t="s">
         <v>433</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C215" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D215" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
         <v>434</v>
       </c>
-      <c r="C215" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
+      <c r="B216" t="s">
         <v>435</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C216" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D216" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
         <v>436</v>
       </c>
-      <c r="C216" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
+      <c r="B217" t="s">
         <v>437</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
         <v>438</v>
       </c>
-      <c r="C217" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
+      <c r="B218" t="s">
         <v>439</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C218" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
         <v>440</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D218" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
+      <c r="B219" t="s">
         <v>441</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
         <v>442</v>
       </c>
-      <c r="C219" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D219" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
+      <c r="B220" t="s">
         <v>443</v>
       </c>
-      <c r="B220" t="s">
+      <c r="C220" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
         <v>444</v>
       </c>
-      <c r="C220" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
+      <c r="B221" t="s">
         <v>445</v>
       </c>
-      <c r="B221" t="s">
+      <c r="C221" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
         <v>446</v>
       </c>
-      <c r="C221" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
+      <c r="B222" t="s">
         <v>447</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
         <v>448</v>
       </c>
-      <c r="C222" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
+      <c r="B223" t="s">
         <v>449</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D223" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
         <v>450</v>
       </c>
-      <c r="C223" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D223" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
+      <c r="B224" t="s">
         <v>451</v>
       </c>
-      <c r="B224" t="s">
+      <c r="C224" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D224" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
         <v>452</v>
       </c>
-      <c r="C224" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D224" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
+      <c r="B225" t="s">
         <v>453</v>
       </c>
-      <c r="B225" t="s">
+      <c r="C225" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
         <v>454</v>
       </c>
-      <c r="C225" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
+      <c r="B226" t="s">
         <v>455</v>
       </c>
-      <c r="B226" t="s">
+      <c r="C226" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
         <v>456</v>
       </c>
-      <c r="C226" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
+      <c r="B227" t="s">
         <v>457</v>
       </c>
-      <c r="B227" t="s">
+      <c r="C227" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
         <v>458</v>
       </c>
-      <c r="C227" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
+      <c r="B228" t="s">
         <v>459</v>
       </c>
-      <c r="B228" t="s">
+      <c r="C228" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
         <v>460</v>
       </c>
-      <c r="C228" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
+      <c r="B229" t="s">
         <v>461</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D229" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
         <v>462</v>
       </c>
-      <c r="C229" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
+      <c r="B230" t="s">
         <v>463</v>
       </c>
-      <c r="B230" t="s">
+      <c r="C230" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
         <v>464</v>
       </c>
-      <c r="C230" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
+      <c r="B231" t="s">
         <v>465</v>
       </c>
-      <c r="B231" t="s">
+      <c r="C231" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
         <v>466</v>
       </c>
-      <c r="C231" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
+      <c r="B232" t="s">
         <v>467</v>
       </c>
-      <c r="B232" t="s">
+      <c r="C232" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D232" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
         <v>468</v>
       </c>
-      <c r="C232" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
+      <c r="B233" t="s">
         <v>469</v>
       </c>
-      <c r="B233" t="s">
+      <c r="C233" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D233" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
         <v>470</v>
       </c>
-      <c r="C233" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
+      <c r="B234" t="s">
         <v>471</v>
       </c>
-      <c r="B234" t="s">
+      <c r="C234" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
         <v>472</v>
       </c>
-      <c r="C234" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
+      <c r="B235" t="s">
         <v>473</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C235" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
         <v>474</v>
       </c>
-      <c r="C235" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
+      <c r="B236" t="s">
         <v>475</v>
       </c>
-      <c r="B236" t="s">
+      <c r="C236" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D236" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
         <v>476</v>
       </c>
-      <c r="C236" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
+      <c r="B237" t="s">
         <v>477</v>
       </c>
-      <c r="B237" t="s">
+      <c r="C237" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D237" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
         <v>478</v>
       </c>
-      <c r="C237" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
+      <c r="B238" t="s">
         <v>479</v>
       </c>
-      <c r="B238" t="s">
+      <c r="C238" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D238" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
         <v>480</v>
       </c>
-      <c r="C238" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
+      <c r="B239" t="s">
         <v>481</v>
       </c>
-      <c r="B239" t="s">
+      <c r="C239" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
         <v>482</v>
       </c>
-      <c r="C239" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
+      <c r="B240" t="s">
         <v>483</v>
       </c>
-      <c r="B240" t="s">
+      <c r="C240" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D240" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
         <v>484</v>
       </c>
-      <c r="C240" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
+      <c r="B241" t="s">
         <v>485</v>
       </c>
-      <c r="B241" t="s">
+      <c r="C241" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D241" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
         <v>486</v>
       </c>
-      <c r="C241" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
+      <c r="B242" t="s">
         <v>487</v>
       </c>
-      <c r="B242" t="s">
+      <c r="C242" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
         <v>488</v>
       </c>
-      <c r="C242" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
+      <c r="B243" t="s">
         <v>489</v>
       </c>
-      <c r="B243" t="s">
+      <c r="C243" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
         <v>490</v>
       </c>
-      <c r="C243" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
+      <c r="B244" t="s">
         <v>491</v>
       </c>
-      <c r="B244" t="s">
+      <c r="C244" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D244" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
         <v>492</v>
       </c>
-      <c r="C244" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
+      <c r="B245" t="s">
         <v>493</v>
       </c>
-      <c r="B245" t="s">
+      <c r="C245" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D245" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
         <v>494</v>
       </c>
-      <c r="C245" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D245" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+      <c r="B246" t="s">
         <v>495</v>
       </c>
-      <c r="B246" t="s">
+      <c r="C246" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D246" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
         <v>496</v>
       </c>
-      <c r="C246" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
+      <c r="B247" t="s">
         <v>497</v>
       </c>
-      <c r="B247" t="s">
+      <c r="C247" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D247" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
         <v>498</v>
       </c>
-      <c r="C247" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+      <c r="B248" t="s">
         <v>499</v>
       </c>
-      <c r="B248" t="s">
+      <c r="C248" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D248" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
         <v>500</v>
       </c>
-      <c r="C248" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
+      <c r="B249" t="s">
         <v>501</v>
       </c>
-      <c r="B249" t="s">
+      <c r="C249" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D249" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
         <v>502</v>
       </c>
-      <c r="C249" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
+      <c r="B250" t="s">
         <v>503</v>
       </c>
-      <c r="B250" t="s">
+      <c r="C250" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D250" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
         <v>504</v>
       </c>
-      <c r="C250" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
+      <c r="B251" t="s">
         <v>505</v>
       </c>
-      <c r="B251" t="s">
+      <c r="C251" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D251" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
         <v>506</v>
       </c>
-      <c r="C251" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
+      <c r="B252" t="s">
         <v>507</v>
       </c>
-      <c r="B252" t="s">
+      <c r="C252" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
         <v>508</v>
       </c>
-      <c r="C252" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
+      <c r="B253" t="s">
         <v>509</v>
       </c>
-      <c r="B253" t="s">
+      <c r="C253" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D253" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
         <v>510</v>
       </c>
-      <c r="C253" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
+      <c r="B254" t="s">
         <v>511</v>
       </c>
-      <c r="B254" t="s">
+      <c r="C254" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
         <v>512</v>
       </c>
-      <c r="C254" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
+      <c r="B255" t="s">
         <v>513</v>
       </c>
-      <c r="B255" t="s">
+      <c r="C255" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D255" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
         <v>514</v>
       </c>
-      <c r="C255" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
+      <c r="B256" t="s">
         <v>515</v>
       </c>
-      <c r="B256" t="s">
+      <c r="C256" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
         <v>516</v>
       </c>
-      <c r="C256" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
+      <c r="B257" t="s">
         <v>517</v>
       </c>
-      <c r="B257" t="s">
+      <c r="C257" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
         <v>518</v>
       </c>
-      <c r="C257" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
+      <c r="B258" t="s">
         <v>519</v>
       </c>
-      <c r="B258" t="s">
+      <c r="C258" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
         <v>520</v>
       </c>
-      <c r="C258" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D258" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
+      <c r="B259" t="s">
         <v>521</v>
       </c>
-      <c r="B259" t="s">
+      <c r="C259" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
         <v>522</v>
       </c>
-      <c r="C259" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
+      <c r="B260" t="s">
         <v>523</v>
       </c>
-      <c r="B260" t="s">
+      <c r="C260" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
         <v>524</v>
       </c>
-      <c r="C260" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
+      <c r="B261" t="s">
         <v>525</v>
       </c>
-      <c r="B261" t="s">
+      <c r="C261" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D261" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
         <v>526</v>
       </c>
-      <c r="C261" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
+      <c r="B262" t="s">
         <v>527</v>
       </c>
-      <c r="B262" t="s">
+      <c r="C262" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
         <v>528</v>
       </c>
-      <c r="C262" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
+      <c r="B263" t="s">
         <v>529</v>
       </c>
-      <c r="B263" t="s">
+      <c r="C263" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D263" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
         <v>530</v>
       </c>
-      <c r="C263" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
+      <c r="B264" t="s">
         <v>531</v>
       </c>
-      <c r="B264" t="s">
+      <c r="C264" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D264" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
         <v>532</v>
       </c>
-      <c r="C264" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
+      <c r="B265" t="s">
         <v>533</v>
       </c>
-      <c r="B265" t="s">
+      <c r="C265" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
         <v>534</v>
       </c>
-      <c r="C265" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
+      <c r="B266" t="s">
         <v>535</v>
       </c>
-      <c r="B266" t="s">
+      <c r="C266" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
         <v>536</v>
       </c>
-      <c r="C266" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
+      <c r="B267" t="s">
         <v>537</v>
       </c>
-      <c r="B267" t="s">
+      <c r="C267" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
         <v>538</v>
       </c>
-      <c r="C267" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
+      <c r="B268" t="s">
         <v>539</v>
       </c>
-      <c r="B268" t="s">
+      <c r="C268" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D268" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
         <v>540</v>
       </c>
-      <c r="C268" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
+      <c r="B269" t="s">
         <v>541</v>
       </c>
-      <c r="B269" t="s">
+      <c r="C269" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D269" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
         <v>542</v>
       </c>
-      <c r="C269" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
+      <c r="B270" t="s">
         <v>543</v>
       </c>
-      <c r="B270" t="s">
+      <c r="C270" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D270" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
         <v>544</v>
       </c>
-      <c r="C270" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D270" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
+      <c r="B271" t="s">
         <v>545</v>
       </c>
-      <c r="B271" t="s">
+      <c r="C271" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D271" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
         <v>546</v>
       </c>
-      <c r="C271" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
+      <c r="B272" t="s">
         <v>547</v>
       </c>
-      <c r="B272" t="s">
+      <c r="C272" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D272" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
         <v>548</v>
       </c>
-      <c r="C272" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
+      <c r="B273" t="s">
         <v>549</v>
       </c>
-      <c r="B273" t="s">
+      <c r="C273" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D273" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
         <v>550</v>
       </c>
-      <c r="C273" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
+      <c r="B274" t="s">
         <v>551</v>
       </c>
-      <c r="B274" t="s">
+      <c r="C274" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D274" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
         <v>552</v>
       </c>
-      <c r="C274" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D274" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
+      <c r="B275" t="s">
         <v>553</v>
       </c>
-      <c r="B275" t="s">
+      <c r="C275" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D275" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
         <v>554</v>
       </c>
-      <c r="C275" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D275" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
+      <c r="B276" t="s">
         <v>555</v>
       </c>
-      <c r="B276" t="s">
+      <c r="C276" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D276" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
         <v>556</v>
       </c>
-      <c r="C276" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D276" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
+      <c r="B277" t="s">
         <v>557</v>
       </c>
-      <c r="B277" t="s">
+      <c r="C277" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D277" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
         <v>558</v>
       </c>
-      <c r="C277" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D277" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
+      <c r="B278" t="s">
         <v>559</v>
       </c>
-      <c r="B278" t="s">
+      <c r="C278" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D278" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
         <v>560</v>
       </c>
-      <c r="C278" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D278" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
+      <c r="B279" t="s">
         <v>561</v>
       </c>
-      <c r="B279" t="s">
+      <c r="C279" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
         <v>562</v>
       </c>
-      <c r="C279" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D279" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
+      <c r="B280" t="s">
         <v>563</v>
       </c>
-      <c r="B280" t="s">
+      <c r="C280" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D280" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
         <v>564</v>
       </c>
-      <c r="C280" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D280" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
+      <c r="B281" t="s">
         <v>565</v>
       </c>
-      <c r="B281" t="s">
+      <c r="C281" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D281" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
         <v>566</v>
       </c>
-      <c r="C281" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D281" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
+      <c r="B282" t="s">
         <v>567</v>
       </c>
-      <c r="B282" t="s">
+      <c r="C282" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D282" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
         <v>568</v>
       </c>
-      <c r="C282" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
+      <c r="B283" t="s">
         <v>569</v>
       </c>
-      <c r="B283" t="s">
+      <c r="C283" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
         <v>570</v>
       </c>
-      <c r="C283" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
+      <c r="B284" t="s">
         <v>571</v>
       </c>
-      <c r="B284" t="s">
+      <c r="C284" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D284" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
         <v>572</v>
       </c>
-      <c r="C284" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
+      <c r="B285" t="s">
         <v>573</v>
       </c>
-      <c r="B285" t="s">
+      <c r="C285" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D285" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
         <v>574</v>
       </c>
-      <c r="C285" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
+      <c r="B286" t="s">
         <v>575</v>
       </c>
-      <c r="B286" t="s">
+      <c r="C286" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D286" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
         <v>576</v>
       </c>
-      <c r="C286" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
+      <c r="B287" t="s">
         <v>577</v>
       </c>
-      <c r="B287" t="s">
+      <c r="C287" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D287" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
         <v>578</v>
       </c>
-      <c r="C287" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D287" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
+      <c r="B288" t="s">
         <v>579</v>
       </c>
-      <c r="B288" t="s">
+      <c r="C288" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D288" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
         <v>580</v>
       </c>
-      <c r="C288" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D288" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
+      <c r="B289" t="s">
         <v>581</v>
       </c>
-      <c r="B289" t="s">
+      <c r="C289" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D289" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
         <v>582</v>
       </c>
-      <c r="C289" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D289" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
+      <c r="B290" t="s">
         <v>583</v>
       </c>
-      <c r="B290" t="s">
+      <c r="C290" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D290" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
         <v>584</v>
       </c>
-      <c r="C290" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D290" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
+      <c r="B291" t="s">
         <v>585</v>
       </c>
-      <c r="B291" t="s">
+      <c r="C291" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D291" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
         <v>586</v>
       </c>
-      <c r="C291" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D291" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
+      <c r="B292" t="s">
         <v>587</v>
       </c>
-      <c r="B292" t="s">
+      <c r="C292" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D292" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
         <v>588</v>
       </c>
-      <c r="C292" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D292" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
+      <c r="B293" t="s">
         <v>589</v>
       </c>
-      <c r="B293" t="s">
+      <c r="C293" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D293" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
         <v>590</v>
       </c>
-      <c r="C293" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D293" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
+      <c r="B294" t="s">
         <v>591</v>
       </c>
-      <c r="B294" t="s">
+      <c r="C294" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D294" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
         <v>592</v>
       </c>
-      <c r="C294" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D294" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
+      <c r="B295" t="s">
         <v>593</v>
       </c>
-      <c r="B295" t="s">
+      <c r="C295" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
         <v>594</v>
       </c>
-      <c r="C295" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D295" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
+      <c r="B296" t="s">
         <v>595</v>
       </c>
-      <c r="B296" t="s">
+      <c r="C296" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D296" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
         <v>596</v>
       </c>
-      <c r="C296" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D296" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
+      <c r="B297" t="s">
         <v>597</v>
       </c>
-      <c r="B297" t="s">
+      <c r="C297" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
         <v>598</v>
       </c>
-      <c r="C297" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D297" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
+      <c r="B298" t="s">
         <v>599</v>
       </c>
-      <c r="B298" t="s">
+      <c r="C298" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D298" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
         <v>600</v>
       </c>
-      <c r="C298" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D298" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
+      <c r="B299" t="s">
         <v>601</v>
       </c>
-      <c r="B299" t="s">
+      <c r="C299" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D299" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
         <v>602</v>
       </c>
-      <c r="C299" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D299" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
+      <c r="B300" t="s">
         <v>603</v>
       </c>
-      <c r="B300" t="s">
+      <c r="C300" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D300" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
         <v>604</v>
       </c>
-      <c r="C300" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D300" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
+      <c r="B301" t="s">
         <v>605</v>
       </c>
-      <c r="B301" t="s">
+      <c r="C301" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
         <v>606</v>
       </c>
-      <c r="C301" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D301" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
+      <c r="B302" t="s">
         <v>607</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
         <v>608</v>
       </c>
-      <c r="C302" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D302" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
+      <c r="B303" t="s">
         <v>609</v>
       </c>
-      <c r="B303" t="s">
+      <c r="C303" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D303" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
         <v>610</v>
       </c>
-      <c r="C303" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D303" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
+      <c r="B304" t="s">
         <v>611</v>
       </c>
-      <c r="B304" t="s">
+      <c r="C304" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D304" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
         <v>612</v>
       </c>
-      <c r="C304" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D304" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
+      <c r="B305" t="s">
         <v>613</v>
       </c>
-      <c r="B305" t="s">
+      <c r="C305" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D305" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
         <v>614</v>
       </c>
-      <c r="C305" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D305" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
+      <c r="B306" t="s">
         <v>615</v>
       </c>
-      <c r="B306" t="s">
+      <c r="C306" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D306" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
         <v>616</v>
       </c>
-      <c r="C306" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D306" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
+      <c r="B307" t="s">
         <v>617</v>
       </c>
-      <c r="B307" t="s">
+      <c r="C307" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D307" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
         <v>618</v>
       </c>
-      <c r="C307" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D307" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
+      <c r="B308" t="s">
         <v>619</v>
       </c>
-      <c r="B308" t="s">
+      <c r="C308" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D308" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
         <v>620</v>
       </c>
-      <c r="C308" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
+      <c r="B309" t="s">
         <v>621</v>
       </c>
-      <c r="B309" t="s">
+      <c r="C309" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D309" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
         <v>622</v>
       </c>
-      <c r="C309" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D309" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
+      <c r="B310" t="s">
         <v>623</v>
       </c>
-      <c r="B310" t="s">
+      <c r="C310" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D310" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
         <v>624</v>
       </c>
-      <c r="C310" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D310" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
+      <c r="B311" t="s">
         <v>625</v>
       </c>
-      <c r="B311" t="s">
+      <c r="C311" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D311" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
         <v>626</v>
       </c>
-      <c r="C311" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
+      <c r="B312" t="s">
         <v>627</v>
       </c>
-      <c r="B312" t="s">
+      <c r="C312" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D312" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
         <v>628</v>
       </c>
-      <c r="C312" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D312" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
+      <c r="B313" t="s">
         <v>629</v>
       </c>
-      <c r="B313" t="s">
+      <c r="C313" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D313" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
         <v>630</v>
       </c>
-      <c r="C313" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D313" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
+      <c r="B314" t="s">
         <v>631</v>
       </c>
-      <c r="B314" t="s">
+      <c r="C314" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D314" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
         <v>632</v>
       </c>
-      <c r="C314" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
+      <c r="B315" t="s">
         <v>633</v>
       </c>
-      <c r="B315" t="s">
+      <c r="C315" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D315" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
         <v>634</v>
       </c>
-      <c r="C315" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D315" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
+      <c r="B316" t="s">
         <v>635</v>
       </c>
-      <c r="B316" t="s">
+      <c r="C316" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D316" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
         <v>636</v>
       </c>
-      <c r="C316" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
+      <c r="B317" t="s">
         <v>637</v>
       </c>
-      <c r="B317" t="s">
+      <c r="C317" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D317" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
         <v>638</v>
       </c>
-      <c r="C317" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D317" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
+      <c r="B318" t="s">
         <v>639</v>
       </c>
-      <c r="B318" t="s">
+      <c r="C318" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D318" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
         <v>640</v>
       </c>
-      <c r="C318" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
+      <c r="B319" t="s">
         <v>641</v>
       </c>
-      <c r="B319" t="s">
+      <c r="C319" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D319" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
         <v>642</v>
       </c>
-      <c r="C319" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D319" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
+      <c r="B320" t="s">
         <v>643</v>
       </c>
-      <c r="B320" t="s">
+      <c r="C320" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D320" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
         <v>644</v>
       </c>
-      <c r="C320" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D320" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
+      <c r="B321" t="s">
         <v>645</v>
       </c>
-      <c r="B321" t="s">
+      <c r="C321" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D321" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
         <v>646</v>
       </c>
-      <c r="C321" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D321" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
+      <c r="B322" t="s">
         <v>647</v>
       </c>
-      <c r="B322" t="s">
+      <c r="C322" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D322" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
         <v>648</v>
       </c>
-      <c r="C322" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D322" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
+      <c r="B323" t="s">
         <v>649</v>
       </c>
-      <c r="B323" t="s">
+      <c r="C323" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D323" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
         <v>650</v>
       </c>
-      <c r="C323" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D323" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
+      <c r="B324" t="s">
         <v>651</v>
       </c>
-      <c r="B324" t="s">
+      <c r="C324" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D324" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
         <v>652</v>
       </c>
-      <c r="C324" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
+      <c r="B325" t="s">
         <v>653</v>
       </c>
-      <c r="B325" t="s">
+      <c r="C325" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D325" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
         <v>654</v>
       </c>
-      <c r="C325" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D325" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
+      <c r="B326" t="s">
         <v>655</v>
       </c>
-      <c r="B326" t="s">
+      <c r="C326" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D326" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
         <v>656</v>
       </c>
-      <c r="C326" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D326" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
+      <c r="B327" t="s">
         <v>657</v>
       </c>
-      <c r="B327" t="s">
+      <c r="C327" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D327" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
         <v>658</v>
       </c>
-      <c r="C327" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D327" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
+      <c r="B328" t="s">
         <v>659</v>
       </c>
-      <c r="B328" t="s">
+      <c r="C328" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D328" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
         <v>660</v>
       </c>
-      <c r="C328" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D328" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
+      <c r="B329" t="s">
         <v>661</v>
       </c>
-      <c r="B329" t="s">
+      <c r="C329" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D329" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
         <v>662</v>
       </c>
-      <c r="C329" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D329" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
+      <c r="B330" t="s">
         <v>663</v>
       </c>
-      <c r="B330" t="s">
+      <c r="C330" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D330" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
         <v>664</v>
       </c>
-      <c r="C330" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D330" t="s">
-        <v>8</v>
+      <c r="B331" t="s">
+        <v>665</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D331" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>666</v>
+      </c>
+      <c r="B332" t="s">
+        <v>667</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D332" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>668</v>
+      </c>
+      <c r="B333" t="s">
+        <v>669</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D333" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>670</v>
+      </c>
+      <c r="B334" t="s">
+        <v>671</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D334" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>672</v>
+      </c>
+      <c r="B335" t="s">
+        <v>673</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D335" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>674</v>
+      </c>
+      <c r="B336" t="s">
+        <v>675</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D336" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>676</v>
+      </c>
+      <c r="B337" t="s">
+        <v>677</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D337" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>678</v>
+      </c>
+      <c r="B338" t="s">
+        <v>679</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D338" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>680</v>
+      </c>
+      <c r="B339" t="s">
+        <v>681</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D339" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>682</v>
+      </c>
+      <c r="B340" t="s">
+        <v>683</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D340" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>684</v>
+      </c>
+      <c r="B341" t="s">
+        <v>685</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D341" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>686</v>
+      </c>
+      <c r="B342" t="s">
+        <v>687</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D342" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>688</v>
+      </c>
+      <c r="B343" t="s">
+        <v>689</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D343" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>690</v>
+      </c>
+      <c r="B344" t="s">
+        <v>691</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>692</v>
+      </c>
+      <c r="B345" t="s">
+        <v>693</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>694</v>
+      </c>
+      <c r="B346" t="s">
+        <v>695</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D346" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>696</v>
+      </c>
+      <c r="B347" t="s">
+        <v>697</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D347" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>698</v>
+      </c>
+      <c r="B348" t="s">
+        <v>699</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D348" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>700</v>
+      </c>
+      <c r="B349" t="s">
+        <v>701</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D349" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>702</v>
+      </c>
+      <c r="B350" t="s">
+        <v>703</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D350" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>704</v>
+      </c>
+      <c r="B351" t="s">
+        <v>705</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D351" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>706</v>
+      </c>
+      <c r="B352" t="s">
+        <v>707</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D352" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>708</v>
+      </c>
+      <c r="B353" t="s">
+        <v>709</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D353" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>710</v>
+      </c>
+      <c r="B354" t="s">
+        <v>711</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D354" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>712</v>
+      </c>
+      <c r="B355" t="s">
+        <v>713</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D355" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>714</v>
+      </c>
+      <c r="B356" t="s">
+        <v>715</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>716</v>
+      </c>
+      <c r="B357" t="s">
+        <v>717</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D357" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>718</v>
+      </c>
+      <c r="B358" t="s">
+        <v>719</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D358" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>720</v>
+      </c>
+      <c r="B359" t="s">
+        <v>721</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D359" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>722</v>
+      </c>
+      <c r="B360" t="s">
+        <v>723</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D360" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>724</v>
+      </c>
+      <c r="B361" t="s">
+        <v>725</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D361" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>726</v>
+      </c>
+      <c r="B362" t="s">
+        <v>727</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D362" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>728</v>
+      </c>
+      <c r="B363" t="s">
+        <v>729</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D363" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>730</v>
+      </c>
+      <c r="B364" t="s">
+        <v>731</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D364" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>732</v>
+      </c>
+      <c r="B365" t="s">
+        <v>733</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D365" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>734</v>
+      </c>
+      <c r="B366" t="s">
+        <v>735</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D366" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>736</v>
+      </c>
+      <c r="B367" t="s">
+        <v>737</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D367" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>738</v>
+      </c>
+      <c r="B368" t="s">
+        <v>739</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D368" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>740</v>
+      </c>
+      <c r="B369" t="s">
+        <v>741</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D369" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>742</v>
+      </c>
+      <c r="B370" t="s">
+        <v>743</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D370" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>744</v>
+      </c>
+      <c r="B371" t="s">
+        <v>745</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D371" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>746</v>
+      </c>
+      <c r="B372" t="s">
+        <v>747</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D372" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>748</v>
+      </c>
+      <c r="B373" t="s">
+        <v>749</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D373" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>750</v>
+      </c>
+      <c r="B374" t="s">
+        <v>751</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D374" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>752</v>
+      </c>
+      <c r="B375" t="s">
+        <v>753</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D375" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>754</v>
+      </c>
+      <c r="B376" t="s">
+        <v>755</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D376" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>756</v>
+      </c>
+      <c r="B377" t="s">
+        <v>757</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>758</v>
+      </c>
+      <c r="B378" t="s">
+        <v>759</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D378" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>760</v>
+      </c>
+      <c r="B379" t="s">
+        <v>761</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D379" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>762</v>
+      </c>
+      <c r="B380" t="s">
+        <v>763</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D380" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>764</v>
+      </c>
+      <c r="B381" t="s">
+        <v>765</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D381" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>766</v>
+      </c>
+      <c r="B382" t="s">
+        <v>767</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>768</v>
+      </c>
+      <c r="B383" t="s">
+        <v>769</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D383" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>770</v>
+      </c>
+      <c r="B384" t="s">
+        <v>771</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D384" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>772</v>
+      </c>
+      <c r="B385" t="s">
+        <v>773</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D385" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>774</v>
+      </c>
+      <c r="B386" t="s">
+        <v>775</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D386" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>776</v>
+      </c>
+      <c r="B387" t="s">
+        <v>777</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D387" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>778</v>
+      </c>
+      <c r="B388" t="s">
+        <v>779</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D388" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>780</v>
+      </c>
+      <c r="B389" t="s">
+        <v>781</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D389" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>782</v>
+      </c>
+      <c r="B390" t="s">
+        <v>783</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D390" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>784</v>
+      </c>
+      <c r="B391" t="s">
+        <v>785</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D391" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>786</v>
+      </c>
+      <c r="B392" t="s">
+        <v>787</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D392" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>788</v>
+      </c>
+      <c r="B393" t="s">
+        <v>789</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D393" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>790</v>
+      </c>
+      <c r="B394" t="s">
+        <v>791</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D394" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>792</v>
+      </c>
+      <c r="B395" t="s">
+        <v>793</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D395" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>794</v>
+      </c>
+      <c r="B396" t="s">
+        <v>795</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D396" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D330" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D396" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6901,6 +8512,72 @@
     <hyperlink ref="C328" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
     <hyperlink ref="C329" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
     <hyperlink ref="C330" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C331" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C332" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C333" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C334" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C335" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C336" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C337" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C338" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C339" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C340" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C341" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C342" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C343" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C344" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C345" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C346" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C347" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C348" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C349" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C350" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C351" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C352" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C353" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C354" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C355" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C356" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C357" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C358" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C359" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C360" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C361" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C362" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C363" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C364" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C365" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C366" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C367" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C368" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C369" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C370" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C371" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C372" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C373" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C374" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C375" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C376" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C377" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C378" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C379" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C380" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C381" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C382" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C383" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C384" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C385" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C386" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C387" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C388" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C389" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C390" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C391" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C392" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C393" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C394" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C395" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C396" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7385FF6-880A-4B74-A895-4751B9026E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBB5DDD-6040-41AA-98B1-81FCA092835F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="892">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -121,12 +121,24 @@
     <t>All Exclusive</t>
   </si>
   <si>
+    <t>alle for to</t>
+  </si>
+  <si>
+    <t>Alle for to</t>
+  </si>
+  <si>
     <t>alle for én</t>
   </si>
   <si>
     <t>Alle For Én</t>
   </si>
   <si>
+    <t>alletiders afrika</t>
+  </si>
+  <si>
+    <t>Alletiders Afrika</t>
+  </si>
+  <si>
     <t>alletiders asien</t>
   </si>
   <si>
@@ -181,6 +193,12 @@
     <t>Antikkrejlerne Med Kendisser</t>
   </si>
   <si>
+    <t>aphaca - brug for hinanden</t>
+  </si>
+  <si>
+    <t>Aphaca - Brug for hinanden</t>
+  </si>
+  <si>
     <t>apollo: tilbage til månen</t>
   </si>
   <si>
@@ -199,6 +217,12 @@
     <t>Asterix &amp; Obelix i dragens rige</t>
   </si>
   <si>
+    <t>asterix og briterne</t>
+  </si>
+  <si>
+    <t>Asterix og briterne</t>
+  </si>
+  <si>
     <t>asterix: sejren over cæsar</t>
   </si>
   <si>
@@ -289,6 +313,12 @@
     <t>Bjerglægen</t>
   </si>
   <si>
+    <t>blodige beretninger fra europa</t>
+  </si>
+  <si>
+    <t>Blodige beretninger fra Europa</t>
+  </si>
+  <si>
     <t>bluey kortfilmer</t>
   </si>
   <si>
@@ -403,6 +433,12 @@
     <t>Danske Katastrofer</t>
   </si>
   <si>
+    <t>danske vidundere</t>
+  </si>
+  <si>
+    <t>Danske vidundere</t>
+  </si>
+  <si>
     <t>de 5 i fedtefadet</t>
   </si>
   <si>
@@ -493,6 +529,12 @@
     <t>Der Kan Man Se</t>
   </si>
   <si>
+    <t>det første modelbureau for indiens transkønnede</t>
+  </si>
+  <si>
+    <t>Det første modelbureau for Indiens transkønnede</t>
+  </si>
+  <si>
     <t>det lille hus på prærien</t>
   </si>
   <si>
@@ -1051,12 +1093,24 @@
     <t>Hitlers sidste kampe</t>
   </si>
   <si>
+    <t>hjelp! jeg er en fisk</t>
+  </si>
+  <si>
+    <t>Hjelp! Jeg er en fisk</t>
+  </si>
+  <si>
     <t>hjem til gården</t>
   </si>
   <si>
     <t>Hjem Til Gården</t>
   </si>
   <si>
+    <t>hjælp! jeg er en fisk</t>
+  </si>
+  <si>
+    <t>Hjælp! Jeg er en fisk</t>
+  </si>
+  <si>
     <t>hjørnebjørne</t>
   </si>
   <si>
@@ -1087,6 +1141,12 @@
     <t>Hunden Ib</t>
   </si>
   <si>
+    <t>hundens verden</t>
+  </si>
+  <si>
+    <t>Hundens verden</t>
+  </si>
+  <si>
     <t>huse med hemmeligheder</t>
   </si>
   <si>
@@ -1183,6 +1243,12 @@
     <t>I seriemördarens samling</t>
   </si>
   <si>
+    <t>i sindet på en forbryder</t>
+  </si>
+  <si>
+    <t>I Sindet på en Forbryder</t>
+  </si>
+  <si>
     <t>idas fristelser</t>
   </si>
   <si>
@@ -1771,6 +1837,12 @@
     <t>Olsen Banden På Dybt Vand</t>
   </si>
   <si>
+    <t>oman - arabiens naturperle</t>
+  </si>
+  <si>
+    <t>Oman - Arabiens naturperle</t>
+  </si>
+  <si>
     <t>onkel morfar</t>
   </si>
   <si>
@@ -2077,6 +2149,12 @@
     <t>Skat Eller Skrammel</t>
   </si>
   <si>
+    <t>skildpadden</t>
+  </si>
+  <si>
+    <t>Skildpadden</t>
+  </si>
+  <si>
     <t>skjelvet</t>
   </si>
   <si>
@@ -2101,6 +2179,24 @@
     <t>Skælvet</t>
   </si>
   <si>
+    <t>smurfene: den hemmelige landsbyen</t>
+  </si>
+  <si>
+    <t>Smurfene: Den hemmelige landsbyen</t>
+  </si>
+  <si>
+    <t>smølferne – den hemmelige landsby</t>
+  </si>
+  <si>
+    <t>Smølferne – Den hemmelige landsby</t>
+  </si>
+  <si>
+    <t>smølferne: den hemmelige landsby</t>
+  </si>
+  <si>
+    <t>Smølferne: Den hemmelige landsby</t>
+  </si>
+  <si>
     <t>snurre snups byggevenner</t>
   </si>
   <si>
@@ -2335,24 +2431,54 @@
     <t>The Mentalist</t>
   </si>
   <si>
+    <t>til døden os skiller</t>
+  </si>
+  <si>
+    <t>Til døden os skiller</t>
+  </si>
+  <si>
+    <t>tintins eventyr</t>
+  </si>
+  <si>
+    <t>Tintins eventyr</t>
+  </si>
+  <si>
     <t>tirsdagsanalysen</t>
   </si>
   <si>
     <t>Tirsdagsanalysen</t>
   </si>
   <si>
+    <t>to brødre og et forbandet løfte</t>
+  </si>
+  <si>
+    <t>To brødre og et forbandet løfte</t>
+  </si>
+  <si>
     <t>to på flugt</t>
   </si>
   <si>
     <t>To på flugt</t>
   </si>
   <si>
+    <t>togferie for dummies</t>
+  </si>
+  <si>
+    <t>Togferie for Dummies</t>
+  </si>
+  <si>
     <t>toppen af toppen</t>
   </si>
   <si>
     <t>Toppen Af Toppen</t>
   </si>
   <si>
+    <t>troldspejlet</t>
+  </si>
+  <si>
+    <t>Troldspejlet</t>
+  </si>
+  <si>
     <t>uforglemt</t>
   </si>
   <si>
@@ -2425,6 +2551,12 @@
     <t>Verdens Største Opdagelser</t>
   </si>
   <si>
+    <t>verdens vildeste hoteller</t>
+  </si>
+  <si>
+    <t>Verdens vildeste hoteller</t>
+  </si>
+  <si>
     <t>verdensdamer</t>
   </si>
   <si>
@@ -2561,13 +2693,19 @@
   </si>
   <si>
     <t>Æblerup</t>
+  </si>
+  <si>
+    <t>ørnens øje</t>
+  </si>
+  <si>
+    <t>Ørnens øje</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2582,6 +2720,14 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -2615,12 +2761,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2924,7 +3071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E421"/>
+  <dimension ref="A1:E444"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -3143,9 +3290,6 @@
       <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -3171,9 +3315,6 @@
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -3185,6 +3326,9 @@
       <c r="C18" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -3210,9 +3354,6 @@
       <c r="C20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -3308,9 +3449,6 @@
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D27" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -3364,9 +3502,6 @@
       <c r="C31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D31" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -3476,6 +3611,9 @@
       <c r="C39" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -3487,6 +3625,9 @@
       <c r="C40" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -3526,9 +3667,6 @@
       <c r="C43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D43" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -3540,9 +3678,6 @@
       <c r="C44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D44" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -3568,6 +3703,9 @@
       <c r="C46" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -3579,9 +3717,6 @@
       <c r="C47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D47" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -3635,9 +3770,6 @@
       <c r="C51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D51" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -3691,6 +3823,9 @@
       <c r="C55" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
@@ -3758,9 +3893,6 @@
       <c r="C60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -3828,6 +3960,9 @@
       <c r="C65" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
@@ -3839,6 +3974,9 @@
       <c r="C66" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -3850,9 +3988,6 @@
       <c r="C67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D67" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -3906,9 +4041,6 @@
       <c r="C71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D71" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -4001,9 +4133,6 @@
       <c r="C78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D78" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
@@ -4015,6 +4144,9 @@
       <c r="C79" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D79" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
@@ -4026,6 +4158,9 @@
       <c r="C80" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D80" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
@@ -4037,6 +4172,9 @@
       <c r="C81" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D81" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
@@ -4062,9 +4200,6 @@
       <c r="C83" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D83" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -4104,9 +4239,6 @@
       <c r="C86" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D86" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
@@ -4118,9 +4250,6 @@
       <c r="C87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D87" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
@@ -4132,9 +4261,6 @@
       <c r="C88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D88" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
@@ -4160,6 +4286,9 @@
       <c r="C90" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D90" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
@@ -4213,6 +4342,9 @@
       <c r="C94" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D94" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -4252,9 +4384,6 @@
       <c r="C97" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D97" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
@@ -4280,6 +4409,9 @@
       <c r="C99" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D99" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
@@ -4305,9 +4437,6 @@
       <c r="C101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D101" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
@@ -4375,9 +4504,6 @@
       <c r="C106" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D106" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
@@ -4403,6 +4529,9 @@
       <c r="C108" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D108" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
@@ -4498,9 +4627,6 @@
       <c r="C115" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D115" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
@@ -4680,6 +4806,9 @@
       <c r="C128" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D128" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
@@ -4691,6 +4820,9 @@
       <c r="C129" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D129" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
@@ -4716,6 +4848,9 @@
       <c r="C131" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D131" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
@@ -4741,6 +4876,9 @@
       <c r="C133" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D133" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -4766,9 +4904,6 @@
       <c r="C135" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D135" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
@@ -4780,9 +4915,6 @@
       <c r="C136" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D136" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
@@ -4808,9 +4940,6 @@
       <c r="C138" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D138" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
@@ -4836,9 +4965,6 @@
       <c r="C140" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D140" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
@@ -4948,6 +5074,9 @@
       <c r="C148" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D148" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
@@ -5029,6 +5158,9 @@
       <c r="C154" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D154" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
@@ -5040,9 +5172,6 @@
       <c r="C155" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D155" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
@@ -5124,9 +5253,6 @@
       <c r="C161" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D161" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
@@ -5180,6 +5306,9 @@
       <c r="C165" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D165" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
@@ -5247,6 +5376,9 @@
       <c r="C170" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D170" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
@@ -5350,9 +5482,6 @@
       <c r="C178" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D178" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
@@ -5364,9 +5493,6 @@
       <c r="C179" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D179" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
@@ -5378,6 +5504,9 @@
       <c r="C180" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D180" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
@@ -5428,6 +5557,9 @@
       <c r="C184" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D184" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
@@ -5464,9 +5596,6 @@
       <c r="C187" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D187" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
@@ -5506,9 +5635,6 @@
       <c r="C190" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D190" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
@@ -5520,9 +5646,6 @@
       <c r="C191" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D191" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
@@ -5562,9 +5685,6 @@
       <c r="C194" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D194" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
@@ -5576,9 +5696,6 @@
       <c r="C195" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D195" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
@@ -5674,9 +5791,6 @@
       <c r="C202" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D202" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
@@ -5786,6 +5900,9 @@
       <c r="C210" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D210" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
@@ -5839,6 +5956,9 @@
       <c r="C214" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D214" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
@@ -5934,9 +6054,6 @@
       <c r="C221" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D221" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
@@ -5948,6 +6065,9 @@
       <c r="C222" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D222" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
@@ -5987,9 +6107,6 @@
       <c r="C225" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D225" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
@@ -6099,9 +6216,6 @@
       <c r="C233" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D233" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
@@ -6180,6 +6294,9 @@
       <c r="C239" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D239" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
@@ -6233,6 +6350,9 @@
       <c r="C243" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D243" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
@@ -6244,6 +6364,9 @@
       <c r="C244" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D244" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
@@ -6311,9 +6434,6 @@
       <c r="C249" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D249" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
@@ -6325,9 +6445,6 @@
       <c r="C250" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D250" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
@@ -6353,6 +6470,9 @@
       <c r="C252" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D252" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
@@ -6378,9 +6498,6 @@
       <c r="C254" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D254" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
@@ -6392,9 +6509,6 @@
       <c r="C255" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D255" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
@@ -6504,9 +6618,6 @@
       <c r="C263" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D263" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
@@ -6616,6 +6727,9 @@
       <c r="C271" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D271" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
@@ -6627,6 +6741,9 @@
       <c r="C272" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D272" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
@@ -6764,9 +6881,6 @@
       <c r="C282" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D282" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
@@ -6778,9 +6892,6 @@
       <c r="C283" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D283" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
@@ -7030,9 +7141,6 @@
       <c r="C301" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D301" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
@@ -7282,6 +7390,9 @@
       <c r="C319" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D319" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
@@ -7447,9 +7558,6 @@
       <c r="C331" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D331" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
@@ -7755,9 +7863,6 @@
       <c r="C353" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D353" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
@@ -7825,9 +7930,6 @@
       <c r="C358" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D358" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
@@ -7839,9 +7941,6 @@
       <c r="C359" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D359" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
@@ -7853,9 +7952,6 @@
       <c r="C360" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D360" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
@@ -7909,6 +8005,9 @@
       <c r="C364" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D364" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
@@ -7920,6 +8019,9 @@
       <c r="C365" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D365" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
@@ -8085,6 +8187,9 @@
       <c r="C377" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D377" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
@@ -8124,9 +8229,6 @@
       <c r="C380" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D380" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
@@ -8138,9 +8240,6 @@
       <c r="C381" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D381" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
@@ -8152,6 +8251,9 @@
       <c r="C382" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D382" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
@@ -8177,6 +8279,9 @@
       <c r="C384" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D384" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
@@ -8300,9 +8405,6 @@
       <c r="C393" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D393" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
@@ -8370,9 +8472,6 @@
       <c r="C398" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D398" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
@@ -8398,9 +8497,6 @@
       <c r="C400" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D400" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
@@ -8423,9 +8519,6 @@
       <c r="C402" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D402" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
@@ -8437,9 +8530,6 @@
       <c r="C403" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D403" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
@@ -8465,9 +8555,6 @@
       <c r="C405" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D405" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
@@ -8479,6 +8566,9 @@
       <c r="C406" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D406" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
@@ -8490,9 +8580,6 @@
       <c r="C407" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D407" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
@@ -8574,6 +8661,9 @@
       <c r="C413" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D413" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
@@ -8669,9 +8759,6 @@
       <c r="C420" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D420" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
@@ -8687,10 +8774,326 @@
         <v>7</v>
       </c>
     </row>
+    <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>846</v>
+      </c>
+      <c r="B422" t="s">
+        <v>847</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D422" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>848</v>
+      </c>
+      <c r="B423" t="s">
+        <v>849</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>850</v>
+      </c>
+      <c r="B424" t="s">
+        <v>851</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D424" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>852</v>
+      </c>
+      <c r="B425" t="s">
+        <v>853</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D425" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>854</v>
+      </c>
+      <c r="B426" t="s">
+        <v>855</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D426" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>856</v>
+      </c>
+      <c r="B427" t="s">
+        <v>857</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D427" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>858</v>
+      </c>
+      <c r="B428" t="s">
+        <v>859</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>860</v>
+      </c>
+      <c r="B429" t="s">
+        <v>861</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D429" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>862</v>
+      </c>
+      <c r="B430" t="s">
+        <v>863</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D430" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>864</v>
+      </c>
+      <c r="B431" t="s">
+        <v>865</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D431" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>866</v>
+      </c>
+      <c r="B432" t="s">
+        <v>867</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D432" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>868</v>
+      </c>
+      <c r="B433" t="s">
+        <v>869</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D433" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>870</v>
+      </c>
+      <c r="B434" t="s">
+        <v>871</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D434" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>872</v>
+      </c>
+      <c r="B435" t="s">
+        <v>873</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D435" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>874</v>
+      </c>
+      <c r="B436" t="s">
+        <v>875</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D436" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>876</v>
+      </c>
+      <c r="B437" t="s">
+        <v>877</v>
+      </c>
+      <c r="C437" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D437" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>878</v>
+      </c>
+      <c r="B438" t="s">
+        <v>879</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D438" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>880</v>
+      </c>
+      <c r="B439" t="s">
+        <v>881</v>
+      </c>
+      <c r="C439" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D439" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>882</v>
+      </c>
+      <c r="B440" t="s">
+        <v>883</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D440" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>884</v>
+      </c>
+      <c r="B441" t="s">
+        <v>885</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D441" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>886</v>
+      </c>
+      <c r="B442" t="s">
+        <v>887</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D442" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>888</v>
+      </c>
+      <c r="B443" t="s">
+        <v>889</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D443" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>890</v>
+      </c>
+      <c r="B444" t="s">
+        <v>891</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D444" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D421" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D444" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9115,6 +9518,29 @@
     <hyperlink ref="C419" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
     <hyperlink ref="C420" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
     <hyperlink ref="C421" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C422" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C423" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C424" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C425" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C426" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C427" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C428" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C429" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C430" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C431" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C432" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C433" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C434" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C435" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C436" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C437" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C438" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C439" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C440" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C441" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C442" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C443" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C444" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBB5DDD-6040-41AA-98B1-81FCA092835F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA000499-1617-463C-9226-F15EA08CA917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="902">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -931,6 +931,12 @@
     <t>Franske Drømmeslotte</t>
   </si>
   <si>
+    <t>gabbys dukkehus: filmen</t>
+  </si>
+  <si>
+    <t>Gabbys dukkehus: Filmen</t>
+  </si>
+  <si>
     <t>gadebetjentene</t>
   </si>
   <si>
@@ -1237,6 +1243,12 @@
     <t>I En Klasse For Sig</t>
   </si>
   <si>
+    <t>i hovedet på en gerningsmand</t>
+  </si>
+  <si>
+    <t>I hovedet på en gerningsmand</t>
+  </si>
+  <si>
     <t>i seriemördarens samling</t>
   </si>
   <si>
@@ -1393,6 +1405,12 @@
     <t>Kriminalkommissær Barnaby</t>
   </si>
   <si>
+    <t>krummerne - alt på spil</t>
+  </si>
+  <si>
+    <t>Krummerne - alt på spil</t>
+  </si>
+  <si>
     <t>kurs mod danske kyster</t>
   </si>
   <si>
@@ -1771,6 +1789,12 @@
     <t>Mumien</t>
   </si>
   <si>
+    <t>mysteriet om den danske nazi-donor</t>
+  </si>
+  <si>
+    <t>Mysteriet om den danske nazi-donor</t>
+  </si>
+  <si>
     <t>måneskin i bakkekøbing</t>
   </si>
   <si>
@@ -2159,6 +2183,12 @@
   </si>
   <si>
     <t>Skjelvet</t>
+  </si>
+  <si>
+    <t>skyggesiden</t>
+  </si>
+  <si>
+    <t>Skyggesiden</t>
   </si>
   <si>
     <t>skyllet væk</t>
@@ -2705,7 +2735,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2720,14 +2750,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -2761,13 +2783,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3071,7 +3092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E444"/>
+  <dimension ref="A1:E449"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -3290,6 +3311,9 @@
       <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -3315,6 +3339,9 @@
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -3354,6 +3381,9 @@
       <c r="C20" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -3449,6 +3479,9 @@
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -3502,6 +3535,9 @@
       <c r="C31" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -3717,6 +3753,9 @@
       <c r="C47" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -3893,6 +3932,9 @@
       <c r="C60" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D60" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -3988,6 +4030,9 @@
       <c r="C67" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -4200,6 +4245,9 @@
       <c r="C83" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D83" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -4915,6 +4963,9 @@
       <c r="C136" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D136" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
@@ -4965,6 +5016,9 @@
       <c r="C140" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D140" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
@@ -5172,6 +5226,9 @@
       <c r="C155" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D155" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
@@ -5253,6 +5310,9 @@
       <c r="C161" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D161" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
@@ -5264,9 +5324,6 @@
       <c r="C162" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D162" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
@@ -5404,6 +5461,9 @@
       <c r="C172" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D172" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
@@ -5471,6 +5531,9 @@
       <c r="C177" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D177" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
@@ -5482,6 +5545,9 @@
       <c r="C178" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D178" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
@@ -5493,6 +5559,9 @@
       <c r="C179" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D179" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
@@ -5518,6 +5587,9 @@
       <c r="C181" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D181" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
@@ -5571,6 +5643,9 @@
       <c r="C185" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D185" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
@@ -5596,6 +5671,9 @@
       <c r="C187" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D187" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
@@ -5635,6 +5713,9 @@
       <c r="C190" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D190" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
@@ -5646,6 +5727,9 @@
       <c r="C191" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D191" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
@@ -5685,6 +5769,9 @@
       <c r="C194" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D194" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
@@ -5696,6 +5783,9 @@
       <c r="C195" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D195" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
@@ -5791,6 +5881,9 @@
       <c r="C202" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D202" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
@@ -6054,6 +6147,9 @@
       <c r="C221" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D221" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
@@ -6107,6 +6203,9 @@
       <c r="C225" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D225" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
@@ -6216,6 +6315,9 @@
       <c r="C233" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D233" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
@@ -6283,6 +6385,9 @@
       <c r="C238" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D238" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
@@ -6322,9 +6427,6 @@
       <c r="C241" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D241" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
@@ -6434,6 +6536,9 @@
       <c r="C249" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D249" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
@@ -6445,6 +6550,9 @@
       <c r="C250" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D250" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
@@ -6484,9 +6592,6 @@
       <c r="C253" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D253" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
@@ -6498,6 +6603,9 @@
       <c r="C254" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D254" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
@@ -6509,6 +6617,9 @@
       <c r="C255" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D255" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
@@ -6548,9 +6659,6 @@
       <c r="C258" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D258" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
@@ -6618,6 +6726,9 @@
       <c r="C263" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D263" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
@@ -6881,6 +6992,9 @@
       <c r="C282" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D282" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
@@ -6892,6 +7006,9 @@
       <c r="C283" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D283" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
@@ -6931,9 +7048,6 @@
       <c r="C286" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D286" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
@@ -7141,6 +7255,9 @@
       <c r="C301" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D301" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
@@ -7558,6 +7675,9 @@
       <c r="C331" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D331" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
@@ -7863,6 +7983,9 @@
       <c r="C353" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D353" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
@@ -7916,9 +8039,6 @@
       <c r="C357" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D357" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
@@ -7930,6 +8050,9 @@
       <c r="C358" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D358" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
@@ -7952,6 +8075,9 @@
       <c r="C360" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D360" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
@@ -8229,6 +8355,9 @@
       <c r="C380" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D380" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
@@ -8240,6 +8369,9 @@
       <c r="C381" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D381" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
@@ -8293,9 +8425,6 @@
       <c r="C385" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D385" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
@@ -8307,9 +8436,6 @@
       <c r="C386" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D386" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
@@ -8405,6 +8531,9 @@
       <c r="C393" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D393" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
@@ -8472,6 +8601,9 @@
       <c r="C398" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D398" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
@@ -8497,6 +8629,9 @@
       <c r="C400" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D400" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
@@ -8508,6 +8643,9 @@
       <c r="C401" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D401" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
@@ -8519,6 +8657,9 @@
       <c r="C402" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D402" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
@@ -8530,6 +8671,9 @@
       <c r="C403" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D403" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
@@ -8555,6 +8699,9 @@
       <c r="C405" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D405" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
@@ -8580,6 +8727,9 @@
       <c r="C407" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D407" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
@@ -8591,9 +8741,6 @@
       <c r="C408" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D408" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
@@ -8619,9 +8766,6 @@
       <c r="C410" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D410" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
@@ -8647,9 +8791,6 @@
       <c r="C412" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D412" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
@@ -8759,6 +8900,9 @@
       <c r="C420" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D420" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
@@ -8798,6 +8942,9 @@
       <c r="C423" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D423" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
@@ -8862,8 +9009,11 @@
       <c r="B428" t="s">
         <v>859</v>
       </c>
-      <c r="C428" s="3" t="s">
-        <v>6</v>
+      <c r="C428" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D428" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -8932,9 +9082,6 @@
       <c r="C433" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D433" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
@@ -9090,10 +9237,80 @@
         <v>7</v>
       </c>
     </row>
+    <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>892</v>
+      </c>
+      <c r="B445" t="s">
+        <v>893</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D445" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>894</v>
+      </c>
+      <c r="B446" t="s">
+        <v>895</v>
+      </c>
+      <c r="C446" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D446" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>896</v>
+      </c>
+      <c r="B447" t="s">
+        <v>897</v>
+      </c>
+      <c r="C447" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D447" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>898</v>
+      </c>
+      <c r="B448" t="s">
+        <v>899</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D448" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>900</v>
+      </c>
+      <c r="B449" t="s">
+        <v>901</v>
+      </c>
+      <c r="C449" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D449" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D444" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D449" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9541,6 +9758,11 @@
     <hyperlink ref="C442" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
     <hyperlink ref="C443" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
     <hyperlink ref="C444" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C445" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C446" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C447" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C448" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C449" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A96ECF-EE79-4AD9-A017-08CAD03F72B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B930F75-CF7A-4BDC-8849-6CA9D67A9244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="1044">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -103,6 +103,12 @@
     <t>Aftenshowet</t>
   </si>
   <si>
+    <t>alene hjemme med porno</t>
+  </si>
+  <si>
+    <t>Alene hjemme med porno</t>
+  </si>
+  <si>
     <t>alene i vildmarken</t>
   </si>
   <si>
@@ -187,6 +193,12 @@
     <t>Ambulancen - liv eller død</t>
   </si>
   <si>
+    <t>andre folks børn</t>
+  </si>
+  <si>
+    <t>Andre folks børn</t>
+  </si>
+  <si>
     <t>andre rieu: welcome to my world</t>
   </si>
   <si>
@@ -283,6 +295,12 @@
     <t>Beck</t>
   </si>
   <si>
+    <t>beier på alpehotellet</t>
+  </si>
+  <si>
+    <t>Beier på alpehotellet</t>
+  </si>
+  <si>
     <t>beliggenhed, beliggenhed, beliggenhed</t>
   </si>
   <si>
@@ -445,6 +463,12 @@
     <t>Conquistadorernes Storhed Og Fald</t>
   </si>
   <si>
+    <t>conquistadors: the rise and fall</t>
+  </si>
+  <si>
+    <t>Conquistadors: The Rise and Fall</t>
+  </si>
+  <si>
     <t>cykelmyggen og minibillen</t>
   </si>
   <si>
@@ -529,6 +553,12 @@
     <t>Den Grimme Ælling Og Mig</t>
   </si>
   <si>
+    <t>den magiske klub</t>
+  </si>
+  <si>
+    <t>Den magiske klub</t>
+  </si>
+  <si>
     <t>den magiske månerejse</t>
   </si>
   <si>
@@ -631,6 +661,12 @@
     <t>Dexter: Resurrection</t>
   </si>
   <si>
+    <t>dianas bryllup</t>
+  </si>
+  <si>
+    <t>Dianas bryllup</t>
+  </si>
+  <si>
     <t>dicte</t>
   </si>
   <si>
@@ -1129,6 +1165,12 @@
     <t>Grænsepatruljen Usa</t>
   </si>
   <si>
+    <t>grænsevagterne - sverige</t>
+  </si>
+  <si>
+    <t>Grænsevagterne - Sverige</t>
+  </si>
+  <si>
     <t>gummi tarzan</t>
   </si>
   <si>
@@ -1459,6 +1501,12 @@
     <t>Ja For Fanø!</t>
   </si>
   <si>
+    <t>jagerpilotens sidste mission</t>
+  </si>
+  <si>
+    <t>Jagerpilotens sidste mission</t>
+  </si>
+  <si>
     <t>jakten på rød oktober</t>
   </si>
   <si>
@@ -1549,6 +1597,12 @@
     <t>Koch'En På Toppen</t>
   </si>
   <si>
+    <t>kodeknækkerne</t>
+  </si>
+  <si>
+    <t>Kodeknækkerne</t>
+  </si>
+  <si>
     <t>kollision</t>
   </si>
   <si>
@@ -1561,6 +1615,12 @@
     <t>Kommissar Van der Valk</t>
   </si>
   <si>
+    <t>kompani o.r.d.</t>
+  </si>
+  <si>
+    <t>Kompani O.R.D.</t>
+  </si>
+  <si>
     <t>krejlerkongen</t>
   </si>
   <si>
@@ -1621,6 +1681,12 @@
     <t>Kærlighed Hvor Kragerne Vender</t>
   </si>
   <si>
+    <t>købmænd på 1. klasse</t>
+  </si>
+  <si>
+    <t>Købmænd på 1. klasse</t>
+  </si>
+  <si>
     <t>køkkenet</t>
   </si>
   <si>
@@ -2767,6 +2833,12 @@
     <t>The Mentalist</t>
   </si>
   <si>
+    <t>the world's most famous tiger</t>
+  </si>
+  <si>
+    <t>The World's Most Famous Tiger</t>
+  </si>
+  <si>
     <t>til døden os skiller</t>
   </si>
   <si>
@@ -3017,6 +3089,12 @@
   </si>
   <si>
     <t>Vintervejens Helte</t>
+  </si>
+  <si>
+    <t>vivis nye numse</t>
+  </si>
+  <si>
+    <t>Vivis Nye Numse</t>
   </si>
   <si>
     <t>voksne mennesker</t>
@@ -3440,7 +3518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E507"/>
+  <dimension ref="A1:E520"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -3469,10 +3547,10 @@
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
@@ -3483,10 +3561,10 @@
     </row>
     <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
@@ -3497,10 +3575,10 @@
     </row>
     <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
@@ -3511,10 +3589,10 @@
     </row>
     <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -3525,10 +3603,10 @@
     </row>
     <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6</v>
@@ -3539,10 +3617,10 @@
     </row>
     <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>6</v>
@@ -3553,10 +3631,10 @@
     </row>
     <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>6</v>
@@ -3567,10 +3645,10 @@
     </row>
     <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>6</v>
@@ -3581,10 +3659,10 @@
     </row>
     <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>6</v>
@@ -3595,10 +3673,10 @@
     </row>
     <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>6</v>
@@ -3609,10 +3687,10 @@
     </row>
     <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>6</v>
@@ -3623,10 +3701,10 @@
     </row>
     <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>6</v>
@@ -3637,10 +3715,10 @@
     </row>
     <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>6</v>
@@ -3651,10 +3729,10 @@
     </row>
     <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>6</v>
@@ -3665,10 +3743,10 @@
     </row>
     <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>6</v>
@@ -3679,10 +3757,10 @@
     </row>
     <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>6</v>
@@ -3693,10 +3771,10 @@
     </row>
     <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>6</v>
@@ -3707,10 +3785,10 @@
     </row>
     <row r="19" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>6</v>
@@ -3721,10 +3799,10 @@
     </row>
     <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>6</v>
@@ -3735,10 +3813,10 @@
     </row>
     <row r="21" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>6</v>
@@ -3749,10 +3827,10 @@
     </row>
     <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>6</v>
@@ -3763,10 +3841,10 @@
     </row>
     <row r="23" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>6</v>
@@ -3777,10 +3855,10 @@
     </row>
     <row r="24" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>6</v>
@@ -3791,10 +3869,10 @@
     </row>
     <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>6</v>
@@ -3805,10 +3883,10 @@
     </row>
     <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>6</v>
@@ -3819,10 +3897,10 @@
     </row>
     <row r="27" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>6</v>
@@ -3833,10 +3911,10 @@
     </row>
     <row r="28" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>6</v>
@@ -3847,10 +3925,10 @@
     </row>
     <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>6</v>
@@ -3861,10 +3939,10 @@
     </row>
     <row r="30" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>6</v>
@@ -3875,10 +3953,10 @@
     </row>
     <row r="31" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>6</v>
@@ -3889,10 +3967,10 @@
     </row>
     <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
@@ -3903,10 +3981,10 @@
     </row>
     <row r="33" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>6</v>
@@ -3917,10 +3995,10 @@
     </row>
     <row r="34" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>6</v>
@@ -3931,10 +4009,10 @@
     </row>
     <row r="35" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>6</v>
@@ -3945,10 +4023,10 @@
     </row>
     <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>6</v>
@@ -3959,10 +4037,10 @@
     </row>
     <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>6</v>
@@ -3973,10 +4051,10 @@
     </row>
     <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>6</v>
@@ -3987,10 +4065,10 @@
     </row>
     <row r="39" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>6</v>
@@ -4001,10 +4079,10 @@
     </row>
     <row r="40" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>6</v>
@@ -4015,10 +4093,10 @@
     </row>
     <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
@@ -4029,10 +4107,10 @@
     </row>
     <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -4057,10 +4135,10 @@
     </row>
     <row r="44" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -4071,10 +4149,10 @@
     </row>
     <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
@@ -4085,10 +4163,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>6</v>
@@ -4099,10 +4177,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6</v>
@@ -4113,10 +4191,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6</v>
@@ -4127,10 +4205,10 @@
     </row>
     <row r="49" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -4141,10 +4219,10 @@
     </row>
     <row r="50" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>6</v>
@@ -4155,10 +4233,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>6</v>
@@ -4169,10 +4247,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
@@ -4183,10 +4261,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
@@ -4197,10 +4275,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
@@ -4253,10 +4331,10 @@
     </row>
     <row r="58" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B58" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>6</v>
@@ -4267,10 +4345,10 @@
     </row>
     <row r="59" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>6</v>
@@ -4281,10 +4359,10 @@
     </row>
     <row r="60" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B60" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>6</v>
@@ -4295,10 +4373,10 @@
     </row>
     <row r="61" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B61" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>6</v>
@@ -4309,10 +4387,10 @@
     </row>
     <row r="62" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>6</v>
@@ -4323,10 +4401,10 @@
     </row>
     <row r="63" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>6</v>
@@ -4337,10 +4415,10 @@
     </row>
     <row r="64" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>6</v>
@@ -4351,10 +4429,10 @@
     </row>
     <row r="65" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -4365,10 +4443,10 @@
     </row>
     <row r="66" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>6</v>
@@ -4379,10 +4457,10 @@
     </row>
     <row r="67" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>6</v>
@@ -4393,10 +4471,10 @@
     </row>
     <row r="68" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>6</v>
@@ -4407,10 +4485,10 @@
     </row>
     <row r="69" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>6</v>
@@ -4421,10 +4499,10 @@
     </row>
     <row r="70" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B70" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>6</v>
@@ -4435,10 +4513,10 @@
     </row>
     <row r="71" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>6</v>
@@ -4449,10 +4527,10 @@
     </row>
     <row r="72" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>6</v>
@@ -4463,10 +4541,10 @@
     </row>
     <row r="73" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>6</v>
@@ -4477,10 +4555,10 @@
     </row>
     <row r="74" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="B74" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>6</v>
@@ -4491,10 +4569,10 @@
     </row>
     <row r="75" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="B75" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>6</v>
@@ -4505,10 +4583,10 @@
     </row>
     <row r="76" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B76" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>6</v>
@@ -4519,10 +4597,10 @@
     </row>
     <row r="77" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B77" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>6</v>
@@ -4533,10 +4611,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B78" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>6</v>
@@ -4547,10 +4625,10 @@
     </row>
     <row r="79" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>6</v>
@@ -4561,10 +4639,10 @@
     </row>
     <row r="80" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B80" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -4575,10 +4653,10 @@
     </row>
     <row r="81" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="B81" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>6</v>
@@ -4589,10 +4667,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="B82" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
@@ -4603,10 +4681,10 @@
     </row>
     <row r="83" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="B83" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>6</v>
@@ -4617,10 +4695,10 @@
     </row>
     <row r="84" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="B84" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>6</v>
@@ -4631,10 +4709,10 @@
     </row>
     <row r="85" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="B85" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>6</v>
@@ -4645,10 +4723,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="B86" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>6</v>
@@ -4659,10 +4737,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B87" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>6</v>
@@ -4673,10 +4751,10 @@
     </row>
     <row r="88" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="B88" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>6</v>
@@ -4687,10 +4765,10 @@
     </row>
     <row r="89" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B89" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>6</v>
@@ -4701,10 +4779,10 @@
     </row>
     <row r="90" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B90" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>6</v>
@@ -4715,10 +4793,10 @@
     </row>
     <row r="91" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B91" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>6</v>
@@ -4729,10 +4807,10 @@
     </row>
     <row r="92" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B92" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>6</v>
@@ -4743,10 +4821,10 @@
     </row>
     <row r="93" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="B93" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>6</v>
@@ -4757,10 +4835,10 @@
     </row>
     <row r="94" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>6</v>
@@ -4771,10 +4849,10 @@
     </row>
     <row r="95" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="B95" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>6</v>
@@ -4785,10 +4863,10 @@
     </row>
     <row r="96" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B96" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>6</v>
@@ -4799,10 +4877,10 @@
     </row>
     <row r="97" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B97" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>6</v>
@@ -4813,10 +4891,10 @@
     </row>
     <row r="98" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B98" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>6</v>
@@ -4827,10 +4905,10 @@
     </row>
     <row r="99" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="B99" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>6</v>
@@ -4841,10 +4919,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B100" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>6</v>
@@ -4855,10 +4933,10 @@
     </row>
     <row r="101" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="B101" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>6</v>
@@ -4869,10 +4947,10 @@
     </row>
     <row r="102" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="B102" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>6</v>
@@ -4883,10 +4961,10 @@
     </row>
     <row r="103" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="B103" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>6</v>
@@ -4897,10 +4975,10 @@
     </row>
     <row r="104" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="B104" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -4911,10 +4989,10 @@
     </row>
     <row r="105" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="B105" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>6</v>
@@ -4925,10 +5003,10 @@
     </row>
     <row r="106" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B106" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>6</v>
@@ -4939,10 +5017,10 @@
     </row>
     <row r="107" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="B107" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>6</v>
@@ -4953,10 +5031,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="B108" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>6</v>
@@ -4967,10 +5045,10 @@
     </row>
     <row r="109" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="B109" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>6</v>
@@ -4981,10 +5059,10 @@
     </row>
     <row r="110" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="B110" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>6</v>
@@ -4995,10 +5073,10 @@
     </row>
     <row r="111" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B111" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>6</v>
@@ -5009,10 +5087,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B112" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>6</v>
@@ -5023,10 +5101,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="B113" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>6</v>
@@ -5037,10 +5115,10 @@
     </row>
     <row r="114" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="B114" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>6</v>
@@ -5051,10 +5129,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="B115" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>6</v>
@@ -5065,10 +5143,10 @@
     </row>
     <row r="116" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B116" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>6</v>
@@ -5079,10 +5157,10 @@
     </row>
     <row r="117" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B117" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>6</v>
@@ -5093,10 +5171,10 @@
     </row>
     <row r="118" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="B118" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>6</v>
@@ -5107,10 +5185,10 @@
     </row>
     <row r="119" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="B119" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>6</v>
@@ -5121,10 +5199,10 @@
     </row>
     <row r="120" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B120" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>6</v>
@@ -5135,10 +5213,10 @@
     </row>
     <row r="121" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B121" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>6</v>
@@ -5149,10 +5227,10 @@
     </row>
     <row r="122" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B122" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>6</v>
@@ -5163,10 +5241,10 @@
     </row>
     <row r="123" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B123" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>6</v>
@@ -5177,10 +5255,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="B124" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -5191,10 +5269,10 @@
     </row>
     <row r="125" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B125" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>6</v>
@@ -5205,10 +5283,10 @@
     </row>
     <row r="126" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B126" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>6</v>
@@ -5219,10 +5297,10 @@
     </row>
     <row r="127" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="B127" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>6</v>
@@ -5233,10 +5311,10 @@
     </row>
     <row r="128" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="B128" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>6</v>
@@ -5247,10 +5325,10 @@
     </row>
     <row r="129" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="B129" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>6</v>
@@ -5261,10 +5339,10 @@
     </row>
     <row r="130" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B130" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>6</v>
@@ -5275,10 +5353,10 @@
     </row>
     <row r="131" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="B131" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>6</v>
@@ -5289,10 +5367,10 @@
     </row>
     <row r="132" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B132" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>6</v>
@@ -5303,10 +5381,10 @@
     </row>
     <row r="133" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B133" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>6</v>
@@ -5317,10 +5395,10 @@
     </row>
     <row r="134" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="B134" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>6</v>
@@ -5331,10 +5409,10 @@
     </row>
     <row r="135" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="B135" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>6</v>
@@ -5345,10 +5423,10 @@
     </row>
     <row r="136" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="B136" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>6</v>
@@ -5359,10 +5437,10 @@
     </row>
     <row r="137" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B137" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>6</v>
@@ -5373,10 +5451,10 @@
     </row>
     <row r="138" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B138" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>6</v>
@@ -5387,10 +5465,10 @@
     </row>
     <row r="139" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B139" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>6</v>
@@ -5401,10 +5479,10 @@
     </row>
     <row r="140" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B140" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>6</v>
@@ -5415,10 +5493,10 @@
     </row>
     <row r="141" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="B141" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>6</v>
@@ -5429,10 +5507,10 @@
     </row>
     <row r="142" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="B142" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>6</v>
@@ -5443,10 +5521,10 @@
     </row>
     <row r="143" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B143" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>6</v>
@@ -5457,10 +5535,10 @@
     </row>
     <row r="144" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="B144" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>6</v>
@@ -5471,10 +5549,10 @@
     </row>
     <row r="145" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="B145" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>6</v>
@@ -5485,10 +5563,10 @@
     </row>
     <row r="146" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="B146" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>6</v>
@@ -5499,10 +5577,10 @@
     </row>
     <row r="147" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="B147" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>6</v>
@@ -5513,10 +5591,10 @@
     </row>
     <row r="148" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="B148" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>6</v>
@@ -5527,10 +5605,10 @@
     </row>
     <row r="149" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B149" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>6</v>
@@ -5541,10 +5619,10 @@
     </row>
     <row r="150" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="B150" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>6</v>
@@ -5555,10 +5633,10 @@
     </row>
     <row r="151" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="B151" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>6</v>
@@ -5569,10 +5647,10 @@
     </row>
     <row r="152" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="B152" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>6</v>
@@ -5583,10 +5661,10 @@
     </row>
     <row r="153" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="B153" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>6</v>
@@ -5597,10 +5675,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="B154" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>6</v>
@@ -5611,10 +5689,10 @@
     </row>
     <row r="155" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="B155" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>6</v>
@@ -5625,10 +5703,10 @@
     </row>
     <row r="156" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="B156" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>6</v>
@@ -5639,10 +5717,10 @@
     </row>
     <row r="157" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B157" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>6</v>
@@ -5653,10 +5731,10 @@
     </row>
     <row r="158" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="B158" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>6</v>
@@ -5667,10 +5745,10 @@
     </row>
     <row r="159" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="B159" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>6</v>
@@ -5681,10 +5759,10 @@
     </row>
     <row r="160" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="B160" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>6</v>
@@ -5695,10 +5773,10 @@
     </row>
     <row r="161" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="B161" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>6</v>
@@ -5709,10 +5787,10 @@
     </row>
     <row r="162" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="B162" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>6</v>
@@ -5723,10 +5801,10 @@
     </row>
     <row r="163" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="B163" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>6</v>
@@ -5737,10 +5815,10 @@
     </row>
     <row r="164" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="B164" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>6</v>
@@ -5751,10 +5829,10 @@
     </row>
     <row r="165" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="B165" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>6</v>
@@ -5765,10 +5843,10 @@
     </row>
     <row r="166" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="B166" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>6</v>
@@ -5779,10 +5857,10 @@
     </row>
     <row r="167" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="B167" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>6</v>
@@ -5793,10 +5871,10 @@
     </row>
     <row r="168" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B168" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>6</v>
@@ -5807,10 +5885,10 @@
     </row>
     <row r="169" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="B169" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>6</v>
@@ -5821,10 +5899,10 @@
     </row>
     <row r="170" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="B170" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>6</v>
@@ -5835,10 +5913,10 @@
     </row>
     <row r="171" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="B171" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>6</v>
@@ -5849,10 +5927,10 @@
     </row>
     <row r="172" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="B172" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>6</v>
@@ -5863,10 +5941,10 @@
     </row>
     <row r="173" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="B173" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>6</v>
@@ -5877,10 +5955,10 @@
     </row>
     <row r="174" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B174" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>6</v>
@@ -5891,10 +5969,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="B175" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>6</v>
@@ -5905,10 +5983,10 @@
     </row>
     <row r="176" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="B176" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>6</v>
@@ -5919,10 +5997,10 @@
     </row>
     <row r="177" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="B177" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>6</v>
@@ -5933,10 +6011,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="B178" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>6</v>
@@ -5947,10 +6025,10 @@
     </row>
     <row r="179" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="B179" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>6</v>
@@ -5961,10 +6039,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="B180" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>6</v>
@@ -5975,10 +6053,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="B181" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>6</v>
@@ -5989,10 +6067,10 @@
     </row>
     <row r="182" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="B182" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>6</v>
@@ -6003,10 +6081,10 @@
     </row>
     <row r="183" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="B183" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -6017,10 +6095,10 @@
     </row>
     <row r="184" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B184" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>6</v>
@@ -6031,10 +6109,10 @@
     </row>
     <row r="185" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="B185" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>6</v>
@@ -6045,10 +6123,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="B186" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>6</v>
@@ -6059,10 +6137,10 @@
     </row>
     <row r="187" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="B187" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>6</v>
@@ -6073,10 +6151,10 @@
     </row>
     <row r="188" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="B188" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>6</v>
@@ -6087,10 +6165,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="B189" t="s">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -6101,10 +6179,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="B190" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>6</v>
@@ -6115,10 +6193,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="B191" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>6</v>
@@ -6129,10 +6207,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="B192" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>6</v>
@@ -6143,10 +6221,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="B193" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>6</v>
@@ -6157,10 +6235,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="B194" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>6</v>
@@ -6171,10 +6249,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="B195" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>6</v>
@@ -6185,10 +6263,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="B196" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>6</v>
@@ -6199,10 +6277,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="B197" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>6</v>
@@ -6213,10 +6291,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="B198" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>6</v>
@@ -6227,10 +6305,10 @@
     </row>
     <row r="199" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="B199" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>6</v>
@@ -6241,10 +6319,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="B200" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>6</v>
@@ -6255,10 +6333,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="B201" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>6</v>
@@ -6269,10 +6347,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="B202" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>6</v>
@@ -6283,10 +6361,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="B203" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>6</v>
@@ -6297,10 +6375,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="B204" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>6</v>
@@ -6311,10 +6389,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="B205" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>6</v>
@@ -6325,10 +6403,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="B206" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>6</v>
@@ -6339,10 +6417,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B207" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>6</v>
@@ -6353,10 +6431,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="B208" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>6</v>
@@ -6367,10 +6445,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="B209" t="s">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>6</v>
@@ -6381,10 +6459,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="B210" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>6</v>
@@ -6395,10 +6473,10 @@
     </row>
     <row r="211" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="B211" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>6</v>
@@ -6409,10 +6487,10 @@
     </row>
     <row r="212" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="B212" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>6</v>
@@ -6423,10 +6501,10 @@
     </row>
     <row r="213" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="B213" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>6</v>
@@ -6437,10 +6515,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="B214" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>6</v>
@@ -6451,10 +6529,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="B215" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>6</v>
@@ -6465,10 +6543,10 @@
     </row>
     <row r="216" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="B216" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>6</v>
@@ -6479,10 +6557,10 @@
     </row>
     <row r="217" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="B217" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>6</v>
@@ -6493,10 +6571,10 @@
     </row>
     <row r="218" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="B218" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>6</v>
@@ -6507,10 +6585,10 @@
     </row>
     <row r="219" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="B219" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>6</v>
@@ -6521,10 +6599,10 @@
     </row>
     <row r="220" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="B220" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>6</v>
@@ -6535,10 +6613,10 @@
     </row>
     <row r="221" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="B221" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>6</v>
@@ -6549,10 +6627,10 @@
     </row>
     <row r="222" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="B222" t="s">
-        <v>521</v>
+        <v>499</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>6</v>
@@ -6563,10 +6641,10 @@
     </row>
     <row r="223" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="B223" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>6</v>
@@ -6577,10 +6655,10 @@
     </row>
     <row r="224" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="B224" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>6</v>
@@ -6591,10 +6669,10 @@
     </row>
     <row r="225" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="B225" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -6605,10 +6683,10 @@
     </row>
     <row r="226" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="B226" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>6</v>
@@ -6619,10 +6697,10 @@
     </row>
     <row r="227" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="B227" t="s">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>6</v>
@@ -6633,10 +6711,10 @@
     </row>
     <row r="228" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="B228" t="s">
-        <v>533</v>
+        <v>511</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>6</v>
@@ -6647,10 +6725,10 @@
     </row>
     <row r="229" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="B229" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -6661,10 +6739,10 @@
     </row>
     <row r="230" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="B230" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>6</v>
@@ -6675,10 +6753,10 @@
     </row>
     <row r="231" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="B231" t="s">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>6</v>
@@ -6689,10 +6767,10 @@
     </row>
     <row r="232" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="B232" t="s">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -6703,10 +6781,10 @@
     </row>
     <row r="233" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>544</v>
+        <v>520</v>
       </c>
       <c r="B233" t="s">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -6717,10 +6795,10 @@
     </row>
     <row r="234" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="B234" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>6</v>
@@ -6731,10 +6809,10 @@
     </row>
     <row r="235" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="B235" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>6</v>
@@ -6745,10 +6823,10 @@
     </row>
     <row r="236" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="B236" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
@@ -6759,10 +6837,10 @@
     </row>
     <row r="237" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>552</v>
+        <v>532</v>
       </c>
       <c r="B237" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
@@ -6773,10 +6851,10 @@
     </row>
     <row r="238" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="B238" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>6</v>
@@ -6787,10 +6865,10 @@
     </row>
     <row r="239" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="B239" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
@@ -6801,10 +6879,10 @@
     </row>
     <row r="240" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="B240" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
@@ -6815,10 +6893,10 @@
     </row>
     <row r="241" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B241" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
@@ -6829,10 +6907,10 @@
     </row>
     <row r="242" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B242" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -6843,10 +6921,10 @@
     </row>
     <row r="243" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
       <c r="B243" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
@@ -6857,10 +6935,10 @@
     </row>
     <row r="244" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="B244" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -6871,10 +6949,10 @@
     </row>
     <row r="245" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="B245" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -6885,10 +6963,10 @@
     </row>
     <row r="246" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="B246" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
@@ -6899,10 +6977,10 @@
     </row>
     <row r="247" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>578</v>
+        <v>554</v>
       </c>
       <c r="B247" t="s">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
@@ -6913,10 +6991,10 @@
     </row>
     <row r="248" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="B248" t="s">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
@@ -6927,10 +7005,10 @@
     </row>
     <row r="249" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>582</v>
+        <v>558</v>
       </c>
       <c r="B249" t="s">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
@@ -6941,10 +7019,10 @@
     </row>
     <row r="250" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="B250" t="s">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
@@ -6955,10 +7033,10 @@
     </row>
     <row r="251" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="B251" t="s">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>6</v>
@@ -6969,10 +7047,10 @@
     </row>
     <row r="252" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="B252" t="s">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
@@ -6983,10 +7061,10 @@
     </row>
     <row r="253" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="B253" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>6</v>
@@ -6997,10 +7075,10 @@
     </row>
     <row r="254" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="B254" t="s">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>6</v>
@@ -7011,10 +7089,10 @@
     </row>
     <row r="255" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="B255" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>6</v>
@@ -7025,10 +7103,10 @@
     </row>
     <row r="256" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
       <c r="B256" t="s">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>6</v>
@@ -7039,10 +7117,10 @@
     </row>
     <row r="257" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>598</v>
+        <v>576</v>
       </c>
       <c r="B257" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>6</v>
@@ -7053,10 +7131,10 @@
     </row>
     <row r="258" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
       <c r="B258" t="s">
-        <v>601</v>
+        <v>579</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>6</v>
@@ -7067,10 +7145,10 @@
     </row>
     <row r="259" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="B259" t="s">
-        <v>603</v>
+        <v>581</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>6</v>
@@ -7081,10 +7159,10 @@
     </row>
     <row r="260" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="B260" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -7095,10 +7173,10 @@
     </row>
     <row r="261" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="B261" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>6</v>
@@ -7109,10 +7187,10 @@
     </row>
     <row r="262" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="B262" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>6</v>
@@ -7123,10 +7201,10 @@
     </row>
     <row r="263" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="B263" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>6</v>
@@ -7137,10 +7215,10 @@
     </row>
     <row r="264" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="B264" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>6</v>
@@ -7151,10 +7229,10 @@
     </row>
     <row r="265" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>614</v>
+        <v>594</v>
       </c>
       <c r="B265" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>6</v>
@@ -7165,10 +7243,10 @@
     </row>
     <row r="266" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>616</v>
+        <v>596</v>
       </c>
       <c r="B266" t="s">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>6</v>
@@ -7179,10 +7257,10 @@
     </row>
     <row r="267" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="B267" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>6</v>
@@ -7193,10 +7271,10 @@
     </row>
     <row r="268" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="B268" t="s">
-        <v>621</v>
+        <v>603</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>6</v>
@@ -7207,10 +7285,10 @@
     </row>
     <row r="269" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="B269" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>6</v>
@@ -7221,10 +7299,10 @@
     </row>
     <row r="270" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="B270" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>6</v>
@@ -7235,10 +7313,10 @@
     </row>
     <row r="271" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="B271" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>6</v>
@@ -7249,10 +7327,10 @@
     </row>
     <row r="272" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="B272" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>6</v>
@@ -7263,10 +7341,10 @@
     </row>
     <row r="273" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="B273" t="s">
-        <v>631</v>
+        <v>613</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>6</v>
@@ -7277,10 +7355,10 @@
     </row>
     <row r="274" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="B274" t="s">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>6</v>
@@ -7291,10 +7369,10 @@
     </row>
     <row r="275" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>638</v>
+        <v>616</v>
       </c>
       <c r="B275" t="s">
-        <v>639</v>
+        <v>617</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>6</v>
@@ -7305,10 +7383,10 @@
     </row>
     <row r="276" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
       <c r="B276" t="s">
-        <v>645</v>
+        <v>619</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>6</v>
@@ -7319,10 +7397,10 @@
     </row>
     <row r="277" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>646</v>
+        <v>620</v>
       </c>
       <c r="B277" t="s">
-        <v>647</v>
+        <v>621</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>6</v>
@@ -7333,10 +7411,10 @@
     </row>
     <row r="278" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>652</v>
+        <v>622</v>
       </c>
       <c r="B278" t="s">
-        <v>653</v>
+        <v>623</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>6</v>
@@ -7347,10 +7425,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>654</v>
+        <v>624</v>
       </c>
       <c r="B279" t="s">
-        <v>655</v>
+        <v>625</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>6</v>
@@ -7361,10 +7439,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>656</v>
+        <v>626</v>
       </c>
       <c r="B280" t="s">
-        <v>657</v>
+        <v>627</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>6</v>
@@ -7375,10 +7453,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>658</v>
+        <v>628</v>
       </c>
       <c r="B281" t="s">
-        <v>659</v>
+        <v>629</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>6</v>
@@ -7389,10 +7467,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="B282" t="s">
-        <v>661</v>
+        <v>631</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>6</v>
@@ -7403,10 +7481,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>662</v>
+        <v>632</v>
       </c>
       <c r="B283" t="s">
-        <v>663</v>
+        <v>633</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>6</v>
@@ -7417,10 +7495,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>664</v>
+        <v>634</v>
       </c>
       <c r="B284" t="s">
-        <v>665</v>
+        <v>635</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>6</v>
@@ -7431,10 +7509,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>670</v>
+        <v>636</v>
       </c>
       <c r="B285" t="s">
-        <v>671</v>
+        <v>637</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -7445,10 +7523,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>672</v>
+        <v>638</v>
       </c>
       <c r="B286" t="s">
-        <v>673</v>
+        <v>639</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>6</v>
@@ -7459,10 +7537,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>674</v>
+        <v>640</v>
       </c>
       <c r="B287" t="s">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>6</v>
@@ -7473,10 +7551,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>676</v>
+        <v>642</v>
       </c>
       <c r="B288" t="s">
-        <v>677</v>
+        <v>643</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>6</v>
@@ -7487,10 +7565,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>678</v>
+        <v>644</v>
       </c>
       <c r="B289" t="s">
-        <v>679</v>
+        <v>645</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>6</v>
@@ -7501,10 +7579,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>680</v>
+        <v>646</v>
       </c>
       <c r="B290" t="s">
-        <v>681</v>
+        <v>647</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>6</v>
@@ -7515,10 +7593,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>682</v>
+        <v>648</v>
       </c>
       <c r="B291" t="s">
-        <v>683</v>
+        <v>649</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>6</v>
@@ -7529,10 +7607,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>684</v>
+        <v>650</v>
       </c>
       <c r="B292" t="s">
-        <v>685</v>
+        <v>651</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>6</v>
@@ -7543,10 +7621,10 @@
     </row>
     <row r="293" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>686</v>
+        <v>652</v>
       </c>
       <c r="B293" t="s">
-        <v>687</v>
+        <v>653</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>6</v>
@@ -7557,10 +7635,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>688</v>
+        <v>656</v>
       </c>
       <c r="B294" t="s">
-        <v>689</v>
+        <v>657</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>6</v>
@@ -7571,10 +7649,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>690</v>
+        <v>658</v>
       </c>
       <c r="B295" t="s">
-        <v>691</v>
+        <v>659</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>6</v>
@@ -7585,10 +7663,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>692</v>
+        <v>660</v>
       </c>
       <c r="B296" t="s">
-        <v>693</v>
+        <v>661</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>6</v>
@@ -7599,10 +7677,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>696</v>
+        <v>662</v>
       </c>
       <c r="B297" t="s">
-        <v>697</v>
+        <v>663</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>6</v>
@@ -7613,10 +7691,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>698</v>
+        <v>664</v>
       </c>
       <c r="B298" t="s">
-        <v>699</v>
+        <v>665</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>6</v>
@@ -7627,10 +7705,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>700</v>
+        <v>666</v>
       </c>
       <c r="B299" t="s">
-        <v>701</v>
+        <v>667</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>6</v>
@@ -7641,10 +7719,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>702</v>
+        <v>668</v>
       </c>
       <c r="B300" t="s">
-        <v>703</v>
+        <v>669</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>6</v>
@@ -7655,10 +7733,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>704</v>
+        <v>670</v>
       </c>
       <c r="B301" t="s">
-        <v>705</v>
+        <v>671</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>6</v>
@@ -7669,10 +7747,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>706</v>
+        <v>672</v>
       </c>
       <c r="B302" t="s">
-        <v>707</v>
+        <v>673</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -7683,10 +7761,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>708</v>
+        <v>674</v>
       </c>
       <c r="B303" t="s">
-        <v>709</v>
+        <v>675</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -7697,10 +7775,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>710</v>
+        <v>676</v>
       </c>
       <c r="B304" t="s">
-        <v>711</v>
+        <v>677</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -7711,10 +7789,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>712</v>
+        <v>678</v>
       </c>
       <c r="B305" t="s">
-        <v>713</v>
+        <v>679</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>6</v>
@@ -7725,10 +7803,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>714</v>
+        <v>680</v>
       </c>
       <c r="B306" t="s">
-        <v>715</v>
+        <v>681</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -7739,10 +7817,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>716</v>
+        <v>682</v>
       </c>
       <c r="B307" t="s">
-        <v>717</v>
+        <v>683</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>6</v>
@@ -7753,10 +7831,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>718</v>
+        <v>684</v>
       </c>
       <c r="B308" t="s">
-        <v>719</v>
+        <v>685</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>6</v>
@@ -7767,10 +7845,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>720</v>
+        <v>686</v>
       </c>
       <c r="B309" t="s">
-        <v>721</v>
+        <v>687</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>6</v>
@@ -7781,10 +7859,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>722</v>
+        <v>688</v>
       </c>
       <c r="B310" t="s">
-        <v>723</v>
+        <v>689</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -7795,10 +7873,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>724</v>
+        <v>690</v>
       </c>
       <c r="B311" t="s">
-        <v>725</v>
+        <v>691</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>6</v>
@@ -7809,10 +7887,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>726</v>
+        <v>692</v>
       </c>
       <c r="B312" t="s">
-        <v>727</v>
+        <v>693</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -7823,10 +7901,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>728</v>
+        <v>694</v>
       </c>
       <c r="B313" t="s">
-        <v>729</v>
+        <v>695</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -7837,10 +7915,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>730</v>
+        <v>696</v>
       </c>
       <c r="B314" t="s">
-        <v>731</v>
+        <v>697</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -7851,10 +7929,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>732</v>
+        <v>698</v>
       </c>
       <c r="B315" t="s">
-        <v>733</v>
+        <v>699</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>6</v>
@@ -7865,10 +7943,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>734</v>
+        <v>700</v>
       </c>
       <c r="B316" t="s">
-        <v>735</v>
+        <v>701</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>6</v>
@@ -7879,10 +7957,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>736</v>
+        <v>702</v>
       </c>
       <c r="B317" t="s">
-        <v>737</v>
+        <v>703</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>6</v>
@@ -7893,10 +7971,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>738</v>
+        <v>704</v>
       </c>
       <c r="B318" t="s">
-        <v>739</v>
+        <v>705</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>6</v>
@@ -7907,10 +7985,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>740</v>
+        <v>706</v>
       </c>
       <c r="B319" t="s">
-        <v>741</v>
+        <v>707</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>6</v>
@@ -7921,10 +7999,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>742</v>
+        <v>708</v>
       </c>
       <c r="B320" t="s">
-        <v>743</v>
+        <v>709</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>6</v>
@@ -7935,10 +8013,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>744</v>
+        <v>710</v>
       </c>
       <c r="B321" t="s">
-        <v>745</v>
+        <v>711</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>6</v>
@@ -7949,10 +8027,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>746</v>
+        <v>712</v>
       </c>
       <c r="B322" t="s">
-        <v>747</v>
+        <v>713</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -7963,10 +8041,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>748</v>
+        <v>714</v>
       </c>
       <c r="B323" t="s">
-        <v>749</v>
+        <v>715</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>6</v>
@@ -7977,10 +8055,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>750</v>
+        <v>716</v>
       </c>
       <c r="B324" t="s">
-        <v>751</v>
+        <v>717</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>6</v>
@@ -7991,10 +8069,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>754</v>
+        <v>718</v>
       </c>
       <c r="B325" t="s">
-        <v>755</v>
+        <v>719</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>6</v>
@@ -8005,10 +8083,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>756</v>
+        <v>720</v>
       </c>
       <c r="B326" t="s">
-        <v>757</v>
+        <v>721</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>6</v>
@@ -8019,10 +8097,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>758</v>
+        <v>722</v>
       </c>
       <c r="B327" t="s">
-        <v>759</v>
+        <v>723</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>6</v>
@@ -8033,10 +8111,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>760</v>
+        <v>724</v>
       </c>
       <c r="B328" t="s">
-        <v>761</v>
+        <v>725</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>6</v>
@@ -8047,10 +8125,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>762</v>
+        <v>726</v>
       </c>
       <c r="B329" t="s">
-        <v>763</v>
+        <v>727</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>6</v>
@@ -8061,10 +8139,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>764</v>
+        <v>728</v>
       </c>
       <c r="B330" t="s">
-        <v>765</v>
+        <v>729</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -8075,10 +8153,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>766</v>
+        <v>730</v>
       </c>
       <c r="B331" t="s">
-        <v>767</v>
+        <v>731</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>6</v>
@@ -8089,10 +8167,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>768</v>
+        <v>732</v>
       </c>
       <c r="B332" t="s">
-        <v>769</v>
+        <v>733</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>6</v>
@@ -8103,10 +8181,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>770</v>
+        <v>734</v>
       </c>
       <c r="B333" t="s">
-        <v>771</v>
+        <v>735</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>6</v>
@@ -8117,10 +8195,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>772</v>
+        <v>736</v>
       </c>
       <c r="B334" t="s">
-        <v>773</v>
+        <v>737</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>6</v>
@@ -8131,10 +8209,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="B335" t="s">
-        <v>775</v>
+        <v>739</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>6</v>
@@ -8145,10 +8223,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>776</v>
+        <v>740</v>
       </c>
       <c r="B336" t="s">
-        <v>777</v>
+        <v>741</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>6</v>
@@ -8159,10 +8237,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>778</v>
+        <v>742</v>
       </c>
       <c r="B337" t="s">
-        <v>779</v>
+        <v>743</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>6</v>
@@ -8173,10 +8251,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>780</v>
+        <v>744</v>
       </c>
       <c r="B338" t="s">
-        <v>781</v>
+        <v>745</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>6</v>
@@ -8187,10 +8265,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>782</v>
+        <v>746</v>
       </c>
       <c r="B339" t="s">
-        <v>783</v>
+        <v>747</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>6</v>
@@ -8201,10 +8279,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>784</v>
+        <v>748</v>
       </c>
       <c r="B340" t="s">
-        <v>785</v>
+        <v>749</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>6</v>
@@ -8215,10 +8293,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>786</v>
+        <v>750</v>
       </c>
       <c r="B341" t="s">
-        <v>787</v>
+        <v>751</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>6</v>
@@ -8229,10 +8307,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>788</v>
+        <v>752</v>
       </c>
       <c r="B342" t="s">
-        <v>789</v>
+        <v>753</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>6</v>
@@ -8243,10 +8321,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>790</v>
+        <v>754</v>
       </c>
       <c r="B343" t="s">
-        <v>791</v>
+        <v>755</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>6</v>
@@ -8257,10 +8335,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>792</v>
+        <v>756</v>
       </c>
       <c r="B344" t="s">
-        <v>793</v>
+        <v>757</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>6</v>
@@ -8271,10 +8349,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>794</v>
+        <v>758</v>
       </c>
       <c r="B345" t="s">
-        <v>795</v>
+        <v>759</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>6</v>
@@ -8285,10 +8363,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>796</v>
+        <v>760</v>
       </c>
       <c r="B346" t="s">
-        <v>797</v>
+        <v>761</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>6</v>
@@ -8299,10 +8377,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>798</v>
+        <v>762</v>
       </c>
       <c r="B347" t="s">
-        <v>799</v>
+        <v>763</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>6</v>
@@ -8313,10 +8391,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>800</v>
+        <v>764</v>
       </c>
       <c r="B348" t="s">
-        <v>801</v>
+        <v>765</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>6</v>
@@ -8327,10 +8405,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>802</v>
+        <v>766</v>
       </c>
       <c r="B349" t="s">
-        <v>803</v>
+        <v>767</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>6</v>
@@ -8341,10 +8419,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>804</v>
+        <v>768</v>
       </c>
       <c r="B350" t="s">
-        <v>805</v>
+        <v>769</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>6</v>
@@ -8355,10 +8433,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>806</v>
+        <v>770</v>
       </c>
       <c r="B351" t="s">
-        <v>807</v>
+        <v>771</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>6</v>
@@ -8369,10 +8447,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>808</v>
+        <v>772</v>
       </c>
       <c r="B352" t="s">
-        <v>809</v>
+        <v>773</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>6</v>
@@ -8383,10 +8461,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>812</v>
+        <v>776</v>
       </c>
       <c r="B353" t="s">
-        <v>813</v>
+        <v>777</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>6</v>
@@ -8397,10 +8475,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>816</v>
+        <v>778</v>
       </c>
       <c r="B354" t="s">
-        <v>817</v>
+        <v>779</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>6</v>
@@ -8411,10 +8489,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>818</v>
+        <v>780</v>
       </c>
       <c r="B355" t="s">
-        <v>819</v>
+        <v>781</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>6</v>
@@ -8425,10 +8503,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>820</v>
+        <v>782</v>
       </c>
       <c r="B356" t="s">
-        <v>821</v>
+        <v>783</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>6</v>
@@ -8439,10 +8517,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>822</v>
+        <v>784</v>
       </c>
       <c r="B357" t="s">
-        <v>823</v>
+        <v>785</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>6</v>
@@ -8453,10 +8531,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>824</v>
+        <v>786</v>
       </c>
       <c r="B358" t="s">
-        <v>825</v>
+        <v>787</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>6</v>
@@ -8467,10 +8545,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>826</v>
+        <v>788</v>
       </c>
       <c r="B359" t="s">
-        <v>827</v>
+        <v>789</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>6</v>
@@ -8481,10 +8559,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>828</v>
+        <v>790</v>
       </c>
       <c r="B360" t="s">
-        <v>829</v>
+        <v>791</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>6</v>
@@ -8495,10 +8573,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>830</v>
+        <v>792</v>
       </c>
       <c r="B361" t="s">
-        <v>831</v>
+        <v>793</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>6</v>
@@ -8509,10 +8587,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>832</v>
+        <v>794</v>
       </c>
       <c r="B362" t="s">
-        <v>833</v>
+        <v>795</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -8523,10 +8601,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>834</v>
+        <v>796</v>
       </c>
       <c r="B363" t="s">
-        <v>835</v>
+        <v>797</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>6</v>
@@ -8537,10 +8615,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>836</v>
+        <v>798</v>
       </c>
       <c r="B364" t="s">
-        <v>837</v>
+        <v>799</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>6</v>
@@ -8551,10 +8629,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>838</v>
+        <v>800</v>
       </c>
       <c r="B365" t="s">
-        <v>839</v>
+        <v>801</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>6</v>
@@ -8565,10 +8643,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>840</v>
+        <v>802</v>
       </c>
       <c r="B366" t="s">
-        <v>841</v>
+        <v>803</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>6</v>
@@ -8579,10 +8657,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>842</v>
+        <v>804</v>
       </c>
       <c r="B367" t="s">
-        <v>843</v>
+        <v>805</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>6</v>
@@ -8593,10 +8671,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>844</v>
+        <v>806</v>
       </c>
       <c r="B368" t="s">
-        <v>845</v>
+        <v>807</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>6</v>
@@ -8607,10 +8685,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>846</v>
+        <v>808</v>
       </c>
       <c r="B369" t="s">
-        <v>847</v>
+        <v>809</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>6</v>
@@ -8621,10 +8699,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>848</v>
+        <v>810</v>
       </c>
       <c r="B370" t="s">
-        <v>849</v>
+        <v>811</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>6</v>
@@ -8635,10 +8713,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>850</v>
+        <v>812</v>
       </c>
       <c r="B371" t="s">
-        <v>851</v>
+        <v>813</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>6</v>
@@ -8649,10 +8727,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>852</v>
+        <v>814</v>
       </c>
       <c r="B372" t="s">
-        <v>853</v>
+        <v>815</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>6</v>
@@ -8663,10 +8741,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>854</v>
+        <v>816</v>
       </c>
       <c r="B373" t="s">
-        <v>855</v>
+        <v>817</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>6</v>
@@ -8677,10 +8755,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>856</v>
+        <v>818</v>
       </c>
       <c r="B374" t="s">
-        <v>857</v>
+        <v>819</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>6</v>
@@ -8691,10 +8769,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="B375" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>6</v>
@@ -8705,10 +8783,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
       <c r="B376" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>6</v>
@@ -8719,10 +8797,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>862</v>
+        <v>824</v>
       </c>
       <c r="B377" t="s">
-        <v>863</v>
+        <v>825</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>6</v>
@@ -8733,10 +8811,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>864</v>
+        <v>826</v>
       </c>
       <c r="B378" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>6</v>
@@ -8747,10 +8825,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>870</v>
+        <v>828</v>
       </c>
       <c r="B379" t="s">
-        <v>871</v>
+        <v>829</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>6</v>
@@ -8761,10 +8839,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>876</v>
+        <v>830</v>
       </c>
       <c r="B380" t="s">
-        <v>877</v>
+        <v>831</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>6</v>
@@ -8775,10 +8853,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>878</v>
+        <v>834</v>
       </c>
       <c r="B381" t="s">
-        <v>879</v>
+        <v>835</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>6</v>
@@ -8789,10 +8867,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>880</v>
+        <v>838</v>
       </c>
       <c r="B382" t="s">
-        <v>881</v>
+        <v>839</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>6</v>
@@ -8803,10 +8881,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="B383" t="s">
-        <v>883</v>
+        <v>841</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>6</v>
@@ -8817,10 +8895,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>884</v>
+        <v>842</v>
       </c>
       <c r="B384" t="s">
-        <v>885</v>
+        <v>843</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>6</v>
@@ -8831,10 +8909,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>886</v>
+        <v>844</v>
       </c>
       <c r="B385" t="s">
-        <v>887</v>
+        <v>845</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>6</v>
@@ -8845,10 +8923,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>888</v>
+        <v>846</v>
       </c>
       <c r="B386" t="s">
-        <v>889</v>
+        <v>847</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>6</v>
@@ -8859,10 +8937,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>890</v>
+        <v>848</v>
       </c>
       <c r="B387" t="s">
-        <v>891</v>
+        <v>849</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>6</v>
@@ -8873,10 +8951,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>892</v>
+        <v>850</v>
       </c>
       <c r="B388" t="s">
-        <v>893</v>
+        <v>851</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>6</v>
@@ -8887,10 +8965,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>894</v>
+        <v>852</v>
       </c>
       <c r="B389" t="s">
-        <v>895</v>
+        <v>853</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>6</v>
@@ -8901,10 +8979,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>896</v>
+        <v>854</v>
       </c>
       <c r="B390" t="s">
-        <v>897</v>
+        <v>855</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>6</v>
@@ -8915,10 +8993,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>898</v>
+        <v>856</v>
       </c>
       <c r="B391" t="s">
-        <v>899</v>
+        <v>857</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>6</v>
@@ -8929,10 +9007,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>900</v>
+        <v>858</v>
       </c>
       <c r="B392" t="s">
-        <v>901</v>
+        <v>859</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>6</v>
@@ -8943,10 +9021,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>902</v>
+        <v>860</v>
       </c>
       <c r="B393" t="s">
-        <v>903</v>
+        <v>861</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>6</v>
@@ -8957,10 +9035,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>904</v>
+        <v>862</v>
       </c>
       <c r="B394" t="s">
-        <v>905</v>
+        <v>863</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>6</v>
@@ -8971,10 +9049,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>906</v>
+        <v>864</v>
       </c>
       <c r="B395" t="s">
-        <v>907</v>
+        <v>865</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>6</v>
@@ -8985,10 +9063,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>908</v>
+        <v>866</v>
       </c>
       <c r="B396" t="s">
-        <v>909</v>
+        <v>867</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>6</v>
@@ -8999,10 +9077,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>910</v>
+        <v>868</v>
       </c>
       <c r="B397" t="s">
-        <v>911</v>
+        <v>869</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>6</v>
@@ -9013,10 +9091,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>912</v>
+        <v>870</v>
       </c>
       <c r="B398" t="s">
-        <v>913</v>
+        <v>871</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>6</v>
@@ -9027,10 +9105,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>914</v>
+        <v>872</v>
       </c>
       <c r="B399" t="s">
-        <v>915</v>
+        <v>873</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>6</v>
@@ -9041,10 +9119,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>916</v>
+        <v>874</v>
       </c>
       <c r="B400" t="s">
-        <v>917</v>
+        <v>875</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>6</v>
@@ -9055,10 +9133,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>918</v>
+        <v>876</v>
       </c>
       <c r="B401" t="s">
-        <v>919</v>
+        <v>877</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>6</v>
@@ -9069,10 +9147,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>920</v>
+        <v>878</v>
       </c>
       <c r="B402" t="s">
-        <v>921</v>
+        <v>879</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>6</v>
@@ -9083,10 +9161,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>922</v>
+        <v>880</v>
       </c>
       <c r="B403" t="s">
-        <v>923</v>
+        <v>881</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>6</v>
@@ -9097,10 +9175,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>924</v>
+        <v>882</v>
       </c>
       <c r="B404" t="s">
-        <v>925</v>
+        <v>883</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>6</v>
@@ -9111,10 +9189,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>926</v>
+        <v>884</v>
       </c>
       <c r="B405" t="s">
-        <v>927</v>
+        <v>885</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>6</v>
@@ -9125,10 +9203,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>928</v>
+        <v>886</v>
       </c>
       <c r="B406" t="s">
-        <v>929</v>
+        <v>887</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>6</v>
@@ -9139,10 +9217,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>932</v>
+        <v>892</v>
       </c>
       <c r="B407" t="s">
-        <v>933</v>
+        <v>893</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>6</v>
@@ -9153,10 +9231,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>934</v>
+        <v>898</v>
       </c>
       <c r="B408" t="s">
-        <v>935</v>
+        <v>899</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>6</v>
@@ -9167,10 +9245,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>936</v>
+        <v>900</v>
       </c>
       <c r="B409" t="s">
-        <v>937</v>
+        <v>901</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>6</v>
@@ -9181,10 +9259,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>938</v>
+        <v>902</v>
       </c>
       <c r="B410" t="s">
-        <v>939</v>
+        <v>903</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>6</v>
@@ -9195,10 +9273,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>940</v>
+        <v>904</v>
       </c>
       <c r="B411" t="s">
-        <v>941</v>
+        <v>905</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>6</v>
@@ -9209,10 +9287,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>944</v>
+        <v>906</v>
       </c>
       <c r="B412" t="s">
-        <v>945</v>
+        <v>907</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>6</v>
@@ -9223,10 +9301,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>946</v>
+        <v>908</v>
       </c>
       <c r="B413" t="s">
-        <v>947</v>
+        <v>909</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>6</v>
@@ -9237,10 +9315,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>948</v>
+        <v>910</v>
       </c>
       <c r="B414" t="s">
-        <v>949</v>
+        <v>911</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>6</v>
@@ -9251,10 +9329,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>950</v>
+        <v>912</v>
       </c>
       <c r="B415" t="s">
-        <v>951</v>
+        <v>913</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>6</v>
@@ -9265,10 +9343,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>952</v>
+        <v>914</v>
       </c>
       <c r="B416" t="s">
-        <v>953</v>
+        <v>915</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>6</v>
@@ -9279,10 +9357,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>954</v>
+        <v>916</v>
       </c>
       <c r="B417" t="s">
-        <v>955</v>
+        <v>917</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>6</v>
@@ -9293,10 +9371,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>956</v>
+        <v>918</v>
       </c>
       <c r="B418" t="s">
-        <v>957</v>
+        <v>919</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>6</v>
@@ -9307,10 +9385,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>960</v>
+        <v>920</v>
       </c>
       <c r="B419" t="s">
-        <v>961</v>
+        <v>921</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -9321,10 +9399,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>962</v>
+        <v>922</v>
       </c>
       <c r="B420" t="s">
-        <v>963</v>
+        <v>923</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>6</v>
@@ -9335,10 +9413,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>964</v>
+        <v>924</v>
       </c>
       <c r="B421" t="s">
-        <v>965</v>
+        <v>925</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>6</v>
@@ -9349,10 +9427,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="B422" t="s">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>6</v>
@@ -9363,10 +9441,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>968</v>
+        <v>928</v>
       </c>
       <c r="B423" t="s">
-        <v>969</v>
+        <v>929</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>6</v>
@@ -9377,10 +9455,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="B424" t="s">
-        <v>971</v>
+        <v>931</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>6</v>
@@ -9391,10 +9469,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>972</v>
+        <v>932</v>
       </c>
       <c r="B425" t="s">
-        <v>973</v>
+        <v>933</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>6</v>
@@ -9405,10 +9483,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>974</v>
+        <v>934</v>
       </c>
       <c r="B426" t="s">
-        <v>975</v>
+        <v>935</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>6</v>
@@ -9419,10 +9497,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>976</v>
+        <v>938</v>
       </c>
       <c r="B427" t="s">
-        <v>977</v>
+        <v>939</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>6</v>
@@ -9433,10 +9511,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="B428" t="s">
-        <v>981</v>
+        <v>941</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -9447,10 +9525,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>982</v>
+        <v>942</v>
       </c>
       <c r="B429" t="s">
-        <v>983</v>
+        <v>943</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>6</v>
@@ -9461,10 +9539,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>984</v>
+        <v>944</v>
       </c>
       <c r="B430" t="s">
-        <v>985</v>
+        <v>945</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>6</v>
@@ -9475,10 +9553,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>986</v>
+        <v>946</v>
       </c>
       <c r="B431" t="s">
-        <v>987</v>
+        <v>947</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>6</v>
@@ -9489,10 +9567,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>988</v>
+        <v>948</v>
       </c>
       <c r="B432" t="s">
-        <v>989</v>
+        <v>949</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>6</v>
@@ -9503,10 +9581,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="B433" t="s">
-        <v>991</v>
+        <v>951</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>6</v>
@@ -9517,10 +9595,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>992</v>
+        <v>952</v>
       </c>
       <c r="B434" t="s">
-        <v>993</v>
+        <v>953</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>6</v>
@@ -9531,10 +9609,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>994</v>
+        <v>956</v>
       </c>
       <c r="B435" t="s">
-        <v>995</v>
+        <v>957</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>6</v>
@@ -9545,10 +9623,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>996</v>
+        <v>958</v>
       </c>
       <c r="B436" t="s">
-        <v>997</v>
+        <v>959</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>6</v>
@@ -9559,10 +9637,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>998</v>
+        <v>960</v>
       </c>
       <c r="B437" t="s">
-        <v>999</v>
+        <v>961</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>6</v>
@@ -9573,10 +9651,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1000</v>
+        <v>962</v>
       </c>
       <c r="B438" t="s">
-        <v>1001</v>
+        <v>963</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>6</v>
@@ -9587,10 +9665,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>1002</v>
+        <v>964</v>
       </c>
       <c r="B439" t="s">
-        <v>1003</v>
+        <v>965</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>6</v>
@@ -9601,10 +9679,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>1004</v>
+        <v>968</v>
       </c>
       <c r="B440" t="s">
-        <v>1005</v>
+        <v>969</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>6</v>
@@ -9615,10 +9693,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1006</v>
+        <v>970</v>
       </c>
       <c r="B441" t="s">
-        <v>1007</v>
+        <v>971</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>6</v>
@@ -9629,10 +9707,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1008</v>
+        <v>972</v>
       </c>
       <c r="B442" t="s">
-        <v>1009</v>
+        <v>973</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>6</v>
@@ -9643,10 +9721,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>1010</v>
+        <v>974</v>
       </c>
       <c r="B443" t="s">
-        <v>1011</v>
+        <v>975</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>6</v>
@@ -9657,10 +9735,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1012</v>
+        <v>976</v>
       </c>
       <c r="B444" t="s">
-        <v>1013</v>
+        <v>977</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>6</v>
@@ -9671,10 +9749,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1014</v>
+        <v>978</v>
       </c>
       <c r="B445" t="s">
-        <v>1015</v>
+        <v>979</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>6</v>
@@ -9685,10 +9763,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>1016</v>
+        <v>980</v>
       </c>
       <c r="B446" t="s">
-        <v>1017</v>
+        <v>981</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>6</v>
@@ -9699,10 +9777,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>28</v>
+        <v>982</v>
       </c>
       <c r="B447" t="s">
-        <v>29</v>
+        <v>983</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>6</v>
@@ -9713,10 +9791,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>78</v>
+        <v>984</v>
       </c>
       <c r="B448" t="s">
-        <v>79</v>
+        <v>985</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>6</v>
@@ -9727,43 +9805,52 @@
     </row>
     <row r="449" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>92</v>
+        <v>986</v>
       </c>
       <c r="B449" t="s">
-        <v>93</v>
+        <v>987</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D449" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>94</v>
+        <v>988</v>
       </c>
       <c r="B450" t="s">
-        <v>95</v>
+        <v>989</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D450" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="451" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>108</v>
+        <v>990</v>
       </c>
       <c r="B451" t="s">
-        <v>109</v>
+        <v>991</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D451" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>118</v>
+        <v>992</v>
       </c>
       <c r="B452" t="s">
-        <v>119</v>
+        <v>993</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>6</v>
@@ -9774,10 +9861,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>124</v>
+        <v>994</v>
       </c>
       <c r="B453" t="s">
-        <v>125</v>
+        <v>995</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>6</v>
@@ -9788,10 +9875,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>132</v>
+        <v>996</v>
       </c>
       <c r="B454" t="s">
-        <v>133</v>
+        <v>997</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>6</v>
@@ -9802,10 +9889,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>134</v>
+        <v>998</v>
       </c>
       <c r="B455" t="s">
-        <v>135</v>
+        <v>999</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>6</v>
@@ -9816,10 +9903,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="B456" t="s">
-        <v>141</v>
+        <v>1001</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>6</v>
@@ -9830,10 +9917,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>158</v>
+        <v>1004</v>
       </c>
       <c r="B457" t="s">
-        <v>159</v>
+        <v>1005</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>6</v>
@@ -9844,32 +9931,38 @@
     </row>
     <row r="458" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>162</v>
+        <v>1006</v>
       </c>
       <c r="B458" t="s">
-        <v>163</v>
+        <v>1007</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D458" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="459" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>164</v>
+        <v>1008</v>
       </c>
       <c r="B459" t="s">
-        <v>165</v>
+        <v>1009</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D459" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="460" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>172</v>
+        <v>1010</v>
       </c>
       <c r="B460" t="s">
-        <v>173</v>
+        <v>1011</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>6</v>
@@ -9880,10 +9973,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>176</v>
+        <v>1012</v>
       </c>
       <c r="B461" t="s">
-        <v>177</v>
+        <v>1013</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>6</v>
@@ -9894,21 +9987,24 @@
     </row>
     <row r="462" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>180</v>
+        <v>1014</v>
       </c>
       <c r="B462" t="s">
-        <v>181</v>
+        <v>1015</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D462" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="463" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>196</v>
+        <v>1016</v>
       </c>
       <c r="B463" t="s">
-        <v>197</v>
+        <v>1017</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>6</v>
@@ -9919,43 +10015,52 @@
     </row>
     <row r="464" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>198</v>
+        <v>1018</v>
       </c>
       <c r="B464" t="s">
-        <v>199</v>
+        <v>1019</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D464" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="465" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>200</v>
+        <v>1020</v>
       </c>
       <c r="B465" t="s">
-        <v>201</v>
+        <v>1021</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D465" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="466" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>202</v>
+        <v>1024</v>
       </c>
       <c r="B466" t="s">
-        <v>203</v>
+        <v>1025</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D466" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="467" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>214</v>
+        <v>1026</v>
       </c>
       <c r="B467" t="s">
-        <v>215</v>
+        <v>1027</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>6</v>
@@ -9966,10 +10071,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>216</v>
+        <v>1028</v>
       </c>
       <c r="B468" t="s">
-        <v>217</v>
+        <v>1029</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>6</v>
@@ -9980,76 +10085,94 @@
     </row>
     <row r="469" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>224</v>
+        <v>1030</v>
       </c>
       <c r="B469" t="s">
-        <v>225</v>
+        <v>1031</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D469" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="470" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>232</v>
+        <v>1032</v>
       </c>
       <c r="B470" t="s">
-        <v>233</v>
+        <v>1033</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D470" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="471" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>242</v>
+        <v>1034</v>
       </c>
       <c r="B471" t="s">
-        <v>243</v>
+        <v>1035</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D471" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="472" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>262</v>
+        <v>1036</v>
       </c>
       <c r="B472" t="s">
-        <v>263</v>
+        <v>1037</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D472" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="473" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>304</v>
+        <v>1038</v>
       </c>
       <c r="B473" t="s">
-        <v>305</v>
+        <v>1039</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D473" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="474" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>310</v>
+        <v>1040</v>
       </c>
       <c r="B474" t="s">
-        <v>311</v>
+        <v>1041</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D474" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="475" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>336</v>
+        <v>1042</v>
       </c>
       <c r="B475" t="s">
-        <v>337</v>
+        <v>1043</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>6</v>
@@ -10060,46 +10183,49 @@
     </row>
     <row r="476" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>344</v>
+        <v>5</v>
       </c>
       <c r="B476" t="s">
-        <v>345</v>
+        <v>5</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D476" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="477" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>354</v>
+        <v>26</v>
       </c>
       <c r="B477" t="s">
-        <v>355</v>
+        <v>27</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D477" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="478" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>366</v>
+        <v>56</v>
       </c>
       <c r="B478" t="s">
-        <v>367</v>
+        <v>57</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D478" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="479" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>390</v>
+        <v>90</v>
       </c>
       <c r="B479" t="s">
-        <v>391</v>
+        <v>91</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>6</v>
@@ -10110,66 +10236,54 @@
     </row>
     <row r="480" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>392</v>
+        <v>98</v>
       </c>
       <c r="B480" t="s">
-        <v>393</v>
+        <v>99</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D480" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="481" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>396</v>
+        <v>100</v>
       </c>
       <c r="B481" t="s">
-        <v>397</v>
+        <v>101</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D481" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="482" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>442</v>
+        <v>114</v>
       </c>
       <c r="B482" t="s">
-        <v>443</v>
+        <v>115</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D482" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="483" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>510</v>
+        <v>146</v>
       </c>
       <c r="B483" t="s">
-        <v>511</v>
+        <v>147</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D483" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="484" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>540</v>
+        <v>170</v>
       </c>
       <c r="B484" t="s">
-        <v>541</v>
+        <v>171</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>6</v>
@@ -10177,10 +10291,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>564</v>
+        <v>172</v>
       </c>
       <c r="B485" t="s">
-        <v>565</v>
+        <v>173</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>6</v>
@@ -10188,10 +10302,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>574</v>
+        <v>176</v>
       </c>
       <c r="B486" t="s">
-        <v>575</v>
+        <v>177</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>6</v>
@@ -10202,10 +10316,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>576</v>
+        <v>190</v>
       </c>
       <c r="B487" t="s">
-        <v>577</v>
+        <v>191</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>6</v>
@@ -10213,10 +10327,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>632</v>
+        <v>208</v>
       </c>
       <c r="B488" t="s">
-        <v>633</v>
+        <v>209</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>6</v>
@@ -10224,122 +10338,98 @@
     </row>
     <row r="489" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>636</v>
+        <v>210</v>
       </c>
       <c r="B489" t="s">
-        <v>637</v>
+        <v>211</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D489" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="490" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>640</v>
+        <v>212</v>
       </c>
       <c r="B490" t="s">
-        <v>641</v>
+        <v>213</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D490" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="491" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>642</v>
+        <v>214</v>
       </c>
       <c r="B491" t="s">
-        <v>643</v>
+        <v>215</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D491" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="492" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>648</v>
+        <v>236</v>
       </c>
       <c r="B492" t="s">
-        <v>649</v>
+        <v>237</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D492" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="493" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>650</v>
+        <v>244</v>
       </c>
       <c r="B493" t="s">
-        <v>651</v>
+        <v>245</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D493" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="494" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>666</v>
+        <v>254</v>
       </c>
       <c r="B494" t="s">
-        <v>667</v>
+        <v>255</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D494" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="495" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>668</v>
+        <v>274</v>
       </c>
       <c r="B495" t="s">
-        <v>669</v>
+        <v>275</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D495" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="496" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>694</v>
+        <v>316</v>
       </c>
       <c r="B496" t="s">
-        <v>695</v>
+        <v>317</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D496" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="497" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>752</v>
+        <v>322</v>
       </c>
       <c r="B497" t="s">
-        <v>753</v>
+        <v>323</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>6</v>
@@ -10347,10 +10437,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>810</v>
+        <v>366</v>
       </c>
       <c r="B498" t="s">
-        <v>811</v>
+        <v>367</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>6</v>
@@ -10358,10 +10448,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>814</v>
+        <v>378</v>
       </c>
       <c r="B499" t="s">
-        <v>815</v>
+        <v>379</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>6</v>
@@ -10369,65 +10459,80 @@
     </row>
     <row r="500" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>866</v>
+        <v>380</v>
       </c>
       <c r="B500" t="s">
-        <v>867</v>
+        <v>381</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D500" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="501" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>868</v>
+        <v>492</v>
       </c>
       <c r="B501" t="s">
-        <v>869</v>
+        <v>493</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D501" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="502" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>872</v>
+        <v>524</v>
       </c>
       <c r="B502" t="s">
-        <v>873</v>
+        <v>525</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D502" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="503" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>874</v>
+        <v>530</v>
       </c>
       <c r="B503" t="s">
-        <v>875</v>
+        <v>531</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D503" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="504" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>930</v>
+        <v>552</v>
       </c>
       <c r="B504" t="s">
-        <v>931</v>
+        <v>553</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D504" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="505" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>942</v>
+        <v>562</v>
       </c>
       <c r="B505" t="s">
-        <v>943</v>
+        <v>563</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>6</v>
@@ -10435,547 +10540,709 @@
     </row>
     <row r="506" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>958</v>
+        <v>586</v>
       </c>
       <c r="B506" t="s">
-        <v>959</v>
+        <v>587</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D506" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="507" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>978</v>
+        <v>598</v>
       </c>
       <c r="B507" t="s">
-        <v>979</v>
+        <v>599</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
+        <v>654</v>
+      </c>
+      <c r="B508" t="s">
+        <v>655</v>
+      </c>
+      <c r="C508" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
+        <v>774</v>
+      </c>
+      <c r="B509" t="s">
+        <v>775</v>
+      </c>
+      <c r="C509" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
+        <v>832</v>
+      </c>
+      <c r="B510" t="s">
+        <v>833</v>
+      </c>
+      <c r="C510" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
+        <v>836</v>
+      </c>
+      <c r="B511" t="s">
+        <v>837</v>
+      </c>
+      <c r="C511" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>888</v>
+      </c>
+      <c r="B512" t="s">
+        <v>889</v>
+      </c>
+      <c r="C512" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
+        <v>890</v>
+      </c>
+      <c r="B513" t="s">
+        <v>891</v>
+      </c>
+      <c r="C513" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
+        <v>894</v>
+      </c>
+      <c r="B514" t="s">
+        <v>895</v>
+      </c>
+      <c r="C514" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D514" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
+        <v>896</v>
+      </c>
+      <c r="B515" t="s">
+        <v>897</v>
+      </c>
+      <c r="C515" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
+        <v>936</v>
+      </c>
+      <c r="B516" t="s">
+        <v>937</v>
+      </c>
+      <c r="C516" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D516" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
+        <v>954</v>
+      </c>
+      <c r="B517" t="s">
+        <v>955</v>
+      </c>
+      <c r="C517" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
+        <v>966</v>
+      </c>
+      <c r="B518" t="s">
+        <v>967</v>
+      </c>
+      <c r="C518" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C519" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C520" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D520" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E507">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E520">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D507" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D520" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C447" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="C13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C15" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="C16" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C22" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C26" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C27" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C29" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="C30" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="C34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C35" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C36" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C448" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C449" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C450" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C476" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C477" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C11" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C20" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C21" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C22" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C23" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C24" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C478" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C25" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C26" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="C27" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C28" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C29" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C30" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C31" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="C32" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="C33" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C34" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C35" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C36" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="C37" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C38" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C39" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C40" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C479" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C41" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C42" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
     <hyperlink ref="C43" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C44" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C45" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C46" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C47" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C48" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C451" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C49" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C50" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C51" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C52" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C452" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C53" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C54" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C453" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C480" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C481" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C44" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C45" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C46" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C47" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C48" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C49" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C482" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C50" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C51" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C52" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C53" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C54" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
     <hyperlink ref="C55" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
     <hyperlink ref="C56" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
     <hyperlink ref="C57" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C454" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C455" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C58" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C59" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C456" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C60" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C61" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C62" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C63" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C64" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C65" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C66" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C67" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C457" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C68" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C458" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C459" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C69" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C70" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C71" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C460" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C72" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C461" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C73" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C462" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C74" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C75" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C76" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C77" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C78" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C79" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C80" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C463" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C464" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C465" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C466" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C81" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C82" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C83" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C84" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C85" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C467" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="C468" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="C86" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="C87" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C88" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="C469" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C89" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="C90" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C91" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C470" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C92" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="C93" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C94" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="C95" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C471" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="C96" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="C97" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="C98" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="C99" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="C100" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C101" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C102" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C103" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="C104" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C472" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="C105" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C106" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="C107" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C108" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="C109" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C110" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="C111" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C112" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="C113" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C114" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C115" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C116" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C117" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C118" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C119" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C120" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C121" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C122" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C123" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C124" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C473" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C125" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C126" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C474" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C127" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C128" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C129" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C130" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C131" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C132" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C133" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C134" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C135" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C136" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C137" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C138" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C475" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C139" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C140" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C141" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C476" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C142" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C143" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C144" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C145" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C477" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C146" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C147" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C148" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C149" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C150" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C478" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C151" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C152" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C153" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C154" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C155" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C156" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C157" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C158" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C159" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C160" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C161" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C479" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C480" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C162" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C481" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C163" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C164" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C165" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C166" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C167" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C168" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C169" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C170" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C171" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="C172" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C173" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C174" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C175" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C176" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C177" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C178" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C179" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C180" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C181" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C182" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C183" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C184" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C482" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C185" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C186" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C187" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C188" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C189" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C190" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C191" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C192" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C193" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C194" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C195" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C196" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C197" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C198" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C199" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C200" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="C201" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="C202" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="C203" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="C204" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="C205" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="C206" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="C207" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="C208" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="C209" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="C210" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="C211" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="C212" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="C213" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="C214" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="C215" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="C216" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="C217" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="C483" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="C218" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="C219" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="C220" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="C221" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="C222" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="C223" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="C224" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="C225" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="C226" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="C227" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="C228" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="C229" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="C230" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="C231" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="C484" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="C232" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="C233" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="C234" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="C235" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="C236" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="C237" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="C238" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="C239" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="C240" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="C241" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="C242" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="C485" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="C243" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="C244" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="C245" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="C246" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="C486" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="C487" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="C247" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="C248" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="C249" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="C250" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="C251" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="C252" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="C253" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="C254" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="C255" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="C256" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C257" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C258" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="C259" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="C260" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="C261" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="C262" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C263" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C264" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C265" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C266" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C267" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C268" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C269" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C270" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="C271" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="C272" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="C273" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="C488" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C274" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C489" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C275" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C490" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C491" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C276" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="C277" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C492" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C493" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C278" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C279" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C280" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C281" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C282" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C283" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C284" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C494" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C495" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C285" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C286" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C287" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C288" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C289" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C290" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C291" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C292" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C293" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C294" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C295" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C296" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C496" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C297" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C298" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C299" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C300" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C301" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C302" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="C303" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="C304" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C305" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C306" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C307" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C308" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C309" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="C310" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C311" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C312" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C313" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C314" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C315" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C316" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C317" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C318" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C319" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C320" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C321" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C322" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C323" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C324" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C497" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C325" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C326" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C327" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C328" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C329" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C330" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C331" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C332" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C333" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C334" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C335" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C336" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C337" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C338" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C339" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C340" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C341" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C342" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C343" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C344" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C345" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C346" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C347" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C348" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C349" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C350" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C351" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C352" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C498" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C353" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C499" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C354" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C355" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C356" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C357" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C358" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C359" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C360" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C361" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C362" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C363" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C364" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C365" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C366" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C367" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C368" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C369" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C370" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C371" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C372" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C373" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C374" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C375" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C376" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C377" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C378" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C500" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C501" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C379" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C502" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C503" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C380" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C381" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C382" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C383" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C384" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C385" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C386" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C387" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C388" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C389" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C390" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C391" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C392" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C393" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C394" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C395" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C396" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C397" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C398" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C399" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C400" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C401" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C402" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C403" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C404" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C405" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C406" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C504" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C407" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C408" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C409" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C410" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C411" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C505" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C412" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C413" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C414" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C415" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C416" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C417" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C418" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C506" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C419" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C420" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C421" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C422" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C423" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C424" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C425" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C426" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C427" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C507" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C428" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C429" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C430" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C431" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C432" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C433" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C434" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C435" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C436" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C437" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C438" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C439" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C440" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C441" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C442" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C443" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C444" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C445" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C446" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C58" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C59" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C60" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C61" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C62" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C63" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C64" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C483" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C65" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C66" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C67" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C68" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C69" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C70" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C71" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C72" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C73" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C74" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C75" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C484" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C485" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C76" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C486" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C77" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C78" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C79" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C80" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C81" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C82" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C487" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C83" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C84" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C85" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C86" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C87" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C88" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C89" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C90" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C488" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C489" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C490" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C491" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C91" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="C92" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="C93" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="C94" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C95" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C96" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C97" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="C98" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C99" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C100" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C492" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="C101" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C102" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="C103" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C493" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="C104" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="C105" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="C106" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="C107" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="C494" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C108" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C109" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C110" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="C111" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C112" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C113" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C114" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="C115" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C116" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="C495" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="C117" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="C118" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="C119" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C120" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C121" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C122" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C123" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C124" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C125" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C126" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C127" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C128" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C129" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C130" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C131" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C132" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C133" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C134" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C135" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C136" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C496" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C137" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C138" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C497" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C139" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C140" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C141" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C142" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C143" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C144" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C145" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C146" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C147" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="C148" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C149" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C150" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C151" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C152" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C153" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C154" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C155" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C156" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C157" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C158" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C159" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C498" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C160" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C161" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C162" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C163" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C164" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C499" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C500" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C165" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C166" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C167" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C168" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C169" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C170" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C171" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C172" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C173" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C174" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C175" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C176" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C177" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C178" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C179" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C180" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C181" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C182" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C183" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C184" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C185" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C186" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C187" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C188" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C189" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C190" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C191" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C192" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C193" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C194" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C195" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C196" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C197" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C198" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C199" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C200" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C201" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C202" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C203" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C204" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C205" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C206" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C207" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C208" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C209" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C210" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C211" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C212" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="C213" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="C214" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="C215" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="C216" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="C217" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="C218" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="C219" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="C501" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="C220" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C221" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="C222" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="C223" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="C224" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="C225" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="C226" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="C227" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="C228" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="C229" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="C230" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C231" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="C232" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="C233" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="C234" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="C502" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C235" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="C236" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="C503" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="C237" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="C238" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="C239" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="C240" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="C241" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="C242" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="C243" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="C244" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="C245" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="C246" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="C504" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="C247" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C248" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="C249" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="C250" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="C505" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="C251" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C252" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="C253" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="C254" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="C255" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="C256" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C257" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="C258" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="C259" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="C260" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="C261" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C506" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="C262" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="C263" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="C264" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="C265" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C266" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="C507" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C267" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C268" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="C269" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C270" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="C271" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="C272" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C273" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C274" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C275" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C276" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C277" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C278" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C279" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C280" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="C281" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="C282" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="C283" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C284" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C285" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C286" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C287" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C288" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C289" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C290" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="C291" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C292" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C293" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C508" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C294" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C295" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C296" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C297" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C298" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C299" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C300" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C301" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C302" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C303" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C304" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C305" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C306" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C307" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C308" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C309" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C310" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C311" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C312" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C313" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C314" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C315" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C316" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C317" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C318" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C319" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C320" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C321" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C322" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C323" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C324" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C325" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C326" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C327" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C328" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C329" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C330" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C331" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C332" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C333" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C334" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C335" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C336" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C337" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C338" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C339" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C340" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C341" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C342" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C343" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C344" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C345" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C346" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C347" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C348" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C349" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C350" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C351" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C352" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C509" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C353" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C354" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C355" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C356" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C357" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C358" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C359" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C360" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C361" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C362" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C363" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C364" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C365" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C366" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C367" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C368" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C369" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C370" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C371" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C372" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C373" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C374" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C375" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C376" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C377" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C378" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C379" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C380" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C510" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C381" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C511" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C382" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C383" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C384" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C385" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C386" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C387" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C388" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C389" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C390" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C391" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C392" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C393" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C394" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C395" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C396" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C397" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C398" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C399" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C400" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C401" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C402" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C403" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C404" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C405" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C406" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C512" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C513" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C407" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C514" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C515" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C408" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C409" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C410" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C411" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C412" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C413" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C414" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C415" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C416" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C417" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C418" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C419" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C420" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C421" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C422" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C423" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C424" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C425" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C426" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C516" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C427" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C428" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C429" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C430" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C431" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C432" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C433" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C434" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C517" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C435" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C436" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C437" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C438" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C439" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C518" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C440" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C441" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C442" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C443" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C444" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C445" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C446" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C447" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C448" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C449" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C450" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C451" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C452" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C453" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C454" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C455" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C456" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C519" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C457" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C458" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C459" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C460" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C461" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C462" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C463" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C464" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C465" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C520" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C466" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C467" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C468" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C469" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C470" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C471" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C472" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C473" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C474" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="C475" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B930F75-CF7A-4BDC-8849-6CA9D67A9244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE1B240-EC02-471D-A951-9B4D37A985BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danske backdrops" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="1044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="1044">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -3161,7 +3161,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3178,6 +3178,14 @@
     <font>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3209,12 +3217,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3518,8 +3527,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E520"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E521"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -3528,7 +3537,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3545,7 +3554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3559,7 +3568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3573,7 +3582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3587,7 +3596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -3601,7 +3610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3615,7 +3624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -3629,7 +3638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -3643,7 +3652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3657,7 +3666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -3671,7 +3680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -3685,7 +3694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -3699,7 +3708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -3713,7 +3722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -3727,7 +3736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -3741,7 +3750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -3755,7 +3764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -3769,7 +3778,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -3783,7 +3792,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -3797,7 +3806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -3811,7 +3820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -3825,7 +3834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -3839,7 +3848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -3853,7 +3862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -3867,7 +3876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -3881,7 +3890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -3895,7 +3904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -3909,7 +3918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -3923,7 +3932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -3937,7 +3946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -3951,7 +3960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -3965,7 +3974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -3979,7 +3988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -3993,7 +4002,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -4007,7 +4016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -4021,7 +4030,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -4035,7 +4044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -4049,7 +4058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -4063,7 +4072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -4077,7 +4086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -4091,7 +4100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -4105,7 +4114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -4119,7 +4128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -4133,7 +4142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -4147,7 +4156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -4161,7 +4170,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -4175,7 +4184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>108</v>
       </c>
@@ -4189,7 +4198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>110</v>
       </c>
@@ -4203,7 +4212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -4217,7 +4226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>116</v>
       </c>
@@ -4231,7 +4240,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>118</v>
       </c>
@@ -4245,7 +4254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>120</v>
       </c>
@@ -4259,7 +4268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>122</v>
       </c>
@@ -4273,7 +4282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>124</v>
       </c>
@@ -4287,7 +4296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>126</v>
       </c>
@@ -4301,7 +4310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>128</v>
       </c>
@@ -4315,7 +4324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>130</v>
       </c>
@@ -4329,7 +4338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>132</v>
       </c>
@@ -4343,7 +4352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>134</v>
       </c>
@@ -4357,7 +4366,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>136</v>
       </c>
@@ -4371,7 +4380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>138</v>
       </c>
@@ -4385,7 +4394,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>140</v>
       </c>
@@ -4399,7 +4408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>142</v>
       </c>
@@ -4413,7 +4422,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>144</v>
       </c>
@@ -4427,7 +4436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>148</v>
       </c>
@@ -4441,7 +4450,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>150</v>
       </c>
@@ -4455,7 +4464,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>152</v>
       </c>
@@ -4469,7 +4478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>154</v>
       </c>
@@ -4483,7 +4492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>156</v>
       </c>
@@ -4497,7 +4506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>158</v>
       </c>
@@ -4511,7 +4520,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>160</v>
       </c>
@@ -4525,7 +4534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>162</v>
       </c>
@@ -4539,7 +4548,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>164</v>
       </c>
@@ -4553,7 +4562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>166</v>
       </c>
@@ -4567,7 +4576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>168</v>
       </c>
@@ -4581,7 +4590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>174</v>
       </c>
@@ -4595,7 +4604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>178</v>
       </c>
@@ -4609,7 +4618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>180</v>
       </c>
@@ -4623,7 +4632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>182</v>
       </c>
@@ -4637,7 +4646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>184</v>
       </c>
@@ -4651,7 +4660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>186</v>
       </c>
@@ -4665,7 +4674,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>188</v>
       </c>
@@ -4679,7 +4688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>192</v>
       </c>
@@ -4693,7 +4702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>194</v>
       </c>
@@ -4707,7 +4716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>196</v>
       </c>
@@ -4721,7 +4730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>198</v>
       </c>
@@ -4735,7 +4744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>200</v>
       </c>
@@ -4749,7 +4758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>202</v>
       </c>
@@ -4763,7 +4772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>204</v>
       </c>
@@ -4777,7 +4786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>206</v>
       </c>
@@ -4791,7 +4800,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>216</v>
       </c>
@@ -4805,7 +4814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>218</v>
       </c>
@@ -4819,7 +4828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>220</v>
       </c>
@@ -4833,7 +4842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>222</v>
       </c>
@@ -4847,7 +4856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>224</v>
       </c>
@@ -4861,7 +4870,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>226</v>
       </c>
@@ -4875,7 +4884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>228</v>
       </c>
@@ -4889,7 +4898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>230</v>
       </c>
@@ -4903,7 +4912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>232</v>
       </c>
@@ -4917,7 +4926,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>234</v>
       </c>
@@ -4931,7 +4940,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>238</v>
       </c>
@@ -4945,7 +4954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>240</v>
       </c>
@@ -4959,7 +4968,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>242</v>
       </c>
@@ -4973,7 +4982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>246</v>
       </c>
@@ -4987,7 +4996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>248</v>
       </c>
@@ -5001,7 +5010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>250</v>
       </c>
@@ -5015,7 +5024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>252</v>
       </c>
@@ -5029,7 +5038,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>256</v>
       </c>
@@ -5043,7 +5052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>258</v>
       </c>
@@ -5057,7 +5066,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>260</v>
       </c>
@@ -5071,7 +5080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>262</v>
       </c>
@@ -5085,7 +5094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>264</v>
       </c>
@@ -5099,7 +5108,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>266</v>
       </c>
@@ -5113,7 +5122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>268</v>
       </c>
@@ -5127,7 +5136,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>270</v>
       </c>
@@ -5141,7 +5150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>272</v>
       </c>
@@ -5155,7 +5164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>276</v>
       </c>
@@ -5169,7 +5178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>278</v>
       </c>
@@ -5183,7 +5192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>280</v>
       </c>
@@ -5197,7 +5206,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>282</v>
       </c>
@@ -5211,7 +5220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>284</v>
       </c>
@@ -5225,7 +5234,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>286</v>
       </c>
@@ -5239,7 +5248,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>288</v>
       </c>
@@ -5253,7 +5262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>290</v>
       </c>
@@ -5267,7 +5276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>292</v>
       </c>
@@ -5281,7 +5290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>294</v>
       </c>
@@ -5295,7 +5304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>296</v>
       </c>
@@ -5309,7 +5318,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>298</v>
       </c>
@@ -5323,7 +5332,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>300</v>
       </c>
@@ -5337,7 +5346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>302</v>
       </c>
@@ -5351,7 +5360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>304</v>
       </c>
@@ -5365,7 +5374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>306</v>
       </c>
@@ -5379,7 +5388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>308</v>
       </c>
@@ -5393,7 +5402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>310</v>
       </c>
@@ -5407,7 +5416,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>312</v>
       </c>
@@ -5421,7 +5430,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>314</v>
       </c>
@@ -5435,7 +5444,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>318</v>
       </c>
@@ -5449,7 +5458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>320</v>
       </c>
@@ -5463,7 +5472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>324</v>
       </c>
@@ -5477,7 +5486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>326</v>
       </c>
@@ -5491,7 +5500,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>328</v>
       </c>
@@ -5505,7 +5514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>330</v>
       </c>
@@ -5519,7 +5528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>332</v>
       </c>
@@ -5533,7 +5542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>334</v>
       </c>
@@ -5547,7 +5556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>336</v>
       </c>
@@ -5561,7 +5570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>338</v>
       </c>
@@ -5575,7 +5584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>340</v>
       </c>
@@ -5589,7 +5598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>342</v>
       </c>
@@ -5603,7 +5612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>344</v>
       </c>
@@ -5617,7 +5626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>346</v>
       </c>
@@ -5631,7 +5640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>348</v>
       </c>
@@ -5645,7 +5654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>350</v>
       </c>
@@ -5659,7 +5668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>352</v>
       </c>
@@ -5673,7 +5682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>354</v>
       </c>
@@ -5687,7 +5696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>356</v>
       </c>
@@ -5701,7 +5710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>358</v>
       </c>
@@ -5715,7 +5724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>360</v>
       </c>
@@ -5729,7 +5738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>362</v>
       </c>
@@ -5743,7 +5752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>364</v>
       </c>
@@ -5757,7 +5766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>368</v>
       </c>
@@ -5771,7 +5780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>370</v>
       </c>
@@ -5785,7 +5794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>372</v>
       </c>
@@ -5799,7 +5808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>374</v>
       </c>
@@ -5813,7 +5822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>376</v>
       </c>
@@ -5827,7 +5836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>382</v>
       </c>
@@ -5841,7 +5850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>384</v>
       </c>
@@ -5855,7 +5864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>386</v>
       </c>
@@ -5869,7 +5878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>388</v>
       </c>
@@ -5883,7 +5892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>390</v>
       </c>
@@ -5897,7 +5906,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>392</v>
       </c>
@@ -5911,7 +5920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>394</v>
       </c>
@@ -5925,7 +5934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>396</v>
       </c>
@@ -5939,7 +5948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>398</v>
       </c>
@@ -5953,7 +5962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>400</v>
       </c>
@@ -5967,7 +5976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>402</v>
       </c>
@@ -5981,7 +5990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>404</v>
       </c>
@@ -5995,7 +6004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>406</v>
       </c>
@@ -6009,7 +6018,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>408</v>
       </c>
@@ -6023,7 +6032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>410</v>
       </c>
@@ -6037,7 +6046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>412</v>
       </c>
@@ -6051,7 +6060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>414</v>
       </c>
@@ -6065,7 +6074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>416</v>
       </c>
@@ -6079,7 +6088,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>418</v>
       </c>
@@ -6093,7 +6102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>420</v>
       </c>
@@ -6107,7 +6116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>422</v>
       </c>
@@ -6121,7 +6130,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>424</v>
       </c>
@@ -6135,7 +6144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>426</v>
       </c>
@@ -6149,7 +6158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>428</v>
       </c>
@@ -6163,7 +6172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>430</v>
       </c>
@@ -6177,7 +6186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>432</v>
       </c>
@@ -6191,7 +6200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>434</v>
       </c>
@@ -6205,7 +6214,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>436</v>
       </c>
@@ -6219,7 +6228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>438</v>
       </c>
@@ -6233,7 +6242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>440</v>
       </c>
@@ -6247,7 +6256,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>442</v>
       </c>
@@ -6261,7 +6270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>444</v>
       </c>
@@ -6275,7 +6284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>446</v>
       </c>
@@ -6289,7 +6298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>448</v>
       </c>
@@ -6303,7 +6312,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>450</v>
       </c>
@@ -6317,7 +6326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>452</v>
       </c>
@@ -6331,7 +6340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>454</v>
       </c>
@@ -6345,7 +6354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>456</v>
       </c>
@@ -6359,7 +6368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>458</v>
       </c>
@@ -6373,7 +6382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>460</v>
       </c>
@@ -6387,7 +6396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>462</v>
       </c>
@@ -6401,7 +6410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>464</v>
       </c>
@@ -6415,7 +6424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>466</v>
       </c>
@@ -6429,7 +6438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>468</v>
       </c>
@@ -6443,7 +6452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>470</v>
       </c>
@@ -6457,7 +6466,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>472</v>
       </c>
@@ -6471,7 +6480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>474</v>
       </c>
@@ -6485,7 +6494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>476</v>
       </c>
@@ -6499,7 +6508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>478</v>
       </c>
@@ -6513,7 +6522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>480</v>
       </c>
@@ -6527,7 +6536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>482</v>
       </c>
@@ -6541,7 +6550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>484</v>
       </c>
@@ -6555,7 +6564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>486</v>
       </c>
@@ -6569,7 +6578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>488</v>
       </c>
@@ -6583,7 +6592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>490</v>
       </c>
@@ -6597,7 +6606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>494</v>
       </c>
@@ -6611,7 +6620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>496</v>
       </c>
@@ -6625,7 +6634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>498</v>
       </c>
@@ -6639,7 +6648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>500</v>
       </c>
@@ -6653,7 +6662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>502</v>
       </c>
@@ -6667,7 +6676,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>504</v>
       </c>
@@ -6681,7 +6690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>506</v>
       </c>
@@ -6695,7 +6704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>508</v>
       </c>
@@ -6709,7 +6718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>510</v>
       </c>
@@ -6723,7 +6732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>512</v>
       </c>
@@ -6737,7 +6746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>514</v>
       </c>
@@ -6751,7 +6760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>516</v>
       </c>
@@ -6765,7 +6774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>518</v>
       </c>
@@ -6779,7 +6788,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>520</v>
       </c>
@@ -6793,7 +6802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>522</v>
       </c>
@@ -6807,7 +6816,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>526</v>
       </c>
@@ -6821,7 +6830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>528</v>
       </c>
@@ -6835,7 +6844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>532</v>
       </c>
@@ -6849,7 +6858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>534</v>
       </c>
@@ -6863,7 +6872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>536</v>
       </c>
@@ -6877,7 +6886,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>538</v>
       </c>
@@ -6891,7 +6900,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>540</v>
       </c>
@@ -6905,7 +6914,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>542</v>
       </c>
@@ -6919,7 +6928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>544</v>
       </c>
@@ -6933,7 +6942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>546</v>
       </c>
@@ -6947,7 +6956,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>548</v>
       </c>
@@ -6961,7 +6970,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>550</v>
       </c>
@@ -6975,7 +6984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>554</v>
       </c>
@@ -6989,7 +6998,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>556</v>
       </c>
@@ -7003,7 +7012,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>558</v>
       </c>
@@ -7017,7 +7026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>560</v>
       </c>
@@ -7031,7 +7040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>564</v>
       </c>
@@ -7045,7 +7054,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>566</v>
       </c>
@@ -7059,7 +7068,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>568</v>
       </c>
@@ -7073,7 +7082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>570</v>
       </c>
@@ -7087,7 +7096,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>572</v>
       </c>
@@ -7101,7 +7110,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>574</v>
       </c>
@@ -7115,7 +7124,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>576</v>
       </c>
@@ -7129,7 +7138,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>578</v>
       </c>
@@ -7143,7 +7152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>580</v>
       </c>
@@ -7157,7 +7166,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>582</v>
       </c>
@@ -7171,7 +7180,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>584</v>
       </c>
@@ -7185,7 +7194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>588</v>
       </c>
@@ -7199,7 +7208,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>590</v>
       </c>
@@ -7213,7 +7222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>592</v>
       </c>
@@ -7227,7 +7236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>594</v>
       </c>
@@ -7241,7 +7250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>596</v>
       </c>
@@ -7255,7 +7264,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>600</v>
       </c>
@@ -7269,7 +7278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>602</v>
       </c>
@@ -7283,7 +7292,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>604</v>
       </c>
@@ -7297,7 +7306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>606</v>
       </c>
@@ -7311,7 +7320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>608</v>
       </c>
@@ -7325,7 +7334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>610</v>
       </c>
@@ -7339,7 +7348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>612</v>
       </c>
@@ -7353,7 +7362,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>614</v>
       </c>
@@ -7367,7 +7376,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>616</v>
       </c>
@@ -7381,7 +7390,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>618</v>
       </c>
@@ -7395,7 +7404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>620</v>
       </c>
@@ -7409,7 +7418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>622</v>
       </c>
@@ -7423,7 +7432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>624</v>
       </c>
@@ -7437,7 +7446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>626</v>
       </c>
@@ -7451,7 +7460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>628</v>
       </c>
@@ -7465,7 +7474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>630</v>
       </c>
@@ -7479,7 +7488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>632</v>
       </c>
@@ -7493,7 +7502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>634</v>
       </c>
@@ -7507,7 +7516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>636</v>
       </c>
@@ -7521,7 +7530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>638</v>
       </c>
@@ -7535,7 +7544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>640</v>
       </c>
@@ -7549,7 +7558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>642</v>
       </c>
@@ -7563,7 +7572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>644</v>
       </c>
@@ -7577,7 +7586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>646</v>
       </c>
@@ -7591,7 +7600,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>648</v>
       </c>
@@ -7605,7 +7614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>650</v>
       </c>
@@ -7619,7 +7628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>652</v>
       </c>
@@ -7633,7 +7642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>656</v>
       </c>
@@ -7647,7 +7656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>658</v>
       </c>
@@ -7661,7 +7670,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>660</v>
       </c>
@@ -7675,7 +7684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>662</v>
       </c>
@@ -7689,7 +7698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>664</v>
       </c>
@@ -7703,7 +7712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>666</v>
       </c>
@@ -7717,7 +7726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>668</v>
       </c>
@@ -7731,7 +7740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>670</v>
       </c>
@@ -7745,7 +7754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>672</v>
       </c>
@@ -7759,7 +7768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>674</v>
       </c>
@@ -7773,7 +7782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>676</v>
       </c>
@@ -7787,7 +7796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>678</v>
       </c>
@@ -7801,7 +7810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>680</v>
       </c>
@@ -7815,7 +7824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>682</v>
       </c>
@@ -7829,7 +7838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>684</v>
       </c>
@@ -7843,7 +7852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>686</v>
       </c>
@@ -7857,7 +7866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>688</v>
       </c>
@@ -7871,7 +7880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>690</v>
       </c>
@@ -7885,7 +7894,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>692</v>
       </c>
@@ -7899,7 +7908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>694</v>
       </c>
@@ -7913,7 +7922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>696</v>
       </c>
@@ -7927,7 +7936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>698</v>
       </c>
@@ -7941,7 +7950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>700</v>
       </c>
@@ -7955,7 +7964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>702</v>
       </c>
@@ -7969,7 +7978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>704</v>
       </c>
@@ -7983,7 +7992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>706</v>
       </c>
@@ -7997,7 +8006,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>708</v>
       </c>
@@ -8011,7 +8020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>710</v>
       </c>
@@ -8025,7 +8034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>712</v>
       </c>
@@ -8039,7 +8048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>714</v>
       </c>
@@ -8053,7 +8062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>716</v>
       </c>
@@ -8067,7 +8076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>718</v>
       </c>
@@ -8081,7 +8090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>720</v>
       </c>
@@ -8095,7 +8104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>722</v>
       </c>
@@ -8109,7 +8118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>724</v>
       </c>
@@ -8123,7 +8132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>726</v>
       </c>
@@ -8137,7 +8146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>728</v>
       </c>
@@ -8151,7 +8160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>730</v>
       </c>
@@ -8165,7 +8174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>732</v>
       </c>
@@ -8179,7 +8188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>734</v>
       </c>
@@ -8193,7 +8202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>736</v>
       </c>
@@ -8207,7 +8216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>738</v>
       </c>
@@ -8221,7 +8230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>740</v>
       </c>
@@ -8235,7 +8244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>742</v>
       </c>
@@ -8249,7 +8258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>744</v>
       </c>
@@ -8263,7 +8272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>746</v>
       </c>
@@ -8277,7 +8286,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>748</v>
       </c>
@@ -8291,7 +8300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>750</v>
       </c>
@@ -8305,7 +8314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>752</v>
       </c>
@@ -8319,7 +8328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>754</v>
       </c>
@@ -8333,7 +8342,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>756</v>
       </c>
@@ -8347,7 +8356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>758</v>
       </c>
@@ -8361,7 +8370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>760</v>
       </c>
@@ -8375,7 +8384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>762</v>
       </c>
@@ -8389,7 +8398,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>764</v>
       </c>
@@ -8403,7 +8412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>766</v>
       </c>
@@ -8417,7 +8426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>768</v>
       </c>
@@ -8431,7 +8440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>770</v>
       </c>
@@ -8445,7 +8454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>772</v>
       </c>
@@ -8459,7 +8468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>776</v>
       </c>
@@ -8473,7 +8482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>778</v>
       </c>
@@ -8487,7 +8496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>780</v>
       </c>
@@ -8501,7 +8510,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>782</v>
       </c>
@@ -8515,7 +8524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>784</v>
       </c>
@@ -8529,7 +8538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>786</v>
       </c>
@@ -8543,7 +8552,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>788</v>
       </c>
@@ -8557,7 +8566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>790</v>
       </c>
@@ -8571,7 +8580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>792</v>
       </c>
@@ -8585,7 +8594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>794</v>
       </c>
@@ -8599,7 +8608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>796</v>
       </c>
@@ -8609,11 +8618,8 @@
       <c r="C363" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D363" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>798</v>
       </c>
@@ -8627,7 +8633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>800</v>
       </c>
@@ -8641,7 +8647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>802</v>
       </c>
@@ -8655,7 +8661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>804</v>
       </c>
@@ -8669,7 +8675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>806</v>
       </c>
@@ -8683,7 +8689,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>808</v>
       </c>
@@ -8697,7 +8703,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>810</v>
       </c>
@@ -8711,7 +8717,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>812</v>
       </c>
@@ -8725,7 +8731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>814</v>
       </c>
@@ -8739,7 +8745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>816</v>
       </c>
@@ -8753,7 +8759,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>818</v>
       </c>
@@ -8767,7 +8773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>820</v>
       </c>
@@ -8781,7 +8787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>822</v>
       </c>
@@ -8795,7 +8801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>824</v>
       </c>
@@ -8809,7 +8815,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>826</v>
       </c>
@@ -8823,7 +8829,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>828</v>
       </c>
@@ -8837,7 +8843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>830</v>
       </c>
@@ -8851,7 +8857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>834</v>
       </c>
@@ -8865,7 +8871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>838</v>
       </c>
@@ -8879,7 +8885,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>840</v>
       </c>
@@ -8893,7 +8899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>842</v>
       </c>
@@ -8907,7 +8913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>844</v>
       </c>
@@ -8921,7 +8927,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>846</v>
       </c>
@@ -8935,7 +8941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>848</v>
       </c>
@@ -8949,7 +8955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>850</v>
       </c>
@@ -8963,7 +8969,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>852</v>
       </c>
@@ -8977,7 +8983,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="390" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>854</v>
       </c>
@@ -8991,7 +8997,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>856</v>
       </c>
@@ -9005,7 +9011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>858</v>
       </c>
@@ -9019,7 +9025,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>860</v>
       </c>
@@ -9033,7 +9039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>862</v>
       </c>
@@ -9047,7 +9053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>864</v>
       </c>
@@ -9061,7 +9067,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="396" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>866</v>
       </c>
@@ -9075,7 +9081,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>868</v>
       </c>
@@ -9089,7 +9095,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>870</v>
       </c>
@@ -9103,7 +9109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>872</v>
       </c>
@@ -9117,7 +9123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>874</v>
       </c>
@@ -9131,7 +9137,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>876</v>
       </c>
@@ -9145,7 +9151,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>878</v>
       </c>
@@ -9159,7 +9165,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>880</v>
       </c>
@@ -9173,7 +9179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>882</v>
       </c>
@@ -9187,7 +9193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>884</v>
       </c>
@@ -9201,7 +9207,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>886</v>
       </c>
@@ -9215,7 +9221,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>892</v>
       </c>
@@ -9229,7 +9235,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>898</v>
       </c>
@@ -9243,7 +9249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>900</v>
       </c>
@@ -9257,7 +9263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>902</v>
       </c>
@@ -9271,7 +9277,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>904</v>
       </c>
@@ -9285,7 +9291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>906</v>
       </c>
@@ -9299,7 +9305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>908</v>
       </c>
@@ -9313,7 +9319,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>910</v>
       </c>
@@ -9327,7 +9333,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>912</v>
       </c>
@@ -9341,7 +9347,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>914</v>
       </c>
@@ -9355,7 +9361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>916</v>
       </c>
@@ -9369,7 +9375,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>918</v>
       </c>
@@ -9383,7 +9389,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>920</v>
       </c>
@@ -9397,7 +9403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="420" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>922</v>
       </c>
@@ -9411,7 +9417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>924</v>
       </c>
@@ -9425,7 +9431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>926</v>
       </c>
@@ -9439,7 +9445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="423" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>928</v>
       </c>
@@ -9453,7 +9459,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="424" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>930</v>
       </c>
@@ -9467,7 +9473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="425" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>932</v>
       </c>
@@ -9481,7 +9487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="426" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>934</v>
       </c>
@@ -9495,7 +9501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>938</v>
       </c>
@@ -9509,7 +9515,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>940</v>
       </c>
@@ -9523,7 +9529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="429" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>942</v>
       </c>
@@ -9537,7 +9543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>944</v>
       </c>
@@ -9551,7 +9557,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>946</v>
       </c>
@@ -9565,7 +9571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>948</v>
       </c>
@@ -9579,7 +9585,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>950</v>
       </c>
@@ -9593,7 +9599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>952</v>
       </c>
@@ -9607,7 +9613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>956</v>
       </c>
@@ -9621,7 +9627,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>958</v>
       </c>
@@ -9635,7 +9641,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>960</v>
       </c>
@@ -9649,7 +9655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>962</v>
       </c>
@@ -9663,7 +9669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>964</v>
       </c>
@@ -9677,7 +9683,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>968</v>
       </c>
@@ -9691,7 +9697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>970</v>
       </c>
@@ -9705,7 +9711,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>972</v>
       </c>
@@ -9719,7 +9725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>974</v>
       </c>
@@ -9733,7 +9739,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>976</v>
       </c>
@@ -9747,7 +9753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>978</v>
       </c>
@@ -9761,7 +9767,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>980</v>
       </c>
@@ -9775,7 +9781,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>982</v>
       </c>
@@ -9789,7 +9795,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>984</v>
       </c>
@@ -9803,7 +9809,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>986</v>
       </c>
@@ -9817,7 +9823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>988</v>
       </c>
@@ -9831,7 +9837,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>990</v>
       </c>
@@ -9845,7 +9851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>992</v>
       </c>
@@ -9859,7 +9865,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="453" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>994</v>
       </c>
@@ -9873,7 +9879,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>996</v>
       </c>
@@ -9887,7 +9893,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="455" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>998</v>
       </c>
@@ -9901,7 +9907,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1000</v>
       </c>
@@ -9915,7 +9921,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1004</v>
       </c>
@@ -9929,7 +9935,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="458" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1006</v>
       </c>
@@ -9943,7 +9949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1008</v>
       </c>
@@ -9957,7 +9963,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="460" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1010</v>
       </c>
@@ -9971,7 +9977,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1012</v>
       </c>
@@ -9985,7 +9991,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1014</v>
       </c>
@@ -9999,7 +10005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1016</v>
       </c>
@@ -10013,7 +10019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1018</v>
       </c>
@@ -10027,7 +10033,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="465" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1020</v>
       </c>
@@ -10041,7 +10047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1024</v>
       </c>
@@ -10055,7 +10061,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1026</v>
       </c>
@@ -10069,7 +10075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="468" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1028</v>
       </c>
@@ -10083,7 +10089,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="469" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1030</v>
       </c>
@@ -10097,7 +10103,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1032</v>
       </c>
@@ -10111,7 +10117,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1034</v>
       </c>
@@ -10125,7 +10131,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1036</v>
       </c>
@@ -10139,7 +10145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="473" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1038</v>
       </c>
@@ -10153,7 +10159,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="474" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1040</v>
       </c>
@@ -10167,7 +10173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="475" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1042</v>
       </c>
@@ -10181,7 +10187,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="476" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>5</v>
       </c>
@@ -10192,7 +10198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="477" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>26</v>
       </c>
@@ -10206,7 +10212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="478" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>56</v>
       </c>
@@ -10220,7 +10226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>90</v>
       </c>
@@ -10234,7 +10240,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="480" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>98</v>
       </c>
@@ -10245,7 +10251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="481" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>100</v>
       </c>
@@ -10256,7 +10262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="482" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>114</v>
       </c>
@@ -10267,7 +10273,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="483" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>146</v>
       </c>
@@ -10278,7 +10284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="484" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>170</v>
       </c>
@@ -10289,7 +10295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="485" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>172</v>
       </c>
@@ -10300,7 +10306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="486" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>176</v>
       </c>
@@ -10314,7 +10320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>190</v>
       </c>
@@ -10325,7 +10331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="488" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>208</v>
       </c>
@@ -10336,7 +10342,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>210</v>
       </c>
@@ -10347,7 +10353,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>212</v>
       </c>
@@ -10358,7 +10364,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>214</v>
       </c>
@@ -10369,7 +10375,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="492" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>236</v>
       </c>
@@ -10380,7 +10386,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="493" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>244</v>
       </c>
@@ -10391,7 +10397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="494" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>254</v>
       </c>
@@ -10402,7 +10408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="495" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>274</v>
       </c>
@@ -10413,7 +10419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="496" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>316</v>
       </c>
@@ -10424,7 +10430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>322</v>
       </c>
@@ -10435,7 +10441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>366</v>
       </c>
@@ -10446,7 +10452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="499" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>378</v>
       </c>
@@ -10457,7 +10463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>380</v>
       </c>
@@ -10471,7 +10477,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="501" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>492</v>
       </c>
@@ -10485,7 +10491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="502" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>524</v>
       </c>
@@ -10499,7 +10505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="503" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>530</v>
       </c>
@@ -10513,7 +10519,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="504" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>552</v>
       </c>
@@ -10527,7 +10533,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="505" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>562</v>
       </c>
@@ -10538,7 +10544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="506" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>586</v>
       </c>
@@ -10549,7 +10555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="507" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>598</v>
       </c>
@@ -10560,7 +10566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>654</v>
       </c>
@@ -10571,7 +10577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>774</v>
       </c>
@@ -10582,7 +10588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="510" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>832</v>
       </c>
@@ -10593,7 +10599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="511" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>836</v>
       </c>
@@ -10604,7 +10610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="512" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>888</v>
       </c>
@@ -10615,7 +10621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>890</v>
       </c>
@@ -10626,7 +10632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>894</v>
       </c>
@@ -10640,7 +10646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>896</v>
       </c>
@@ -10651,7 +10657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>936</v>
       </c>
@@ -10665,7 +10671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>954</v>
       </c>
@@ -10676,7 +10682,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>966</v>
       </c>
@@ -10687,7 +10693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>1002</v>
       </c>
@@ -10698,7 +10704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="520" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1022</v>
       </c>
@@ -10711,6 +10717,9 @@
       <c r="D520" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D521" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}">

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A68A98-C501-49FB-A1FE-69B3626EC8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ACFDB7-1E63-40D6-AE70-2A53FF12BA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="1121">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -370,6 +370,12 @@
     <t>Bluey Kortfilmer</t>
   </si>
   <si>
+    <t>boligfix for nul og niks</t>
+  </si>
+  <si>
+    <t>Boligfix for nul og niks</t>
+  </si>
+  <si>
     <t>bolighaj finder hjem</t>
   </si>
   <si>
@@ -832,6 +838,12 @@
     <t>Ekstreme Samlere</t>
   </si>
   <si>
+    <t>emilie meng - en efterforskning går galt</t>
+  </si>
+  <si>
+    <t>Emilie Meng - en efterforskning går galt</t>
+  </si>
+  <si>
     <t>et hus af ler</t>
   </si>
   <si>
@@ -1312,6 +1324,12 @@
     <t>Heino Hansens første afskedsshow</t>
   </si>
   <si>
+    <t>heino og vildmarksholdet</t>
+  </si>
+  <si>
+    <t>Heino og Vildmarksholdet</t>
+  </si>
+  <si>
     <t>helt sort</t>
   </si>
   <si>
@@ -1720,6 +1738,12 @@
     <t>Krejlerkongen</t>
   </si>
   <si>
+    <t>kriminalinspektør banks</t>
+  </si>
+  <si>
+    <t>Kriminalinspektør Banks</t>
+  </si>
+  <si>
     <t>kriminalkommissær barnaby</t>
   </si>
   <si>
@@ -2146,6 +2170,12 @@
     <t>Mordene I Marlow</t>
   </si>
   <si>
+    <t>mordet i landsbyen - da rygterne tog magten (2:3)</t>
+  </si>
+  <si>
+    <t>Mordet i landsbyen - da rygterne tog magten (2:3)</t>
+  </si>
+  <si>
     <t>mordet i orientekspressen</t>
   </si>
   <si>
@@ -3004,6 +3034,18 @@
     <t>Til Døden Skiller Os Ad</t>
   </si>
   <si>
+    <t>tilbage til fremtiden</t>
+  </si>
+  <si>
+    <t>Tilbage til fremtiden</t>
+  </si>
+  <si>
+    <t>tilbake til fremtiden</t>
+  </si>
+  <si>
+    <t>Tilbake til fremtiden</t>
+  </si>
+  <si>
     <t>tills döden skiljer oss åt</t>
   </si>
   <si>
@@ -3058,6 +3100,12 @@
     <t>Toppen Af Toppen</t>
   </si>
   <si>
+    <t>total tillid - kinas masseovervågning</t>
+  </si>
+  <si>
+    <t>Total tillid - Kinas masseovervågning</t>
+  </si>
+  <si>
     <t>troldspejlet</t>
   </si>
   <si>
@@ -3182,6 +3230,12 @@
   </si>
   <si>
     <t>Verdensmænd - Bobos surprise</t>
+  </si>
+  <si>
+    <t>vesta-linnea</t>
+  </si>
+  <si>
+    <t>Vesta-Linnea</t>
   </si>
   <si>
     <t>vestens vildeste hamster</t>
@@ -3695,7 +3749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E549"/>
+  <dimension ref="A1:E558"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -3892,10 +3946,10 @@
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>6</v>
@@ -3906,10 +3960,10 @@
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>6</v>
@@ -3920,10 +3974,10 @@
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>6</v>
@@ -3934,10 +3988,10 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>6</v>
@@ -3948,10 +4002,10 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>6</v>
@@ -3962,10 +4016,10 @@
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>6</v>
@@ -3976,10 +4030,10 @@
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>6</v>
@@ -3990,10 +4044,10 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>6</v>
@@ -4004,10 +4058,10 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>6</v>
@@ -4018,10 +4072,10 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>6</v>
@@ -4032,10 +4086,10 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>6</v>
@@ -4046,10 +4100,10 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>6</v>
@@ -4060,10 +4114,10 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>6</v>
@@ -4074,10 +4128,10 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>6</v>
@@ -4088,10 +4142,10 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>6</v>
@@ -4102,10 +4156,10 @@
     </row>
     <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>6</v>
@@ -4116,10 +4170,10 @@
     </row>
     <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>6</v>
@@ -4130,10 +4184,10 @@
     </row>
     <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>6</v>
@@ -4144,10 +4198,10 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
@@ -4158,10 +4212,10 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>6</v>
@@ -4172,10 +4226,10 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>6</v>
@@ -4186,10 +4240,10 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>6</v>
@@ -4200,10 +4254,10 @@
     </row>
     <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>6</v>
@@ -4214,10 +4268,10 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>6</v>
@@ -4228,10 +4282,10 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>6</v>
@@ -4242,10 +4296,10 @@
     </row>
     <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>6</v>
@@ -4256,10 +4310,10 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>6</v>
@@ -4270,10 +4324,10 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
@@ -4284,10 +4338,10 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -4298,10 +4352,10 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6</v>
@@ -4312,10 +4366,10 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -4326,10 +4380,10 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
@@ -4340,10 +4394,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>6</v>
@@ -4354,10 +4408,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6</v>
@@ -4368,10 +4422,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6</v>
@@ -4382,10 +4436,10 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -4396,10 +4450,10 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>6</v>
@@ -4410,10 +4464,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>6</v>
@@ -4424,10 +4478,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
@@ -4438,10 +4492,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
@@ -4452,10 +4506,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
@@ -4844,10 +4898,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
@@ -4858,10 +4912,10 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>6</v>
@@ -4872,10 +4926,10 @@
     </row>
     <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B84" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>6</v>
@@ -4886,10 +4940,10 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B85" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>6</v>
@@ -4900,10 +4954,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B86" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>6</v>
@@ -4914,10 +4968,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B87" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>6</v>
@@ -4928,10 +4982,10 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B88" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>6</v>
@@ -4942,10 +4996,10 @@
     </row>
     <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>6</v>
@@ -4956,10 +5010,10 @@
     </row>
     <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B90" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>6</v>
@@ -4970,10 +5024,10 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>6</v>
@@ -4984,10 +5038,10 @@
     </row>
     <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B92" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>6</v>
@@ -4998,10 +5052,10 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>6</v>
@@ -5012,10 +5066,10 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B94" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>6</v>
@@ -5026,10 +5080,10 @@
     </row>
     <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B95" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>6</v>
@@ -5040,10 +5094,10 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B96" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>6</v>
@@ -5054,10 +5108,10 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B97" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>6</v>
@@ -5068,10 +5122,10 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B98" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>6</v>
@@ -5082,10 +5136,10 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B99" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>6</v>
@@ -5096,10 +5150,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B100" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>6</v>
@@ -5110,10 +5164,10 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B101" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>6</v>
@@ -5124,10 +5178,10 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B102" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>6</v>
@@ -5138,10 +5192,10 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B103" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>6</v>
@@ -5152,10 +5206,10 @@
     </row>
     <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B104" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -5166,10 +5220,10 @@
     </row>
     <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B105" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>6</v>
@@ -5180,10 +5234,10 @@
     </row>
     <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B106" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>6</v>
@@ -5194,10 +5248,10 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B107" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>6</v>
@@ -5208,10 +5262,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B108" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>6</v>
@@ -5222,10 +5276,10 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B109" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>6</v>
@@ -5236,10 +5290,10 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B110" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>6</v>
@@ -5250,10 +5304,10 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>6</v>
@@ -5264,10 +5318,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B112" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>6</v>
@@ -5278,10 +5332,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B113" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>6</v>
@@ -5292,10 +5346,10 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B114" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>6</v>
@@ -5306,10 +5360,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B115" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>6</v>
@@ -5320,10 +5374,10 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B116" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>6</v>
@@ -5334,10 +5388,10 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B117" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>6</v>
@@ -5432,10 +5486,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B124" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -5446,10 +5500,10 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B125" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>6</v>
@@ -5460,10 +5514,10 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B126" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>6</v>
@@ -5474,10 +5528,10 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B127" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>6</v>
@@ -5488,10 +5542,10 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B128" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>6</v>
@@ -5502,10 +5556,10 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B129" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>6</v>
@@ -5516,10 +5570,10 @@
     </row>
     <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B130" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>6</v>
@@ -5530,10 +5584,10 @@
     </row>
     <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B131" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>6</v>
@@ -5544,10 +5598,10 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B132" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>6</v>
@@ -5558,10 +5612,10 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B133" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>6</v>
@@ -5572,10 +5626,10 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B134" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>6</v>
@@ -5586,10 +5640,10 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B135" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>6</v>
@@ -5600,10 +5654,10 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B136" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>6</v>
@@ -5614,10 +5668,10 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B137" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>6</v>
@@ -5628,10 +5682,10 @@
     </row>
     <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B138" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>6</v>
@@ -5642,10 +5696,10 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B139" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>6</v>
@@ -5656,10 +5710,10 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B140" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>6</v>
@@ -5670,10 +5724,10 @@
     </row>
     <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B141" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>6</v>
@@ -5684,10 +5738,10 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B142" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>6</v>
@@ -5698,10 +5752,10 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B143" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>6</v>
@@ -5712,10 +5766,10 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B144" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>6</v>
@@ -5726,10 +5780,10 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B145" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>6</v>
@@ -5740,10 +5794,10 @@
     </row>
     <row r="146" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B146" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>6</v>
@@ -5754,10 +5808,10 @@
     </row>
     <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B147" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>6</v>
@@ -5768,10 +5822,10 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B148" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>6</v>
@@ -5782,10 +5836,10 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B149" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>6</v>
@@ -5796,10 +5850,10 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B150" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>6</v>
@@ -5810,10 +5864,10 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B151" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>6</v>
@@ -5824,10 +5878,10 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B152" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>6</v>
@@ -5838,10 +5892,10 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B153" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>6</v>
@@ -5852,10 +5906,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B154" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>6</v>
@@ -5866,10 +5920,10 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B155" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>6</v>
@@ -5880,10 +5934,10 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B156" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>6</v>
@@ -5894,10 +5948,10 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B157" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>6</v>
@@ -5908,10 +5962,10 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B158" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>6</v>
@@ -5922,10 +5976,10 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B159" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>6</v>
@@ -5936,10 +5990,10 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B160" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>6</v>
@@ -5950,10 +6004,10 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B161" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>6</v>
@@ -5964,10 +6018,10 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B162" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>6</v>
@@ -5978,10 +6032,10 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B163" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>6</v>
@@ -5992,10 +6046,10 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B164" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>6</v>
@@ -6006,10 +6060,10 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B165" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>6</v>
@@ -6020,10 +6074,10 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B166" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>6</v>
@@ -6034,10 +6088,10 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B167" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>6</v>
@@ -6048,10 +6102,10 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B168" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>6</v>
@@ -6062,10 +6116,10 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B169" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>6</v>
@@ -6076,10 +6130,10 @@
     </row>
     <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B170" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>6</v>
@@ -6090,10 +6144,10 @@
     </row>
     <row r="171" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B171" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>6</v>
@@ -6104,10 +6158,10 @@
     </row>
     <row r="172" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B172" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>6</v>
@@ -6118,10 +6172,10 @@
     </row>
     <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B173" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>6</v>
@@ -6132,10 +6186,10 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B174" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>6</v>
@@ -6146,10 +6200,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B175" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>6</v>
@@ -6160,10 +6214,10 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B176" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>6</v>
@@ -6174,10 +6228,10 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B177" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>6</v>
@@ -6188,10 +6242,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B178" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>6</v>
@@ -6202,10 +6256,10 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B179" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>6</v>
@@ -6216,10 +6270,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B180" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>6</v>
@@ -6230,10 +6284,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B181" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>6</v>
@@ -6244,10 +6298,10 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B182" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>6</v>
@@ -6258,10 +6312,10 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B183" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -6272,10 +6326,10 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B184" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>6</v>
@@ -6286,10 +6340,10 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B185" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>6</v>
@@ -6300,10 +6354,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B186" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>6</v>
@@ -6314,10 +6368,10 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B187" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>6</v>
@@ -6328,10 +6382,10 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B188" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>6</v>
@@ -6342,10 +6396,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B189" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -6356,10 +6410,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B190" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>6</v>
@@ -6370,10 +6424,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B191" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>6</v>
@@ -6384,10 +6438,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B192" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>6</v>
@@ -6398,10 +6452,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B193" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>6</v>
@@ -6412,10 +6466,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B194" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>6</v>
@@ -6426,10 +6480,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B195" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>6</v>
@@ -6440,10 +6494,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B196" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>6</v>
@@ -6454,10 +6508,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B197" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>6</v>
@@ -6468,10 +6522,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B198" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>6</v>
@@ -6482,10 +6536,10 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B199" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>6</v>
@@ -6496,10 +6550,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B200" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>6</v>
@@ -6510,10 +6564,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B201" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>6</v>
@@ -6524,10 +6578,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B202" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>6</v>
@@ -6538,10 +6592,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B203" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>6</v>
@@ -6552,10 +6606,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B204" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>6</v>
@@ -6566,10 +6620,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B205" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>6</v>
@@ -6580,10 +6634,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B206" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>6</v>
@@ -6594,10 +6648,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B207" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>6</v>
@@ -6608,10 +6662,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B208" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>6</v>
@@ -6622,10 +6676,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B209" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>6</v>
@@ -6636,10 +6690,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B210" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>6</v>
@@ -6650,10 +6704,10 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B211" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>6</v>
@@ -6664,10 +6718,10 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B212" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>6</v>
@@ -6678,10 +6732,10 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B213" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>6</v>
@@ -6692,10 +6746,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B214" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>6</v>
@@ -6706,10 +6760,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B215" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>6</v>
@@ -6720,10 +6774,10 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B216" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>6</v>
@@ -6734,10 +6788,10 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B217" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>6</v>
@@ -6748,10 +6802,10 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B218" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>6</v>
@@ -6762,10 +6816,10 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B219" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>6</v>
@@ -6776,10 +6830,10 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B220" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>6</v>
@@ -6790,10 +6844,10 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B221" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>6</v>
@@ -6804,10 +6858,10 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B222" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>6</v>
@@ -6818,10 +6872,10 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B223" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>6</v>
@@ -6832,10 +6886,10 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B224" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>6</v>
@@ -6846,10 +6900,10 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B225" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -6860,10 +6914,10 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B226" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>6</v>
@@ -6874,10 +6928,10 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B227" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>6</v>
@@ -6888,10 +6942,10 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B228" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>6</v>
@@ -6902,10 +6956,10 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B229" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -6916,10 +6970,10 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B230" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>6</v>
@@ -6930,10 +6984,10 @@
     </row>
     <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B231" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>6</v>
@@ -6944,10 +6998,10 @@
     </row>
     <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B232" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -6958,10 +7012,10 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B233" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -6972,10 +7026,10 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B234" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>6</v>
@@ -6986,10 +7040,10 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B235" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>6</v>
@@ -7000,10 +7054,10 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B236" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
@@ -7014,10 +7068,10 @@
     </row>
     <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B237" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
@@ -7028,10 +7082,10 @@
     </row>
     <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B238" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>6</v>
@@ -7042,10 +7096,10 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B239" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
@@ -7056,10 +7110,10 @@
     </row>
     <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="B240" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
@@ -7070,10 +7124,10 @@
     </row>
     <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="B241" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
@@ -7084,10 +7138,10 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="B242" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -7098,10 +7152,10 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="B243" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
@@ -7112,10 +7166,10 @@
     </row>
     <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="B244" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -7126,10 +7180,10 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="B245" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -7140,10 +7194,10 @@
     </row>
     <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="B246" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
@@ -7154,10 +7208,10 @@
     </row>
     <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="B247" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
@@ -7168,10 +7222,10 @@
     </row>
     <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B248" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
@@ -7182,10 +7236,10 @@
     </row>
     <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B249" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
@@ -7196,10 +7250,10 @@
     </row>
     <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="B250" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
@@ -7210,10 +7264,10 @@
     </row>
     <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="B251" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>6</v>
@@ -7224,10 +7278,10 @@
     </row>
     <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="B252" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
@@ -7238,10 +7292,10 @@
     </row>
     <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B253" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>6</v>
@@ -7252,10 +7306,10 @@
     </row>
     <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B254" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>6</v>
@@ -7266,10 +7320,10 @@
     </row>
     <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="B255" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>6</v>
@@ -7280,10 +7334,10 @@
     </row>
     <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B256" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>6</v>
@@ -7294,10 +7348,10 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="B257" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>6</v>
@@ -7308,10 +7362,10 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="B258" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>6</v>
@@ -7322,10 +7376,10 @@
     </row>
     <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="B259" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>6</v>
@@ -7336,10 +7390,10 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="B260" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -7350,10 +7404,10 @@
     </row>
     <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="B261" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>6</v>
@@ -7364,10 +7418,10 @@
     </row>
     <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="B262" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>6</v>
@@ -7378,10 +7432,10 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="B263" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>6</v>
@@ -7392,10 +7446,10 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="B264" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>6</v>
@@ -7406,10 +7460,10 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="B265" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>6</v>
@@ -7420,10 +7474,10 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B266" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>6</v>
@@ -7434,10 +7488,10 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B267" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>6</v>
@@ -7448,10 +7502,10 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="B268" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>6</v>
@@ -7462,10 +7516,10 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="B269" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>6</v>
@@ -7476,10 +7530,10 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B270" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>6</v>
@@ -7490,10 +7544,10 @@
     </row>
     <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B271" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>6</v>
@@ -7504,10 +7558,10 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B272" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>6</v>
@@ -7518,10 +7572,10 @@
     </row>
     <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B273" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>6</v>
@@ -7532,10 +7586,10 @@
     </row>
     <row r="274" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B274" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>6</v>
@@ -7546,10 +7600,10 @@
     </row>
     <row r="275" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="B275" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>6</v>
@@ -7560,10 +7614,10 @@
     </row>
     <row r="276" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="B276" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>6</v>
@@ -7574,10 +7628,10 @@
     </row>
     <row r="277" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B277" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>6</v>
@@ -7588,10 +7642,10 @@
     </row>
     <row r="278" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="B278" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>6</v>
@@ -7602,10 +7656,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B279" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>6</v>
@@ -7616,10 +7670,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B280" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>6</v>
@@ -7630,10 +7684,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="B281" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>6</v>
@@ -7644,10 +7698,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="B282" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>6</v>
@@ -7658,10 +7712,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="B283" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>6</v>
@@ -7672,10 +7726,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="B284" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>6</v>
@@ -7686,10 +7740,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="B285" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -7700,10 +7754,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="B286" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>6</v>
@@ -7714,10 +7768,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="B287" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>6</v>
@@ -7728,10 +7782,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B288" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>6</v>
@@ -7742,10 +7796,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="B289" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>6</v>
@@ -7756,10 +7810,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="B290" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>6</v>
@@ -7770,10 +7824,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="B291" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>6</v>
@@ -7784,10 +7838,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="B292" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>6</v>
@@ -7798,10 +7852,10 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="B293" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>6</v>
@@ -7812,10 +7866,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="B294" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>6</v>
@@ -7826,10 +7880,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="B295" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>6</v>
@@ -7840,10 +7894,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="B296" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>6</v>
@@ -7854,10 +7908,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="B297" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>6</v>
@@ -7868,10 +7922,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="B298" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>6</v>
@@ -7882,10 +7936,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="B299" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>6</v>
@@ -7896,10 +7950,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="B300" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>6</v>
@@ -7910,10 +7964,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="B301" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>6</v>
@@ -7924,10 +7978,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="B302" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -7938,10 +7992,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="B303" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -7952,10 +8006,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="B304" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -7966,10 +8020,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="B305" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>6</v>
@@ -7980,10 +8034,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="B306" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -7994,10 +8048,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="B307" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>6</v>
@@ -8008,10 +8062,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="B308" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>6</v>
@@ -8022,10 +8076,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="B309" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>6</v>
@@ -8036,10 +8090,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="B310" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -8050,10 +8104,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="B311" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>6</v>
@@ -8064,10 +8118,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="B312" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -8078,10 +8132,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="B313" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -8092,10 +8146,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B314" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -8106,10 +8160,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="B315" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>6</v>
@@ -8120,10 +8174,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="B316" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>6</v>
@@ -8134,10 +8188,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="B317" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>6</v>
@@ -8148,10 +8202,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="B318" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>6</v>
@@ -8162,10 +8216,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="B319" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>6</v>
@@ -8176,10 +8230,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="B320" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>6</v>
@@ -8190,10 +8244,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="B321" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>6</v>
@@ -8204,10 +8258,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="B322" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -8218,10 +8272,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="B323" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>6</v>
@@ -8232,10 +8286,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="B324" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>6</v>
@@ -8246,10 +8300,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="B325" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>6</v>
@@ -8260,10 +8314,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="B326" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>6</v>
@@ -8274,10 +8328,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="B327" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>6</v>
@@ -8288,10 +8342,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="B328" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>6</v>
@@ -8302,10 +8356,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="B329" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>6</v>
@@ -8316,10 +8370,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="B330" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -8330,10 +8384,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="B331" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>6</v>
@@ -8344,10 +8398,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="B332" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>6</v>
@@ -8358,10 +8412,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="B333" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>6</v>
@@ -8372,10 +8426,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="B334" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>6</v>
@@ -8386,10 +8440,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="B335" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>6</v>
@@ -8400,10 +8454,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="B336" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>6</v>
@@ -8414,10 +8468,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="B337" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>6</v>
@@ -8428,10 +8482,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="B338" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>6</v>
@@ -8442,10 +8496,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="B339" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>6</v>
@@ -8456,10 +8510,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="B340" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>6</v>
@@ -8470,10 +8524,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="B341" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>6</v>
@@ -8484,10 +8538,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="B342" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>6</v>
@@ -8498,10 +8552,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="B343" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>6</v>
@@ -8512,10 +8566,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="B344" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>6</v>
@@ -8526,10 +8580,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="B345" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>6</v>
@@ -8540,10 +8594,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="B346" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>6</v>
@@ -8554,10 +8608,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="B347" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>6</v>
@@ -8568,10 +8622,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="B348" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>6</v>
@@ -8582,10 +8636,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="B349" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>6</v>
@@ -8596,10 +8650,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="B350" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>6</v>
@@ -8610,10 +8664,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="B351" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>6</v>
@@ -8624,10 +8678,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="B352" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>6</v>
@@ -8638,10 +8692,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="B353" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>6</v>
@@ -8652,10 +8706,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="B354" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>6</v>
@@ -8666,10 +8720,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="B355" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>6</v>
@@ -8680,10 +8734,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="B356" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>6</v>
@@ -8694,10 +8748,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="B357" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>6</v>
@@ -8708,10 +8762,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="B358" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>6</v>
@@ -8722,10 +8776,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="B359" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>6</v>
@@ -8736,10 +8790,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="B360" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>6</v>
@@ -8750,10 +8804,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="B361" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>6</v>
@@ -8764,10 +8818,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="B362" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -8778,10 +8832,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="B363" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>6</v>
@@ -8792,10 +8846,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="B364" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>6</v>
@@ -8806,10 +8860,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="B365" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>6</v>
@@ -8820,10 +8874,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="B366" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>6</v>
@@ -8834,10 +8888,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B367" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>6</v>
@@ -8848,10 +8902,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="B368" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>6</v>
@@ -8862,10 +8916,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="B369" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>6</v>
@@ -8876,10 +8930,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="B370" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>6</v>
@@ -8890,10 +8944,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="B371" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>6</v>
@@ -8904,10 +8958,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="B372" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>6</v>
@@ -8918,10 +8972,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="B373" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>6</v>
@@ -8932,10 +8986,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="B374" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>6</v>
@@ -8946,10 +9000,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="B375" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>6</v>
@@ -8960,10 +9014,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="B376" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>6</v>
@@ -8974,10 +9028,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="B377" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>6</v>
@@ -8988,10 +9042,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="B378" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>6</v>
@@ -9002,10 +9056,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="B379" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>6</v>
@@ -9016,10 +9070,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="B380" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>6</v>
@@ -9030,10 +9084,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="B381" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>6</v>
@@ -9044,10 +9098,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="B382" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>6</v>
@@ -9058,10 +9112,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="B383" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>6</v>
@@ -9072,10 +9126,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="B384" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>6</v>
@@ -9086,10 +9140,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="B385" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>6</v>
@@ -9100,10 +9154,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="B386" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>6</v>
@@ -9114,10 +9168,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="B387" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>6</v>
@@ -9128,10 +9182,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="B388" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>6</v>
@@ -9142,10 +9196,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="B389" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>6</v>
@@ -9156,10 +9210,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="B390" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>6</v>
@@ -9170,10 +9224,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="B391" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>6</v>
@@ -9184,10 +9238,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B392" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>6</v>
@@ -9198,10 +9252,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="B393" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>6</v>
@@ -9212,10 +9266,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="B394" t="s">
-        <v>864</v>
+        <v>854</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>6</v>
@@ -9226,10 +9280,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="B395" t="s">
-        <v>866</v>
+        <v>856</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>6</v>
@@ -9240,10 +9294,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
       <c r="B396" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>6</v>
@@ -9254,10 +9308,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="B397" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>6</v>
@@ -9268,10 +9322,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="B398" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>6</v>
@@ -9282,10 +9336,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="B399" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>6</v>
@@ -9296,10 +9350,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="B400" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>6</v>
@@ -9310,10 +9364,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
       <c r="B401" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>6</v>
@@ -9324,10 +9378,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="B402" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>6</v>
@@ -9338,10 +9392,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="B403" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>6</v>
@@ -9352,10 +9406,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="B404" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>6</v>
@@ -9366,10 +9420,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>891</v>
+        <v>875</v>
       </c>
       <c r="B405" t="s">
-        <v>892</v>
+        <v>876</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>6</v>
@@ -9380,10 +9434,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="B406" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>6</v>
@@ -9394,10 +9448,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
       <c r="B407" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>6</v>
@@ -9408,10 +9462,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>897</v>
+        <v>883</v>
       </c>
       <c r="B408" t="s">
-        <v>898</v>
+        <v>884</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>6</v>
@@ -9422,10 +9476,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>899</v>
+        <v>885</v>
       </c>
       <c r="B409" t="s">
-        <v>900</v>
+        <v>886</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>6</v>
@@ -9436,10 +9490,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>901</v>
+        <v>887</v>
       </c>
       <c r="B410" t="s">
-        <v>902</v>
+        <v>888</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>6</v>
@@ -9450,10 +9504,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="B411" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>6</v>
@@ -9464,10 +9518,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="B412" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>6</v>
@@ -9478,10 +9532,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="B413" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>6</v>
@@ -9492,10 +9546,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="B414" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>6</v>
@@ -9506,10 +9560,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
       <c r="B415" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>6</v>
@@ -9520,10 +9574,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>913</v>
+        <v>903</v>
       </c>
       <c r="B416" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>6</v>
@@ -9534,10 +9588,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
       <c r="B417" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>6</v>
@@ -9548,10 +9602,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="B418" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>6</v>
@@ -9562,10 +9616,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
       <c r="B419" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -9576,10 +9630,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="B420" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>6</v>
@@ -9590,10 +9644,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="B421" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>6</v>
@@ -9604,10 +9658,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="B422" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>6</v>
@@ -9618,10 +9672,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="B423" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>6</v>
@@ -9632,10 +9686,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="B424" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>6</v>
@@ -9646,10 +9700,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="B425" t="s">
-        <v>934</v>
+        <v>922</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>6</v>
@@ -9660,10 +9714,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="B426" t="s">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>6</v>
@@ -9674,10 +9728,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>937</v>
+        <v>925</v>
       </c>
       <c r="B427" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>6</v>
@@ -9688,10 +9742,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="B428" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -9702,10 +9756,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="B429" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>6</v>
@@ -9716,10 +9770,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="B430" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>6</v>
@@ -9730,10 +9784,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="B431" t="s">
-        <v>948</v>
+        <v>934</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>6</v>
@@ -9744,10 +9798,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B432" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>6</v>
@@ -9758,10 +9812,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>951</v>
+        <v>937</v>
       </c>
       <c r="B433" t="s">
-        <v>952</v>
+        <v>938</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>6</v>
@@ -9772,10 +9826,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>953</v>
+        <v>939</v>
       </c>
       <c r="B434" t="s">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>6</v>
@@ -9786,10 +9840,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>955</v>
+        <v>941</v>
       </c>
       <c r="B435" t="s">
-        <v>956</v>
+        <v>942</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>6</v>
@@ -9800,10 +9854,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="B436" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>6</v>
@@ -9814,10 +9868,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>959</v>
+        <v>945</v>
       </c>
       <c r="B437" t="s">
-        <v>960</v>
+        <v>946</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>6</v>
@@ -9828,10 +9882,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c r="B438" t="s">
-        <v>962</v>
+        <v>948</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>6</v>
@@ -9842,10 +9896,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>963</v>
+        <v>949</v>
       </c>
       <c r="B439" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>6</v>
@@ -9856,10 +9910,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>965</v>
+        <v>951</v>
       </c>
       <c r="B440" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>6</v>
@@ -9870,10 +9924,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>967</v>
+        <v>953</v>
       </c>
       <c r="B441" t="s">
-        <v>968</v>
+        <v>954</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>6</v>
@@ -9884,10 +9938,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="B442" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>6</v>
@@ -9898,10 +9952,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="B443" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>6</v>
@@ -9912,10 +9966,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>973</v>
+        <v>961</v>
       </c>
       <c r="B444" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>6</v>
@@ -9926,10 +9980,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="B445" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>6</v>
@@ -9940,10 +9994,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="B446" t="s">
-        <v>980</v>
+        <v>966</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>6</v>
@@ -9954,10 +10008,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>981</v>
+        <v>967</v>
       </c>
       <c r="B447" t="s">
-        <v>982</v>
+        <v>968</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>6</v>
@@ -9968,10 +10022,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="B448" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>6</v>
@@ -9982,10 +10036,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>985</v>
+        <v>971</v>
       </c>
       <c r="B449" t="s">
-        <v>986</v>
+        <v>972</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>6</v>
@@ -9996,10 +10050,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>987</v>
+        <v>973</v>
       </c>
       <c r="B450" t="s">
-        <v>988</v>
+        <v>974</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>6</v>
@@ -10010,10 +10064,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>989</v>
+        <v>975</v>
       </c>
       <c r="B451" t="s">
-        <v>990</v>
+        <v>976</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>6</v>
@@ -10024,10 +10078,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="B452" t="s">
-        <v>996</v>
+        <v>978</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>6</v>
@@ -10038,10 +10092,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>997</v>
+        <v>979</v>
       </c>
       <c r="B453" t="s">
-        <v>998</v>
+        <v>980</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>6</v>
@@ -10052,10 +10106,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>999</v>
+        <v>981</v>
       </c>
       <c r="B454" t="s">
-        <v>1000</v>
+        <v>982</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>6</v>
@@ -10066,10 +10120,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>1001</v>
+        <v>983</v>
       </c>
       <c r="B455" t="s">
-        <v>1002</v>
+        <v>984</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>6</v>
@@ -10080,10 +10134,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>1003</v>
+        <v>985</v>
       </c>
       <c r="B456" t="s">
-        <v>1004</v>
+        <v>986</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>6</v>
@@ -10094,10 +10148,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>1005</v>
+        <v>987</v>
       </c>
       <c r="B457" t="s">
-        <v>1006</v>
+        <v>988</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>6</v>
@@ -10108,10 +10162,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>1007</v>
+        <v>989</v>
       </c>
       <c r="B458" t="s">
-        <v>1008</v>
+        <v>990</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>6</v>
@@ -10122,10 +10176,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>1009</v>
+        <v>991</v>
       </c>
       <c r="B459" t="s">
-        <v>1010</v>
+        <v>992</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>6</v>
@@ -10136,10 +10190,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="B460" t="s">
-        <v>1014</v>
+        <v>994</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>6</v>
@@ -10150,10 +10204,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>1015</v>
+        <v>995</v>
       </c>
       <c r="B461" t="s">
-        <v>1016</v>
+        <v>996</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>6</v>
@@ -10164,10 +10218,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>1017</v>
+        <v>997</v>
       </c>
       <c r="B462" t="s">
-        <v>1018</v>
+        <v>998</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>6</v>
@@ -10178,10 +10232,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>1019</v>
+        <v>999</v>
       </c>
       <c r="B463" t="s">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>6</v>
@@ -10192,10 +10246,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>1021</v>
+        <v>1001</v>
       </c>
       <c r="B464" t="s">
-        <v>1022</v>
+        <v>1002</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>6</v>
@@ -10206,10 +10260,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>1025</v>
+        <v>1007</v>
       </c>
       <c r="B465" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>6</v>
@@ -10220,10 +10274,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>1027</v>
+        <v>1009</v>
       </c>
       <c r="B466" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>6</v>
@@ -10234,10 +10288,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>1029</v>
+        <v>1011</v>
       </c>
       <c r="B467" t="s">
-        <v>1030</v>
+        <v>1012</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>6</v>
@@ -10248,10 +10302,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="B468" t="s">
-        <v>1032</v>
+        <v>1014</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>6</v>
@@ -10262,10 +10316,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>1033</v>
+        <v>1015</v>
       </c>
       <c r="B469" t="s">
-        <v>1034</v>
+        <v>1016</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>6</v>
@@ -10276,10 +10330,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="B470" t="s">
-        <v>1036</v>
+        <v>1018</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>6</v>
@@ -10290,10 +10344,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="B471" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>6</v>
@@ -10304,10 +10358,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>1039</v>
+        <v>1021</v>
       </c>
       <c r="B472" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>6</v>
@@ -10318,10 +10372,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>1041</v>
+        <v>1023</v>
       </c>
       <c r="B473" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>6</v>
@@ -10332,10 +10386,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>1043</v>
+        <v>1029</v>
       </c>
       <c r="B474" t="s">
-        <v>1044</v>
+        <v>1030</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>6</v>
@@ -10346,10 +10400,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="B475" t="s">
-        <v>1046</v>
+        <v>1032</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>6</v>
@@ -10360,10 +10414,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>1047</v>
+        <v>1033</v>
       </c>
       <c r="B476" t="s">
-        <v>1048</v>
+        <v>1034</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>6</v>
@@ -10374,10 +10428,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>1049</v>
+        <v>1035</v>
       </c>
       <c r="B477" t="s">
-        <v>1050</v>
+        <v>1036</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>6</v>
@@ -10388,10 +10442,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>1051</v>
+        <v>1037</v>
       </c>
       <c r="B478" t="s">
-        <v>1052</v>
+        <v>1038</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -10402,10 +10456,10 @@
     </row>
     <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="B479" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>6</v>
@@ -10416,10 +10470,10 @@
     </row>
     <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="B480" t="s">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>6</v>
@@ -10430,10 +10484,10 @@
     </row>
     <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="B481" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>6</v>
@@ -10444,10 +10498,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>1061</v>
+        <v>1047</v>
       </c>
       <c r="B482" t="s">
-        <v>1062</v>
+        <v>1048</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>6</v>
@@ -10458,10 +10512,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1063</v>
+        <v>1049</v>
       </c>
       <c r="B483" t="s">
-        <v>1064</v>
+        <v>1050</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>6</v>
@@ -10472,10 +10526,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1065</v>
+        <v>1051</v>
       </c>
       <c r="B484" t="s">
-        <v>1066</v>
+        <v>1052</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>6</v>
@@ -10486,10 +10540,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1067</v>
+        <v>1053</v>
       </c>
       <c r="B485" t="s">
-        <v>1068</v>
+        <v>1054</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>6</v>
@@ -10500,10 +10554,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1069</v>
+        <v>1055</v>
       </c>
       <c r="B486" t="s">
-        <v>1070</v>
+        <v>1056</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>6</v>
@@ -10514,10 +10568,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1071</v>
+        <v>1057</v>
       </c>
       <c r="B487" t="s">
-        <v>1072</v>
+        <v>1058</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>6</v>
@@ -10528,10 +10582,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1073</v>
+        <v>1059</v>
       </c>
       <c r="B488" t="s">
-        <v>1074</v>
+        <v>1060</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>6</v>
@@ -10542,10 +10596,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
       <c r="B489" t="s">
-        <v>1076</v>
+        <v>1062</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>6</v>
@@ -10556,10 +10610,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1077</v>
+        <v>1063</v>
       </c>
       <c r="B490" t="s">
-        <v>1078</v>
+        <v>1064</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>6</v>
@@ -10570,10 +10624,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1079</v>
+        <v>1065</v>
       </c>
       <c r="B491" t="s">
-        <v>1080</v>
+        <v>1066</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>6</v>
@@ -10584,10 +10638,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1081</v>
+        <v>1067</v>
       </c>
       <c r="B492" t="s">
-        <v>1082</v>
+        <v>1068</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>6</v>
@@ -10598,10 +10652,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="B493" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>6</v>
@@ -10612,10 +10666,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="B494" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>6</v>
@@ -10626,10 +10680,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="B495" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>6</v>
@@ -10640,192 +10694,192 @@
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C496" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D496" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C497" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D497" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C498" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D498" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C499" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D499" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C500" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D500" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
         <v>1089</v>
       </c>
-      <c r="B496" t="s">
+      <c r="B501" t="s">
         <v>1090</v>
       </c>
-      <c r="C496" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D496" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="497" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
+      <c r="C501" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D501" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
         <v>1091</v>
       </c>
-      <c r="B497" t="s">
+      <c r="B502" t="s">
         <v>1092</v>
       </c>
-      <c r="C497" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D497" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="498" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
+      <c r="C502" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D502" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
         <v>1093</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B503" t="s">
         <v>1094</v>
       </c>
-      <c r="C498" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D498" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="499" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
+      <c r="C503" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D503" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
         <v>1095</v>
       </c>
-      <c r="B499" t="s">
+      <c r="B504" t="s">
         <v>1096</v>
       </c>
-      <c r="C499" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D499" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="500" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
+      <c r="C504" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D504" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
         <v>1097</v>
       </c>
-      <c r="B500" t="s">
+      <c r="B505" t="s">
         <v>1098</v>
       </c>
-      <c r="C500" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D500" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="501" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
+      <c r="C505" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D505" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
         <v>1099</v>
       </c>
-      <c r="B501" t="s">
+      <c r="B506" t="s">
         <v>1100</v>
       </c>
-      <c r="C501" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D501" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="502" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
+      <c r="C506" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D506" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
         <v>1101</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B507" t="s">
         <v>1102</v>
       </c>
-      <c r="C502" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D502" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="503" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>5</v>
-      </c>
-      <c r="B503" t="s">
-        <v>5</v>
-      </c>
-      <c r="C503" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E503" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="504" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
-        <v>33</v>
-      </c>
-      <c r="B504" t="s">
-        <v>34</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D504" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="505" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>103</v>
-      </c>
-      <c r="B505" t="s">
-        <v>104</v>
-      </c>
-      <c r="C505" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E505" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="506" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A506" t="s">
-        <v>105</v>
-      </c>
-      <c r="B506" t="s">
-        <v>106</v>
-      </c>
-      <c r="C506" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E506" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="507" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A507" t="s">
-        <v>117</v>
-      </c>
-      <c r="B507" t="s">
-        <v>118</v>
-      </c>
       <c r="C507" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E507" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="508" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D507" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>121</v>
+        <v>1103</v>
       </c>
       <c r="B508" t="s">
-        <v>122</v>
+        <v>1104</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E508" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="509" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D508" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>179</v>
+        <v>1105</v>
       </c>
       <c r="B509" t="s">
-        <v>180</v>
+        <v>1106</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>6</v>
@@ -10834,110 +10888,110 @@
         <v>10</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>181</v>
+        <v>1107</v>
       </c>
       <c r="B510" t="s">
-        <v>182</v>
+        <v>1108</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E510" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="511" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D510" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>183</v>
+        <v>1109</v>
       </c>
       <c r="B511" t="s">
-        <v>184</v>
+        <v>1110</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E511" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="512" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D511" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>203</v>
+        <v>1111</v>
       </c>
       <c r="B512" t="s">
-        <v>204</v>
+        <v>1112</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E512" t="s">
-        <v>7</v>
+      <c r="D512" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="513" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>221</v>
+        <v>1113</v>
       </c>
       <c r="B513" t="s">
-        <v>222</v>
+        <v>1114</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E513" t="s">
-        <v>7</v>
+      <c r="D513" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="514" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>223</v>
+        <v>1115</v>
       </c>
       <c r="B514" t="s">
-        <v>224</v>
+        <v>1116</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E514" t="s">
-        <v>7</v>
+      <c r="D514" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="515" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>225</v>
+        <v>1117</v>
       </c>
       <c r="B515" t="s">
-        <v>226</v>
+        <v>1118</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E515" t="s">
-        <v>7</v>
+      <c r="D515" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="516" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>227</v>
+        <v>1119</v>
       </c>
       <c r="B516" t="s">
-        <v>228</v>
+        <v>1120</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E516" t="s">
-        <v>7</v>
+      <c r="D516" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="517" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="B517" t="s">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>6</v>
@@ -10948,10 +11002,10 @@
     </row>
     <row r="518" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="B518" t="s">
-        <v>258</v>
+        <v>104</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>6</v>
@@ -10962,10 +11016,10 @@
     </row>
     <row r="519" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>267</v>
+        <v>105</v>
       </c>
       <c r="B519" t="s">
-        <v>268</v>
+        <v>106</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>6</v>
@@ -10976,10 +11030,10 @@
     </row>
     <row r="520" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="B520" t="s">
-        <v>286</v>
+        <v>116</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>6</v>
@@ -10990,10 +11044,10 @@
     </row>
     <row r="521" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>289</v>
+        <v>119</v>
       </c>
       <c r="B521" t="s">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>6</v>
@@ -11004,10 +11058,10 @@
     </row>
     <row r="522" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>331</v>
+        <v>123</v>
       </c>
       <c r="B522" t="s">
-        <v>332</v>
+        <v>124</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>6</v>
@@ -11018,10 +11072,10 @@
     </row>
     <row r="523" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>337</v>
+        <v>183</v>
       </c>
       <c r="B523" t="s">
-        <v>338</v>
+        <v>184</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>6</v>
@@ -11032,10 +11086,10 @@
     </row>
     <row r="524" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>381</v>
+        <v>185</v>
       </c>
       <c r="B524" t="s">
-        <v>382</v>
+        <v>186</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>6</v>
@@ -11046,10 +11100,10 @@
     </row>
     <row r="525" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>393</v>
+        <v>205</v>
       </c>
       <c r="B525" t="s">
-        <v>394</v>
+        <v>206</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>6</v>
@@ -11060,94 +11114,94 @@
     </row>
     <row r="526" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>433</v>
+        <v>223</v>
       </c>
       <c r="B526" t="s">
-        <v>434</v>
+        <v>224</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D526" t="s">
-        <v>10</v>
+      <c r="E526" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="527" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>495</v>
+        <v>225</v>
       </c>
       <c r="B527" t="s">
-        <v>496</v>
+        <v>226</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D527" t="s">
-        <v>10</v>
+      <c r="E527" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="528" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>521</v>
+        <v>227</v>
       </c>
       <c r="B528" t="s">
-        <v>522</v>
+        <v>228</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D528" t="s">
-        <v>10</v>
+      <c r="E528" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="529" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>535</v>
+        <v>229</v>
       </c>
       <c r="B529" t="s">
-        <v>536</v>
+        <v>230</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D529" t="s">
-        <v>10</v>
+      <c r="E529" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="530" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>537</v>
+        <v>251</v>
       </c>
       <c r="B530" t="s">
-        <v>538</v>
+        <v>252</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D530" t="s">
-        <v>10</v>
+      <c r="E530" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="531" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>539</v>
+        <v>259</v>
       </c>
       <c r="B531" t="s">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D531" t="s">
-        <v>10</v>
+      <c r="E531" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="532" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>593</v>
+        <v>269</v>
       </c>
       <c r="B532" t="s">
-        <v>594</v>
+        <v>270</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>6</v>
@@ -11158,24 +11212,24 @@
     </row>
     <row r="533" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>617</v>
+        <v>271</v>
       </c>
       <c r="B533" t="s">
-        <v>618</v>
+        <v>272</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E533" t="s">
-        <v>7</v>
+      <c r="D533" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="534" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>629</v>
+        <v>293</v>
       </c>
       <c r="B534" t="s">
-        <v>630</v>
+        <v>294</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>6</v>
@@ -11186,10 +11240,10 @@
     </row>
     <row r="535" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>689</v>
+        <v>335</v>
       </c>
       <c r="B535" t="s">
-        <v>690</v>
+        <v>336</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>6</v>
@@ -11200,24 +11254,24 @@
     </row>
     <row r="536" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>691</v>
+        <v>341</v>
       </c>
       <c r="B536" t="s">
-        <v>692</v>
+        <v>342</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D536" t="s">
-        <v>10</v>
+      <c r="E536" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>817</v>
+        <v>385</v>
       </c>
       <c r="B537" t="s">
-        <v>818</v>
+        <v>386</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -11228,10 +11282,10 @@
     </row>
     <row r="538" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>839</v>
+        <v>397</v>
       </c>
       <c r="B538" t="s">
-        <v>840</v>
+        <v>398</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>6</v>
@@ -11242,38 +11296,38 @@
     </row>
     <row r="539" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>869</v>
+        <v>433</v>
       </c>
       <c r="B539" t="s">
-        <v>870</v>
+        <v>434</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E539" t="s">
-        <v>7</v>
+      <c r="D539" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="540" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>879</v>
+        <v>571</v>
       </c>
       <c r="B540" t="s">
-        <v>880</v>
+        <v>572</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E540" t="s">
-        <v>7</v>
+      <c r="D540" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="541" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>883</v>
+        <v>601</v>
       </c>
       <c r="B541" t="s">
-        <v>884</v>
+        <v>602</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -11284,24 +11338,24 @@
     </row>
     <row r="542" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>921</v>
+        <v>625</v>
       </c>
       <c r="B542" t="s">
-        <v>922</v>
+        <v>626</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D542" t="s">
-        <v>10</v>
+      <c r="E542" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="543" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>945</v>
+        <v>637</v>
       </c>
       <c r="B543" t="s">
-        <v>946</v>
+        <v>638</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>6</v>
@@ -11312,24 +11366,24 @@
     </row>
     <row r="544" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>977</v>
+        <v>697</v>
       </c>
       <c r="B544" t="s">
-        <v>978</v>
+        <v>698</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D544" t="s">
-        <v>10</v>
+      <c r="E544" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="545" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>991</v>
+        <v>715</v>
       </c>
       <c r="B545" t="s">
-        <v>992</v>
+        <v>716</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>6</v>
@@ -11340,24 +11394,24 @@
     </row>
     <row r="546" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>993</v>
+        <v>827</v>
       </c>
       <c r="B546" t="s">
-        <v>994</v>
+        <v>828</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D546" t="s">
-        <v>10</v>
+      <c r="E546" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="547" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1011</v>
+        <v>849</v>
       </c>
       <c r="B547" t="s">
-        <v>1012</v>
+        <v>850</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>6</v>
@@ -11368,10 +11422,10 @@
     </row>
     <row r="548" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1023</v>
+        <v>879</v>
       </c>
       <c r="B548" t="s">
-        <v>1024</v>
+        <v>880</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>6</v>
@@ -11382,10 +11436,10 @@
     </row>
     <row r="549" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1059</v>
+        <v>889</v>
       </c>
       <c r="B549" t="s">
-        <v>1060</v>
+        <v>890</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>6</v>
@@ -11394,19 +11448,145 @@
         <v>7</v>
       </c>
     </row>
+    <row r="550" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>893</v>
+      </c>
+      <c r="B550" t="s">
+        <v>894</v>
+      </c>
+      <c r="C550" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E550" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>955</v>
+      </c>
+      <c r="B551" t="s">
+        <v>956</v>
+      </c>
+      <c r="C551" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E551" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C552" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D552" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C553" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D553" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C554" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D554" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C555" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E555" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C556" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E556" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C557" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D557" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C558" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E558" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E549">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E558">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D549" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D558" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C503" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C517" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
@@ -11419,52 +11599,52 @@
     <hyperlink ref="C11" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="C12" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="C13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C504" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="C15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C20" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C21" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C22" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C23" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C24" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C25" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C26" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C27" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="C29" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C30" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C31" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C32" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="C33" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C34" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C505" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C506" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C48" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C49" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C50" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C51" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C52" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C507" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C53" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C508" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C54" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C15" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C16" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C22" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C26" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C27" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="C29" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C30" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="C34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="C35" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C36" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C37" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C38" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="C39" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C40" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C41" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C42" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C43" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C44" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C45" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C46" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C47" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C48" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C518" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C519" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C49" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C50" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C51" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C52" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C520" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C53" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C521" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C54" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C522" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
     <hyperlink ref="C55" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
     <hyperlink ref="C56" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
     <hyperlink ref="C57" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
@@ -11492,469 +11672,479 @@
     <hyperlink ref="C79" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
     <hyperlink ref="C80" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
     <hyperlink ref="C81" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C509" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C510" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C511" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C82" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C83" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C84" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C85" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C86" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C87" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C88" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C89" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C90" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C512" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C91" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C92" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C93" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C94" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C95" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C96" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="C97" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="C98" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="C513" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C514" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="C515" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C516" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="C99" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C100" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C101" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C102" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="C103" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C104" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="C105" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C106" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="C107" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="C108" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="C517" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="C109" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="C110" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C111" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C518" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C112" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="C113" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C114" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="C115" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C519" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="C116" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C117" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C82" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C83" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C523" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C524" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C84" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C85" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C86" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C87" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C88" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C89" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C90" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C91" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C92" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C525" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C93" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C94" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C95" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C96" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C97" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C98" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="C99" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="C100" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="C526" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C527" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C528" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C529" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="C101" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C102" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C103" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C104" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="C105" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C106" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="C107" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C108" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="C109" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="C110" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="C530" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="C111" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="C112" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C113" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C531" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C114" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="C115" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C116" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C117" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C532" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="C533" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
     <hyperlink ref="C118" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
     <hyperlink ref="C119" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
     <hyperlink ref="C120" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
     <hyperlink ref="C121" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
     <hyperlink ref="C122" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
     <hyperlink ref="C123" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C520" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C124" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C521" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C125" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C126" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C127" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C128" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C129" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C130" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C131" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C132" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C133" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C134" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C135" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C136" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C137" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C138" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C139" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C140" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C141" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C142" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C143" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C144" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C522" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C145" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C146" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C523" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C147" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C148" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C149" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C150" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C151" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C152" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C153" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C154" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C155" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C156" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C157" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C158" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C159" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C160" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C161" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C162" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C163" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C164" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C165" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C166" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C167" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C524" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C168" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C169" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C170" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C171" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C172" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C525" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C173" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C174" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C175" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C176" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C177" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C178" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C179" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C180" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C181" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C182" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C183" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="C184" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C185" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C186" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C187" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C188" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C189" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C190" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C191" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C526" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C192" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C193" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C194" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C195" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C196" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C197" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C198" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C199" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C200" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C201" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C202" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C203" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C204" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C205" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C206" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C207" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C208" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C209" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C210" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C211" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C212" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="C213" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="C214" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="C215" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="C216" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="C217" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="C218" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="C219" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="C220" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="C221" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="C527" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="C222" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="C223" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="C224" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="C225" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="C226" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="C227" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="C228" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="C229" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="C230" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="C231" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="C232" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="C233" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="C528" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="C234" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="C235" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="C236" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="C237" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="C238" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="C239" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="C529" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="C530" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="C531" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="C240" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="C241" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="C242" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="C243" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="C244" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="C245" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="C246" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="C247" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="C248" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="C249" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="C250" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="C251" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="C252" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="C253" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="C254" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="C255" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="C256" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="C257" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="C258" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="C259" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="C260" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="C261" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="C262" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="C263" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="C264" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="C265" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="C532" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="C266" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="C267" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C268" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C269" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="C270" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="C271" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="C272" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="C273" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C274" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C275" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C276" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C533" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C277" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C278" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C279" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C280" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="C281" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="C534" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="C282" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="C283" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C284" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C285" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C286" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C287" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C288" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C289" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="C290" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C291" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C292" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C293" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C294" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C295" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C296" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C297" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C298" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C299" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C300" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C301" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C302" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C303" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C304" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C305" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C306" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C307" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C308" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C309" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C310" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C535" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C536" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C311" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C312" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C313" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C314" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C315" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C316" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C317" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C318" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="C319" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="C320" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C321" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C322" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C323" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C324" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C325" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="C326" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C327" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C328" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C329" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C330" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C331" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C332" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C333" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C334" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C335" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C336" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C337" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C338" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C339" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C340" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C341" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C342" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C343" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C344" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C345" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C346" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C347" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C348" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C349" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C350" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C351" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C352" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C353" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C354" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C355" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C356" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C357" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C358" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C359" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C360" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C361" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C362" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C363" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C364" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C365" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C366" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C367" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C368" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C369" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C370" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C371" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C372" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C537" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C373" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C374" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C375" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C376" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C377" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C378" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C379" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C380" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C381" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C382" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C538" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C383" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C384" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C385" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C386" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C387" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C388" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C389" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C390" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C391" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C392" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C393" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C394" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C395" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C396" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C539" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C397" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C398" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C399" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C400" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C540" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C401" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C541" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C402" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C403" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C404" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C405" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C406" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C407" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C408" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C409" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C410" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C411" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C412" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C413" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C414" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C415" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C416" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C417" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C418" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C419" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C542" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C420" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C421" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C422" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C423" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C424" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C425" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C426" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C427" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C428" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C429" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C430" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C543" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C431" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C432" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C433" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C434" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C435" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C436" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C437" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C438" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C439" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C440" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C441" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C442" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C443" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C444" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C445" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C544" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C446" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C447" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C448" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C449" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C450" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C451" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C545" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C546" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C452" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C453" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C454" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C455" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C456" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C457" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C458" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C459" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C547" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C460" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C461" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C462" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C463" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="C464" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C548" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="C465" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="C466" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C467" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="C468" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C469" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C470" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C471" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C472" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="C473" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="C474" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="C475" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="C476" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="C477" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="C478" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="C479" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="C480" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="C481" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C549" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C482" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="C483" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="C484" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="C485" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="C486" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="C487" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="C488" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="C489" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="C490" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="C491" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="C492" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="C493" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="C494" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="C495" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C496" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C497" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C498" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C499" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="C500" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="C501" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="C502" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C124" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C125" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C126" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C127" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C534" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C128" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C129" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C130" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C131" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C132" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C133" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C134" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C135" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C136" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C137" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C138" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C139" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C140" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C141" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C142" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C143" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C144" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C145" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C146" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C147" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C535" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C148" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C149" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C536" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="C150" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C151" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C152" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C153" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C154" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C155" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C156" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C157" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C158" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C159" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C160" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C161" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C162" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C163" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C164" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C165" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C166" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C167" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C168" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C169" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C170" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C537" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C171" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C172" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C173" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C174" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C175" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C538" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C176" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C177" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C178" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C179" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C180" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C181" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C182" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C183" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C184" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C185" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C186" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C187" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C188" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C189" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C190" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C191" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C192" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C539" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C193" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C194" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C195" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C196" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C197" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C198" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C199" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C200" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C201" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C202" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C203" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C204" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C205" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C206" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C207" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C208" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C209" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C210" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C211" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C212" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C213" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C214" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="C215" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="C216" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="C217" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="C218" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="C219" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="C220" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="C221" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="C222" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="C223" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C224" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="C225" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="C226" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="C227" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="C228" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="C229" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="C230" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="C231" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="C232" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="C233" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C234" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="C235" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="C236" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="C237" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="C238" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C239" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="C240" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="C241" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="C242" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="C243" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="C244" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="C245" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="C246" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="C247" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="C248" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="C249" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="C250" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="C251" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="C252" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="C253" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C254" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="C255" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="C256" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="C257" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="C258" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C259" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="C260" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="C540" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="C261" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="C262" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C263" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="C264" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="C265" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="C266" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="C267" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C268" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="C269" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="C270" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="C271" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="C272" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C273" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="C274" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C541" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C275" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="C276" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C277" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="C278" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="C279" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C280" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C281" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C282" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C283" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C284" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C285" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C542" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C286" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="C287" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="C288" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="C289" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C290" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C543" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C291" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C292" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C293" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C294" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C295" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="C296" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C297" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C298" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C299" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C300" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C301" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C302" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C303" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C304" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C305" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C306" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C307" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C308" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C309" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C310" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C311" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C312" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C313" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C314" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C315" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C316" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C317" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C318" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C319" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C544" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C320" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C321" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C322" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C323" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C324" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C325" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C326" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C327" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C545" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C328" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C329" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C330" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C331" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C332" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C333" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C334" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C335" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C336" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C337" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C338" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C339" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C340" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C341" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C342" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C343" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C344" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C345" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C346" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C347" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C348" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C349" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C350" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C351" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C352" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C353" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C354" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C355" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C356" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C357" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C358" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C359" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C360" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C361" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C362" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C363" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C364" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C365" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C366" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C367" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C368" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C369" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C370" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C371" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C372" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C373" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C374" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C375" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C376" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C377" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C378" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C379" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C380" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C381" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C382" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C546" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C383" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C384" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C385" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C386" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C387" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C388" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C389" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C390" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C391" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C392" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C547" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C393" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C394" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C395" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C396" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C397" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C398" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C399" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C400" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C401" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C402" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C403" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C404" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C405" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C406" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C548" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C407" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C408" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C409" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C410" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C549" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C411" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C550" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C412" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C413" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C414" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C415" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C416" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C417" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C418" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C419" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C420" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C421" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C422" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C423" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C424" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C425" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C426" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C427" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C428" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C429" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C430" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C431" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C432" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C433" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C434" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C435" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C436" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C437" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C438" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C439" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C440" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C441" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C551" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C442" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C443" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C444" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C445" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C446" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C447" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C448" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C449" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C450" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C451" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C452" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C453" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C454" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C455" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C456" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C457" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C458" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C459" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C460" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C461" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C462" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C463" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C464" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C552" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C553" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C465" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C466" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C467" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C468" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C469" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C470" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C471" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C472" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C473" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C554" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C555" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C474" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C475" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C476" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C477" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C478" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C556" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C479" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="C480" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="C481" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="C482" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="C483" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="C484" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="C485" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="C486" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="C487" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C488" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C489" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="C490" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="C491" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="C492" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="C557" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="C493" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="C494" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="C495" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="C558" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="C496" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="C497" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="C498" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="C499" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="C500" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C501" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C502" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C503" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C504" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C505" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="C506" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="C507" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C508" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="C509" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="C510" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C511" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="C512" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C513" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="C514" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="C515" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="C516" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId558"/>
 </worksheet>
 </file>
--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ACFDB7-1E63-40D6-AE70-2A53FF12BA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F18F1E-3073-4DA9-B8BC-D85E19D58C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danske backdrops" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="1143">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -394,6 +394,12 @@
     <t>Boss Baby - Det Bli'R I Familien</t>
   </si>
   <si>
+    <t>brandbamsen bjørnis</t>
+  </si>
+  <si>
+    <t>Brandbamsen Bjørnis</t>
+  </si>
+  <si>
     <t>bryllup</t>
   </si>
   <si>
@@ -694,6 +700,12 @@
     <t>Det sidste nye med Onkel Reje Onkel Rejes skarpe tænder</t>
   </si>
   <si>
+    <t>det store ramasjang mysterie</t>
+  </si>
+  <si>
+    <t>Det store Ramasjang Mysterie</t>
+  </si>
+  <si>
     <t>dexter</t>
   </si>
   <si>
@@ -1054,6 +1066,12 @@
     <t>Formel 1</t>
   </si>
   <si>
+    <t>formel 1 360°</t>
+  </si>
+  <si>
+    <t>Formel 1 360°</t>
+  </si>
+  <si>
     <t>fornyet mistanke</t>
   </si>
   <si>
@@ -1294,6 +1312,12 @@
     <t>Harry Potter og de vises sten</t>
   </si>
   <si>
+    <t>harry potter og fangen fra azkaban</t>
+  </si>
+  <si>
+    <t>Harry Potter og fangen fra Azkaban</t>
+  </si>
+  <si>
     <t>harry potter og hemmelighedernes kammer</t>
   </si>
   <si>
@@ -1576,6 +1600,12 @@
     <t>Ingemann, Fyn &amp; Lolland-Falster</t>
   </si>
   <si>
+    <t>inspector sun og den sorte enkes forbandelse</t>
+  </si>
+  <si>
+    <t>Inspector Sun og den sorte enkes forbandelse</t>
+  </si>
+  <si>
     <t>ja for fanø</t>
   </si>
   <si>
@@ -1906,6 +1936,12 @@
     <t>Loppe Deluxe</t>
   </si>
   <si>
+    <t>luftens helte</t>
+  </si>
+  <si>
+    <t>Luftens helte</t>
+  </si>
+  <si>
     <t>luftens læger</t>
   </si>
   <si>
@@ -1942,6 +1978,12 @@
     <t>Lykkehjulet</t>
   </si>
   <si>
+    <t>løvernes garde</t>
+  </si>
+  <si>
+    <t>Løvernes garde</t>
+  </si>
+  <si>
     <t>madagascar 3: efterlyst i hele europa</t>
   </si>
   <si>
@@ -2218,6 +2260,12 @@
     <t>Mumien: Dragekeiserens grav</t>
   </si>
   <si>
+    <t>mummidalen</t>
+  </si>
+  <si>
+    <t>Mummidalen</t>
+  </si>
+  <si>
     <t>mysteriet om den danske nazi-donor</t>
   </si>
   <si>
@@ -2794,6 +2842,12 @@
     <t>Sommeren 1985</t>
   </si>
   <si>
+    <t>spektakulære spækhuggere</t>
+  </si>
+  <si>
+    <t>Spektakulære spækhuggere</t>
+  </si>
+  <si>
     <t>spidey och hans fantastiska vänner</t>
   </si>
   <si>
@@ -2884,6 +2938,12 @@
     <t>Strandhotellet</t>
   </si>
   <si>
+    <t>strøgvagterne</t>
+  </si>
+  <si>
+    <t>Strøgvagterne</t>
+  </si>
+  <si>
     <t>sunday</t>
   </si>
   <si>
@@ -3110,6 +3170,12 @@
   </si>
   <si>
     <t>Troldspejlet</t>
+  </si>
+  <si>
+    <t>trolls på verdensturné</t>
+  </si>
+  <si>
+    <t>Trolls på verdensturné</t>
   </si>
   <si>
     <t>troubadouren</t>
@@ -3749,7 +3815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E558"/>
+  <dimension ref="A1:E569"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -4492,10 +4558,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
@@ -4506,10 +4572,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
@@ -4520,10 +4586,10 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>6</v>
@@ -4926,10 +4992,10 @@
     </row>
     <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>6</v>
@@ -5052,10 +5118,10 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B93" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>6</v>
@@ -5164,10 +5230,10 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B101" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>6</v>
@@ -5178,10 +5244,10 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B102" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>6</v>
@@ -5192,10 +5258,10 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B103" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>6</v>
@@ -5206,10 +5272,10 @@
     </row>
     <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B104" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -5220,10 +5286,10 @@
     </row>
     <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B105" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>6</v>
@@ -5234,10 +5300,10 @@
     </row>
     <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B106" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>6</v>
@@ -5248,10 +5314,10 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B107" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>6</v>
@@ -5262,10 +5328,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B108" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>6</v>
@@ -5276,10 +5342,10 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B109" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>6</v>
@@ -5290,10 +5356,10 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B110" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>6</v>
@@ -5318,10 +5384,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>6</v>
@@ -5332,10 +5398,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>6</v>
@@ -5360,10 +5426,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B115" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>6</v>
@@ -5374,10 +5440,10 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B116" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>6</v>
@@ -5388,10 +5454,10 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B117" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>6</v>
@@ -5402,10 +5468,10 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B118" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>6</v>
@@ -5542,10 +5608,10 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B128" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>6</v>
@@ -5556,10 +5622,10 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B129" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>6</v>
@@ -5822,10 +5888,10 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B148" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>6</v>
@@ -5836,10 +5902,10 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B149" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>6</v>
@@ -5850,10 +5916,10 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B150" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>6</v>
@@ -5864,10 +5930,10 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B151" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>6</v>
@@ -5878,10 +5944,10 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B152" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>6</v>
@@ -5892,10 +5958,10 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B153" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>6</v>
@@ -5906,10 +5972,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B154" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>6</v>
@@ -5920,10 +5986,10 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B155" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>6</v>
@@ -5934,10 +6000,10 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B156" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>6</v>
@@ -5948,10 +6014,10 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B157" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>6</v>
@@ -5962,10 +6028,10 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B158" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>6</v>
@@ -5976,10 +6042,10 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B159" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>6</v>
@@ -5990,10 +6056,10 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B160" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>6</v>
@@ -6004,10 +6070,10 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B161" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>6</v>
@@ -6018,10 +6084,10 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B162" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>6</v>
@@ -6032,10 +6098,10 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B163" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>6</v>
@@ -6046,10 +6112,10 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B164" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>6</v>
@@ -6060,10 +6126,10 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B165" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>6</v>
@@ -6074,10 +6140,10 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B166" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>6</v>
@@ -6088,10 +6154,10 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B167" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>6</v>
@@ -6102,10 +6168,10 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B168" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>6</v>
@@ -6116,10 +6182,10 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B169" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>6</v>
@@ -6130,10 +6196,10 @@
     </row>
     <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B170" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>6</v>
@@ -6172,10 +6238,10 @@
     </row>
     <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B173" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>6</v>
@@ -6186,10 +6252,10 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B174" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>6</v>
@@ -6200,10 +6266,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B175" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>6</v>
@@ -6242,10 +6308,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B178" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>6</v>
@@ -6256,10 +6322,10 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B179" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>6</v>
@@ -6270,10 +6336,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B180" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>6</v>
@@ -6284,10 +6350,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B181" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>6</v>
@@ -6298,10 +6364,10 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B182" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>6</v>
@@ -6312,10 +6378,10 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B183" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -6326,10 +6392,10 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B184" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>6</v>
@@ -6340,10 +6406,10 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B185" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>6</v>
@@ -6354,10 +6420,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B186" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>6</v>
@@ -6368,10 +6434,10 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B187" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>6</v>
@@ -6382,10 +6448,10 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B188" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>6</v>
@@ -6396,10 +6462,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B189" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -6410,10 +6476,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B190" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>6</v>
@@ -6424,10 +6490,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B191" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>6</v>
@@ -6438,10 +6504,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B192" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>6</v>
@@ -6452,10 +6518,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B193" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>6</v>
@@ -6466,10 +6532,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B194" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>6</v>
@@ -6480,10 +6546,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B195" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>6</v>
@@ -6494,10 +6560,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B196" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>6</v>
@@ -6508,10 +6574,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B197" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>6</v>
@@ -6522,10 +6588,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B198" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>6</v>
@@ -6536,10 +6602,10 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B199" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>6</v>
@@ -6550,10 +6616,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B200" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>6</v>
@@ -6564,10 +6630,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B201" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>6</v>
@@ -6578,10 +6644,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B202" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>6</v>
@@ -6592,10 +6658,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B203" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>6</v>
@@ -6606,10 +6672,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B204" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>6</v>
@@ -6620,10 +6686,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B205" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>6</v>
@@ -6634,10 +6700,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B206" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>6</v>
@@ -6648,10 +6714,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B207" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>6</v>
@@ -6662,10 +6728,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B208" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>6</v>
@@ -6676,10 +6742,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B209" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>6</v>
@@ -6690,10 +6756,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B210" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>6</v>
@@ -6704,10 +6770,10 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B211" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>6</v>
@@ -6718,10 +6784,10 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>6</v>
@@ -6732,10 +6798,10 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>6</v>
@@ -6746,10 +6812,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B214" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>6</v>
@@ -6760,10 +6826,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B215" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>6</v>
@@ -6774,10 +6840,10 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B216" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>6</v>
@@ -6788,10 +6854,10 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>6</v>
@@ -6802,10 +6868,10 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B218" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>6</v>
@@ -6816,10 +6882,10 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B219" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>6</v>
@@ -6830,10 +6896,10 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B220" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>6</v>
@@ -6844,10 +6910,10 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B221" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>6</v>
@@ -6858,10 +6924,10 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B222" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>6</v>
@@ -6872,10 +6938,10 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B223" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>6</v>
@@ -6886,10 +6952,10 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B224" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>6</v>
@@ -6900,10 +6966,10 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B225" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -6914,10 +6980,10 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B226" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>6</v>
@@ -6928,10 +6994,10 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B227" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>6</v>
@@ -6942,10 +7008,10 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B228" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>6</v>
@@ -6956,10 +7022,10 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B229" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -6970,10 +7036,10 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B230" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>6</v>
@@ -6984,10 +7050,10 @@
     </row>
     <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B231" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>6</v>
@@ -6998,10 +7064,10 @@
     </row>
     <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B232" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -7012,10 +7078,10 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B233" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -7026,10 +7092,10 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B234" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>6</v>
@@ -7040,10 +7106,10 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B235" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>6</v>
@@ -7054,10 +7120,10 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B236" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
@@ -7068,10 +7134,10 @@
     </row>
     <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B237" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
@@ -7082,10 +7148,10 @@
     </row>
     <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B238" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>6</v>
@@ -7096,10 +7162,10 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B239" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
@@ -7110,10 +7176,10 @@
     </row>
     <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B240" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
@@ -7124,10 +7190,10 @@
     </row>
     <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B241" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
@@ -7138,10 +7204,10 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B242" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -7152,10 +7218,10 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B243" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
@@ -7166,10 +7232,10 @@
     </row>
     <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B244" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -7180,10 +7246,10 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B245" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -7194,10 +7260,10 @@
     </row>
     <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B246" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
@@ -7208,10 +7274,10 @@
     </row>
     <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B247" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
@@ -7222,10 +7288,10 @@
     </row>
     <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B248" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
@@ -7236,10 +7302,10 @@
     </row>
     <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B249" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
@@ -7250,10 +7316,10 @@
     </row>
     <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B250" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
@@ -7264,10 +7330,10 @@
     </row>
     <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B251" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>6</v>
@@ -7278,10 +7344,10 @@
     </row>
     <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B252" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
@@ -7292,10 +7358,10 @@
     </row>
     <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B253" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>6</v>
@@ -7306,10 +7372,10 @@
     </row>
     <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B254" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>6</v>
@@ -7320,10 +7386,10 @@
     </row>
     <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B255" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>6</v>
@@ -7334,10 +7400,10 @@
     </row>
     <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B256" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>6</v>
@@ -7348,10 +7414,10 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B257" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>6</v>
@@ -7362,10 +7428,10 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B258" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>6</v>
@@ -7376,10 +7442,10 @@
     </row>
     <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B259" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>6</v>
@@ -7390,10 +7456,10 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B260" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -7404,10 +7470,10 @@
     </row>
     <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B261" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>6</v>
@@ -7418,10 +7484,10 @@
     </row>
     <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B262" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>6</v>
@@ -7432,10 +7498,10 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B263" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>6</v>
@@ -7446,10 +7512,10 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B264" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>6</v>
@@ -7460,10 +7526,10 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B265" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>6</v>
@@ -7474,10 +7540,10 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B266" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>6</v>
@@ -7488,10 +7554,10 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B267" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>6</v>
@@ -7502,10 +7568,10 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B268" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>6</v>
@@ -7516,10 +7582,10 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B269" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>6</v>
@@ -7530,10 +7596,10 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B270" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>6</v>
@@ -7544,10 +7610,10 @@
     </row>
     <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B271" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>6</v>
@@ -7558,10 +7624,10 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B272" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>6</v>
@@ -7572,10 +7638,10 @@
     </row>
     <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B273" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>6</v>
@@ -7586,10 +7652,10 @@
     </row>
     <row r="274" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B274" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>6</v>
@@ -7656,10 +7722,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B279" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>6</v>
@@ -7670,10 +7736,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B280" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>6</v>
@@ -7684,10 +7750,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B281" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>6</v>
@@ -7698,10 +7764,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B282" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>6</v>
@@ -7712,10 +7778,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B283" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>6</v>
@@ -7726,10 +7792,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B284" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>6</v>
@@ -7740,10 +7806,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B285" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -7810,10 +7876,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B290" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>6</v>
@@ -7824,10 +7890,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B291" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>6</v>
@@ -7838,10 +7904,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B292" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>6</v>
@@ -7852,10 +7918,10 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B293" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>6</v>
@@ -7866,10 +7932,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B294" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>6</v>
@@ -7880,10 +7946,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B295" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>6</v>
@@ -7894,10 +7960,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B296" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>6</v>
@@ -7908,10 +7974,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B297" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>6</v>
@@ -7922,10 +7988,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B298" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>6</v>
@@ -7936,10 +8002,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B299" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>6</v>
@@ -7950,10 +8016,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B300" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>6</v>
@@ -7964,10 +8030,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B301" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>6</v>
@@ -7978,10 +8044,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B302" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -7992,10 +8058,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B303" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -8006,10 +8072,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="B304" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -8020,10 +8086,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B305" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>6</v>
@@ -8034,10 +8100,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B306" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -8048,10 +8114,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="B307" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>6</v>
@@ -8062,10 +8128,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B308" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>6</v>
@@ -8076,10 +8142,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B309" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>6</v>
@@ -8090,10 +8156,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="B310" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -8104,10 +8170,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B311" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>6</v>
@@ -8118,10 +8184,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B312" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -8132,10 +8198,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="B313" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -8146,10 +8212,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B314" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -8160,10 +8226,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B315" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>6</v>
@@ -8174,10 +8240,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B316" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>6</v>
@@ -8188,10 +8254,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B317" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>6</v>
@@ -8202,10 +8268,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B318" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>6</v>
@@ -8216,10 +8282,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B319" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>6</v>
@@ -8230,10 +8296,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B320" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>6</v>
@@ -8244,10 +8310,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B321" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>6</v>
@@ -8258,10 +8324,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B322" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -8272,10 +8338,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B323" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>6</v>
@@ -8286,10 +8352,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B324" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>6</v>
@@ -8300,10 +8366,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="B325" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>6</v>
@@ -8314,10 +8380,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="B326" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>6</v>
@@ -8328,10 +8394,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="B327" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>6</v>
@@ -8342,10 +8408,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B328" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>6</v>
@@ -8356,10 +8422,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B329" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>6</v>
@@ -8370,10 +8436,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B330" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -8384,10 +8450,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B331" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>6</v>
@@ -8398,10 +8464,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B332" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>6</v>
@@ -8412,10 +8478,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B333" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>6</v>
@@ -8426,10 +8492,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B334" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>6</v>
@@ -8440,10 +8506,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B335" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>6</v>
@@ -8454,10 +8520,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B336" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>6</v>
@@ -8468,10 +8534,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B337" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>6</v>
@@ -8482,10 +8548,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B338" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>6</v>
@@ -8496,10 +8562,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B339" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>6</v>
@@ -8510,10 +8576,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="B340" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>6</v>
@@ -8524,10 +8590,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="B341" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>6</v>
@@ -8538,10 +8604,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="B342" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>6</v>
@@ -8552,10 +8618,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="B343" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>6</v>
@@ -8566,10 +8632,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="B344" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>6</v>
@@ -8580,10 +8646,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="B345" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>6</v>
@@ -8594,10 +8660,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="B346" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>6</v>
@@ -8608,10 +8674,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="B347" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>6</v>
@@ -8622,10 +8688,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="B348" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>6</v>
@@ -8636,10 +8702,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B349" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>6</v>
@@ -8650,10 +8716,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="B350" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>6</v>
@@ -8664,10 +8730,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="B351" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>6</v>
@@ -8678,10 +8744,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B352" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>6</v>
@@ -8692,10 +8758,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B353" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>6</v>
@@ -8706,10 +8772,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B354" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>6</v>
@@ -8720,10 +8786,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="B355" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>6</v>
@@ -8734,10 +8800,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="B356" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>6</v>
@@ -8748,10 +8814,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="B357" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>6</v>
@@ -8762,10 +8828,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="B358" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>6</v>
@@ -8776,10 +8842,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B359" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>6</v>
@@ -8790,10 +8856,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="B360" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>6</v>
@@ -8804,10 +8870,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="B361" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>6</v>
@@ -8818,10 +8884,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="B362" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -8832,10 +8898,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="B363" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>6</v>
@@ -8846,10 +8912,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="B364" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>6</v>
@@ -8860,10 +8926,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="B365" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>6</v>
@@ -8874,10 +8940,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="B366" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>6</v>
@@ -8888,10 +8954,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="B367" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>6</v>
@@ -8902,10 +8968,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B368" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>6</v>
@@ -8916,10 +8982,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="B369" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>6</v>
@@ -8930,10 +8996,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="B370" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>6</v>
@@ -8944,10 +9010,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="B371" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>6</v>
@@ -8958,10 +9024,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="B372" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>6</v>
@@ -8972,10 +9038,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="B373" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>6</v>
@@ -8986,10 +9052,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="B374" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>6</v>
@@ -9000,10 +9066,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="B375" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>6</v>
@@ -9014,10 +9080,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="B376" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>6</v>
@@ -9028,10 +9094,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="B377" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>6</v>
@@ -9042,10 +9108,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B378" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>6</v>
@@ -9056,10 +9122,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B379" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>6</v>
@@ -9070,10 +9136,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="B380" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>6</v>
@@ -9084,10 +9150,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="B381" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>6</v>
@@ -9098,10 +9164,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="B382" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>6</v>
@@ -9112,10 +9178,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B383" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>6</v>
@@ -9126,10 +9192,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B384" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>6</v>
@@ -9140,10 +9206,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B385" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>6</v>
@@ -9154,10 +9220,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B386" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>6</v>
@@ -9168,10 +9234,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="B387" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>6</v>
@@ -9182,10 +9248,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="B388" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>6</v>
@@ -9196,10 +9262,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="B389" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>6</v>
@@ -9210,10 +9276,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="B390" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>6</v>
@@ -9224,10 +9290,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="B391" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>6</v>
@@ -9238,10 +9304,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B392" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>6</v>
@@ -9252,10 +9318,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B393" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>6</v>
@@ -9266,10 +9332,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="B394" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>6</v>
@@ -9280,10 +9346,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="B395" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>6</v>
@@ -9294,10 +9360,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B396" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>6</v>
@@ -9308,10 +9374,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B397" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>6</v>
@@ -9322,10 +9388,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="B398" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>6</v>
@@ -9336,10 +9402,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="B399" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>6</v>
@@ -9350,10 +9416,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="B400" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>6</v>
@@ -9364,10 +9430,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="B401" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>6</v>
@@ -9378,10 +9444,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="B402" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>6</v>
@@ -9392,10 +9458,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="B403" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>6</v>
@@ -9406,10 +9472,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="B404" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>6</v>
@@ -9420,10 +9486,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="B405" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>6</v>
@@ -9434,10 +9500,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="B406" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>6</v>
@@ -9448,10 +9514,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B407" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>6</v>
@@ -9462,10 +9528,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="B408" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>6</v>
@@ -9476,10 +9542,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B409" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>6</v>
@@ -9490,10 +9556,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B410" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>6</v>
@@ -9504,10 +9570,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B411" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>6</v>
@@ -9518,10 +9584,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B412" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>6</v>
@@ -9532,10 +9598,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B413" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>6</v>
@@ -9546,10 +9612,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B414" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>6</v>
@@ -9560,10 +9626,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B415" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>6</v>
@@ -9574,10 +9640,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="B416" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>6</v>
@@ -9588,10 +9654,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="B417" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>6</v>
@@ -9602,10 +9668,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="B418" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>6</v>
@@ -9616,10 +9682,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B419" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -9630,10 +9696,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="B420" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>6</v>
@@ -9644,10 +9710,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="B421" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>6</v>
@@ -9658,10 +9724,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="B422" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>6</v>
@@ -9672,10 +9738,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="B423" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>6</v>
@@ -9686,10 +9752,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B424" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>6</v>
@@ -9700,10 +9766,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="B425" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>6</v>
@@ -9714,10 +9780,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="B426" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>6</v>
@@ -9728,10 +9794,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="B427" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>6</v>
@@ -9742,10 +9808,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="B428" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -9756,10 +9822,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="B429" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>6</v>
@@ -9770,10 +9836,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B430" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>6</v>
@@ -9784,10 +9850,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="B431" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>6</v>
@@ -9798,10 +9864,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="B432" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>6</v>
@@ -9812,10 +9878,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="B433" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>6</v>
@@ -9826,10 +9892,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="B434" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>6</v>
@@ -9840,10 +9906,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="B435" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>6</v>
@@ -9854,10 +9920,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="B436" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>6</v>
@@ -9868,10 +9934,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="B437" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>6</v>
@@ -9882,10 +9948,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="B438" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>6</v>
@@ -9896,10 +9962,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="B439" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>6</v>
@@ -9910,10 +9976,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="B440" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>6</v>
@@ -9924,10 +9990,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="B441" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>6</v>
@@ -9938,10 +10004,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="B442" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>6</v>
@@ -9952,10 +10018,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="B443" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>6</v>
@@ -9966,10 +10032,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B444" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>6</v>
@@ -9980,10 +10046,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B445" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>6</v>
@@ -9994,10 +10060,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="B446" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>6</v>
@@ -10008,10 +10074,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="B447" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>6</v>
@@ -10022,10 +10088,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="B448" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>6</v>
@@ -10036,10 +10102,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="B449" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>6</v>
@@ -10050,10 +10116,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="B450" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>6</v>
@@ -10064,10 +10130,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="B451" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>6</v>
@@ -10078,10 +10144,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="B452" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>6</v>
@@ -10092,10 +10158,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="B453" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>6</v>
@@ -10106,10 +10172,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="B454" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>6</v>
@@ -10120,10 +10186,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="B455" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>6</v>
@@ -10134,10 +10200,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="B456" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>6</v>
@@ -10148,10 +10214,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="B457" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>6</v>
@@ -10162,10 +10228,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="B458" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>6</v>
@@ -10176,10 +10242,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="B459" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>6</v>
@@ -10190,10 +10256,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>993</v>
+        <v>1003</v>
       </c>
       <c r="B460" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>6</v>
@@ -10204,10 +10270,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B461" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>6</v>
@@ -10218,10 +10284,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="B462" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>6</v>
@@ -10232,10 +10298,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
       <c r="B463" t="s">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>6</v>
@@ -10246,10 +10312,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="B464" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>6</v>
@@ -10260,10 +10326,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B465" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>6</v>
@@ -10274,10 +10340,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="B466" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>6</v>
@@ -10288,10 +10354,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="B467" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>6</v>
@@ -10302,10 +10368,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="B468" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>6</v>
@@ -10316,10 +10382,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="B469" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>6</v>
@@ -10330,10 +10396,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B470" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>6</v>
@@ -10344,10 +10410,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="B471" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>6</v>
@@ -10358,10 +10424,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="B472" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>6</v>
@@ -10372,10 +10438,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="B473" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>6</v>
@@ -10386,10 +10452,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B474" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>6</v>
@@ -10400,10 +10466,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B475" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>6</v>
@@ -10414,10 +10480,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B476" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>6</v>
@@ -10428,10 +10494,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B477" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>6</v>
@@ -10442,10 +10508,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B478" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -10498,10 +10564,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B482" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>6</v>
@@ -10512,10 +10578,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B483" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>6</v>
@@ -10526,10 +10592,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="B484" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>6</v>
@@ -10540,10 +10606,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="B485" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>6</v>
@@ -10554,10 +10620,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="B486" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>6</v>
@@ -10568,10 +10634,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="B487" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>6</v>
@@ -10582,10 +10648,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="B488" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>6</v>
@@ -10596,10 +10662,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="B489" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>6</v>
@@ -10610,10 +10676,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="B490" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>6</v>
@@ -10624,10 +10690,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="B491" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>6</v>
@@ -10638,10 +10704,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="B492" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>6</v>
@@ -10652,10 +10718,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B493" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>6</v>
@@ -10666,10 +10732,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="B494" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>6</v>
@@ -10680,10 +10746,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="B495" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>6</v>
@@ -10694,10 +10760,10 @@
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B496" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>6</v>
@@ -10708,10 +10774,10 @@
     </row>
     <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B497" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>6</v>
@@ -10722,10 +10788,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B498" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>6</v>
@@ -10736,10 +10802,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B499" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>6</v>
@@ -10750,10 +10816,10 @@
     </row>
     <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B500" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>6</v>
@@ -10764,10 +10830,10 @@
     </row>
     <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B501" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>6</v>
@@ -10778,10 +10844,10 @@
     </row>
     <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B502" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>6</v>
@@ -10792,10 +10858,10 @@
     </row>
     <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B503" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>6</v>
@@ -10806,10 +10872,10 @@
     </row>
     <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B504" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>6</v>
@@ -10820,10 +10886,10 @@
     </row>
     <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B505" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>6</v>
@@ -10834,10 +10900,10 @@
     </row>
     <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B506" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>6</v>
@@ -10848,10 +10914,10 @@
     </row>
     <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="B507" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>6</v>
@@ -10862,10 +10928,10 @@
     </row>
     <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="B508" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>6</v>
@@ -10876,10 +10942,10 @@
     </row>
     <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="B509" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>6</v>
@@ -10890,10 +10956,10 @@
     </row>
     <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="B510" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>6</v>
@@ -10904,10 +10970,10 @@
     </row>
     <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B511" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>6</v>
@@ -10918,10 +10984,10 @@
     </row>
     <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="B512" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>6</v>
@@ -10930,12 +10996,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B513" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>6</v>
@@ -10944,12 +11010,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="B514" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>6</v>
@@ -10958,12 +11024,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="B515" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>6</v>
@@ -10972,12 +11038,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B516" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>6</v>
@@ -10986,54 +11052,54 @@
         <v>10</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>5</v>
+        <v>1125</v>
       </c>
       <c r="B517" t="s">
-        <v>5</v>
+        <v>1126</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E517" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="518" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D517" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>103</v>
+        <v>1127</v>
       </c>
       <c r="B518" t="s">
-        <v>104</v>
+        <v>1128</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E518" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="519" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D518" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>105</v>
+        <v>1129</v>
       </c>
       <c r="B519" t="s">
-        <v>106</v>
+        <v>1130</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E519" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="520" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D519" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>115</v>
+        <v>1131</v>
       </c>
       <c r="B520" t="s">
-        <v>116</v>
+        <v>1132</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>6</v>
@@ -11042,91 +11108,91 @@
         <v>10</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>119</v>
+        <v>1133</v>
       </c>
       <c r="B521" t="s">
-        <v>120</v>
+        <v>1134</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E521" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="522" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D521" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C522" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D522" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C523" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D523" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D524" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C525" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D525" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
         <v>123</v>
       </c>
-      <c r="B522" t="s">
+      <c r="B526" t="s">
         <v>124</v>
       </c>
-      <c r="C522" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E522" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="523" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A523" t="s">
-        <v>183</v>
-      </c>
-      <c r="B523" t="s">
-        <v>184</v>
-      </c>
-      <c r="C523" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E523" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="524" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A524" t="s">
-        <v>185</v>
-      </c>
-      <c r="B524" t="s">
-        <v>186</v>
-      </c>
-      <c r="C524" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E524" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="525" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A525" t="s">
-        <v>205</v>
-      </c>
-      <c r="B525" t="s">
-        <v>206</v>
-      </c>
-      <c r="C525" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E525" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="526" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A526" t="s">
-        <v>223</v>
-      </c>
-      <c r="B526" t="s">
-        <v>224</v>
-      </c>
       <c r="C526" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E526" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="527" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D526" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>225</v>
       </c>
@@ -11136,86 +11202,86 @@
       <c r="C527" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E527" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="528" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D527" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="B528" t="s">
-        <v>228</v>
+        <v>348</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E528" t="s">
-        <v>7</v>
+      <c r="D528" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="529" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>229</v>
+        <v>429</v>
       </c>
       <c r="B529" t="s">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E529" t="s">
-        <v>7</v>
+      <c r="D529" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="530" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>251</v>
+        <v>525</v>
       </c>
       <c r="B530" t="s">
-        <v>252</v>
+        <v>526</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E530" t="s">
-        <v>7</v>
+      <c r="D530" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="531" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>259</v>
+        <v>637</v>
       </c>
       <c r="B531" t="s">
-        <v>260</v>
+        <v>638</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E531" t="s">
-        <v>7</v>
+      <c r="D531" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="532" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>269</v>
+        <v>651</v>
       </c>
       <c r="B532" t="s">
-        <v>270</v>
+        <v>652</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E532" t="s">
-        <v>7</v>
+      <c r="D532" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="533" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>271</v>
+        <v>745</v>
       </c>
       <c r="B533" t="s">
-        <v>272</v>
+        <v>746</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>6</v>
@@ -11226,52 +11292,52 @@
     </row>
     <row r="534" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>293</v>
+        <v>939</v>
       </c>
       <c r="B534" t="s">
-        <v>294</v>
+        <v>940</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E534" t="s">
-        <v>7</v>
+      <c r="D534" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="535" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>335</v>
+        <v>971</v>
       </c>
       <c r="B535" t="s">
-        <v>336</v>
+        <v>972</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E535" t="s">
-        <v>7</v>
+      <c r="D535" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="536" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>341</v>
+        <v>1049</v>
       </c>
       <c r="B536" t="s">
-        <v>342</v>
+        <v>1050</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E536" t="s">
-        <v>7</v>
+      <c r="D536" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>385</v>
+        <v>5</v>
       </c>
       <c r="B537" t="s">
-        <v>386</v>
+        <v>5</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -11282,10 +11348,10 @@
     </row>
     <row r="538" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>397</v>
+        <v>103</v>
       </c>
       <c r="B538" t="s">
-        <v>398</v>
+        <v>104</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>6</v>
@@ -11296,24 +11362,24 @@
     </row>
     <row r="539" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>433</v>
+        <v>105</v>
       </c>
       <c r="B539" t="s">
-        <v>434</v>
+        <v>106</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D539" t="s">
-        <v>10</v>
+      <c r="E539" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="540" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>571</v>
+        <v>119</v>
       </c>
       <c r="B540" t="s">
-        <v>572</v>
+        <v>120</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>6</v>
@@ -11324,10 +11390,10 @@
     </row>
     <row r="541" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>601</v>
+        <v>125</v>
       </c>
       <c r="B541" t="s">
-        <v>602</v>
+        <v>126</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -11338,10 +11404,10 @@
     </row>
     <row r="542" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>625</v>
+        <v>185</v>
       </c>
       <c r="B542" t="s">
-        <v>626</v>
+        <v>186</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>6</v>
@@ -11352,10 +11418,10 @@
     </row>
     <row r="543" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>637</v>
+        <v>187</v>
       </c>
       <c r="B543" t="s">
-        <v>638</v>
+        <v>188</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>6</v>
@@ -11366,10 +11432,10 @@
     </row>
     <row r="544" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>697</v>
+        <v>207</v>
       </c>
       <c r="B544" t="s">
-        <v>698</v>
+        <v>208</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>6</v>
@@ -11380,10 +11446,10 @@
     </row>
     <row r="545" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>715</v>
+        <v>227</v>
       </c>
       <c r="B545" t="s">
-        <v>716</v>
+        <v>228</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>6</v>
@@ -11394,24 +11460,24 @@
     </row>
     <row r="546" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>827</v>
+        <v>229</v>
       </c>
       <c r="B546" t="s">
-        <v>828</v>
+        <v>230</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E546" t="s">
-        <v>7</v>
+      <c r="D546" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="547" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>849</v>
+        <v>231</v>
       </c>
       <c r="B547" t="s">
-        <v>850</v>
+        <v>232</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>6</v>
@@ -11422,24 +11488,24 @@
     </row>
     <row r="548" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>879</v>
+        <v>233</v>
       </c>
       <c r="B548" t="s">
-        <v>880</v>
+        <v>234</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E548" t="s">
-        <v>7</v>
+      <c r="D548" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="549" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>889</v>
+        <v>255</v>
       </c>
       <c r="B549" t="s">
-        <v>890</v>
+        <v>256</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>6</v>
@@ -11450,10 +11516,10 @@
     </row>
     <row r="550" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>893</v>
+        <v>263</v>
       </c>
       <c r="B550" t="s">
-        <v>894</v>
+        <v>264</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>6</v>
@@ -11464,10 +11530,10 @@
     </row>
     <row r="551" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>955</v>
+        <v>273</v>
       </c>
       <c r="B551" t="s">
-        <v>956</v>
+        <v>274</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>6</v>
@@ -11478,52 +11544,52 @@
     </row>
     <row r="552" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1003</v>
+        <v>297</v>
       </c>
       <c r="B552" t="s">
-        <v>1004</v>
+        <v>298</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D552" t="s">
-        <v>10</v>
+      <c r="E552" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="553" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1005</v>
+        <v>339</v>
       </c>
       <c r="B553" t="s">
-        <v>1006</v>
+        <v>340</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D553" t="s">
-        <v>10</v>
+      <c r="E553" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="554" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1025</v>
+        <v>345</v>
       </c>
       <c r="B554" t="s">
-        <v>1026</v>
+        <v>346</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D554" t="s">
-        <v>10</v>
+      <c r="E554" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="555" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1027</v>
+        <v>391</v>
       </c>
       <c r="B555" t="s">
-        <v>1028</v>
+        <v>392</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>6</v>
@@ -11534,10 +11600,10 @@
     </row>
     <row r="556" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1039</v>
+        <v>403</v>
       </c>
       <c r="B556" t="s">
-        <v>1040</v>
+        <v>404</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>6</v>
@@ -11548,24 +11614,24 @@
     </row>
     <row r="557" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1069</v>
+        <v>611</v>
       </c>
       <c r="B557" t="s">
-        <v>1070</v>
+        <v>612</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D557" t="s">
-        <v>10</v>
+      <c r="E557" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="558" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1077</v>
+        <v>635</v>
       </c>
       <c r="B558" t="s">
-        <v>1078</v>
+        <v>636</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>6</v>
@@ -11574,19 +11640,173 @@
         <v>7</v>
       </c>
     </row>
+    <row r="559" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>649</v>
+      </c>
+      <c r="B559" t="s">
+        <v>650</v>
+      </c>
+      <c r="C559" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E559" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>711</v>
+      </c>
+      <c r="B560" t="s">
+        <v>712</v>
+      </c>
+      <c r="C560" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E560" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>843</v>
+      </c>
+      <c r="B561" t="s">
+        <v>844</v>
+      </c>
+      <c r="C561" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E561" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>865</v>
+      </c>
+      <c r="B562" t="s">
+        <v>866</v>
+      </c>
+      <c r="C562" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E562" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>895</v>
+      </c>
+      <c r="B563" t="s">
+        <v>896</v>
+      </c>
+      <c r="C563" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E563" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>905</v>
+      </c>
+      <c r="B564" t="s">
+        <v>906</v>
+      </c>
+      <c r="C564" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E564" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>909</v>
+      </c>
+      <c r="B565" t="s">
+        <v>910</v>
+      </c>
+      <c r="C565" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E565" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>975</v>
+      </c>
+      <c r="B566" t="s">
+        <v>976</v>
+      </c>
+      <c r="C566" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E566" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C567" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E567" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C568" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E568" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C569" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E569" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E558">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E569">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D558" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D569" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C517" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C537" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
@@ -11634,18 +11854,18 @@
     <hyperlink ref="C46" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
     <hyperlink ref="C47" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
     <hyperlink ref="C48" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C518" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C519" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C538" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C539" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
     <hyperlink ref="C49" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
     <hyperlink ref="C50" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
     <hyperlink ref="C51" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
     <hyperlink ref="C52" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C520" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C53" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C521" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C54" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C522" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C55" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C53" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C54" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C540" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C55" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C526" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C541" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
     <hyperlink ref="C56" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
     <hyperlink ref="C57" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
     <hyperlink ref="C58" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
@@ -11674,9 +11894,9 @@
     <hyperlink ref="C81" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
     <hyperlink ref="C82" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
     <hyperlink ref="C83" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C523" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C524" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C84" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C84" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C542" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C543" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
     <hyperlink ref="C85" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
     <hyperlink ref="C86" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
     <hyperlink ref="C87" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
@@ -11685,8 +11905,8 @@
     <hyperlink ref="C90" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
     <hyperlink ref="C91" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
     <hyperlink ref="C92" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C525" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C93" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C93" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C544" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
     <hyperlink ref="C94" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
     <hyperlink ref="C95" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
     <hyperlink ref="C96" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
@@ -11694,32 +11914,32 @@
     <hyperlink ref="C98" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
     <hyperlink ref="C99" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
     <hyperlink ref="C100" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C526" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C101" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
     <hyperlink ref="C527" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C528" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="C529" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C101" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C102" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C103" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="C104" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C105" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="C106" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C107" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="C108" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="C109" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="C110" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="C530" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="C545" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C546" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="C547" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C548" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C102" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C103" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="C104" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C105" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="C106" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C107" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="C108" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="C109" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="C110" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
     <hyperlink ref="C111" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C112" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C113" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C531" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C549" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C112" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C113" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
     <hyperlink ref="C114" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C115" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="C116" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C117" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="C532" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C533" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="C118" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="C550" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C115" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C116" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C117" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="C118" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C551" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
     <hyperlink ref="C119" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
     <hyperlink ref="C120" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
     <hyperlink ref="C121" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
@@ -11729,9 +11949,9 @@
     <hyperlink ref="C125" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
     <hyperlink ref="C126" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
     <hyperlink ref="C127" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C534" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C128" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C129" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C128" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C129" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C552" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
     <hyperlink ref="C130" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
     <hyperlink ref="C131" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
     <hyperlink ref="C132" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
@@ -11750,401 +11970,411 @@
     <hyperlink ref="C145" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
     <hyperlink ref="C146" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
     <hyperlink ref="C147" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C535" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C148" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C149" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C536" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C150" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C151" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C152" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C153" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C154" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C155" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C156" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C157" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C158" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C159" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C160" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C161" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C162" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C163" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C164" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C165" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C166" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C167" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C168" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C169" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C170" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C537" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C148" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C149" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C553" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C150" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="C151" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C554" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C528" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C152" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C153" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C154" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C155" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C156" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C157" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C158" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C159" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C160" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C161" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C162" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C163" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C164" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C165" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C166" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C167" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C168" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C169" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C170" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
     <hyperlink ref="C171" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
     <hyperlink ref="C172" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C173" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C174" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C175" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C538" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C555" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C173" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C174" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C175" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
     <hyperlink ref="C176" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
     <hyperlink ref="C177" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C178" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C179" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C180" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C181" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C182" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C183" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C184" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="C185" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C186" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C187" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C188" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C189" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C190" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C191" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C192" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C539" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C193" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C194" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C195" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C196" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C197" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C198" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C199" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C200" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C201" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C202" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C203" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C204" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C205" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C206" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C207" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C208" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C209" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C210" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C211" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C212" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C213" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="C214" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="C215" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="C216" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="C217" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="C218" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="C219" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="C220" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="C221" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="C222" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="C223" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="C224" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="C225" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="C226" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="C227" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="C228" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="C229" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="C230" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="C231" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="C232" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="C233" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="C234" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="C235" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="C236" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="C237" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="C238" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="C239" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="C240" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="C241" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="C242" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="C243" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="C244" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="C245" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="C246" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="C247" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="C248" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="C249" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="C250" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="C251" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="C252" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="C253" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="C254" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="C255" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="C256" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="C257" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="C258" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="C259" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="C260" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="C540" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="C261" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="C262" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="C263" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="C264" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="C265" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="C266" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="C267" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="C268" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="C269" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="C270" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="C271" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="C272" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="C273" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C274" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C541" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C556" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C178" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C179" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C180" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C181" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C182" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C183" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C184" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C185" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C186" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C187" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C188" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C189" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C529" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C190" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C191" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C192" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C193" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C194" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C195" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C196" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C197" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C198" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C199" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C200" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C201" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C202" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C203" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C204" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C205" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C206" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C207" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C208" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C209" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C210" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C211" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C212" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C213" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="C214" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="C215" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="C216" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="C217" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="C218" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="C219" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="C220" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="C221" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="C222" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C223" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="C224" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="C225" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="C226" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="C227" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="C228" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="C229" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="C230" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="C231" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="C232" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C233" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="C234" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="C235" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="C236" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="C530" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C237" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="C238" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="C239" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="C240" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="C241" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="C242" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="C243" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="C244" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="C245" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="C246" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="C247" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="C248" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="C249" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="C250" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="C251" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C252" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="C253" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="C254" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="C255" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="C256" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C257" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="C258" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="C259" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="C260" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="C261" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C262" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="C263" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="C264" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="C265" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="C266" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C267" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="C268" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="C269" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="C270" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="C271" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C272" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="C273" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C274" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
     <hyperlink ref="C275" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
     <hyperlink ref="C276" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
     <hyperlink ref="C277" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
     <hyperlink ref="C278" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C279" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C280" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C281" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C282" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C283" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C284" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C285" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C542" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C557" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C279" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C280" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C281" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C282" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C283" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C284" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C285" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
     <hyperlink ref="C286" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
     <hyperlink ref="C287" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
     <hyperlink ref="C288" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
     <hyperlink ref="C289" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C290" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C543" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C291" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C292" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C293" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C294" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="C295" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C296" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C297" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C298" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C299" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C300" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C301" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C302" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C303" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C304" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C305" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C306" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C307" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C308" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C309" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C310" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C311" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C312" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C313" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C314" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C315" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C316" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C317" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C318" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C319" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C544" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C320" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C321" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C322" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C323" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C324" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="C325" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="C326" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C327" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C545" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C328" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C329" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C330" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="C331" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C332" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C333" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C334" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C335" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C336" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C337" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C338" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C339" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C340" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C341" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C342" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C343" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C344" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C345" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C346" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C347" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C348" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C349" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C350" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C351" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C352" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C353" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C354" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C355" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C356" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C357" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C358" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C359" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C360" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C361" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C362" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C363" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C364" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C365" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C366" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C367" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C368" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C369" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C370" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C371" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C372" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C373" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C374" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C375" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C376" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C377" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C378" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C379" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C380" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C381" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C382" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C546" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C383" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C384" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C385" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C386" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C387" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C388" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C389" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C390" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C391" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C392" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C547" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C393" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C394" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C395" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C396" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C397" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C398" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C399" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C400" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C401" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C402" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C403" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C404" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C405" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C406" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C548" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C407" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C408" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C409" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C410" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C549" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C411" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C550" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C412" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C413" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C414" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C415" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C416" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C417" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C418" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C419" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C420" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C421" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C422" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C423" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C424" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C425" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C426" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C427" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C428" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C429" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C430" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C431" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C432" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C433" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C434" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C435" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C436" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C437" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C438" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C439" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C440" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C441" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C551" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C442" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C443" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C444" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C445" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C446" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C447" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C448" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C449" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C450" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C451" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C452" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C453" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C454" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C455" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C456" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C457" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C458" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C459" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C460" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C461" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C462" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C463" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C464" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C552" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C553" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C465" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C466" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C467" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C468" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C469" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C470" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C471" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="C472" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C473" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="C554" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="C555" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C474" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="C475" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C476" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C477" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C478" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C556" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C558" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C531" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C290" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C291" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C292" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C293" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C294" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="C559" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C532" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C295" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C296" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C297" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C298" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C299" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C300" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C301" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C302" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C303" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C304" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C305" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C306" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C307" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C308" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C309" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C310" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C311" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C312" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C313" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C314" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C315" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C316" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C317" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C318" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C319" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C320" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C321" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C322" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C323" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C560" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C324" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C325" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C326" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C327" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C328" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C329" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C330" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C331" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C332" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C333" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C334" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C335" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C336" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C337" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C338" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C339" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C533" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C340" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C341" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C342" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C343" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C344" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C345" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C346" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C347" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C348" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C349" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C350" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C351" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C352" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C353" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C354" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C355" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C356" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C357" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C358" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C359" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C360" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C361" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C362" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C363" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C364" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C365" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C366" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C367" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C368" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C369" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C370" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C371" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C372" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C373" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C374" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C375" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C376" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C377" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C378" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C379" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C380" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C381" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C382" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C383" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C384" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C385" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C386" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C387" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C561" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C388" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C389" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C390" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C391" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C392" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C393" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C394" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C395" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C396" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C397" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C562" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C398" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C399" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C400" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C401" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C402" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C403" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C404" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C405" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C406" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C407" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C408" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C409" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C410" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C411" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C563" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C412" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C413" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C414" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C415" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C564" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C416" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C565" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C417" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C418" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C419" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C420" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C421" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C422" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C423" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C424" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C425" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C426" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C427" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C428" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C429" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C430" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C534" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C431" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C432" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C433" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C434" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C435" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C436" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C437" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C438" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C439" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C440" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C441" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C442" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C443" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C444" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C445" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C535" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C446" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C566" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C447" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C448" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C449" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C450" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C451" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C452" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C453" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C454" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C455" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C456" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C457" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C458" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C459" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C460" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C461" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C462" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C463" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C464" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C465" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C466" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C467" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C468" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C469" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C470" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C471" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C472" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C473" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C474" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C475" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C476" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C477" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C478" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
     <hyperlink ref="C479" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
     <hyperlink ref="C480" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
     <hyperlink ref="C481" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="C482" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="C483" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="C484" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="C485" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="C486" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="C487" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C488" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C489" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="C490" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="C491" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="C492" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="C557" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="C493" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="C494" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="C495" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="C558" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="C496" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="C497" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="C498" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="C499" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="C500" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C501" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C502" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C503" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C504" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="C505" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="C506" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="C507" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
-    <hyperlink ref="C508" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
-    <hyperlink ref="C509" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
-    <hyperlink ref="C510" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
-    <hyperlink ref="C511" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
-    <hyperlink ref="C512" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
-    <hyperlink ref="C513" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
-    <hyperlink ref="C514" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
-    <hyperlink ref="C515" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
-    <hyperlink ref="C516" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C567" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="C536" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="C482" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="C483" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="C484" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="C485" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C486" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C568" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="C487" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="C488" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="C489" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="C490" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="C491" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="C492" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="C493" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="C494" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="C495" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="C496" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="C497" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="C498" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="C499" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C500" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C501" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C502" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C503" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C504" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="C569" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="C505" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C506" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="C507" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="C508" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C509" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="C510" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C511" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="C512" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="C513" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="C514" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C515" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="C516" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="C517" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="C518" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="C519" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="C520" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="C521" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C522" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="C523" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C524" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="C525" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId558"/>
 </worksheet>
 </file>
--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640BDF7D-A705-41E4-958D-1488EC27D8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD46A964-D719-44B6-A5E0-392CF3B42D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="1213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="1221">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -196,6 +196,12 @@
     <t>Alt forladt</t>
   </si>
   <si>
+    <t>alt på spil</t>
+  </si>
+  <si>
+    <t>Alt på spil</t>
+  </si>
+  <si>
     <t>alvin og de frække jordegern</t>
   </si>
   <si>
@@ -292,6 +298,12 @@
     <t>Bad Guys 2 - de er super barske</t>
   </si>
   <si>
+    <t>badehotellet</t>
+  </si>
+  <si>
+    <t>Badehotellet</t>
+  </si>
+  <si>
     <t>bag stjernerne</t>
   </si>
   <si>
@@ -1294,6 +1306,12 @@
     <t>Grusomme Meg 3</t>
   </si>
   <si>
+    <t>grusomme mig</t>
+  </si>
+  <si>
+    <t>Grusomme mig</t>
+  </si>
+  <si>
     <t>grusomme mig 3</t>
   </si>
   <si>
@@ -1700,6 +1718,12 @@
   </si>
   <si>
     <t>Ingemann, Fyn &amp; Lolland-Falster</t>
+  </si>
+  <si>
+    <t>ingen kender dagen</t>
+  </si>
+  <si>
+    <t>Ingen kender dagen</t>
   </si>
   <si>
     <t>inspector sun og den sorte enkes forbandelse</t>
@@ -4025,7 +4049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E604"/>
+  <dimension ref="A1:E608"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -4138,10 +4162,10 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>6</v>
@@ -4152,10 +4176,10 @@
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>6</v>
@@ -4166,10 +4190,10 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>6</v>
@@ -4180,10 +4204,10 @@
     </row>
     <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>6</v>
@@ -4194,10 +4218,10 @@
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>6</v>
@@ -4208,10 +4232,10 @@
     </row>
     <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>6</v>
@@ -4222,10 +4246,10 @@
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>6</v>
@@ -4236,10 +4260,10 @@
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>6</v>
@@ -4250,10 +4274,10 @@
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>6</v>
@@ -4264,10 +4288,10 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>6</v>
@@ -4278,10 +4302,10 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>6</v>
@@ -4292,10 +4316,10 @@
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>6</v>
@@ -4306,10 +4330,10 @@
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>6</v>
@@ -4320,10 +4344,10 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>6</v>
@@ -4334,10 +4358,10 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>6</v>
@@ -4348,10 +4372,10 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>6</v>
@@ -4362,10 +4386,10 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>6</v>
@@ -4376,10 +4400,10 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>6</v>
@@ -4390,10 +4414,10 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>6</v>
@@ -4404,10 +4428,10 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>6</v>
@@ -4418,10 +4442,10 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>6</v>
@@ -4432,10 +4456,10 @@
     </row>
     <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>6</v>
@@ -4446,10 +4470,10 @@
     </row>
     <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>6</v>
@@ -4460,10 +4484,10 @@
     </row>
     <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>6</v>
@@ -4474,10 +4498,10 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
@@ -4488,10 +4512,10 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>6</v>
@@ -4502,10 +4526,10 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>6</v>
@@ -4516,10 +4540,10 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>6</v>
@@ -4530,10 +4554,10 @@
     </row>
     <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>6</v>
@@ -4544,10 +4568,10 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>6</v>
@@ -4558,10 +4582,10 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>6</v>
@@ -4572,10 +4596,10 @@
     </row>
     <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>6</v>
@@ -4586,10 +4610,10 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>6</v>
@@ -4600,10 +4624,10 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
@@ -4614,10 +4638,10 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -4628,10 +4652,10 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6</v>
@@ -4642,10 +4666,10 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -4656,10 +4680,10 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
@@ -4670,10 +4694,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>6</v>
@@ -4684,10 +4708,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6</v>
@@ -4698,10 +4722,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6</v>
@@ -4712,10 +4736,10 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -4726,10 +4750,10 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>6</v>
@@ -4740,10 +4764,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>6</v>
@@ -4754,10 +4778,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
@@ -4768,10 +4792,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
@@ -4782,10 +4806,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
@@ -4796,10 +4820,10 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B55" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>6</v>
@@ -4810,10 +4834,10 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B56" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>6</v>
@@ -4824,10 +4848,10 @@
     </row>
     <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>6</v>
@@ -4838,10 +4862,10 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>6</v>
@@ -4852,10 +4876,10 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>6</v>
@@ -4866,10 +4890,10 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>6</v>
@@ -4880,10 +4904,10 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>6</v>
@@ -4894,10 +4918,10 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>6</v>
@@ -4908,10 +4932,10 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>6</v>
@@ -4922,10 +4946,10 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>6</v>
@@ -4936,10 +4960,10 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -4950,10 +4974,10 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>6</v>
@@ -4964,10 +4988,10 @@
     </row>
     <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>6</v>
@@ -4978,10 +5002,10 @@
     </row>
     <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>6</v>
@@ -4992,10 +5016,10 @@
     </row>
     <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>6</v>
@@ -5006,10 +5030,10 @@
     </row>
     <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>6</v>
@@ -5020,10 +5044,10 @@
     </row>
     <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>6</v>
@@ -5034,10 +5058,10 @@
     </row>
     <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>6</v>
@@ -5048,10 +5072,10 @@
     </row>
     <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B73" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>6</v>
@@ -5062,10 +5086,10 @@
     </row>
     <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>6</v>
@@ -5076,10 +5100,10 @@
     </row>
     <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>6</v>
@@ -5090,10 +5114,10 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>6</v>
@@ -5104,10 +5128,10 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>6</v>
@@ -5118,10 +5142,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B78" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>6</v>
@@ -5132,10 +5156,10 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B79" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>6</v>
@@ -5146,10 +5170,10 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -5160,10 +5184,10 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B81" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>6</v>
@@ -5174,10 +5198,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
@@ -5188,10 +5212,10 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>6</v>
@@ -5202,10 +5226,10 @@
     </row>
     <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B84" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>6</v>
@@ -5216,10 +5240,10 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B85" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>6</v>
@@ -5230,10 +5254,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B86" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>6</v>
@@ -5244,10 +5268,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B87" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>6</v>
@@ -5258,10 +5282,10 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B88" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>6</v>
@@ -5272,10 +5296,10 @@
     </row>
     <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>6</v>
@@ -5286,10 +5310,10 @@
     </row>
     <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B90" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>6</v>
@@ -5300,10 +5324,10 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>6</v>
@@ -5314,10 +5338,10 @@
     </row>
     <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B92" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>6</v>
@@ -5328,10 +5352,10 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B93" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>6</v>
@@ -5342,10 +5366,10 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B94" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>6</v>
@@ -5356,10 +5380,10 @@
     </row>
     <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B95" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>6</v>
@@ -5370,10 +5394,10 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B96" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>6</v>
@@ -5384,10 +5408,10 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B97" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>6</v>
@@ -5398,10 +5422,10 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B98" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>6</v>
@@ -5412,10 +5436,10 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B99" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>6</v>
@@ -5426,10 +5450,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B100" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>6</v>
@@ -5440,10 +5464,10 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B101" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>6</v>
@@ -5454,10 +5478,10 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B102" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>6</v>
@@ -5468,10 +5492,10 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B103" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>6</v>
@@ -5482,10 +5506,10 @@
     </row>
     <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B104" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -5496,10 +5520,10 @@
     </row>
     <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B105" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>6</v>
@@ -5510,10 +5534,10 @@
     </row>
     <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B106" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>6</v>
@@ -5524,10 +5548,10 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B107" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>6</v>
@@ -5538,10 +5562,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B108" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>6</v>
@@ -5552,10 +5576,10 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B109" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>6</v>
@@ -5566,10 +5590,10 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B110" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>6</v>
@@ -5580,10 +5604,10 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B111" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>6</v>
@@ -5594,10 +5618,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>6</v>
@@ -5608,10 +5632,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>6</v>
@@ -5622,10 +5646,10 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B114" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>6</v>
@@ -5636,10 +5660,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B115" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>6</v>
@@ -5650,10 +5674,10 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B116" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>6</v>
@@ -5664,10 +5688,10 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B117" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>6</v>
@@ -5678,10 +5702,10 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B118" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>6</v>
@@ -5692,10 +5716,10 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B119" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>6</v>
@@ -5706,10 +5730,10 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B120" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>6</v>
@@ -5720,10 +5744,10 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B121" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>6</v>
@@ -5734,10 +5758,10 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B122" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>6</v>
@@ -5748,10 +5772,10 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B123" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>6</v>
@@ -5762,10 +5786,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B124" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -5776,10 +5800,10 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B125" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>6</v>
@@ -5790,10 +5814,10 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B126" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>6</v>
@@ -5804,10 +5828,10 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B127" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>6</v>
@@ -5818,10 +5842,10 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B128" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>6</v>
@@ -5832,10 +5856,10 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B129" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>6</v>
@@ -5846,10 +5870,10 @@
     </row>
     <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B130" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>6</v>
@@ -5860,10 +5884,10 @@
     </row>
     <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B131" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>6</v>
@@ -5874,10 +5898,10 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B132" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>6</v>
@@ -5888,10 +5912,10 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B133" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>6</v>
@@ -5902,10 +5926,10 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B134" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>6</v>
@@ -5916,10 +5940,10 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B135" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>6</v>
@@ -5930,10 +5954,10 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B136" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>6</v>
@@ -5944,10 +5968,10 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B137" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>6</v>
@@ -5958,10 +5982,10 @@
     </row>
     <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B138" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>6</v>
@@ -5972,10 +5996,10 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B139" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>6</v>
@@ -5986,10 +6010,10 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B140" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>6</v>
@@ -6000,10 +6024,10 @@
     </row>
     <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B141" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>6</v>
@@ -6014,10 +6038,10 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B142" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>6</v>
@@ -6028,10 +6052,10 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B143" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>6</v>
@@ -6042,10 +6066,10 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B144" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>6</v>
@@ -6056,10 +6080,10 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B145" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>6</v>
@@ -6070,10 +6094,10 @@
     </row>
     <row r="146" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B146" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>6</v>
@@ -6084,10 +6108,10 @@
     </row>
     <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B147" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>6</v>
@@ -6098,10 +6122,10 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B148" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>6</v>
@@ -6112,10 +6136,10 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B149" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>6</v>
@@ -6126,10 +6150,10 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B150" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>6</v>
@@ -6140,10 +6164,10 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B151" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>6</v>
@@ -6154,10 +6178,10 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B152" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>6</v>
@@ -6168,10 +6192,10 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B153" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>6</v>
@@ -6182,10 +6206,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B154" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>6</v>
@@ -6196,10 +6220,10 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B155" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>6</v>
@@ -6210,10 +6234,10 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B156" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>6</v>
@@ -6224,10 +6248,10 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B157" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>6</v>
@@ -6238,10 +6262,10 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B158" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>6</v>
@@ -6252,10 +6276,10 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B159" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>6</v>
@@ -6266,10 +6290,10 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B160" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>6</v>
@@ -6280,10 +6304,10 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B161" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>6</v>
@@ -6294,10 +6318,10 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B162" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>6</v>
@@ -6308,10 +6332,10 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B163" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>6</v>
@@ -6322,10 +6346,10 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B164" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>6</v>
@@ -6336,10 +6360,10 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="B165" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>6</v>
@@ -6350,10 +6374,10 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="B166" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>6</v>
@@ -6364,10 +6388,10 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B167" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>6</v>
@@ -6378,10 +6402,10 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B168" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>6</v>
@@ -6392,10 +6416,10 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B169" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>6</v>
@@ -6406,10 +6430,10 @@
     </row>
     <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B170" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>6</v>
@@ -6420,10 +6444,10 @@
     </row>
     <row r="171" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B171" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>6</v>
@@ -6434,10 +6458,10 @@
     </row>
     <row r="172" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B172" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>6</v>
@@ -6448,10 +6472,10 @@
     </row>
     <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B173" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>6</v>
@@ -6462,10 +6486,10 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B174" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>6</v>
@@ -6476,10 +6500,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B175" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>6</v>
@@ -6490,10 +6514,10 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B176" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>6</v>
@@ -6504,10 +6528,10 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B177" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>6</v>
@@ -6518,10 +6542,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B178" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>6</v>
@@ -6532,10 +6556,10 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B179" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>6</v>
@@ -6546,10 +6570,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B180" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>6</v>
@@ -6560,10 +6584,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B181" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>6</v>
@@ -6574,10 +6598,10 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B182" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>6</v>
@@ -6588,10 +6612,10 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B183" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -6602,10 +6626,10 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B184" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>6</v>
@@ -6616,10 +6640,10 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B185" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>6</v>
@@ -6630,10 +6654,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B186" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>6</v>
@@ -6644,10 +6668,10 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B187" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>6</v>
@@ -6658,10 +6682,10 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="B188" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>6</v>
@@ -6672,10 +6696,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B189" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -6686,10 +6710,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B190" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>6</v>
@@ -6700,10 +6724,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="B191" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>6</v>
@@ -6714,10 +6738,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="B192" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>6</v>
@@ -6728,10 +6752,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="B193" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>6</v>
@@ -6742,10 +6766,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B194" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>6</v>
@@ -6756,10 +6780,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="B195" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>6</v>
@@ -6770,10 +6794,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="B196" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>6</v>
@@ -6784,10 +6808,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B197" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>6</v>
@@ -6798,10 +6822,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B198" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>6</v>
@@ -6812,10 +6836,10 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B199" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>6</v>
@@ -6826,10 +6850,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B200" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>6</v>
@@ -6840,10 +6864,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B201" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>6</v>
@@ -6854,10 +6878,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B202" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>6</v>
@@ -6868,10 +6892,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B203" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>6</v>
@@ -6882,10 +6906,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B204" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>6</v>
@@ -6896,10 +6920,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B205" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>6</v>
@@ -6910,10 +6934,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B206" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>6</v>
@@ -6924,10 +6948,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B207" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>6</v>
@@ -6938,10 +6962,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B208" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>6</v>
@@ -6952,10 +6976,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B209" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>6</v>
@@ -6966,10 +6990,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B210" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>6</v>
@@ -6980,10 +7004,10 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B211" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>6</v>
@@ -6994,10 +7018,10 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B212" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>6</v>
@@ -7008,10 +7032,10 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B213" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>6</v>
@@ -7022,10 +7046,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B214" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>6</v>
@@ -7036,10 +7060,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B215" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>6</v>
@@ -7050,10 +7074,10 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B216" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>6</v>
@@ -7064,10 +7088,10 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B217" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>6</v>
@@ -7078,10 +7102,10 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B218" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>6</v>
@@ -7092,10 +7116,10 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B219" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>6</v>
@@ -7106,10 +7130,10 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B220" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>6</v>
@@ -7120,10 +7144,10 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B221" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>6</v>
@@ -7134,10 +7158,10 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B222" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>6</v>
@@ -7148,10 +7172,10 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B223" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>6</v>
@@ -7162,10 +7186,10 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="B224" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>6</v>
@@ -7176,10 +7200,10 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="B225" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -7190,10 +7214,10 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="B226" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>6</v>
@@ -7204,10 +7228,10 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="B227" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>6</v>
@@ -7218,10 +7242,10 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="B228" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>6</v>
@@ -7232,10 +7256,10 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="B229" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -7246,10 +7270,10 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="B230" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>6</v>
@@ -7260,10 +7284,10 @@
     </row>
     <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="B231" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>6</v>
@@ -7274,10 +7298,10 @@
     </row>
     <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="B232" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -7288,10 +7312,10 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="B233" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -7302,10 +7326,10 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="B234" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>6</v>
@@ -7316,10 +7340,10 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="B235" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>6</v>
@@ -7330,10 +7354,10 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="B236" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
@@ -7344,10 +7368,10 @@
     </row>
     <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="B237" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
@@ -7358,10 +7382,10 @@
     </row>
     <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="B238" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>6</v>
@@ -7372,10 +7396,10 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="B239" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
@@ -7386,10 +7410,10 @@
     </row>
     <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="B240" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
@@ -7400,10 +7424,10 @@
     </row>
     <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="B241" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
@@ -7414,10 +7438,10 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="B242" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -7428,10 +7452,10 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="B243" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
@@ -7442,10 +7466,10 @@
     </row>
     <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="B244" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -7456,10 +7480,10 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="B245" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -7470,10 +7494,10 @@
     </row>
     <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="B246" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
@@ -7484,10 +7508,10 @@
     </row>
     <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="B247" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
@@ -7498,10 +7522,10 @@
     </row>
     <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="B248" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
@@ -7512,10 +7536,10 @@
     </row>
     <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="B249" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
@@ -7526,10 +7550,10 @@
     </row>
     <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="B250" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
@@ -7540,10 +7564,10 @@
     </row>
     <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="B251" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>6</v>
@@ -7554,10 +7578,10 @@
     </row>
     <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="B252" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
@@ -7568,10 +7592,10 @@
     </row>
     <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="B253" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>6</v>
@@ -7582,10 +7606,10 @@
     </row>
     <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="B254" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>6</v>
@@ -7596,10 +7620,10 @@
     </row>
     <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="B255" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>6</v>
@@ -7610,10 +7634,10 @@
     </row>
     <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="B256" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>6</v>
@@ -7624,10 +7648,10 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="B257" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>6</v>
@@ -7638,10 +7662,10 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="B258" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>6</v>
@@ -7652,10 +7676,10 @@
     </row>
     <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="B259" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>6</v>
@@ -7666,10 +7690,10 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="B260" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -7680,10 +7704,10 @@
     </row>
     <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B261" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>6</v>
@@ -7694,10 +7718,10 @@
     </row>
     <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="B262" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>6</v>
@@ -7708,10 +7732,10 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="B263" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>6</v>
@@ -7722,10 +7746,10 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="B264" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>6</v>
@@ -7736,10 +7760,10 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="B265" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>6</v>
@@ -7750,10 +7774,10 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="B266" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>6</v>
@@ -7764,10 +7788,10 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="B267" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>6</v>
@@ -7778,10 +7802,10 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B268" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>6</v>
@@ -7792,10 +7816,10 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="B269" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>6</v>
@@ -7806,10 +7830,10 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B270" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>6</v>
@@ -7820,10 +7844,10 @@
     </row>
     <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B271" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>6</v>
@@ -7834,10 +7858,10 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="B272" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>6</v>
@@ -7848,10 +7872,10 @@
     </row>
     <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="B273" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>6</v>
@@ -7862,10 +7886,10 @@
     </row>
     <row r="274" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B274" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>6</v>
@@ -7876,10 +7900,10 @@
     </row>
     <row r="275" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B275" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>6</v>
@@ -7890,10 +7914,10 @@
     </row>
     <row r="276" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B276" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>6</v>
@@ -7904,10 +7928,10 @@
     </row>
     <row r="277" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B277" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>6</v>
@@ -7918,10 +7942,10 @@
     </row>
     <row r="278" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B278" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>6</v>
@@ -7932,10 +7956,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B279" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>6</v>
@@ -7946,10 +7970,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="B280" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>6</v>
@@ -7960,10 +7984,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="B281" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>6</v>
@@ -7974,10 +7998,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="B282" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>6</v>
@@ -7988,10 +8012,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="B283" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>6</v>
@@ -8002,10 +8026,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="B284" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>6</v>
@@ -8016,10 +8040,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="B285" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -8030,10 +8054,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="B286" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>6</v>
@@ -8044,10 +8068,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="B287" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>6</v>
@@ -8058,10 +8082,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="B288" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>6</v>
@@ -8072,10 +8096,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="B289" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>6</v>
@@ -8086,10 +8110,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="B290" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>6</v>
@@ -8100,10 +8124,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="B291" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>6</v>
@@ -8114,10 +8138,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="B292" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>6</v>
@@ -8128,10 +8152,10 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="B293" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>6</v>
@@ -8142,10 +8166,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="B294" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>6</v>
@@ -8156,10 +8180,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="B295" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>6</v>
@@ -8170,10 +8194,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="B296" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>6</v>
@@ -8184,10 +8208,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="B297" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>6</v>
@@ -8198,10 +8222,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="B298" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>6</v>
@@ -8212,10 +8236,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="B299" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>6</v>
@@ -8226,10 +8250,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="B300" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>6</v>
@@ -8240,10 +8264,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="B301" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>6</v>
@@ -8254,10 +8278,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="B302" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -8268,10 +8292,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="B303" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -8282,10 +8306,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="B304" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -8296,10 +8320,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="B305" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>6</v>
@@ -8310,10 +8334,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="B306" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -8324,10 +8348,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="B307" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>6</v>
@@ -8338,10 +8362,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="B308" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>6</v>
@@ -8352,10 +8376,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="B309" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>6</v>
@@ -8366,10 +8390,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="B310" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -8380,10 +8404,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="B311" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>6</v>
@@ -8394,10 +8418,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="B312" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -8408,10 +8432,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>687</v>
+        <v>671</v>
       </c>
       <c r="B313" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -8422,10 +8446,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="B314" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -8436,10 +8460,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="B315" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>6</v>
@@ -8450,10 +8474,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="B316" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>6</v>
@@ -8464,10 +8488,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="B317" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>6</v>
@@ -8478,10 +8502,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="B318" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>6</v>
@@ -8492,10 +8516,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="B319" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>6</v>
@@ -8506,10 +8530,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="B320" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>6</v>
@@ -8520,10 +8544,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="B321" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>6</v>
@@ -8534,10 +8558,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="B322" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -8548,10 +8572,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="B323" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>6</v>
@@ -8562,10 +8586,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="B324" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>6</v>
@@ -8576,10 +8600,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="B325" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>6</v>
@@ -8590,10 +8614,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="B326" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>6</v>
@@ -8604,10 +8628,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="B327" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>6</v>
@@ -8618,10 +8642,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="B328" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>6</v>
@@ -8632,10 +8656,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="B329" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>6</v>
@@ -8646,10 +8670,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>725</v>
+        <v>709</v>
       </c>
       <c r="B330" t="s">
-        <v>726</v>
+        <v>710</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -8660,10 +8684,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="B331" t="s">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>6</v>
@@ -8674,10 +8698,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>729</v>
+        <v>713</v>
       </c>
       <c r="B332" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>6</v>
@@ -8688,10 +8712,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="B333" t="s">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>6</v>
@@ -8702,10 +8726,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
       <c r="B334" t="s">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>6</v>
@@ -8716,10 +8740,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>735</v>
+        <v>719</v>
       </c>
       <c r="B335" t="s">
-        <v>736</v>
+        <v>720</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>6</v>
@@ -8730,10 +8754,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="B336" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>6</v>
@@ -8744,10 +8768,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>739</v>
+        <v>723</v>
       </c>
       <c r="B337" t="s">
-        <v>740</v>
+        <v>724</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>6</v>
@@ -8758,10 +8782,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="B338" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>6</v>
@@ -8772,10 +8796,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="B339" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>6</v>
@@ -8786,10 +8810,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>745</v>
+        <v>729</v>
       </c>
       <c r="B340" t="s">
-        <v>746</v>
+        <v>730</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>6</v>
@@ -8800,10 +8824,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
       <c r="B341" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>6</v>
@@ -8814,10 +8838,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="B342" t="s">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>6</v>
@@ -8828,10 +8852,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>751</v>
+        <v>735</v>
       </c>
       <c r="B343" t="s">
-        <v>752</v>
+        <v>736</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>6</v>
@@ -8842,10 +8866,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="B344" t="s">
-        <v>754</v>
+        <v>738</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>6</v>
@@ -8856,10 +8880,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="B345" t="s">
-        <v>756</v>
+        <v>740</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>6</v>
@@ -8870,10 +8894,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>759</v>
+        <v>741</v>
       </c>
       <c r="B346" t="s">
-        <v>760</v>
+        <v>742</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>6</v>
@@ -8884,10 +8908,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="B347" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>6</v>
@@ -8898,10 +8922,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>763</v>
+        <v>745</v>
       </c>
       <c r="B348" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>6</v>
@@ -8912,10 +8936,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="B349" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>6</v>
@@ -8926,10 +8950,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="B350" t="s">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>6</v>
@@ -8940,10 +8964,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="B351" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>6</v>
@@ -8954,10 +8978,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="B352" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>6</v>
@@ -8968,10 +8992,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="B353" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>6</v>
@@ -8982,10 +9006,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="B354" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>6</v>
@@ -8996,10 +9020,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="B355" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>6</v>
@@ -9010,10 +9034,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="B356" t="s">
-        <v>780</v>
+        <v>762</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>6</v>
@@ -9024,10 +9048,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="B357" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>6</v>
@@ -9038,10 +9062,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="B358" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>6</v>
@@ -9052,10 +9076,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="B359" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>6</v>
@@ -9066,10 +9090,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="B360" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>6</v>
@@ -9080,10 +9104,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="B361" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>6</v>
@@ -9094,10 +9118,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="B362" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -9108,10 +9132,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="B363" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>6</v>
@@ -9122,10 +9146,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="B364" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>6</v>
@@ -9136,10 +9160,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="B365" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>6</v>
@@ -9150,10 +9174,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>805</v>
+        <v>783</v>
       </c>
       <c r="B366" t="s">
-        <v>806</v>
+        <v>784</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>6</v>
@@ -9164,10 +9188,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>809</v>
+        <v>785</v>
       </c>
       <c r="B367" t="s">
-        <v>810</v>
+        <v>786</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>6</v>
@@ -9178,10 +9202,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>811</v>
+        <v>787</v>
       </c>
       <c r="B368" t="s">
-        <v>812</v>
+        <v>788</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>6</v>
@@ -9192,10 +9216,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>813</v>
+        <v>789</v>
       </c>
       <c r="B369" t="s">
-        <v>814</v>
+        <v>790</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>6</v>
@@ -9206,10 +9230,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>815</v>
+        <v>791</v>
       </c>
       <c r="B370" t="s">
-        <v>816</v>
+        <v>792</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>6</v>
@@ -9220,10 +9244,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>817</v>
+        <v>793</v>
       </c>
       <c r="B371" t="s">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>6</v>
@@ -9234,10 +9258,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>819</v>
+        <v>795</v>
       </c>
       <c r="B372" t="s">
-        <v>820</v>
+        <v>796</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>6</v>
@@ -9248,10 +9272,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>821</v>
+        <v>797</v>
       </c>
       <c r="B373" t="s">
-        <v>822</v>
+        <v>798</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>6</v>
@@ -9262,10 +9286,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>823</v>
+        <v>799</v>
       </c>
       <c r="B374" t="s">
-        <v>824</v>
+        <v>800</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>6</v>
@@ -9276,10 +9300,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>825</v>
+        <v>801</v>
       </c>
       <c r="B375" t="s">
-        <v>826</v>
+        <v>802</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>6</v>
@@ -9290,10 +9314,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>827</v>
+        <v>803</v>
       </c>
       <c r="B376" t="s">
-        <v>828</v>
+        <v>804</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>6</v>
@@ -9304,10 +9328,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>829</v>
+        <v>805</v>
       </c>
       <c r="B377" t="s">
-        <v>830</v>
+        <v>806</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>6</v>
@@ -9318,10 +9342,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>831</v>
+        <v>809</v>
       </c>
       <c r="B378" t="s">
-        <v>832</v>
+        <v>810</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>6</v>
@@ -9332,10 +9356,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>833</v>
+        <v>811</v>
       </c>
       <c r="B379" t="s">
-        <v>834</v>
+        <v>812</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>6</v>
@@ -9346,10 +9370,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>835</v>
+        <v>813</v>
       </c>
       <c r="B380" t="s">
-        <v>836</v>
+        <v>814</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>6</v>
@@ -9360,10 +9384,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="B381" t="s">
-        <v>838</v>
+        <v>816</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>6</v>
@@ -9374,10 +9398,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>839</v>
+        <v>817</v>
       </c>
       <c r="B382" t="s">
-        <v>840</v>
+        <v>818</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>6</v>
@@ -9388,10 +9412,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>841</v>
+        <v>819</v>
       </c>
       <c r="B383" t="s">
-        <v>842</v>
+        <v>820</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>6</v>
@@ -9402,10 +9426,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>843</v>
+        <v>821</v>
       </c>
       <c r="B384" t="s">
-        <v>844</v>
+        <v>822</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>6</v>
@@ -9416,10 +9440,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>845</v>
+        <v>823</v>
       </c>
       <c r="B385" t="s">
-        <v>846</v>
+        <v>824</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>6</v>
@@ -9430,10 +9454,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>847</v>
+        <v>825</v>
       </c>
       <c r="B386" t="s">
-        <v>848</v>
+        <v>826</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>6</v>
@@ -9444,10 +9468,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>849</v>
+        <v>827</v>
       </c>
       <c r="B387" t="s">
-        <v>850</v>
+        <v>828</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>6</v>
@@ -9458,10 +9482,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>851</v>
+        <v>829</v>
       </c>
       <c r="B388" t="s">
-        <v>852</v>
+        <v>830</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>6</v>
@@ -9472,10 +9496,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>853</v>
+        <v>831</v>
       </c>
       <c r="B389" t="s">
-        <v>854</v>
+        <v>832</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>6</v>
@@ -9486,10 +9510,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>855</v>
+        <v>833</v>
       </c>
       <c r="B390" t="s">
-        <v>856</v>
+        <v>834</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>6</v>
@@ -9500,10 +9524,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>857</v>
+        <v>835</v>
       </c>
       <c r="B391" t="s">
-        <v>858</v>
+        <v>836</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>6</v>
@@ -9514,10 +9538,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>859</v>
+        <v>837</v>
       </c>
       <c r="B392" t="s">
-        <v>860</v>
+        <v>838</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>6</v>
@@ -9528,10 +9552,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>861</v>
+        <v>839</v>
       </c>
       <c r="B393" t="s">
-        <v>862</v>
+        <v>840</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>6</v>
@@ -9542,10 +9566,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>863</v>
+        <v>841</v>
       </c>
       <c r="B394" t="s">
-        <v>864</v>
+        <v>842</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>6</v>
@@ -9556,10 +9580,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>867</v>
+        <v>843</v>
       </c>
       <c r="B395" t="s">
-        <v>868</v>
+        <v>844</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>6</v>
@@ -9570,10 +9594,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>869</v>
+        <v>845</v>
       </c>
       <c r="B396" t="s">
-        <v>870</v>
+        <v>846</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>6</v>
@@ -9584,10 +9608,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>871</v>
+        <v>847</v>
       </c>
       <c r="B397" t="s">
-        <v>872</v>
+        <v>848</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>6</v>
@@ -9598,10 +9622,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>873</v>
+        <v>849</v>
       </c>
       <c r="B398" t="s">
-        <v>874</v>
+        <v>850</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>6</v>
@@ -9612,10 +9636,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="B399" t="s">
-        <v>876</v>
+        <v>852</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>6</v>
@@ -9626,10 +9650,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>877</v>
+        <v>853</v>
       </c>
       <c r="B400" t="s">
-        <v>878</v>
+        <v>854</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>6</v>
@@ -9640,10 +9664,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>879</v>
+        <v>855</v>
       </c>
       <c r="B401" t="s">
-        <v>880</v>
+        <v>856</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>6</v>
@@ -9654,10 +9678,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>881</v>
+        <v>857</v>
       </c>
       <c r="B402" t="s">
-        <v>882</v>
+        <v>858</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>6</v>
@@ -9668,10 +9692,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>883</v>
+        <v>859</v>
       </c>
       <c r="B403" t="s">
-        <v>884</v>
+        <v>860</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>6</v>
@@ -9682,10 +9706,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="B404" t="s">
-        <v>886</v>
+        <v>862</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>6</v>
@@ -9696,10 +9720,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>887</v>
+        <v>863</v>
       </c>
       <c r="B405" t="s">
-        <v>888</v>
+        <v>864</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>6</v>
@@ -9710,10 +9734,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>889</v>
+        <v>865</v>
       </c>
       <c r="B406" t="s">
-        <v>890</v>
+        <v>866</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>6</v>
@@ -9724,10 +9748,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>893</v>
+        <v>867</v>
       </c>
       <c r="B407" t="s">
-        <v>894</v>
+        <v>868</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>6</v>
@@ -9738,10 +9762,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>895</v>
+        <v>869</v>
       </c>
       <c r="B408" t="s">
-        <v>896</v>
+        <v>870</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>6</v>
@@ -9752,10 +9776,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>899</v>
+        <v>871</v>
       </c>
       <c r="B409" t="s">
-        <v>900</v>
+        <v>872</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>6</v>
@@ -9766,10 +9790,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>901</v>
+        <v>873</v>
       </c>
       <c r="B410" t="s">
-        <v>902</v>
+        <v>874</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>6</v>
@@ -9780,10 +9804,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>903</v>
+        <v>875</v>
       </c>
       <c r="B411" t="s">
-        <v>904</v>
+        <v>876</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>6</v>
@@ -9794,10 +9818,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>907</v>
+        <v>877</v>
       </c>
       <c r="B412" t="s">
-        <v>908</v>
+        <v>878</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>6</v>
@@ -9808,10 +9832,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>909</v>
+        <v>879</v>
       </c>
       <c r="B413" t="s">
-        <v>910</v>
+        <v>880</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>6</v>
@@ -9822,10 +9846,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>911</v>
+        <v>881</v>
       </c>
       <c r="B414" t="s">
-        <v>912</v>
+        <v>882</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>6</v>
@@ -9836,10 +9860,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>913</v>
+        <v>883</v>
       </c>
       <c r="B415" t="s">
-        <v>914</v>
+        <v>884</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>6</v>
@@ -9850,10 +9874,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>915</v>
+        <v>885</v>
       </c>
       <c r="B416" t="s">
-        <v>916</v>
+        <v>886</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>6</v>
@@ -9864,10 +9888,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>917</v>
+        <v>887</v>
       </c>
       <c r="B417" t="s">
-        <v>918</v>
+        <v>888</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>6</v>
@@ -9878,10 +9902,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>919</v>
+        <v>889</v>
       </c>
       <c r="B418" t="s">
-        <v>920</v>
+        <v>890</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>6</v>
@@ -9892,10 +9916,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>921</v>
+        <v>891</v>
       </c>
       <c r="B419" t="s">
-        <v>922</v>
+        <v>892</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -9906,10 +9930,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>923</v>
+        <v>893</v>
       </c>
       <c r="B420" t="s">
-        <v>924</v>
+        <v>894</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>6</v>
@@ -9920,10 +9944,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>925</v>
+        <v>895</v>
       </c>
       <c r="B421" t="s">
-        <v>926</v>
+        <v>896</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>6</v>
@@ -9934,10 +9958,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>929</v>
+        <v>897</v>
       </c>
       <c r="B422" t="s">
-        <v>930</v>
+        <v>898</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>6</v>
@@ -9948,10 +9972,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>931</v>
+        <v>899</v>
       </c>
       <c r="B423" t="s">
-        <v>932</v>
+        <v>900</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>6</v>
@@ -9962,10 +9986,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>933</v>
+        <v>901</v>
       </c>
       <c r="B424" t="s">
-        <v>934</v>
+        <v>902</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>6</v>
@@ -9976,10 +10000,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>935</v>
+        <v>903</v>
       </c>
       <c r="B425" t="s">
-        <v>936</v>
+        <v>904</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>6</v>
@@ -9990,10 +10014,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>937</v>
+        <v>905</v>
       </c>
       <c r="B426" t="s">
-        <v>938</v>
+        <v>906</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>6</v>
@@ -10004,10 +10028,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>939</v>
+        <v>907</v>
       </c>
       <c r="B427" t="s">
-        <v>940</v>
+        <v>908</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>6</v>
@@ -10018,10 +10042,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>941</v>
+        <v>909</v>
       </c>
       <c r="B428" t="s">
-        <v>942</v>
+        <v>910</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -10032,10 +10056,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>943</v>
+        <v>911</v>
       </c>
       <c r="B429" t="s">
-        <v>944</v>
+        <v>912</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>6</v>
@@ -10046,10 +10070,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>945</v>
+        <v>915</v>
       </c>
       <c r="B430" t="s">
-        <v>946</v>
+        <v>916</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>6</v>
@@ -10060,10 +10084,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>947</v>
+        <v>917</v>
       </c>
       <c r="B431" t="s">
-        <v>948</v>
+        <v>918</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>6</v>
@@ -10074,10 +10098,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>949</v>
+        <v>919</v>
       </c>
       <c r="B432" t="s">
-        <v>950</v>
+        <v>920</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>6</v>
@@ -10088,10 +10112,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>951</v>
+        <v>921</v>
       </c>
       <c r="B433" t="s">
-        <v>952</v>
+        <v>922</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>6</v>
@@ -10102,10 +10126,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>955</v>
+        <v>923</v>
       </c>
       <c r="B434" t="s">
-        <v>956</v>
+        <v>924</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>6</v>
@@ -10116,10 +10140,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>957</v>
+        <v>925</v>
       </c>
       <c r="B435" t="s">
-        <v>958</v>
+        <v>926</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>6</v>
@@ -10130,10 +10154,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>963</v>
+        <v>927</v>
       </c>
       <c r="B436" t="s">
-        <v>964</v>
+        <v>928</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>6</v>
@@ -10144,10 +10168,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>965</v>
+        <v>929</v>
       </c>
       <c r="B437" t="s">
-        <v>966</v>
+        <v>930</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>6</v>
@@ -10158,10 +10182,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>967</v>
+        <v>931</v>
       </c>
       <c r="B438" t="s">
-        <v>968</v>
+        <v>932</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>6</v>
@@ -10172,10 +10196,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>969</v>
+        <v>933</v>
       </c>
       <c r="B439" t="s">
-        <v>970</v>
+        <v>934</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>6</v>
@@ -10186,10 +10210,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>973</v>
+        <v>937</v>
       </c>
       <c r="B440" t="s">
-        <v>974</v>
+        <v>938</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>6</v>
@@ -10200,10 +10224,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>977</v>
+        <v>939</v>
       </c>
       <c r="B441" t="s">
-        <v>978</v>
+        <v>940</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>6</v>
@@ -10214,10 +10238,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>979</v>
+        <v>941</v>
       </c>
       <c r="B442" t="s">
-        <v>980</v>
+        <v>942</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>6</v>
@@ -10228,10 +10252,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>981</v>
+        <v>943</v>
       </c>
       <c r="B443" t="s">
-        <v>982</v>
+        <v>944</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>6</v>
@@ -10242,10 +10266,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>983</v>
+        <v>945</v>
       </c>
       <c r="B444" t="s">
-        <v>984</v>
+        <v>946</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>6</v>
@@ -10256,10 +10280,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>985</v>
+        <v>947</v>
       </c>
       <c r="B445" t="s">
-        <v>986</v>
+        <v>948</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>6</v>
@@ -10270,10 +10294,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>987</v>
+        <v>949</v>
       </c>
       <c r="B446" t="s">
-        <v>988</v>
+        <v>950</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>6</v>
@@ -10284,10 +10308,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>989</v>
+        <v>951</v>
       </c>
       <c r="B447" t="s">
-        <v>990</v>
+        <v>952</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>6</v>
@@ -10298,10 +10322,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>991</v>
+        <v>953</v>
       </c>
       <c r="B448" t="s">
-        <v>992</v>
+        <v>954</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>6</v>
@@ -10312,10 +10336,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>993</v>
+        <v>955</v>
       </c>
       <c r="B449" t="s">
-        <v>994</v>
+        <v>956</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>6</v>
@@ -10326,10 +10350,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>995</v>
+        <v>957</v>
       </c>
       <c r="B450" t="s">
-        <v>996</v>
+        <v>958</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>6</v>
@@ -10340,10 +10364,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>997</v>
+        <v>959</v>
       </c>
       <c r="B451" t="s">
-        <v>998</v>
+        <v>960</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>6</v>
@@ -10354,10 +10378,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>999</v>
+        <v>963</v>
       </c>
       <c r="B452" t="s">
-        <v>1000</v>
+        <v>964</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>6</v>
@@ -10368,10 +10392,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>1001</v>
+        <v>965</v>
       </c>
       <c r="B453" t="s">
-        <v>1002</v>
+        <v>966</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>6</v>
@@ -10382,10 +10406,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>1003</v>
+        <v>969</v>
       </c>
       <c r="B454" t="s">
-        <v>1004</v>
+        <v>970</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>6</v>
@@ -10396,10 +10420,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>1005</v>
+        <v>971</v>
       </c>
       <c r="B455" t="s">
-        <v>1006</v>
+        <v>972</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>6</v>
@@ -10410,10 +10434,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>1007</v>
+        <v>973</v>
       </c>
       <c r="B456" t="s">
-        <v>1008</v>
+        <v>974</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>6</v>
@@ -10424,10 +10448,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>1009</v>
+        <v>975</v>
       </c>
       <c r="B457" t="s">
-        <v>1010</v>
+        <v>976</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>6</v>
@@ -10438,10 +10462,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>1011</v>
+        <v>977</v>
       </c>
       <c r="B458" t="s">
-        <v>1012</v>
+        <v>978</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>6</v>
@@ -10452,10 +10476,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>1013</v>
+        <v>981</v>
       </c>
       <c r="B459" t="s">
-        <v>1014</v>
+        <v>982</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>6</v>
@@ -10466,10 +10490,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>1017</v>
+        <v>985</v>
       </c>
       <c r="B460" t="s">
-        <v>1018</v>
+        <v>986</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>6</v>
@@ -10480,10 +10504,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>1019</v>
+        <v>987</v>
       </c>
       <c r="B461" t="s">
-        <v>1020</v>
+        <v>988</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>6</v>
@@ -10494,10 +10518,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>1021</v>
+        <v>989</v>
       </c>
       <c r="B462" t="s">
-        <v>1022</v>
+        <v>990</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>6</v>
@@ -10508,10 +10532,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>1023</v>
+        <v>991</v>
       </c>
       <c r="B463" t="s">
-        <v>1024</v>
+        <v>992</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>6</v>
@@ -10522,10 +10546,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>1025</v>
+        <v>993</v>
       </c>
       <c r="B464" t="s">
-        <v>1026</v>
+        <v>994</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>6</v>
@@ -10536,10 +10560,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>1027</v>
+        <v>995</v>
       </c>
       <c r="B465" t="s">
-        <v>1028</v>
+        <v>996</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>6</v>
@@ -10550,10 +10574,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>1029</v>
+        <v>997</v>
       </c>
       <c r="B466" t="s">
-        <v>1030</v>
+        <v>998</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>6</v>
@@ -10564,10 +10588,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>1031</v>
+        <v>999</v>
       </c>
       <c r="B467" t="s">
-        <v>1032</v>
+        <v>1000</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>6</v>
@@ -10578,10 +10602,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>1033</v>
+        <v>1001</v>
       </c>
       <c r="B468" t="s">
-        <v>1034</v>
+        <v>1002</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>6</v>
@@ -10592,10 +10616,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>1035</v>
+        <v>1003</v>
       </c>
       <c r="B469" t="s">
-        <v>1036</v>
+        <v>1004</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>6</v>
@@ -10606,10 +10630,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1037</v>
+        <v>1005</v>
       </c>
       <c r="B470" t="s">
-        <v>1038</v>
+        <v>1006</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>6</v>
@@ -10620,10 +10644,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>1039</v>
+        <v>1007</v>
       </c>
       <c r="B471" t="s">
-        <v>1040</v>
+        <v>1008</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>6</v>
@@ -10634,10 +10658,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>1041</v>
+        <v>1009</v>
       </c>
       <c r="B472" t="s">
-        <v>1042</v>
+        <v>1010</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>6</v>
@@ -10648,10 +10672,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>1045</v>
+        <v>1011</v>
       </c>
       <c r="B473" t="s">
-        <v>1046</v>
+        <v>1012</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>6</v>
@@ -10662,10 +10686,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>1047</v>
+        <v>1013</v>
       </c>
       <c r="B474" t="s">
-        <v>1048</v>
+        <v>1014</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>6</v>
@@ -10676,10 +10700,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>1049</v>
+        <v>1015</v>
       </c>
       <c r="B475" t="s">
-        <v>1050</v>
+        <v>1016</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>6</v>
@@ -10690,10 +10714,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>1051</v>
+        <v>1017</v>
       </c>
       <c r="B476" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>6</v>
@@ -10704,10 +10728,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>1053</v>
+        <v>1019</v>
       </c>
       <c r="B477" t="s">
-        <v>1054</v>
+        <v>1020</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>6</v>
@@ -10718,10 +10742,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>1055</v>
+        <v>1021</v>
       </c>
       <c r="B478" t="s">
-        <v>1056</v>
+        <v>1022</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -10732,10 +10756,10 @@
     </row>
     <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>1057</v>
+        <v>1023</v>
       </c>
       <c r="B479" t="s">
-        <v>1058</v>
+        <v>1024</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>6</v>
@@ -10746,10 +10770,10 @@
     </row>
     <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>1059</v>
+        <v>1025</v>
       </c>
       <c r="B480" t="s">
-        <v>1060</v>
+        <v>1026</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>6</v>
@@ -10760,10 +10784,10 @@
     </row>
     <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>1061</v>
+        <v>1027</v>
       </c>
       <c r="B481" t="s">
-        <v>1062</v>
+        <v>1028</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>6</v>
@@ -10774,10 +10798,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>1063</v>
+        <v>1029</v>
       </c>
       <c r="B482" t="s">
-        <v>1064</v>
+        <v>1030</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>6</v>
@@ -10788,10 +10812,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1065</v>
+        <v>1031</v>
       </c>
       <c r="B483" t="s">
-        <v>1066</v>
+        <v>1032</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>6</v>
@@ -10802,10 +10826,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1067</v>
+        <v>1033</v>
       </c>
       <c r="B484" t="s">
-        <v>1068</v>
+        <v>1034</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>6</v>
@@ -10816,10 +10840,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1069</v>
+        <v>1035</v>
       </c>
       <c r="B485" t="s">
-        <v>1070</v>
+        <v>1036</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>6</v>
@@ -10830,10 +10854,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1071</v>
+        <v>1037</v>
       </c>
       <c r="B486" t="s">
-        <v>1072</v>
+        <v>1038</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>6</v>
@@ -10844,10 +10868,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1073</v>
+        <v>1039</v>
       </c>
       <c r="B487" t="s">
-        <v>1074</v>
+        <v>1040</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>6</v>
@@ -10858,10 +10882,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1075</v>
+        <v>1041</v>
       </c>
       <c r="B488" t="s">
-        <v>1076</v>
+        <v>1042</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>6</v>
@@ -10872,10 +10896,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1077</v>
+        <v>1043</v>
       </c>
       <c r="B489" t="s">
-        <v>1078</v>
+        <v>1044</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>6</v>
@@ -10886,10 +10910,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1079</v>
+        <v>1045</v>
       </c>
       <c r="B490" t="s">
-        <v>1080</v>
+        <v>1046</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>6</v>
@@ -10900,10 +10924,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1081</v>
+        <v>1047</v>
       </c>
       <c r="B491" t="s">
-        <v>1082</v>
+        <v>1048</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>6</v>
@@ -10914,10 +10938,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1083</v>
+        <v>1049</v>
       </c>
       <c r="B492" t="s">
-        <v>1084</v>
+        <v>1050</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>6</v>
@@ -10928,10 +10952,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1085</v>
+        <v>1053</v>
       </c>
       <c r="B493" t="s">
-        <v>1086</v>
+        <v>1054</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>6</v>
@@ -10942,10 +10966,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1087</v>
+        <v>1055</v>
       </c>
       <c r="B494" t="s">
-        <v>1088</v>
+        <v>1056</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>6</v>
@@ -10956,10 +10980,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1089</v>
+        <v>1057</v>
       </c>
       <c r="B495" t="s">
-        <v>1090</v>
+        <v>1058</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>6</v>
@@ -10970,10 +10994,10 @@
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1091</v>
+        <v>1059</v>
       </c>
       <c r="B496" t="s">
-        <v>1092</v>
+        <v>1060</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>6</v>
@@ -10984,10 +11008,10 @@
     </row>
     <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1093</v>
+        <v>1061</v>
       </c>
       <c r="B497" t="s">
-        <v>1094</v>
+        <v>1062</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>6</v>
@@ -10998,10 +11022,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1095</v>
+        <v>1063</v>
       </c>
       <c r="B498" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>6</v>
@@ -11012,10 +11036,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1097</v>
+        <v>1065</v>
       </c>
       <c r="B499" t="s">
-        <v>1098</v>
+        <v>1066</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>6</v>
@@ -11026,10 +11050,10 @@
     </row>
     <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1099</v>
+        <v>1067</v>
       </c>
       <c r="B500" t="s">
-        <v>1100</v>
+        <v>1068</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>6</v>
@@ -11040,10 +11064,10 @@
     </row>
     <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1101</v>
+        <v>1069</v>
       </c>
       <c r="B501" t="s">
-        <v>1102</v>
+        <v>1070</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>6</v>
@@ -11054,10 +11078,10 @@
     </row>
     <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1103</v>
+        <v>1071</v>
       </c>
       <c r="B502" t="s">
-        <v>1104</v>
+        <v>1072</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>6</v>
@@ -11068,10 +11092,10 @@
     </row>
     <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1105</v>
+        <v>1073</v>
       </c>
       <c r="B503" t="s">
-        <v>1106</v>
+        <v>1074</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>6</v>
@@ -11082,10 +11106,10 @@
     </row>
     <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1107</v>
+        <v>1075</v>
       </c>
       <c r="B504" t="s">
-        <v>1108</v>
+        <v>1076</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>6</v>
@@ -11096,10 +11120,10 @@
     </row>
     <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="B505" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>6</v>
@@ -11110,10 +11134,10 @@
     </row>
     <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="B506" t="s">
-        <v>1112</v>
+        <v>1080</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>6</v>
@@ -11124,10 +11148,10 @@
     </row>
     <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1113</v>
+        <v>1081</v>
       </c>
       <c r="B507" t="s">
-        <v>1114</v>
+        <v>1082</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>6</v>
@@ -11138,10 +11162,10 @@
     </row>
     <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1117</v>
+        <v>1083</v>
       </c>
       <c r="B508" t="s">
-        <v>1118</v>
+        <v>1084</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>6</v>
@@ -11152,10 +11176,10 @@
     </row>
     <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1119</v>
+        <v>1085</v>
       </c>
       <c r="B509" t="s">
-        <v>1120</v>
+        <v>1086</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>6</v>
@@ -11166,10 +11190,10 @@
     </row>
     <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1121</v>
+        <v>1087</v>
       </c>
       <c r="B510" t="s">
-        <v>1122</v>
+        <v>1088</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>6</v>
@@ -11180,10 +11204,10 @@
     </row>
     <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1125</v>
+        <v>1089</v>
       </c>
       <c r="B511" t="s">
-        <v>1126</v>
+        <v>1090</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>6</v>
@@ -11194,10 +11218,10 @@
     </row>
     <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1127</v>
+        <v>1091</v>
       </c>
       <c r="B512" t="s">
-        <v>1128</v>
+        <v>1092</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>6</v>
@@ -11208,10 +11232,10 @@
     </row>
     <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1129</v>
+        <v>1093</v>
       </c>
       <c r="B513" t="s">
-        <v>1130</v>
+        <v>1094</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>6</v>
@@ -11222,10 +11246,10 @@
     </row>
     <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1133</v>
+        <v>1095</v>
       </c>
       <c r="B514" t="s">
-        <v>1134</v>
+        <v>1096</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>6</v>
@@ -11236,10 +11260,10 @@
     </row>
     <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1135</v>
+        <v>1097</v>
       </c>
       <c r="B515" t="s">
-        <v>1136</v>
+        <v>1098</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>6</v>
@@ -11250,10 +11274,10 @@
     </row>
     <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1137</v>
+        <v>1099</v>
       </c>
       <c r="B516" t="s">
-        <v>1138</v>
+        <v>1100</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>6</v>
@@ -11264,10 +11288,10 @@
     </row>
     <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1139</v>
+        <v>1101</v>
       </c>
       <c r="B517" t="s">
-        <v>1140</v>
+        <v>1102</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>6</v>
@@ -11278,10 +11302,10 @@
     </row>
     <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1141</v>
+        <v>1103</v>
       </c>
       <c r="B518" t="s">
-        <v>1142</v>
+        <v>1104</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>6</v>
@@ -11292,10 +11316,10 @@
     </row>
     <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1143</v>
+        <v>1105</v>
       </c>
       <c r="B519" t="s">
-        <v>1144</v>
+        <v>1106</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>6</v>
@@ -11306,10 +11330,10 @@
     </row>
     <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1145</v>
+        <v>1107</v>
       </c>
       <c r="B520" t="s">
-        <v>1146</v>
+        <v>1108</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>6</v>
@@ -11320,10 +11344,10 @@
     </row>
     <row r="521" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1147</v>
+        <v>1109</v>
       </c>
       <c r="B521" t="s">
-        <v>1148</v>
+        <v>1110</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>6</v>
@@ -11334,10 +11358,10 @@
     </row>
     <row r="522" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1149</v>
+        <v>1111</v>
       </c>
       <c r="B522" t="s">
-        <v>1150</v>
+        <v>1112</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>6</v>
@@ -11348,10 +11372,10 @@
     </row>
     <row r="523" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1151</v>
+        <v>1113</v>
       </c>
       <c r="B523" t="s">
-        <v>1152</v>
+        <v>1114</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>6</v>
@@ -11362,10 +11386,10 @@
     </row>
     <row r="524" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1153</v>
+        <v>1115</v>
       </c>
       <c r="B524" t="s">
-        <v>1154</v>
+        <v>1116</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>6</v>
@@ -11376,10 +11400,10 @@
     </row>
     <row r="525" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1155</v>
+        <v>1117</v>
       </c>
       <c r="B525" t="s">
-        <v>1156</v>
+        <v>1118</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>6</v>
@@ -11390,10 +11414,10 @@
     </row>
     <row r="526" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1157</v>
+        <v>1119</v>
       </c>
       <c r="B526" t="s">
-        <v>1158</v>
+        <v>1120</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>6</v>
@@ -11404,10 +11428,10 @@
     </row>
     <row r="527" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1159</v>
+        <v>1121</v>
       </c>
       <c r="B527" t="s">
-        <v>1160</v>
+        <v>1122</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>6</v>
@@ -11418,10 +11442,10 @@
     </row>
     <row r="528" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1161</v>
+        <v>1125</v>
       </c>
       <c r="B528" t="s">
-        <v>1162</v>
+        <v>1126</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>6</v>
@@ -11432,10 +11456,10 @@
     </row>
     <row r="529" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1163</v>
+        <v>1127</v>
       </c>
       <c r="B529" t="s">
-        <v>1164</v>
+        <v>1128</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>6</v>
@@ -11446,10 +11470,10 @@
     </row>
     <row r="530" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1165</v>
+        <v>1129</v>
       </c>
       <c r="B530" t="s">
-        <v>1166</v>
+        <v>1130</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>6</v>
@@ -11460,10 +11484,10 @@
     </row>
     <row r="531" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1167</v>
+        <v>1131</v>
       </c>
       <c r="B531" t="s">
-        <v>1168</v>
+        <v>1132</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>6</v>
@@ -11474,10 +11498,10 @@
     </row>
     <row r="532" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1171</v>
+        <v>1133</v>
       </c>
       <c r="B532" t="s">
-        <v>1172</v>
+        <v>1134</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>6</v>
@@ -11488,10 +11512,10 @@
     </row>
     <row r="533" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1173</v>
+        <v>1135</v>
       </c>
       <c r="B533" t="s">
-        <v>1174</v>
+        <v>1136</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>6</v>
@@ -11502,10 +11526,10 @@
     </row>
     <row r="534" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1175</v>
+        <v>1137</v>
       </c>
       <c r="B534" t="s">
-        <v>1176</v>
+        <v>1138</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>6</v>
@@ -11516,10 +11540,10 @@
     </row>
     <row r="535" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1177</v>
+        <v>1141</v>
       </c>
       <c r="B535" t="s">
-        <v>1178</v>
+        <v>1142</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>6</v>
@@ -11530,10 +11554,10 @@
     </row>
     <row r="536" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1179</v>
+        <v>1143</v>
       </c>
       <c r="B536" t="s">
-        <v>1180</v>
+        <v>1144</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>6</v>
@@ -11544,10 +11568,10 @@
     </row>
     <row r="537" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1181</v>
+        <v>1145</v>
       </c>
       <c r="B537" t="s">
-        <v>1182</v>
+        <v>1146</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -11558,10 +11582,10 @@
     </row>
     <row r="538" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1183</v>
+        <v>1147</v>
       </c>
       <c r="B538" t="s">
-        <v>1184</v>
+        <v>1148</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>6</v>
@@ -11572,10 +11596,10 @@
     </row>
     <row r="539" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1185</v>
+        <v>1149</v>
       </c>
       <c r="B539" t="s">
-        <v>1186</v>
+        <v>1150</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>6</v>
@@ -11586,10 +11610,10 @@
     </row>
     <row r="540" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1187</v>
+        <v>1151</v>
       </c>
       <c r="B540" t="s">
-        <v>1188</v>
+        <v>1152</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>6</v>
@@ -11600,10 +11624,10 @@
     </row>
     <row r="541" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1189</v>
+        <v>1153</v>
       </c>
       <c r="B541" t="s">
-        <v>1190</v>
+        <v>1154</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -11614,10 +11638,10 @@
     </row>
     <row r="542" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1191</v>
+        <v>1155</v>
       </c>
       <c r="B542" t="s">
-        <v>1192</v>
+        <v>1156</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>6</v>
@@ -11628,10 +11652,10 @@
     </row>
     <row r="543" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1193</v>
+        <v>1157</v>
       </c>
       <c r="B543" t="s">
-        <v>1194</v>
+        <v>1158</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>6</v>
@@ -11642,10 +11666,10 @@
     </row>
     <row r="544" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1195</v>
+        <v>1159</v>
       </c>
       <c r="B544" t="s">
-        <v>1196</v>
+        <v>1160</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>6</v>
@@ -11654,12 +11678,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1197</v>
+        <v>1161</v>
       </c>
       <c r="B545" t="s">
-        <v>1198</v>
+        <v>1162</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>6</v>
@@ -11668,12 +11692,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1199</v>
+        <v>1163</v>
       </c>
       <c r="B546" t="s">
-        <v>1200</v>
+        <v>1164</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>6</v>
@@ -11682,12 +11706,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1201</v>
+        <v>1165</v>
       </c>
       <c r="B547" t="s">
-        <v>1202</v>
+        <v>1166</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>6</v>
@@ -11696,12 +11720,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1203</v>
+        <v>1167</v>
       </c>
       <c r="B548" t="s">
-        <v>1204</v>
+        <v>1168</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>6</v>
@@ -11710,12 +11734,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1205</v>
+        <v>1169</v>
       </c>
       <c r="B549" t="s">
-        <v>1206</v>
+        <v>1170</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>6</v>
@@ -11724,12 +11748,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1207</v>
+        <v>1171</v>
       </c>
       <c r="B550" t="s">
-        <v>1208</v>
+        <v>1172</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>6</v>
@@ -11738,12 +11762,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1209</v>
+        <v>1173</v>
       </c>
       <c r="B551" t="s">
-        <v>1210</v>
+        <v>1174</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>6</v>
@@ -11752,12 +11776,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1211</v>
+        <v>1175</v>
       </c>
       <c r="B552" t="s">
-        <v>1212</v>
+        <v>1176</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>6</v>
@@ -11766,26 +11790,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>5</v>
+        <v>1179</v>
       </c>
       <c r="B553" t="s">
-        <v>5</v>
+        <v>1180</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E553" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="554" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D553" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>21</v>
+        <v>1181</v>
       </c>
       <c r="B554" t="s">
-        <v>22</v>
+        <v>1182</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>6</v>
@@ -11794,12 +11818,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>41</v>
+        <v>1183</v>
       </c>
       <c r="B555" t="s">
-        <v>42</v>
+        <v>1184</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>6</v>
@@ -11808,12 +11832,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>87</v>
+        <v>1185</v>
       </c>
       <c r="B556" t="s">
-        <v>88</v>
+        <v>1186</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>6</v>
@@ -11822,12 +11846,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>103</v>
+        <v>1187</v>
       </c>
       <c r="B557" t="s">
-        <v>104</v>
+        <v>1188</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>6</v>
@@ -11836,54 +11860,54 @@
         <v>10</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>117</v>
+        <v>1189</v>
       </c>
       <c r="B558" t="s">
-        <v>118</v>
+        <v>1190</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E558" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="559" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D558" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>119</v>
+        <v>1191</v>
       </c>
       <c r="B559" t="s">
-        <v>120</v>
+        <v>1192</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E559" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="560" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D559" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>139</v>
+        <v>1193</v>
       </c>
       <c r="B560" t="s">
-        <v>140</v>
+        <v>1194</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E560" t="s">
-        <v>7</v>
+      <c r="D560" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="561" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>175</v>
+        <v>1195</v>
       </c>
       <c r="B561" t="s">
-        <v>176</v>
+        <v>1196</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>6</v>
@@ -11894,52 +11918,52 @@
     </row>
     <row r="562" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>203</v>
+        <v>1197</v>
       </c>
       <c r="B562" t="s">
-        <v>204</v>
+        <v>1198</v>
       </c>
       <c r="C562" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E562" t="s">
-        <v>7</v>
+      <c r="D562" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="563" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>207</v>
+        <v>1199</v>
       </c>
       <c r="B563" t="s">
-        <v>208</v>
+        <v>1200</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E563" t="s">
-        <v>7</v>
+      <c r="D563" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="564" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>227</v>
+        <v>1201</v>
       </c>
       <c r="B564" t="s">
-        <v>228</v>
+        <v>1202</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E564" t="s">
-        <v>7</v>
+      <c r="D564" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="565" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>247</v>
+        <v>1203</v>
       </c>
       <c r="B565" t="s">
-        <v>248</v>
+        <v>1204</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>6</v>
@@ -11950,122 +11974,122 @@
     </row>
     <row r="566" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>253</v>
+        <v>1205</v>
       </c>
       <c r="B566" t="s">
-        <v>254</v>
+        <v>1206</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E566" t="s">
-        <v>7</v>
+      <c r="D566" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="567" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>277</v>
+        <v>1207</v>
       </c>
       <c r="B567" t="s">
-        <v>278</v>
+        <v>1208</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E567" t="s">
-        <v>7</v>
+      <c r="D567" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="568" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>285</v>
+        <v>1209</v>
       </c>
       <c r="B568" t="s">
-        <v>286</v>
+        <v>1210</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E568" t="s">
-        <v>7</v>
+      <c r="D568" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="569" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>295</v>
+        <v>1211</v>
       </c>
       <c r="B569" t="s">
-        <v>296</v>
+        <v>1212</v>
       </c>
       <c r="C569" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E569" t="s">
-        <v>7</v>
+      <c r="D569" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="570" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>319</v>
+        <v>1213</v>
       </c>
       <c r="B570" t="s">
-        <v>320</v>
+        <v>1214</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E570" t="s">
-        <v>7</v>
+      <c r="D570" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="571" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>363</v>
+        <v>1215</v>
       </c>
       <c r="B571" t="s">
-        <v>364</v>
+        <v>1216</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E571" t="s">
-        <v>7</v>
+      <c r="D571" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="572" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>369</v>
+        <v>1217</v>
       </c>
       <c r="B572" t="s">
-        <v>370</v>
+        <v>1218</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E572" t="s">
-        <v>7</v>
+      <c r="D572" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="573" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>415</v>
+        <v>1219</v>
       </c>
       <c r="B573" t="s">
-        <v>416</v>
+        <v>1220</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E573" t="s">
-        <v>7</v>
+      <c r="D573" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="574" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>427</v>
+        <v>5</v>
       </c>
       <c r="B574" t="s">
-        <v>428</v>
+        <v>5</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>6</v>
@@ -12076,24 +12100,24 @@
     </row>
     <row r="575" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>495</v>
+        <v>57</v>
       </c>
       <c r="B575" t="s">
-        <v>496</v>
+        <v>58</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D575" t="s">
-        <v>10</v>
+      <c r="E575" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="576" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>497</v>
+        <v>91</v>
       </c>
       <c r="B576" t="s">
-        <v>498</v>
+        <v>92</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>6</v>
@@ -12104,52 +12128,52 @@
     </row>
     <row r="577" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>505</v>
+        <v>121</v>
       </c>
       <c r="B577" t="s">
-        <v>506</v>
+        <v>122</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D577" t="s">
-        <v>10</v>
+      <c r="E577" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="578" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>507</v>
+        <v>123</v>
       </c>
       <c r="B578" t="s">
-        <v>508</v>
+        <v>124</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D578" t="s">
-        <v>10</v>
+      <c r="E578" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="579" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>619</v>
+        <v>143</v>
       </c>
       <c r="B579" t="s">
-        <v>620</v>
+        <v>144</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D579" t="s">
-        <v>10</v>
+      <c r="E579" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="580" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>653</v>
+        <v>207</v>
       </c>
       <c r="B580" t="s">
-        <v>654</v>
+        <v>208</v>
       </c>
       <c r="C580" s="2" t="s">
         <v>6</v>
@@ -12160,10 +12184,10 @@
     </row>
     <row r="581" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>677</v>
+        <v>211</v>
       </c>
       <c r="B581" t="s">
-        <v>678</v>
+        <v>212</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>6</v>
@@ -12174,10 +12198,10 @@
     </row>
     <row r="582" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>691</v>
+        <v>231</v>
       </c>
       <c r="B582" t="s">
-        <v>692</v>
+        <v>232</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>6</v>
@@ -12188,24 +12212,24 @@
     </row>
     <row r="583" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>721</v>
+        <v>257</v>
       </c>
       <c r="B583" t="s">
-        <v>722</v>
+        <v>258</v>
       </c>
       <c r="C583" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D583" t="s">
-        <v>10</v>
+      <c r="E583" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="584" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>757</v>
+        <v>281</v>
       </c>
       <c r="B584" t="s">
-        <v>758</v>
+        <v>282</v>
       </c>
       <c r="C584" s="2" t="s">
         <v>6</v>
@@ -12216,91 +12240,94 @@
     </row>
     <row r="585" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>799</v>
+        <v>289</v>
       </c>
       <c r="B585" t="s">
-        <v>800</v>
+        <v>290</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="E585" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="586" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>801</v>
+        <v>299</v>
       </c>
       <c r="B586" t="s">
-        <v>802</v>
+        <v>300</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D586" t="s">
-        <v>10</v>
+      <c r="E586" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="587" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>803</v>
+        <v>323</v>
       </c>
       <c r="B587" t="s">
-        <v>804</v>
+        <v>324</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D587" t="s">
-        <v>10</v>
+      <c r="E587" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="588" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>807</v>
+        <v>367</v>
       </c>
       <c r="B588" t="s">
-        <v>808</v>
+        <v>368</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D588" t="s">
-        <v>10</v>
+      <c r="E588" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="589" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>865</v>
+        <v>373</v>
       </c>
       <c r="B589" t="s">
-        <v>866</v>
+        <v>374</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D589" t="s">
-        <v>10</v>
+      <c r="E589" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="590" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>891</v>
+        <v>419</v>
       </c>
       <c r="B590" t="s">
-        <v>892</v>
+        <v>420</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D590" t="s">
-        <v>10</v>
+      <c r="E590" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="591" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>897</v>
+        <v>427</v>
       </c>
       <c r="B591" t="s">
-        <v>898</v>
+        <v>428</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>6</v>
@@ -12311,10 +12338,10 @@
     </row>
     <row r="592" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>905</v>
+        <v>433</v>
       </c>
       <c r="B592" t="s">
-        <v>906</v>
+        <v>434</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>6</v>
@@ -12325,35 +12352,38 @@
     </row>
     <row r="593" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>927</v>
+        <v>565</v>
       </c>
       <c r="B593" t="s">
-        <v>928</v>
+        <v>566</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E593" t="s">
-        <v>7</v>
+      <c r="D593" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="594" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>953</v>
+        <v>661</v>
       </c>
       <c r="B594" t="s">
-        <v>954</v>
+        <v>662</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="E594" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="595" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>959</v>
+        <v>685</v>
       </c>
       <c r="B595" t="s">
-        <v>960</v>
+        <v>686</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>6</v>
@@ -12364,24 +12394,24 @@
     </row>
     <row r="596" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>961</v>
+        <v>699</v>
       </c>
       <c r="B596" t="s">
-        <v>962</v>
+        <v>700</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D596" t="s">
-        <v>10</v>
+      <c r="E596" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="597" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>971</v>
+        <v>765</v>
       </c>
       <c r="B597" t="s">
-        <v>972</v>
+        <v>766</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>6</v>
@@ -12392,10 +12422,10 @@
     </row>
     <row r="598" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>975</v>
+        <v>807</v>
       </c>
       <c r="B598" t="s">
-        <v>976</v>
+        <v>808</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>6</v>
@@ -12406,24 +12436,24 @@
     </row>
     <row r="599" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1015</v>
+        <v>913</v>
       </c>
       <c r="B599" t="s">
-        <v>1016</v>
+        <v>914</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D599" t="s">
-        <v>10</v>
+      <c r="E599" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="600" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1043</v>
+        <v>935</v>
       </c>
       <c r="B600" t="s">
-        <v>1044</v>
+        <v>936</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -12434,10 +12464,10 @@
     </row>
     <row r="601" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1115</v>
+        <v>961</v>
       </c>
       <c r="B601" t="s">
-        <v>1116</v>
+        <v>962</v>
       </c>
       <c r="C601" s="2" t="s">
         <v>6</v>
@@ -12448,24 +12478,24 @@
     </row>
     <row r="602" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1123</v>
+        <v>967</v>
       </c>
       <c r="B602" t="s">
-        <v>1124</v>
+        <v>968</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D602" t="s">
-        <v>10</v>
+      <c r="E602" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="603" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1131</v>
+        <v>979</v>
       </c>
       <c r="B603" t="s">
-        <v>1132</v>
+        <v>980</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>6</v>
@@ -12476,10 +12506,10 @@
     </row>
     <row r="604" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1169</v>
+        <v>983</v>
       </c>
       <c r="B604" t="s">
-        <v>1170</v>
+        <v>984</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>6</v>
@@ -12488,621 +12518,681 @@
         <v>7</v>
       </c>
     </row>
+    <row r="605" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C605" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E605" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C606" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E606" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="607" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C607" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E607" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C608" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E608" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E604">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E608">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D604" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D608" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C553" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C574" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="C5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="C6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="C7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C554" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C11" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="C12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="C15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C555" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C17" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C19" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C20" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C21" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C22" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C23" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C24" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C25" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C26" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C27" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="C28" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C29" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C30" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C31" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="C32" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C33" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C34" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C35" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C36" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C37" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C38" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C556" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C39" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C40" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C41" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C42" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C43" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C44" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C45" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C557" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C46" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C47" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C48" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C49" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C50" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C51" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C558" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C559" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C52" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C53" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C54" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C55" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C56" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C57" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C58" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C59" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C60" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C560" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C61" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C62" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C63" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C64" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C65" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C66" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C67" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C68" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C69" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C70" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C71" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C72" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C73" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C74" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C75" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C76" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C77" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C561" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C78" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C79" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C80" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C81" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C82" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C83" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C84" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C85" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C86" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C87" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C88" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C89" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C90" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C562" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C91" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C563" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C92" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C93" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C94" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C95" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="C96" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="C97" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="C98" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C99" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="C100" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C564" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="C101" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C102" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C103" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C104" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="C105" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C106" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="C107" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C108" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="C109" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="C565" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="C110" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="C111" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="C566" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C112" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C113" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C114" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="C115" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C116" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="C117" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C118" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="C119" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C120" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="C121" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C122" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="C567" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C123" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="C124" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C125" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C568" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C126" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C127" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C128" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C129" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C569" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C130" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C131" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C132" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C133" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C134" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C135" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C136" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C137" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C138" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C139" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C140" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C570" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C141" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C142" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C143" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C144" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C145" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C146" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C147" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C148" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C149" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C150" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C151" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C152" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C153" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C154" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C155" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C156" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C157" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C158" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C159" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C160" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C161" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C571" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C162" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C163" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C572" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C164" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C165" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C166" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C167" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C168" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C169" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C170" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C171" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C172" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C173" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C174" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C175" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C176" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C177" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C178" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C179" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C180" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C181" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C182" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C183" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C184" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C185" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C573" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="C186" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C187" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C188" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C189" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C190" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C574" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C191" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C192" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C193" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C194" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C195" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C196" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C197" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C198" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C199" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C200" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C201" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C202" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C203" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C204" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C205" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C206" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C207" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C208" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C209" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C210" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C211" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C212" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C213" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C214" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="C215" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="C216" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="C217" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="C218" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="C219" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="C220" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="C221" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="C222" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="C223" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="C575" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="C576" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="C224" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="C225" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="C226" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="C577" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="C578" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="C227" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="C228" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="C229" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="C230" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="C231" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="C232" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="C233" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="C234" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="C235" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="C236" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="C237" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="C238" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="C239" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="C240" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="C241" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="C242" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="C243" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="C244" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="C245" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="C246" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="C247" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="C248" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="C249" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="C250" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="C251" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="C252" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="C253" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="C254" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="C255" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="C256" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="C257" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="C258" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="C259" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="C260" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="C261" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="C262" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="C263" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="C264" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="C265" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="C266" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="C267" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="C268" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="C269" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="C270" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="C271" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C272" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C273" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="C274" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="C275" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="C276" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="C277" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C278" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C279" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C280" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C281" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C579" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C282" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C283" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C284" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="C285" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="C286" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="C287" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="C288" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C289" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C290" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C291" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C292" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C293" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C294" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="C295" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C296" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C297" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C580" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C298" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C299" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C300" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C301" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C302" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C303" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C304" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C305" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C306" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C307" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C308" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C581" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C309" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C310" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C311" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C312" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C313" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C314" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C582" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C315" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C316" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C317" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C318" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C319" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C320" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C321" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C322" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="C323" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="C324" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C325" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C326" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C327" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C328" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C583" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="C329" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C330" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C331" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C332" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C333" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C334" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C335" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C336" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C337" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C338" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C339" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C340" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C341" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C342" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C343" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C344" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C345" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C584" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C346" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C347" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C348" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C349" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C350" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C351" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C352" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C353" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C354" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C355" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C356" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C357" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C358" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C359" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C360" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C361" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C362" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C363" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C364" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C365" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C585" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C586" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C587" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C366" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C588" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C367" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C368" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C369" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C370" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C371" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C372" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C373" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C374" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C375" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C376" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C377" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C378" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C379" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C380" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C381" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C382" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C383" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C384" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C385" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C386" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C387" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C388" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C389" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C390" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C391" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C392" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C393" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C394" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C589" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C395" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C396" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C397" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C398" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C399" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C400" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C401" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C402" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C403" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C404" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C405" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C406" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C590" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C407" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C408" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C591" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C409" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C410" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C411" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C592" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C412" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C413" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C414" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C415" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C416" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C417" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C418" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C419" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C420" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C421" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C593" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C422" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C423" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C424" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C425" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C426" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C427" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C428" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C429" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C430" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C431" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C432" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C433" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C594" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C434" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C435" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C595" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C596" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C436" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C437" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C438" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C439" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C597" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C440" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C598" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C441" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C442" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C443" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C444" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C445" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C446" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C447" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C448" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C449" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C450" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C451" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C452" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C453" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C454" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C455" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C456" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C457" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C458" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C459" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C599" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C460" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C461" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="C462" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C463" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="C464" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="C465" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C466" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="C467" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C468" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C469" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C470" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C471" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="C472" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="C600" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="C473" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="C474" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="C475" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="C476" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="C477" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="C478" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="C479" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C480" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C481" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="C482" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="C483" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="C484" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="C485" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="C486" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="C487" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="C488" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="C489" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="C490" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="C491" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="C492" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="C493" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="C494" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C495" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C496" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C497" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C498" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="C499" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="C500" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="C501" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
-    <hyperlink ref="C502" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
-    <hyperlink ref="C503" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
-    <hyperlink ref="C504" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
-    <hyperlink ref="C505" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
-    <hyperlink ref="C506" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
-    <hyperlink ref="C507" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
-    <hyperlink ref="C601" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
-    <hyperlink ref="C508" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
-    <hyperlink ref="C509" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
-    <hyperlink ref="C510" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
-    <hyperlink ref="C602" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
-    <hyperlink ref="C511" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
-    <hyperlink ref="C512" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
-    <hyperlink ref="C513" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
-    <hyperlink ref="C603" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
-    <hyperlink ref="C514" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
-    <hyperlink ref="C515" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
-    <hyperlink ref="C516" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
-    <hyperlink ref="C517" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
-    <hyperlink ref="C518" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
-    <hyperlink ref="C519" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
-    <hyperlink ref="C520" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
-    <hyperlink ref="C521" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
-    <hyperlink ref="C522" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
-    <hyperlink ref="C523" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
-    <hyperlink ref="C524" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
-    <hyperlink ref="C525" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
-    <hyperlink ref="C526" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
-    <hyperlink ref="C527" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
-    <hyperlink ref="C528" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
-    <hyperlink ref="C529" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
-    <hyperlink ref="C530" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
-    <hyperlink ref="C531" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
-    <hyperlink ref="C604" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
-    <hyperlink ref="C532" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
-    <hyperlink ref="C533" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
-    <hyperlink ref="C534" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
-    <hyperlink ref="C535" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
-    <hyperlink ref="C536" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
-    <hyperlink ref="C537" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
-    <hyperlink ref="C538" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
-    <hyperlink ref="C539" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
-    <hyperlink ref="C540" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
-    <hyperlink ref="C541" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
-    <hyperlink ref="C542" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
-    <hyperlink ref="C543" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
-    <hyperlink ref="C544" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
-    <hyperlink ref="C545" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
-    <hyperlink ref="C546" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
-    <hyperlink ref="C547" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
-    <hyperlink ref="C548" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
-    <hyperlink ref="C549" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
-    <hyperlink ref="C550" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
-    <hyperlink ref="C551" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
-    <hyperlink ref="C552" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C11" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C12" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C15" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C16" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C22" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C575" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C26" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C27" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="C28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C29" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C30" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C31" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C32" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="C33" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="C34" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="C38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C576" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C42" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C43" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C44" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C45" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C46" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C47" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C48" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C49" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C50" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C51" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C52" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C53" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C54" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C55" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C577" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C578" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C56" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C57" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="C58" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C59" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C60" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C61" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C62" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C63" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C64" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C579" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C65" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C66" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C68" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C69" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C70" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C71" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C72" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C73" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C74" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C75" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C76" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C77" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C78" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C79" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C80" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C81" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C82" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C83" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C84" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C85" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C86" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C87" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C88" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C89" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C90" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C91" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C92" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C93" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C94" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C95" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C580" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C96" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C581" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C97" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C98" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C99" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="C100" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="C101" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="C102" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C103" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C104" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C105" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="C582" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C106" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C107" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C108" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="C109" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C110" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="C111" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C112" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="C113" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="C114" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="C115" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="C116" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="C117" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C583" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C118" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C119" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="C120" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C121" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C122" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C123" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="C124" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C125" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="C126" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="C127" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="C128" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="C584" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C129" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C130" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C131" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C585" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C132" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C133" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C134" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C135" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C586" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C136" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C137" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C138" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C139" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C140" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C141" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C142" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C143" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C144" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C145" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C146" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C587" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C147" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C148" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C149" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C150" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C151" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C152" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C153" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C154" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C155" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="C156" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C157" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C158" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C159" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C160" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C161" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C162" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C163" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C164" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C165" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C166" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C167" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C588" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C168" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C169" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C589" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C170" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C171" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C172" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C173" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C174" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C175" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C176" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C177" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C178" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C179" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C180" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C181" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C182" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C183" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C184" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C185" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C186" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C187" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C188" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C189" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C190" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C191" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C590" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C192" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C193" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C194" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C591" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C195" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C196" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C592" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C197" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C198" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C199" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C200" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C201" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C202" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C203" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C204" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C205" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C206" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C207" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C208" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C209" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C210" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C211" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C212" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C213" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C214" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C215" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C216" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C217" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C218" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="C219" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="C220" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="C221" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="C222" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="C223" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="C224" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="C225" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="C226" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="C227" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C228" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="C229" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="C230" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="C231" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="C232" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="C233" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="C234" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="C235" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="C236" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="C237" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C238" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="C239" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="C240" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="C241" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="C242" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C243" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="C244" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="C245" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="C246" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="C247" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="C248" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="C249" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="C250" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="C251" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="C252" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="C253" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="C254" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="C255" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="C256" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="C257" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C258" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="C259" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="C260" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="C261" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="C593" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C262" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="C263" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="C264" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="C265" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="C266" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C267" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="C268" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="C269" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="C270" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="C271" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C272" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="C273" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="C274" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="C275" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="C276" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C277" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="C278" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C279" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C280" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="C281" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C282" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="C283" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="C284" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C285" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C286" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C287" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C288" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C289" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C290" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C291" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C292" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="C293" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="C294" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="C295" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C296" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C297" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C298" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C299" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C300" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C301" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C302" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="C303" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C304" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C305" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C306" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C307" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C308" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C594" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C309" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C310" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C311" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C312" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C313" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C314" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C315" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C316" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C317" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C318" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C319" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C595" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C320" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C321" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C322" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C323" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C324" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C325" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C596" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C326" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C327" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C328" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C329" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C330" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C331" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C332" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C333" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C334" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C335" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C336" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C337" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C338" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C339" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C340" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C341" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C342" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C343" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C344" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C345" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C346" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C347" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C348" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C349" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C350" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C351" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C352" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C353" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C354" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C355" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C356" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C357" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C597" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C358" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C359" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C360" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C361" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C362" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C363" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C364" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C365" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C366" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C367" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C368" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C369" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C370" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C371" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C372" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C373" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C374" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C375" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C376" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C377" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C598" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C378" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C379" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C380" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C381" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C382" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C383" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C384" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C385" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C386" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C387" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C388" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C389" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C390" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C391" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C392" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C393" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C394" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C395" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C396" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C397" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C398" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C399" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C400" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C401" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C402" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C403" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C404" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C405" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C406" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C407" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C408" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C409" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C410" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C411" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C412" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C413" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C414" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C415" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C416" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C417" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C418" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C419" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C420" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C421" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C422" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C423" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C424" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C425" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C426" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C427" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C428" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C429" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C599" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C430" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C431" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C432" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C433" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C434" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C435" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C436" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C437" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C438" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C439" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C600" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C440" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C441" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C442" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C443" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C444" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C445" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C446" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C447" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C448" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C449" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C450" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C451" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C601" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C452" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C453" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C602" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C454" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C455" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C456" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C457" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C458" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C603" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C459" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C604" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C460" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C461" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C462" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C463" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C464" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C465" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C466" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C467" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C468" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C469" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C470" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C471" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C472" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C473" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C474" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C475" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C476" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C477" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C478" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C479" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C480" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C481" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C482" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C483" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C484" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C485" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C486" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C487" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C488" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="C489" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="C490" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="C491" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="C492" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="C605" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="C493" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="C494" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="C495" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C496" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C497" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="C498" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="C499" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="C500" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="C501" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="C502" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="C503" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="C504" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="C505" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="C506" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="C507" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="C508" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="C509" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="C510" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C511" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C512" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C513" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C514" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C515" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="C516" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="C517" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C518" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="C519" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="C520" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C521" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="C522" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C523" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="C524" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="C525" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="C526" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C527" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="C606" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="C528" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="C529" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="C530" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="C531" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="C532" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C533" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="C534" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C607" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="C535" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="C536" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="C537" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="C538" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="C539" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="C540" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="C541" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="C542" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="C543" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="C544" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="C545" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="C546" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="C547" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="C548" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="C549" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="C550" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="C551" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="C552" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="C608" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="C553" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="C554" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="C555" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="C556" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="C557" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="C558" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="C559" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="C560" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="C561" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="C562" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="C563" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="C564" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="C565" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="C566" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="C567" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="C568" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="C569" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C570" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="C571" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="C572" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="C573" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD46A964-D719-44B6-A5E0-392CF3B42D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1522EDB-A708-48E1-9644-46C7F0B07013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1233">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -712,6 +712,12 @@
     <t>Den store britiske bagedyst</t>
   </si>
   <si>
+    <t>den store gatsby</t>
+  </si>
+  <si>
+    <t>Den store Gatsby</t>
+  </si>
+  <si>
     <t>den tapre prins ivandoes heroiske færd</t>
   </si>
   <si>
@@ -1300,6 +1306,18 @@
     <t>Grinchen</t>
   </si>
   <si>
+    <t>grusomme meg</t>
+  </si>
+  <si>
+    <t>Grusomme meg</t>
+  </si>
+  <si>
+    <t>grusomme meg 2</t>
+  </si>
+  <si>
+    <t>Grusomme meg 2</t>
+  </si>
+  <si>
     <t>grusomme meg 3</t>
   </si>
   <si>
@@ -1312,6 +1330,12 @@
     <t>Grusomme mig</t>
   </si>
   <si>
+    <t>grusomme mig 2</t>
+  </si>
+  <si>
+    <t>Grusomme mig 2</t>
+  </si>
+  <si>
     <t>grusomme mig 3</t>
   </si>
   <si>
@@ -1864,6 +1888,12 @@
     <t>Kidnapning</t>
   </si>
   <si>
+    <t>klostrets mørke hemmeligheder</t>
+  </si>
+  <si>
+    <t>Klostrets mørke hemmeligheder</t>
+  </si>
+  <si>
     <t>klovn</t>
   </si>
   <si>
@@ -2378,6 +2408,12 @@
   </si>
   <si>
     <t>Mordet i landsbyen - da rygterne tog magten (2:3)</t>
+  </si>
+  <si>
+    <t>mordet i landsbyen - da rygterne tog magten (3:3)</t>
+  </si>
+  <si>
+    <t>Mordet i landsbyen - da rygterne tog magten (3:3)</t>
   </si>
   <si>
     <t>mordet i orientekspressen</t>
@@ -4049,7 +4085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E608"/>
+  <dimension ref="A1:E614"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -4638,10 +4674,10 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -4652,10 +4688,10 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6</v>
@@ -4666,10 +4702,10 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -4680,10 +4716,10 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
@@ -4694,10 +4730,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>6</v>
@@ -4708,10 +4744,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6</v>
@@ -4722,10 +4758,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6</v>
@@ -4736,10 +4772,10 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -4750,10 +4786,10 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>6</v>
@@ -4764,10 +4800,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>6</v>
@@ -4778,10 +4814,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
@@ -4792,10 +4828,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
@@ -4806,10 +4842,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
@@ -4820,10 +4856,10 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>6</v>
@@ -4834,10 +4870,10 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>6</v>
@@ -4848,10 +4884,10 @@
     </row>
     <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>6</v>
@@ -4862,10 +4898,10 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B58" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>6</v>
@@ -4876,10 +4912,10 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>6</v>
@@ -4890,10 +4926,10 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>6</v>
@@ -4904,10 +4940,10 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>6</v>
@@ -4918,10 +4954,10 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B62" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>6</v>
@@ -4932,10 +4968,10 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>6</v>
@@ -4946,10 +4982,10 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>6</v>
@@ -4960,10 +4996,10 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -4974,10 +5010,10 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B66" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>6</v>
@@ -4988,10 +5024,10 @@
     </row>
     <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>6</v>
@@ -5002,10 +5038,10 @@
     </row>
     <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>6</v>
@@ -5016,10 +5052,10 @@
     </row>
     <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B69" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>6</v>
@@ -5030,10 +5066,10 @@
     </row>
     <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B70" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>6</v>
@@ -5044,10 +5080,10 @@
     </row>
     <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>6</v>
@@ -5058,10 +5094,10 @@
     </row>
     <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B72" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>6</v>
@@ -5072,10 +5108,10 @@
     </row>
     <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>6</v>
@@ -5086,10 +5122,10 @@
     </row>
     <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>6</v>
@@ -5100,10 +5136,10 @@
     </row>
     <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>6</v>
@@ -5114,10 +5150,10 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>6</v>
@@ -5128,10 +5164,10 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B77" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>6</v>
@@ -5142,10 +5178,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>6</v>
@@ -5156,10 +5192,10 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>6</v>
@@ -5170,10 +5206,10 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -5184,10 +5220,10 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B81" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>6</v>
@@ -5198,10 +5234,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B82" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
@@ -5212,10 +5248,10 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B83" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>6</v>
@@ -5226,10 +5262,10 @@
     </row>
     <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B84" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>6</v>
@@ -5240,10 +5276,10 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B85" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>6</v>
@@ -5254,10 +5290,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B86" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>6</v>
@@ -5268,10 +5304,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B87" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>6</v>
@@ -5282,10 +5318,10 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>6</v>
@@ -5296,10 +5332,10 @@
     </row>
     <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B89" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>6</v>
@@ -5310,10 +5346,10 @@
     </row>
     <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B90" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>6</v>
@@ -5324,10 +5360,10 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B91" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>6</v>
@@ -5338,10 +5374,10 @@
     </row>
     <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>6</v>
@@ -5352,10 +5388,10 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B93" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>6</v>
@@ -5366,10 +5402,10 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B94" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>6</v>
@@ -5380,10 +5416,10 @@
     </row>
     <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>6</v>
@@ -5394,10 +5430,10 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B96" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>6</v>
@@ -5408,10 +5444,10 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B97" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>6</v>
@@ -5422,10 +5458,10 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B98" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>6</v>
@@ -5436,10 +5472,10 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B99" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>6</v>
@@ -5450,10 +5486,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B100" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>6</v>
@@ -5464,10 +5500,10 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B101" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>6</v>
@@ -5478,10 +5514,10 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B102" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>6</v>
@@ -5492,10 +5528,10 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B103" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>6</v>
@@ -5506,10 +5542,10 @@
     </row>
     <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B104" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -5520,10 +5556,10 @@
     </row>
     <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B105" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>6</v>
@@ -5534,10 +5570,10 @@
     </row>
     <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B106" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>6</v>
@@ -5702,10 +5738,10 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B118" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>6</v>
@@ -5856,10 +5892,10 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B129" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>6</v>
@@ -5898,10 +5934,10 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B132" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>6</v>
@@ -5954,10 +5990,10 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B136" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>6</v>
@@ -6108,10 +6144,10 @@
     </row>
     <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B147" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>6</v>
@@ -6402,10 +6438,10 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B168" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>6</v>
@@ -6430,10 +6466,10 @@
     </row>
     <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B170" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>6</v>
@@ -6738,10 +6774,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B192" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>6</v>
@@ -6780,10 +6816,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B195" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>6</v>
@@ -6794,10 +6830,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B196" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>6</v>
@@ -6808,10 +6844,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B197" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>6</v>
@@ -6822,10 +6858,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B198" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>6</v>
@@ -6836,10 +6872,10 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B199" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>6</v>
@@ -6850,10 +6886,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B200" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>6</v>
@@ -6864,10 +6900,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B201" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>6</v>
@@ -6878,10 +6914,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B202" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>6</v>
@@ -6892,10 +6928,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B203" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>6</v>
@@ -6906,10 +6942,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B204" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>6</v>
@@ -6920,10 +6956,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B205" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>6</v>
@@ -6934,10 +6970,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B206" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>6</v>
@@ -6948,10 +6984,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B207" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>6</v>
@@ -6962,10 +6998,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B208" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>6</v>
@@ -6976,10 +7012,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B209" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>6</v>
@@ -6990,10 +7026,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B210" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>6</v>
@@ -7004,10 +7040,10 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B211" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>6</v>
@@ -7018,10 +7054,10 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B212" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>6</v>
@@ -7032,10 +7068,10 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B213" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>6</v>
@@ -7046,10 +7082,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B214" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>6</v>
@@ -7060,10 +7096,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B215" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>6</v>
@@ -7074,10 +7110,10 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B216" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>6</v>
@@ -7088,10 +7124,10 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B217" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>6</v>
@@ -7102,10 +7138,10 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B218" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>6</v>
@@ -7116,10 +7152,10 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B219" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>6</v>
@@ -7130,10 +7166,10 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>6</v>
@@ -7144,10 +7180,10 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B221" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>6</v>
@@ -7158,10 +7194,10 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B222" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>6</v>
@@ -7172,10 +7208,10 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B223" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>6</v>
@@ -7186,10 +7222,10 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B224" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>6</v>
@@ -7200,10 +7236,10 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B225" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -7214,10 +7250,10 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B226" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>6</v>
@@ -7228,10 +7264,10 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B227" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>6</v>
@@ -7242,10 +7278,10 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B228" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>6</v>
@@ -7256,10 +7292,10 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B229" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -7270,10 +7306,10 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B230" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>6</v>
@@ -7284,10 +7320,10 @@
     </row>
     <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B231" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>6</v>
@@ -7298,10 +7334,10 @@
     </row>
     <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B232" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -7312,10 +7348,10 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B233" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -7326,10 +7362,10 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B234" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>6</v>
@@ -7340,10 +7376,10 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B235" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>6</v>
@@ -7354,10 +7390,10 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B236" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
@@ -7368,10 +7404,10 @@
     </row>
     <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B237" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
@@ -7382,10 +7418,10 @@
     </row>
     <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B238" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>6</v>
@@ -7396,10 +7432,10 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B239" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
@@ -7410,10 +7446,10 @@
     </row>
     <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B240" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
@@ -7424,10 +7460,10 @@
     </row>
     <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B241" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
@@ -7438,10 +7474,10 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B242" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -7452,10 +7488,10 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B243" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>6</v>
@@ -7466,10 +7502,10 @@
     </row>
     <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B244" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -7480,10 +7516,10 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B245" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -7494,10 +7530,10 @@
     </row>
     <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B246" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>6</v>
@@ -7508,10 +7544,10 @@
     </row>
     <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B247" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
@@ -7522,10 +7558,10 @@
     </row>
     <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B248" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
@@ -7536,10 +7572,10 @@
     </row>
     <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B249" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>6</v>
@@ -7550,10 +7586,10 @@
     </row>
     <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B250" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>6</v>
@@ -7564,10 +7600,10 @@
     </row>
     <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B251" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>6</v>
@@ -7578,10 +7614,10 @@
     </row>
     <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B252" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>6</v>
@@ -7592,10 +7628,10 @@
     </row>
     <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B253" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>6</v>
@@ -7606,10 +7642,10 @@
     </row>
     <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B254" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>6</v>
@@ -7620,10 +7656,10 @@
     </row>
     <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B255" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>6</v>
@@ -7634,10 +7670,10 @@
     </row>
     <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B256" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>6</v>
@@ -7648,10 +7684,10 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B257" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>6</v>
@@ -7662,10 +7698,10 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B258" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>6</v>
@@ -7676,10 +7712,10 @@
     </row>
     <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B259" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>6</v>
@@ -7690,10 +7726,10 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B260" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -7704,10 +7740,10 @@
     </row>
     <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B261" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>6</v>
@@ -7718,10 +7754,10 @@
     </row>
     <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B262" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>6</v>
@@ -7732,10 +7768,10 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B263" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>6</v>
@@ -7746,10 +7782,10 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B264" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>6</v>
@@ -7760,10 +7796,10 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B265" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>6</v>
@@ -7774,10 +7810,10 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B266" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>6</v>
@@ -7788,10 +7824,10 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B267" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>6</v>
@@ -7802,10 +7838,10 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B268" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>6</v>
@@ -7816,10 +7852,10 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B269" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>6</v>
@@ -7830,10 +7866,10 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B270" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>6</v>
@@ -7844,10 +7880,10 @@
     </row>
     <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B271" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>6</v>
@@ -7858,10 +7894,10 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B272" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>6</v>
@@ -7872,10 +7908,10 @@
     </row>
     <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B273" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>6</v>
@@ -7886,10 +7922,10 @@
     </row>
     <row r="274" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B274" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>6</v>
@@ -7900,10 +7936,10 @@
     </row>
     <row r="275" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B275" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>6</v>
@@ -7914,10 +7950,10 @@
     </row>
     <row r="276" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B276" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>6</v>
@@ -7928,10 +7964,10 @@
     </row>
     <row r="277" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B277" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>6</v>
@@ -7942,10 +7978,10 @@
     </row>
     <row r="278" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B278" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>6</v>
@@ -7956,10 +7992,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B279" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>6</v>
@@ -7970,10 +8006,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B280" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>6</v>
@@ -7984,10 +8020,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B281" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>6</v>
@@ -7998,10 +8034,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B282" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>6</v>
@@ -8012,10 +8048,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B283" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>6</v>
@@ -8026,10 +8062,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B284" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>6</v>
@@ -8040,10 +8076,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B285" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -8054,10 +8090,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B286" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>6</v>
@@ -8068,10 +8104,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B287" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>6</v>
@@ -8082,10 +8118,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B288" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>6</v>
@@ -8096,10 +8132,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B289" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>6</v>
@@ -8110,10 +8146,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B290" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>6</v>
@@ -8124,10 +8160,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B291" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>6</v>
@@ -8138,10 +8174,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B292" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>6</v>
@@ -8152,10 +8188,10 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B293" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>6</v>
@@ -8166,10 +8202,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B294" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>6</v>
@@ -8180,10 +8216,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B295" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>6</v>
@@ -8194,10 +8230,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B296" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>6</v>
@@ -8208,10 +8244,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B297" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>6</v>
@@ -8222,10 +8258,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B298" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>6</v>
@@ -8236,10 +8272,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B299" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>6</v>
@@ -8250,10 +8286,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B300" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>6</v>
@@ -8264,10 +8300,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B301" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>6</v>
@@ -8278,10 +8314,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B302" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -8292,10 +8328,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B303" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -8306,10 +8342,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B304" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -8320,10 +8356,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B305" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>6</v>
@@ -8334,10 +8370,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B306" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -8348,10 +8384,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B307" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>6</v>
@@ -8362,10 +8398,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B308" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>6</v>
@@ -8376,10 +8412,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B309" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>6</v>
@@ -8390,10 +8426,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B310" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -8404,10 +8440,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B311" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>6</v>
@@ -8418,10 +8454,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B312" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -8432,10 +8468,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B313" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -8446,10 +8482,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B314" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -8460,10 +8496,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B315" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>6</v>
@@ -8474,10 +8510,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B316" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>6</v>
@@ -8488,10 +8524,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B317" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>6</v>
@@ -8502,10 +8538,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B318" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>6</v>
@@ -8516,10 +8552,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B319" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>6</v>
@@ -8530,10 +8566,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B320" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>6</v>
@@ -8544,10 +8580,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B321" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>6</v>
@@ -8558,10 +8594,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B322" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -8572,10 +8608,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B323" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>6</v>
@@ -8586,10 +8622,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B324" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>6</v>
@@ -8600,10 +8636,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B325" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>6</v>
@@ -8614,10 +8650,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B326" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>6</v>
@@ -8628,10 +8664,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B327" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>6</v>
@@ -8642,10 +8678,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B328" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>6</v>
@@ -8656,10 +8692,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B329" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>6</v>
@@ -8670,10 +8706,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B330" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -8684,10 +8720,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B331" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>6</v>
@@ -8698,10 +8734,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B332" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>6</v>
@@ -8712,10 +8748,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B333" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>6</v>
@@ -8726,10 +8762,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B334" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>6</v>
@@ -8740,10 +8776,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B335" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>6</v>
@@ -8754,10 +8790,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B336" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>6</v>
@@ -8768,10 +8804,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B337" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>6</v>
@@ -8782,10 +8818,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B338" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>6</v>
@@ -8796,10 +8832,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B339" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>6</v>
@@ -8810,10 +8846,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B340" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>6</v>
@@ -8824,10 +8860,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B341" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>6</v>
@@ -8838,10 +8874,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B342" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>6</v>
@@ -8852,10 +8888,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B343" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>6</v>
@@ -8866,10 +8902,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B344" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>6</v>
@@ -8880,10 +8916,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B345" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>6</v>
@@ -8894,10 +8930,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B346" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>6</v>
@@ -8908,10 +8944,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B347" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>6</v>
@@ -8922,10 +8958,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B348" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>6</v>
@@ -8936,10 +8972,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B349" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>6</v>
@@ -8950,10 +8986,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B350" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>6</v>
@@ -8964,10 +9000,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B351" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>6</v>
@@ -8978,10 +9014,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B352" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>6</v>
@@ -8992,10 +9028,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B353" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>6</v>
@@ -9006,10 +9042,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B354" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>6</v>
@@ -9020,10 +9056,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B355" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>6</v>
@@ -9034,10 +9070,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B356" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>6</v>
@@ -9048,10 +9084,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B357" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>6</v>
@@ -9062,10 +9098,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B358" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>6</v>
@@ -9076,10 +9112,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B359" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>6</v>
@@ -9090,10 +9126,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B360" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>6</v>
@@ -9104,10 +9140,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B361" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>6</v>
@@ -9118,10 +9154,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B362" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -9132,10 +9168,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="B363" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>6</v>
@@ -9146,10 +9182,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="B364" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>6</v>
@@ -9160,10 +9196,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="B365" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>6</v>
@@ -9174,10 +9210,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B366" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>6</v>
@@ -9188,10 +9224,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B367" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>6</v>
@@ -9202,10 +9238,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B368" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>6</v>
@@ -9216,10 +9252,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B369" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>6</v>
@@ -9230,10 +9266,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="B370" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>6</v>
@@ -9244,10 +9280,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="B371" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>6</v>
@@ -9258,10 +9294,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="B372" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>6</v>
@@ -9272,10 +9308,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B373" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>6</v>
@@ -9286,10 +9322,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="B374" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>6</v>
@@ -9300,10 +9336,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="B375" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>6</v>
@@ -9314,10 +9350,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="B376" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>6</v>
@@ -9328,10 +9364,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="B377" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>6</v>
@@ -9342,10 +9378,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B378" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>6</v>
@@ -9356,10 +9392,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="B379" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>6</v>
@@ -9370,10 +9406,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="B380" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>6</v>
@@ -9384,10 +9420,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="B381" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>6</v>
@@ -9398,10 +9434,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B382" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>6</v>
@@ -9412,10 +9448,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B383" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>6</v>
@@ -9426,10 +9462,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="B384" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>6</v>
@@ -9440,10 +9476,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="B385" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>6</v>
@@ -9454,10 +9490,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="B386" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>6</v>
@@ -9468,10 +9504,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B387" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>6</v>
@@ -9482,10 +9518,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="B388" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>6</v>
@@ -9496,10 +9532,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="B389" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>6</v>
@@ -9510,10 +9546,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="B390" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>6</v>
@@ -9524,10 +9560,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="B391" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>6</v>
@@ -9538,10 +9574,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="B392" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>6</v>
@@ -9552,10 +9588,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="B393" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>6</v>
@@ -9566,10 +9602,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="B394" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>6</v>
@@ -9580,10 +9616,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="B395" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>6</v>
@@ -9594,10 +9630,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="B396" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>6</v>
@@ -9608,10 +9644,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B397" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>6</v>
@@ -9622,10 +9658,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="B398" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>6</v>
@@ -9636,10 +9672,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="B399" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>6</v>
@@ -9650,10 +9686,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="B400" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>6</v>
@@ -9664,10 +9700,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="B401" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>6</v>
@@ -9678,10 +9714,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B402" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>6</v>
@@ -9692,10 +9728,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="B403" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>6</v>
@@ -9706,10 +9742,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="B404" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>6</v>
@@ -9720,10 +9756,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="B405" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>6</v>
@@ -9734,10 +9770,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="B406" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>6</v>
@@ -9748,10 +9784,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="B407" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>6</v>
@@ -9762,10 +9798,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="B408" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>6</v>
@@ -9776,10 +9812,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="B409" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>6</v>
@@ -9790,10 +9826,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="B410" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>6</v>
@@ -9804,10 +9840,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="B411" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>6</v>
@@ -9818,10 +9854,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="B412" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>6</v>
@@ -9832,10 +9868,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B413" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>6</v>
@@ -9846,10 +9882,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="B414" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>6</v>
@@ -9860,10 +9896,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="B415" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>6</v>
@@ -9874,10 +9910,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="B416" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>6</v>
@@ -9888,10 +9924,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="B417" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>6</v>
@@ -9902,10 +9938,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="B418" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>6</v>
@@ -9916,10 +9952,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B419" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -9930,10 +9966,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="B420" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>6</v>
@@ -9944,10 +9980,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="B421" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>6</v>
@@ -9958,10 +9994,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="B422" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>6</v>
@@ -9972,10 +10008,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="B423" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>6</v>
@@ -9986,10 +10022,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="B424" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>6</v>
@@ -10000,10 +10036,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="B425" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>6</v>
@@ -10014,10 +10050,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="B426" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>6</v>
@@ -10028,10 +10064,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="B427" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>6</v>
@@ -10042,10 +10078,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B428" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -10056,10 +10092,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="B429" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>6</v>
@@ -10070,10 +10106,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="B430" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>6</v>
@@ -10084,10 +10120,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B431" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>6</v>
@@ -10098,10 +10134,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="B432" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>6</v>
@@ -10112,10 +10148,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="B433" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>6</v>
@@ -10126,10 +10162,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="B434" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>6</v>
@@ -10140,10 +10176,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="B435" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>6</v>
@@ -10154,10 +10190,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="B436" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>6</v>
@@ -10168,10 +10204,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="B437" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>6</v>
@@ -10182,10 +10218,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B438" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>6</v>
@@ -10196,10 +10232,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="B439" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>6</v>
@@ -10210,10 +10246,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="B440" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>6</v>
@@ -10224,10 +10260,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B441" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>6</v>
@@ -10238,10 +10274,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B442" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>6</v>
@@ -10252,10 +10288,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="B443" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>6</v>
@@ -10266,10 +10302,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B444" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>6</v>
@@ -10280,10 +10316,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="B445" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>6</v>
@@ -10294,10 +10330,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="B446" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>6</v>
@@ -10308,10 +10344,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="B447" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>6</v>
@@ -10322,10 +10358,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B448" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>6</v>
@@ -10336,10 +10372,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="B449" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>6</v>
@@ -10350,10 +10386,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="B450" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>6</v>
@@ -10364,10 +10400,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="B451" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>6</v>
@@ -10378,10 +10414,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="B452" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>6</v>
@@ -10392,10 +10428,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="B453" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>6</v>
@@ -10406,10 +10442,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B454" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>6</v>
@@ -10420,10 +10456,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="B455" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>6</v>
@@ -10434,10 +10470,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="B456" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>6</v>
@@ -10448,10 +10484,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="B457" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>6</v>
@@ -10462,10 +10498,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="B458" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>6</v>
@@ -10476,10 +10512,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="B459" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>6</v>
@@ -10490,10 +10526,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B460" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>6</v>
@@ -10504,10 +10540,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B461" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>6</v>
@@ -10518,10 +10554,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="B462" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>6</v>
@@ -10532,10 +10568,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="B463" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>6</v>
@@ -10546,10 +10582,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="B464" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>6</v>
@@ -10560,10 +10596,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="B465" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>6</v>
@@ -10574,10 +10610,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="B466" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>6</v>
@@ -10588,10 +10624,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="B467" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>6</v>
@@ -10602,10 +10638,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="B468" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>6</v>
@@ -10616,10 +10652,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="B469" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>6</v>
@@ -10630,10 +10666,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="B470" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>6</v>
@@ -10644,10 +10680,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B471" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>6</v>
@@ -10658,10 +10694,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="B472" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>6</v>
@@ -10672,10 +10708,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="B473" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>6</v>
@@ -10686,10 +10722,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="B474" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>6</v>
@@ -10700,10 +10736,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="B475" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>6</v>
@@ -10714,10 +10750,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B476" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>6</v>
@@ -10728,10 +10764,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="B477" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>6</v>
@@ -10742,10 +10778,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="B478" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -10756,10 +10792,10 @@
     </row>
     <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="B479" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>6</v>
@@ -10770,10 +10806,10 @@
     </row>
     <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="B480" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>6</v>
@@ -10784,10 +10820,10 @@
     </row>
     <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="B481" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>6</v>
@@ -10798,10 +10834,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="B482" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>6</v>
@@ -10812,10 +10848,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="B483" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>6</v>
@@ -10826,10 +10862,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="B484" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>6</v>
@@ -10840,10 +10876,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="B485" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>6</v>
@@ -10854,10 +10890,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="B486" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>6</v>
@@ -10868,10 +10904,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="B487" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>6</v>
@@ -10882,10 +10918,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="B488" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>6</v>
@@ -10896,10 +10932,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="B489" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>6</v>
@@ -10910,10 +10946,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B490" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>6</v>
@@ -10924,10 +10960,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="B491" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>6</v>
@@ -10938,10 +10974,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="B492" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>6</v>
@@ -10952,10 +10988,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="B493" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>6</v>
@@ -10966,10 +11002,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="B494" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>6</v>
@@ -10980,10 +11016,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="B495" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>6</v>
@@ -10994,10 +11030,10 @@
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="B496" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>6</v>
@@ -11008,10 +11044,10 @@
     </row>
     <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="B497" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>6</v>
@@ -11022,10 +11058,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="B498" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>6</v>
@@ -11036,10 +11072,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="B499" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>6</v>
@@ -11050,10 +11086,10 @@
     </row>
     <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="B500" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>6</v>
@@ -11064,10 +11100,10 @@
     </row>
     <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="B501" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>6</v>
@@ -11078,10 +11114,10 @@
     </row>
     <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="B502" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>6</v>
@@ -11092,10 +11128,10 @@
     </row>
     <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="B503" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>6</v>
@@ -11106,10 +11142,10 @@
     </row>
     <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="B504" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>6</v>
@@ -11120,10 +11156,10 @@
     </row>
     <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="B505" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>6</v>
@@ -11134,10 +11170,10 @@
     </row>
     <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="B506" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>6</v>
@@ -11148,10 +11184,10 @@
     </row>
     <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="B507" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>6</v>
@@ -11162,10 +11198,10 @@
     </row>
     <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="B508" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>6</v>
@@ -11176,10 +11212,10 @@
     </row>
     <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B509" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>6</v>
@@ -11190,10 +11226,10 @@
     </row>
     <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="B510" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>6</v>
@@ -11204,10 +11240,10 @@
     </row>
     <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="B511" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>6</v>
@@ -11218,10 +11254,10 @@
     </row>
     <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="B512" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>6</v>
@@ -11232,10 +11268,10 @@
     </row>
     <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="B513" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>6</v>
@@ -11246,10 +11282,10 @@
     </row>
     <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="B514" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>6</v>
@@ -11260,10 +11296,10 @@
     </row>
     <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="B515" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>6</v>
@@ -11274,10 +11310,10 @@
     </row>
     <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="B516" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>6</v>
@@ -11288,10 +11324,10 @@
     </row>
     <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="B517" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>6</v>
@@ -11302,10 +11338,10 @@
     </row>
     <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="B518" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>6</v>
@@ -11316,10 +11352,10 @@
     </row>
     <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="B519" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>6</v>
@@ -11330,10 +11366,10 @@
     </row>
     <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="B520" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>6</v>
@@ -11344,10 +11380,10 @@
     </row>
     <row r="521" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B521" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>6</v>
@@ -11358,10 +11394,10 @@
     </row>
     <row r="522" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="B522" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>6</v>
@@ -11372,10 +11408,10 @@
     </row>
     <row r="523" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="B523" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>6</v>
@@ -11386,10 +11422,10 @@
     </row>
     <row r="524" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="B524" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>6</v>
@@ -11400,10 +11436,10 @@
     </row>
     <row r="525" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="B525" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>6</v>
@@ -11414,10 +11450,10 @@
     </row>
     <row r="526" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="B526" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>6</v>
@@ -11428,10 +11464,10 @@
     </row>
     <row r="527" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="B527" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>6</v>
@@ -11442,10 +11478,10 @@
     </row>
     <row r="528" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B528" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>6</v>
@@ -11456,10 +11492,10 @@
     </row>
     <row r="529" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="B529" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>6</v>
@@ -11470,10 +11506,10 @@
     </row>
     <row r="530" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B530" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>6</v>
@@ -11484,10 +11520,10 @@
     </row>
     <row r="531" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="B531" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>6</v>
@@ -11498,10 +11534,10 @@
     </row>
     <row r="532" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="B532" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>6</v>
@@ -11512,10 +11548,10 @@
     </row>
     <row r="533" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="B533" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>6</v>
@@ -11526,10 +11562,10 @@
     </row>
     <row r="534" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="B534" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>6</v>
@@ -11540,10 +11576,10 @@
     </row>
     <row r="535" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B535" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>6</v>
@@ -11554,10 +11590,10 @@
     </row>
     <row r="536" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="B536" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>6</v>
@@ -11568,10 +11604,10 @@
     </row>
     <row r="537" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="B537" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -11582,10 +11618,10 @@
     </row>
     <row r="538" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="B538" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>6</v>
@@ -11596,10 +11632,10 @@
     </row>
     <row r="539" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="B539" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>6</v>
@@ -11610,10 +11646,10 @@
     </row>
     <row r="540" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="B540" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>6</v>
@@ -11624,10 +11660,10 @@
     </row>
     <row r="541" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="B541" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -11638,10 +11674,10 @@
     </row>
     <row r="542" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="B542" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>6</v>
@@ -11652,10 +11688,10 @@
     </row>
     <row r="543" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="B543" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>6</v>
@@ -11666,10 +11702,10 @@
     </row>
     <row r="544" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="B544" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>6</v>
@@ -11680,10 +11716,10 @@
     </row>
     <row r="545" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="B545" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>6</v>
@@ -11694,10 +11730,10 @@
     </row>
     <row r="546" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="B546" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>6</v>
@@ -11708,10 +11744,10 @@
     </row>
     <row r="547" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="B547" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>6</v>
@@ -11722,10 +11758,10 @@
     </row>
     <row r="548" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="B548" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>6</v>
@@ -11736,10 +11772,10 @@
     </row>
     <row r="549" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="B549" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>6</v>
@@ -11750,10 +11786,10 @@
     </row>
     <row r="550" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="B550" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>6</v>
@@ -11764,10 +11800,10 @@
     </row>
     <row r="551" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="B551" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>6</v>
@@ -11778,10 +11814,10 @@
     </row>
     <row r="552" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="B552" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>6</v>
@@ -11792,10 +11828,10 @@
     </row>
     <row r="553" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="B553" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>6</v>
@@ -11806,10 +11842,10 @@
     </row>
     <row r="554" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B554" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>6</v>
@@ -11820,10 +11856,10 @@
     </row>
     <row r="555" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="B555" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>6</v>
@@ -11834,10 +11870,10 @@
     </row>
     <row r="556" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="B556" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>6</v>
@@ -11848,10 +11884,10 @@
     </row>
     <row r="557" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="B557" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>6</v>
@@ -11862,10 +11898,10 @@
     </row>
     <row r="558" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="B558" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>6</v>
@@ -11876,10 +11912,10 @@
     </row>
     <row r="559" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="B559" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>6</v>
@@ -11890,10 +11926,10 @@
     </row>
     <row r="560" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="B560" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>6</v>
@@ -11902,12 +11938,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="B561" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>6</v>
@@ -11916,12 +11952,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="B562" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="C562" s="2" t="s">
         <v>6</v>
@@ -11930,12 +11966,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="B563" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>6</v>
@@ -11944,12 +11980,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="B564" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>6</v>
@@ -11958,12 +11994,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="B565" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>6</v>
@@ -11972,12 +12008,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="B566" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>6</v>
@@ -11986,12 +12022,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="B567" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>6</v>
@@ -12000,12 +12036,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="B568" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>6</v>
@@ -12014,12 +12050,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="B569" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="C569" s="2" t="s">
         <v>6</v>
@@ -12028,12 +12064,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B570" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>6</v>
@@ -12042,12 +12078,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="B571" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>6</v>
@@ -12056,12 +12092,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="B572" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>6</v>
@@ -12070,12 +12106,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="B573" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>6</v>
@@ -12084,40 +12120,40 @@
         <v>10</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>5</v>
+        <v>1227</v>
       </c>
       <c r="B574" t="s">
-        <v>5</v>
+        <v>1228</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E574" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="575" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D574" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>57</v>
+        <v>1229</v>
       </c>
       <c r="B575" t="s">
-        <v>58</v>
+        <v>1230</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E575" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="576" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D575" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>91</v>
+        <v>1231</v>
       </c>
       <c r="B576" t="s">
-        <v>92</v>
+        <v>1232</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>6</v>
@@ -12128,10 +12164,10 @@
     </row>
     <row r="577" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="B577" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>6</v>
@@ -12142,10 +12178,10 @@
     </row>
     <row r="578" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="B578" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>6</v>
@@ -12156,10 +12192,10 @@
     </row>
     <row r="579" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="B579" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>6</v>
@@ -12170,10 +12206,10 @@
     </row>
     <row r="580" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>207</v>
+        <v>123</v>
       </c>
       <c r="B580" t="s">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="C580" s="2" t="s">
         <v>6</v>
@@ -12184,10 +12220,10 @@
     </row>
     <row r="581" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>211</v>
+        <v>143</v>
       </c>
       <c r="B581" t="s">
-        <v>212</v>
+        <v>144</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>6</v>
@@ -12198,10 +12234,10 @@
     </row>
     <row r="582" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="B582" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>6</v>
@@ -12212,10 +12248,10 @@
     </row>
     <row r="583" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="B583" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="C583" s="2" t="s">
         <v>6</v>
@@ -12226,24 +12262,24 @@
     </row>
     <row r="584" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>281</v>
+        <v>229</v>
       </c>
       <c r="B584" t="s">
-        <v>282</v>
+        <v>230</v>
       </c>
       <c r="C584" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E584" t="s">
-        <v>7</v>
+      <c r="D584" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="585" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="B585" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>6</v>
@@ -12254,10 +12290,10 @@
     </row>
     <row r="586" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="B586" t="s">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>6</v>
@@ -12268,10 +12304,10 @@
     </row>
     <row r="587" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="B587" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>6</v>
@@ -12282,10 +12318,10 @@
     </row>
     <row r="588" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>367</v>
+        <v>291</v>
       </c>
       <c r="B588" t="s">
-        <v>368</v>
+        <v>292</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>6</v>
@@ -12296,10 +12332,10 @@
     </row>
     <row r="589" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>373</v>
+        <v>301</v>
       </c>
       <c r="B589" t="s">
-        <v>374</v>
+        <v>302</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>6</v>
@@ -12310,10 +12346,10 @@
     </row>
     <row r="590" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>419</v>
+        <v>325</v>
       </c>
       <c r="B590" t="s">
-        <v>420</v>
+        <v>326</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>6</v>
@@ -12324,24 +12360,24 @@
     </row>
     <row r="591" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>427</v>
+        <v>369</v>
       </c>
       <c r="B591" t="s">
-        <v>428</v>
+        <v>370</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D591" t="s">
-        <v>10</v>
+      <c r="E591" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="592" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>433</v>
+        <v>375</v>
       </c>
       <c r="B592" t="s">
-        <v>434</v>
+        <v>376</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>6</v>
@@ -12352,66 +12388,66 @@
     </row>
     <row r="593" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>565</v>
+        <v>421</v>
       </c>
       <c r="B593" t="s">
-        <v>566</v>
+        <v>422</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D593" t="s">
-        <v>10</v>
+      <c r="E593" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="594" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>661</v>
+        <v>427</v>
       </c>
       <c r="B594" t="s">
-        <v>662</v>
+        <v>428</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E594" t="s">
-        <v>7</v>
+      <c r="D594" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="595" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>685</v>
+        <v>429</v>
       </c>
       <c r="B595" t="s">
-        <v>686</v>
+        <v>430</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E595" t="s">
-        <v>7</v>
+      <c r="D595" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="596" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>699</v>
+        <v>435</v>
       </c>
       <c r="B596" t="s">
-        <v>700</v>
+        <v>436</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E596" t="s">
-        <v>7</v>
+      <c r="D596" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="597" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>765</v>
+        <v>441</v>
       </c>
       <c r="B597" t="s">
-        <v>766</v>
+        <v>442</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>6</v>
@@ -12422,10 +12458,10 @@
     </row>
     <row r="598" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>807</v>
+        <v>621</v>
       </c>
       <c r="B598" t="s">
-        <v>808</v>
+        <v>622</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>6</v>
@@ -12436,10 +12472,10 @@
     </row>
     <row r="599" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>913</v>
+        <v>671</v>
       </c>
       <c r="B599" t="s">
-        <v>914</v>
+        <v>672</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>6</v>
@@ -12450,10 +12486,10 @@
     </row>
     <row r="600" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>935</v>
+        <v>695</v>
       </c>
       <c r="B600" t="s">
-        <v>936</v>
+        <v>696</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -12464,10 +12500,10 @@
     </row>
     <row r="601" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>961</v>
+        <v>709</v>
       </c>
       <c r="B601" t="s">
-        <v>962</v>
+        <v>710</v>
       </c>
       <c r="C601" s="2" t="s">
         <v>6</v>
@@ -12478,10 +12514,10 @@
     </row>
     <row r="602" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>967</v>
+        <v>775</v>
       </c>
       <c r="B602" t="s">
-        <v>968</v>
+        <v>776</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>6</v>
@@ -12492,24 +12528,24 @@
     </row>
     <row r="603" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>979</v>
+        <v>795</v>
       </c>
       <c r="B603" t="s">
-        <v>980</v>
+        <v>796</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E603" t="s">
-        <v>7</v>
+      <c r="D603" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="604" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>983</v>
+        <v>819</v>
       </c>
       <c r="B604" t="s">
-        <v>984</v>
+        <v>820</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>6</v>
@@ -12520,10 +12556,10 @@
     </row>
     <row r="605" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1051</v>
+        <v>925</v>
       </c>
       <c r="B605" t="s">
-        <v>1052</v>
+        <v>926</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>6</v>
@@ -12534,10 +12570,10 @@
     </row>
     <row r="606" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1123</v>
+        <v>947</v>
       </c>
       <c r="B606" t="s">
-        <v>1124</v>
+        <v>948</v>
       </c>
       <c r="C606" s="2" t="s">
         <v>6</v>
@@ -12548,10 +12584,10 @@
     </row>
     <row r="607" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1139</v>
+        <v>973</v>
       </c>
       <c r="B607" t="s">
-        <v>1140</v>
+        <v>974</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>6</v>
@@ -12562,10 +12598,10 @@
     </row>
     <row r="608" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1177</v>
+        <v>979</v>
       </c>
       <c r="B608" t="s">
-        <v>1178</v>
+        <v>980</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>6</v>
@@ -12574,19 +12610,103 @@
         <v>7</v>
       </c>
     </row>
+    <row r="609" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>991</v>
+      </c>
+      <c r="B609" t="s">
+        <v>992</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E609" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>995</v>
+      </c>
+      <c r="B610" t="s">
+        <v>996</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E610" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C611" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E611" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C612" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E612" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E613" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A614" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E614" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E608">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E614">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D608" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D614" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C574" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C577" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
@@ -12611,7 +12731,7 @@
     <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
     <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
     <hyperlink ref="C25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C575" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C578" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
     <hyperlink ref="C26" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
     <hyperlink ref="C27" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
     <hyperlink ref="C28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
@@ -12628,78 +12748,78 @@
     <hyperlink ref="C39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
     <hyperlink ref="C40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
     <hyperlink ref="C41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C576" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C42" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C43" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C44" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C45" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C46" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C47" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C48" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C49" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C50" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C51" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C52" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C53" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C54" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C55" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C577" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C578" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C56" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C57" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C58" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C59" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C60" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C61" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C62" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C63" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C64" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C579" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C65" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C66" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C68" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C69" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C70" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C71" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C72" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C73" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C74" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C75" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C76" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C77" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C78" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C79" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C80" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C81" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C82" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C83" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C84" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C85" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C86" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C87" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C88" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C89" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C90" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C91" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C92" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C93" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C94" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C95" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C580" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C96" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C581" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C97" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C98" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="C99" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="C100" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="C101" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C102" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="C103" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C104" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="C105" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C582" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C106" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C48" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C49" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C50" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C51" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C52" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C53" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C54" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C55" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C56" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C579" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C580" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C57" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C58" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="C59" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C60" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C61" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C62" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C63" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C64" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C65" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C581" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C66" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C67" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C68" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C69" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C70" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C71" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C72" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C73" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C74" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C75" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C76" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C77" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C78" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C79" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C80" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C81" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C82" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C83" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C84" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C85" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C86" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C87" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C88" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C89" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C90" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C91" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C92" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C93" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C94" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C95" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C96" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C582" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C97" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C583" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C98" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C99" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C100" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="C101" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="C102" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="C103" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C104" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C105" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C584" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="C106" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C585" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
     <hyperlink ref="C107" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
     <hyperlink ref="C108" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
     <hyperlink ref="C109" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
@@ -12711,8 +12831,8 @@
     <hyperlink ref="C115" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
     <hyperlink ref="C116" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
     <hyperlink ref="C117" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C583" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C118" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C118" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C586" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
     <hyperlink ref="C119" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
     <hyperlink ref="C120" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
     <hyperlink ref="C121" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
@@ -12723,17 +12843,17 @@
     <hyperlink ref="C126" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
     <hyperlink ref="C127" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
     <hyperlink ref="C128" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="C584" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C129" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C129" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C587" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
     <hyperlink ref="C130" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
     <hyperlink ref="C131" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C585" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C132" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C132" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C588" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
     <hyperlink ref="C133" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
     <hyperlink ref="C134" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
     <hyperlink ref="C135" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C586" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C136" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C136" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C589" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
     <hyperlink ref="C137" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
     <hyperlink ref="C138" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
     <hyperlink ref="C139" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
@@ -12744,8 +12864,8 @@
     <hyperlink ref="C144" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
     <hyperlink ref="C145" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
     <hyperlink ref="C146" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C587" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C147" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C147" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C590" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
     <hyperlink ref="C148" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
     <hyperlink ref="C149" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
     <hyperlink ref="C150" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
@@ -12766,11 +12886,11 @@
     <hyperlink ref="C165" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
     <hyperlink ref="C166" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
     <hyperlink ref="C167" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C588" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C168" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C168" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C591" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
     <hyperlink ref="C169" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C589" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C170" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C170" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C592" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
     <hyperlink ref="C171" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
     <hyperlink ref="C172" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
     <hyperlink ref="C173" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
@@ -12792,407 +12912,413 @@
     <hyperlink ref="C189" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
     <hyperlink ref="C190" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
     <hyperlink ref="C191" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C590" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C192" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C192" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C593" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
     <hyperlink ref="C193" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
     <hyperlink ref="C194" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C591" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C195" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C196" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C592" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C197" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C198" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C199" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C200" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C201" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C202" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C203" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C204" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C205" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C206" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C207" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C208" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C209" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C210" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C211" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C212" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C213" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C214" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C215" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C216" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C217" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="C218" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="C219" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="C220" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="C221" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="C222" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="C223" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="C224" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="C225" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="C226" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="C227" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="C228" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="C229" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="C230" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="C231" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="C232" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="C233" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="C234" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="C235" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="C236" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="C237" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="C238" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="C239" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="C240" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="C241" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="C242" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="C243" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="C244" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="C245" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="C246" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="C247" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="C248" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="C249" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="C250" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="C251" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="C252" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="C253" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="C254" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="C255" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="C256" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="C257" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="C258" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="C259" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="C260" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="C261" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="C593" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="C262" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="C263" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="C264" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="C265" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="C266" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="C267" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="C268" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="C269" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="C270" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="C271" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="C272" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="C273" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="C274" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="C275" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="C276" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="C277" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C278" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C279" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="C280" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="C281" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="C282" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="C283" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C284" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C285" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C286" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C287" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C288" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C289" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C290" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C291" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="C292" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="C293" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="C294" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="C295" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C296" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C297" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C298" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C299" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C300" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C301" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="C302" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C303" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C304" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C305" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C306" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C307" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C308" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C594" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C309" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C310" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C311" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C312" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C313" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C314" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C315" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C316" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C317" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C318" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C319" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C595" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C320" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C321" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C322" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C323" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C324" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C325" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C596" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C326" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C327" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C328" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C329" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="C330" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="C331" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C332" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C333" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C334" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C335" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C336" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="C337" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C338" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C339" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C340" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C341" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C342" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C343" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C344" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C345" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C346" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C347" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C348" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C349" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C350" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C351" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C352" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C353" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C354" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C355" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C356" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C357" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C597" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C358" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C359" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C360" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C361" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C362" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C363" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C364" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C365" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C366" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C367" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C368" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C369" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C370" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C371" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C372" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C373" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C374" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C375" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C376" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C377" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C598" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C378" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C379" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C380" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C381" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C382" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C383" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C384" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C385" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C386" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C387" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C388" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C389" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C390" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C391" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C392" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C393" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C394" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C395" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C396" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C397" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C398" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C399" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C400" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C401" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C402" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C403" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C404" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C405" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C406" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C407" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C408" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C409" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C410" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C411" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C412" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C413" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C414" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C415" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C416" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C417" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C418" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C419" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C420" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C421" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C422" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C423" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C424" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C425" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C426" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C427" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C428" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C429" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C599" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C430" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C431" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C432" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C433" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C434" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C435" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C436" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C437" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C438" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C439" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C600" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C440" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C441" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C442" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C443" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C444" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C445" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C446" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C447" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C448" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C449" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C450" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C451" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C601" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C452" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C453" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C602" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C454" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C455" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C456" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C457" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C458" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C603" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C459" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C604" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C460" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C461" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C462" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C463" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C464" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C465" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C466" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C467" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C468" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C469" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C470" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C471" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C472" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C473" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C474" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C475" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C476" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C477" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="C478" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C479" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="C480" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="C481" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C482" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="C483" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C484" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C485" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C486" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C487" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="C488" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="C489" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="C490" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="C491" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="C492" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="C605" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="C493" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="C494" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="C495" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C496" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C497" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="C498" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="C499" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="C500" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="C501" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="C502" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="C503" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="C504" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="C505" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="C506" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="C507" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="C508" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="C509" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="C510" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C511" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C512" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C513" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C514" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="C515" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="C516" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="C517" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
-    <hyperlink ref="C518" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
-    <hyperlink ref="C519" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
-    <hyperlink ref="C520" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
-    <hyperlink ref="C521" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
-    <hyperlink ref="C522" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
-    <hyperlink ref="C523" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
-    <hyperlink ref="C524" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
-    <hyperlink ref="C525" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
-    <hyperlink ref="C526" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
-    <hyperlink ref="C527" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
-    <hyperlink ref="C606" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
-    <hyperlink ref="C528" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
-    <hyperlink ref="C529" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
-    <hyperlink ref="C530" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
-    <hyperlink ref="C531" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
-    <hyperlink ref="C532" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
-    <hyperlink ref="C533" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
-    <hyperlink ref="C534" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
-    <hyperlink ref="C607" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
-    <hyperlink ref="C535" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
-    <hyperlink ref="C536" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
-    <hyperlink ref="C537" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
-    <hyperlink ref="C538" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
-    <hyperlink ref="C539" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
-    <hyperlink ref="C540" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
-    <hyperlink ref="C541" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
-    <hyperlink ref="C542" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
-    <hyperlink ref="C543" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
-    <hyperlink ref="C544" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
-    <hyperlink ref="C545" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
-    <hyperlink ref="C546" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
-    <hyperlink ref="C547" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
-    <hyperlink ref="C548" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
-    <hyperlink ref="C549" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
-    <hyperlink ref="C550" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
-    <hyperlink ref="C551" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
-    <hyperlink ref="C552" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
-    <hyperlink ref="C608" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
-    <hyperlink ref="C553" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
-    <hyperlink ref="C554" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
-    <hyperlink ref="C555" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
-    <hyperlink ref="C556" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
-    <hyperlink ref="C557" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
-    <hyperlink ref="C558" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
-    <hyperlink ref="C559" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
-    <hyperlink ref="C560" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
-    <hyperlink ref="C561" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
-    <hyperlink ref="C562" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
-    <hyperlink ref="C563" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
-    <hyperlink ref="C564" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
-    <hyperlink ref="C565" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
-    <hyperlink ref="C566" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
-    <hyperlink ref="C567" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
-    <hyperlink ref="C568" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
-    <hyperlink ref="C569" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
-    <hyperlink ref="C570" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
-    <hyperlink ref="C571" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
-    <hyperlink ref="C572" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
-    <hyperlink ref="C573" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="C594" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C595" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C195" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C196" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C596" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C197" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C198" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C597" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C199" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C200" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C201" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C202" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C203" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C204" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C205" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C206" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C207" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C208" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C209" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C210" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C211" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C212" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C213" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C214" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C215" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C216" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="C217" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="C218" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="C219" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="C220" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="C221" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="C222" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="C223" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="C224" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="C225" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C226" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="C227" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="C228" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="C229" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="C230" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="C231" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="C232" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="C233" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="C234" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="C235" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C236" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="C237" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="C238" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="C239" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="C240" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C241" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="C242" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="C243" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="C244" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="C245" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="C246" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="C247" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="C248" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="C249" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="C250" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="C251" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="C252" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="C253" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="C254" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="C255" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C256" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="C257" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="C258" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="C259" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="C260" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C261" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="C262" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="C263" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="C264" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="C265" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C266" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="C267" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="C268" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="C269" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="C270" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C271" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="C272" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="C273" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="C274" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="C275" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C276" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="C277" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C278" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C279" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="C280" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C281" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="C282" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="C283" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C284" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C285" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C286" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C287" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C598" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C288" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C289" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C290" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="C291" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="C292" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="C293" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C294" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C295" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C296" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C297" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C298" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C299" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C300" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="C301" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C302" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C303" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C304" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C305" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C306" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C307" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C308" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C309" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C310" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C311" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C599" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C312" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C313" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C314" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C315" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C316" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C317" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C318" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C319" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C320" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C321" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C322" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C600" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C323" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C324" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C325" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C326" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C327" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C328" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C601" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C329" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C330" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C331" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C332" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C333" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C334" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C335" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C336" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C337" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C338" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C339" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C340" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C341" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C342" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C343" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C344" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C345" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C346" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C347" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C348" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C349" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C350" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C351" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C352" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C353" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C354" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C355" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C356" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C357" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C358" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C359" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C360" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C602" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C361" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C362" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C363" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C364" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C365" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C366" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C367" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C368" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C369" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C603" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C370" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C371" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C372" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C373" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C374" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C375" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C376" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C377" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C378" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C379" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C380" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C604" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C381" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C382" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C383" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C384" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C385" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C386" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C387" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C388" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C389" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C390" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C391" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C392" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C393" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C394" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C395" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C396" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C397" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C398" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C399" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C400" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C401" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C402" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C403" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C404" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C405" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C406" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C407" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C408" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C409" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C410" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C411" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C412" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C413" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C414" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C415" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C416" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C417" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C418" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C419" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C420" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C421" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C422" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C423" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C424" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C425" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C426" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C427" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C428" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C429" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C430" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C431" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C432" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C605" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C433" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C434" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C435" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C436" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C437" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C438" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C439" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C440" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C441" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C442" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C606" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C443" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C444" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C445" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C446" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C447" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C448" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C449" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C450" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C451" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C452" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C453" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C454" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C607" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C455" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C456" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C608" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C457" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C458" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C459" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C460" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C461" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C609" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C462" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C610" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C463" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C464" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C465" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C466" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C467" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C468" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C469" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C470" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C471" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C472" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C473" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C474" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C475" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C476" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C477" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C478" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C479" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C480" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C481" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C482" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C483" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C484" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C485" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="C486" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="C487" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="C488" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="C489" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="C490" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="C491" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="C492" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="C493" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C494" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C495" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="C611" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="C496" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="C497" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="C498" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="C499" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="C500" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="C501" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="C502" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="C503" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="C504" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="C505" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="C506" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="C507" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C508" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C509" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C510" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C511" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C512" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="C513" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="C514" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C515" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="C516" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="C517" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C518" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="C519" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C520" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="C521" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="C522" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="C523" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C524" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="C525" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="C526" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="C527" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="C528" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="C529" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="C530" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C612" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="C531" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C532" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="C533" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="C534" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="C535" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="C536" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="C537" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="C613" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="C538" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="C539" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="C540" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="C541" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="C542" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="C543" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="C544" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="C545" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="C546" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="C547" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="C548" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="C549" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="C550" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="C551" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="C552" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="C553" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="C554" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="C555" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="C614" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="C556" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="C557" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="C558" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="C559" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="C560" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="C561" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="C562" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="C563" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="C564" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="C565" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="C566" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C567" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="C568" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="C569" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="C570" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="C571" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
+    <hyperlink ref="C572" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
+    <hyperlink ref="C573" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
+    <hyperlink ref="C574" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
+    <hyperlink ref="C575" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
+    <hyperlink ref="C576" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3720FC0E-AE76-4F8F-8971-ED50593DABB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B78F1A8-1652-40EC-8EB0-F25F9BEB7803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2553" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="1311">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -292,6 +292,18 @@
     <t>Astérix &amp; Obélix: L'empire du milieu</t>
   </si>
   <si>
+    <t>atomic blonde</t>
+  </si>
+  <si>
+    <t>Atomic Blonde</t>
+  </si>
+  <si>
+    <t>baby, baby, baby</t>
+  </si>
+  <si>
+    <t>Baby, Baby, Baby</t>
+  </si>
+  <si>
     <t>bad guys 2 - de er super barske</t>
   </si>
   <si>
@@ -370,6 +382,12 @@
     <t>Beier på alpehotellet</t>
   </si>
   <si>
+    <t>bekkens helter</t>
+  </si>
+  <si>
+    <t>Bekkens helter</t>
+  </si>
+  <si>
     <t>beliggenhed, beliggenhed, beliggenhed</t>
   </si>
   <si>
@@ -610,6 +628,18 @@
     <t>Danmarks Dummeste</t>
   </si>
   <si>
+    <t>danser med ulve</t>
+  </si>
+  <si>
+    <t>Danser med ulve</t>
+  </si>
+  <si>
+    <t>danser med ulver</t>
+  </si>
+  <si>
+    <t>Danser med ulver</t>
+  </si>
+  <si>
     <t>danske drømme</t>
   </si>
   <si>
@@ -1252,6 +1282,12 @@
     <t>Fra Bøllehund Til Bedsteven</t>
   </si>
   <si>
+    <t>fra lade til landevej</t>
+  </si>
+  <si>
+    <t>Fra lade til landevej</t>
+  </si>
+  <si>
     <t>frank &amp; kastaniegaarden</t>
   </si>
   <si>
@@ -1474,6 +1510,18 @@
     <t>Harry Potter og fangen fra Azkaban</t>
   </si>
   <si>
+    <t>harry potter og føniksordenen</t>
+  </si>
+  <si>
+    <t>Harry Potter og Føniksordenen</t>
+  </si>
+  <si>
+    <t>harry potter og fønixordenen</t>
+  </si>
+  <si>
+    <t>Harry Potter og Fønixordenen</t>
+  </si>
+  <si>
     <t>harry potter og hemmelighedernes kammer</t>
   </si>
   <si>
@@ -2230,6 +2278,12 @@
     <t>Lykkehjulet</t>
   </si>
   <si>
+    <t>lyset i havet</t>
+  </si>
+  <si>
+    <t>Lyset i havet</t>
+  </si>
+  <si>
     <t>løvernes garde</t>
   </si>
   <si>
@@ -2278,6 +2332,12 @@
     <t>Masha Og Bjørnen</t>
   </si>
   <si>
+    <t>max og mule</t>
+  </si>
+  <si>
+    <t>Max og Mule</t>
+  </si>
+  <si>
     <t>mayafolkets tabte verden</t>
   </si>
   <si>
@@ -3472,6 +3532,18 @@
     <t>The Blacklist</t>
   </si>
   <si>
+    <t>the handmaid's tale</t>
+  </si>
+  <si>
+    <t>The Handmaid's Tale</t>
+  </si>
+  <si>
+    <t>the handmaid’s tale</t>
+  </si>
+  <si>
+    <t>The Handmaid’s Tale</t>
+  </si>
+  <si>
     <t>the holdovers</t>
   </si>
   <si>
@@ -3712,6 +3784,12 @@
     <t>Verdensmænd - Bobos surprise</t>
   </si>
   <si>
+    <t>verner panton – en dansk designikon</t>
+  </si>
+  <si>
+    <t>Verner Panton – en dansk designikon</t>
+  </si>
+  <si>
     <t>vesta-linnea</t>
   </si>
   <si>
@@ -3860,6 +3938,18 @@
   </si>
   <si>
     <t>Æblerup</t>
+  </si>
+  <si>
+    <t>æblet &amp; ormen</t>
+  </si>
+  <si>
+    <t>Æblet &amp; ormen</t>
+  </si>
+  <si>
+    <t>æblet og ormen</t>
+  </si>
+  <si>
+    <t>Æblet og ormen</t>
   </si>
   <si>
     <t>ørnens øje</t>
@@ -4229,7 +4319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E638"/>
+  <dimension ref="A1:E653"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -4804,10 +4894,10 @@
     </row>
     <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
@@ -4818,10 +4908,10 @@
     </row>
     <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -4832,10 +4922,10 @@
     </row>
     <row r="43" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6</v>
@@ -4846,10 +4936,10 @@
     </row>
     <row r="44" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -4860,10 +4950,10 @@
     </row>
     <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
@@ -4874,10 +4964,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>6</v>
@@ -4888,10 +4978,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6</v>
@@ -4902,10 +4992,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6</v>
@@ -4916,10 +5006,10 @@
     </row>
     <row r="49" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -4930,10 +5020,10 @@
     </row>
     <row r="50" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>6</v>
@@ -4944,10 +5034,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>6</v>
@@ -4958,10 +5048,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
@@ -4972,10 +5062,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
@@ -4986,10 +5076,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
@@ -5000,10 +5090,10 @@
     </row>
     <row r="55" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>6</v>
@@ -5014,10 +5104,10 @@
     </row>
     <row r="56" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>6</v>
@@ -5028,10 +5118,10 @@
     </row>
     <row r="57" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>6</v>
@@ -5042,10 +5132,10 @@
     </row>
     <row r="58" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>6</v>
@@ -5056,10 +5146,10 @@
     </row>
     <row r="59" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>6</v>
@@ -5070,10 +5160,10 @@
     </row>
     <row r="60" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>6</v>
@@ -5084,10 +5174,10 @@
     </row>
     <row r="61" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>6</v>
@@ -5098,10 +5188,10 @@
     </row>
     <row r="62" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>6</v>
@@ -5112,10 +5202,10 @@
     </row>
     <row r="63" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>6</v>
@@ -5126,10 +5216,10 @@
     </row>
     <row r="64" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B64" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>6</v>
@@ -5140,10 +5230,10 @@
     </row>
     <row r="65" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -5182,10 +5272,10 @@
     </row>
     <row r="68" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>6</v>
@@ -5196,10 +5286,10 @@
     </row>
     <row r="69" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>6</v>
@@ -5210,10 +5300,10 @@
     </row>
     <row r="70" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>6</v>
@@ -5224,10 +5314,10 @@
     </row>
     <row r="71" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>6</v>
@@ -5238,10 +5328,10 @@
     </row>
     <row r="72" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>6</v>
@@ -5252,10 +5342,10 @@
     </row>
     <row r="73" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B73" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>6</v>
@@ -5266,10 +5356,10 @@
     </row>
     <row r="74" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>6</v>
@@ -5280,10 +5370,10 @@
     </row>
     <row r="75" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>6</v>
@@ -5294,10 +5384,10 @@
     </row>
     <row r="76" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>6</v>
@@ -5308,10 +5398,10 @@
     </row>
     <row r="77" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>6</v>
@@ -5322,10 +5412,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>6</v>
@@ -5336,10 +5426,10 @@
     </row>
     <row r="79" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>6</v>
@@ -5350,10 +5440,10 @@
     </row>
     <row r="80" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -5364,10 +5454,10 @@
     </row>
     <row r="81" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>6</v>
@@ -5378,10 +5468,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B82" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
@@ -5392,10 +5482,10 @@
     </row>
     <row r="83" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B83" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>6</v>
@@ -5406,10 +5496,10 @@
     </row>
     <row r="84" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>6</v>
@@ -5420,10 +5510,10 @@
     </row>
     <row r="85" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B85" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>6</v>
@@ -5434,10 +5524,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B86" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>6</v>
@@ -5448,10 +5538,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B87" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>6</v>
@@ -5462,10 +5552,10 @@
     </row>
     <row r="88" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B88" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>6</v>
@@ -5476,10 +5566,10 @@
     </row>
     <row r="89" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B89" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>6</v>
@@ -5490,10 +5580,10 @@
     </row>
     <row r="90" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B90" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>6</v>
@@ -5504,10 +5594,10 @@
     </row>
     <row r="91" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B91" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>6</v>
@@ -5518,10 +5608,10 @@
     </row>
     <row r="92" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B92" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>6</v>
@@ -5532,10 +5622,10 @@
     </row>
     <row r="93" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B93" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>6</v>
@@ -5546,10 +5636,10 @@
     </row>
     <row r="94" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B94" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>6</v>
@@ -5560,10 +5650,10 @@
     </row>
     <row r="95" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B95" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>6</v>
@@ -5574,10 +5664,10 @@
     </row>
     <row r="96" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B96" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>6</v>
@@ -5602,10 +5692,10 @@
     </row>
     <row r="98" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B98" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>6</v>
@@ -5616,10 +5706,10 @@
     </row>
     <row r="99" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B99" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>6</v>
@@ -5630,10 +5720,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B100" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>6</v>
@@ -5658,10 +5748,10 @@
     </row>
     <row r="102" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B102" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>6</v>
@@ -5672,10 +5762,10 @@
     </row>
     <row r="103" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B103" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>6</v>
@@ -5686,10 +5776,10 @@
     </row>
     <row r="104" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B104" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -5700,10 +5790,10 @@
     </row>
     <row r="105" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B105" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>6</v>
@@ -5714,10 +5804,10 @@
     </row>
     <row r="106" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B106" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>6</v>
@@ -5728,10 +5818,10 @@
     </row>
     <row r="107" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B107" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>6</v>
@@ -5798,10 +5888,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B112" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>6</v>
@@ -5812,10 +5902,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B113" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>6</v>
@@ -5826,10 +5916,10 @@
     </row>
     <row r="114" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B114" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>6</v>
@@ -5840,10 +5930,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B115" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>6</v>
@@ -5854,10 +5944,10 @@
     </row>
     <row r="116" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B116" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>6</v>
@@ -5868,10 +5958,10 @@
     </row>
     <row r="117" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B117" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>6</v>
@@ -5882,10 +5972,10 @@
     </row>
     <row r="118" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B118" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>6</v>
@@ -5896,10 +5986,10 @@
     </row>
     <row r="119" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B119" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>6</v>
@@ -5966,10 +6056,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B124" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -6064,10 +6154,10 @@
     </row>
     <row r="131" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B131" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>6</v>
@@ -6078,10 +6168,10 @@
     </row>
     <row r="132" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B132" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>6</v>
@@ -6092,10 +6182,10 @@
     </row>
     <row r="133" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B133" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>6</v>
@@ -6106,10 +6196,10 @@
     </row>
     <row r="134" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B134" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>6</v>
@@ -6120,10 +6210,10 @@
     </row>
     <row r="135" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B135" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>6</v>
@@ -6134,10 +6224,10 @@
     </row>
     <row r="136" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B136" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>6</v>
@@ -6148,10 +6238,10 @@
     </row>
     <row r="137" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B137" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>6</v>
@@ -6162,10 +6252,10 @@
     </row>
     <row r="138" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B138" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>6</v>
@@ -6176,10 +6266,10 @@
     </row>
     <row r="139" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B139" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>6</v>
@@ -6190,10 +6280,10 @@
     </row>
     <row r="140" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B140" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>6</v>
@@ -6204,10 +6294,10 @@
     </row>
     <row r="141" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B141" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>6</v>
@@ -6218,10 +6308,10 @@
     </row>
     <row r="142" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B142" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>6</v>
@@ -6232,10 +6322,10 @@
     </row>
     <row r="143" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B143" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>6</v>
@@ -6246,10 +6336,10 @@
     </row>
     <row r="144" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B144" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>6</v>
@@ -6260,10 +6350,10 @@
     </row>
     <row r="145" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B145" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>6</v>
@@ -6274,10 +6364,10 @@
     </row>
     <row r="146" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B146" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>6</v>
@@ -6288,10 +6378,10 @@
     </row>
     <row r="147" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B147" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>6</v>
@@ -6302,10 +6392,10 @@
     </row>
     <row r="148" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B148" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>6</v>
@@ -6316,10 +6406,10 @@
     </row>
     <row r="149" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B149" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>6</v>
@@ -6330,10 +6420,10 @@
     </row>
     <row r="150" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B150" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>6</v>
@@ -6344,10 +6434,10 @@
     </row>
     <row r="151" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B151" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>6</v>
@@ -6358,10 +6448,10 @@
     </row>
     <row r="152" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B152" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>6</v>
@@ -6372,10 +6462,10 @@
     </row>
     <row r="153" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B153" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>6</v>
@@ -6386,10 +6476,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B154" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>6</v>
@@ -6400,10 +6490,10 @@
     </row>
     <row r="155" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B155" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>6</v>
@@ -6414,10 +6504,10 @@
     </row>
     <row r="156" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B156" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>6</v>
@@ -6428,10 +6518,10 @@
     </row>
     <row r="157" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B157" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>6</v>
@@ -6442,10 +6532,10 @@
     </row>
     <row r="158" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B158" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>6</v>
@@ -6456,10 +6546,10 @@
     </row>
     <row r="159" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B159" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>6</v>
@@ -6470,10 +6560,10 @@
     </row>
     <row r="160" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B160" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>6</v>
@@ -6484,10 +6574,10 @@
     </row>
     <row r="161" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B161" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>6</v>
@@ -6498,10 +6588,10 @@
     </row>
     <row r="162" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B162" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>6</v>
@@ -6512,10 +6602,10 @@
     </row>
     <row r="163" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B163" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>6</v>
@@ -6526,10 +6616,10 @@
     </row>
     <row r="164" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B164" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>6</v>
@@ -6540,10 +6630,10 @@
     </row>
     <row r="165" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B165" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>6</v>
@@ -6554,10 +6644,10 @@
     </row>
     <row r="166" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B166" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>6</v>
@@ -6568,10 +6658,10 @@
     </row>
     <row r="167" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B167" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>6</v>
@@ -6582,10 +6672,10 @@
     </row>
     <row r="168" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B168" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>6</v>
@@ -6596,10 +6686,10 @@
     </row>
     <row r="169" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B169" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>6</v>
@@ -6610,10 +6700,10 @@
     </row>
     <row r="170" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B170" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>6</v>
@@ -6624,10 +6714,10 @@
     </row>
     <row r="171" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B171" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>6</v>
@@ -6638,10 +6728,10 @@
     </row>
     <row r="172" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B172" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>6</v>
@@ -6652,10 +6742,10 @@
     </row>
     <row r="173" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B173" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>6</v>
@@ -6666,10 +6756,10 @@
     </row>
     <row r="174" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B174" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>6</v>
@@ -6680,10 +6770,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B175" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>6</v>
@@ -6694,10 +6784,10 @@
     </row>
     <row r="176" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B176" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>6</v>
@@ -6708,10 +6798,10 @@
     </row>
     <row r="177" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B177" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>6</v>
@@ -6722,10 +6812,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B178" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>6</v>
@@ -6736,10 +6826,10 @@
     </row>
     <row r="179" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B179" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>6</v>
@@ -6750,10 +6840,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B180" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>6</v>
@@ -6764,10 +6854,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B181" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>6</v>
@@ -6778,10 +6868,10 @@
     </row>
     <row r="182" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B182" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>6</v>
@@ -6792,10 +6882,10 @@
     </row>
     <row r="183" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B183" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -6806,10 +6896,10 @@
     </row>
     <row r="184" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B184" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>6</v>
@@ -6820,10 +6910,10 @@
     </row>
     <row r="185" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B185" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>6</v>
@@ -6834,10 +6924,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B186" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>6</v>
@@ -6946,10 +7036,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B194" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>6</v>
@@ -6960,10 +7050,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B195" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>6</v>
@@ -6974,10 +7064,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B196" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>6</v>
@@ -6988,10 +7078,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B197" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>6</v>
@@ -7002,10 +7092,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B198" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>6</v>
@@ -7016,10 +7106,10 @@
     </row>
     <row r="199" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B199" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>6</v>
@@ -7072,10 +7162,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B203" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>6</v>
@@ -7086,10 +7176,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B204" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>6</v>
@@ -7100,10 +7190,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B205" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>6</v>
@@ -7114,10 +7204,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B206" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>6</v>
@@ -7128,10 +7218,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B207" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>6</v>
@@ -7142,10 +7232,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B208" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>6</v>
@@ -7338,10 +7428,10 @@
     </row>
     <row r="222" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B222" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>6</v>
@@ -7352,10 +7442,10 @@
     </row>
     <row r="223" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B223" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>6</v>
@@ -7366,10 +7456,10 @@
     </row>
     <row r="224" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B224" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>6</v>
@@ -7380,10 +7470,10 @@
     </row>
     <row r="225" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B225" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -7394,10 +7484,10 @@
     </row>
     <row r="226" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B226" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>6</v>
@@ -7408,10 +7498,10 @@
     </row>
     <row r="227" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B227" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>6</v>
@@ -7422,10 +7512,10 @@
     </row>
     <row r="228" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B228" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>6</v>
@@ -7436,10 +7526,10 @@
     </row>
     <row r="229" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B229" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -7450,10 +7540,10 @@
     </row>
     <row r="230" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B230" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>6</v>
@@ -7464,10 +7554,10 @@
     </row>
     <row r="231" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B231" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>6</v>
@@ -7478,10 +7568,10 @@
     </row>
     <row r="232" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B232" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -7492,10 +7582,10 @@
     </row>
     <row r="233" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B233" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -7506,10 +7596,10 @@
     </row>
     <row r="234" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B234" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>6</v>
@@ -7520,10 +7610,10 @@
     </row>
     <row r="235" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B235" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>6</v>
@@ -7534,10 +7624,10 @@
     </row>
     <row r="236" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B236" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
@@ -7548,10 +7638,10 @@
     </row>
     <row r="237" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B237" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
@@ -8038,10 +8128,10 @@
     </row>
     <row r="272" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B272" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>6</v>
@@ -8052,10 +8142,10 @@
     </row>
     <row r="273" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B273" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>6</v>
@@ -8066,10 +8156,10 @@
     </row>
     <row r="274" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B274" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>6</v>
@@ -8080,10 +8170,10 @@
     </row>
     <row r="275" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B275" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>6</v>
@@ -8094,10 +8184,10 @@
     </row>
     <row r="276" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B276" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>6</v>
@@ -8108,10 +8198,10 @@
     </row>
     <row r="277" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B277" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>6</v>
@@ -8122,10 +8212,10 @@
     </row>
     <row r="278" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B278" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>6</v>
@@ -8136,10 +8226,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B279" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>6</v>
@@ -8150,10 +8240,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B280" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>6</v>
@@ -8164,10 +8254,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B281" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>6</v>
@@ -8178,10 +8268,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B282" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>6</v>
@@ -8192,10 +8282,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B283" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>6</v>
@@ -8206,10 +8296,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B284" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>6</v>
@@ -8220,10 +8310,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B285" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -8234,10 +8324,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B286" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>6</v>
@@ -8248,10 +8338,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B287" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>6</v>
@@ -8262,10 +8352,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B288" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>6</v>
@@ -8276,10 +8366,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B289" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>6</v>
@@ -8290,10 +8380,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B290" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>6</v>
@@ -8304,10 +8394,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B291" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>6</v>
@@ -8318,10 +8408,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="B292" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>6</v>
@@ -8332,10 +8422,10 @@
     </row>
     <row r="293" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B293" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>6</v>
@@ -8346,10 +8436,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B294" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>6</v>
@@ -8360,10 +8450,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B295" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>6</v>
@@ -8374,10 +8464,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B296" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>6</v>
@@ -8388,10 +8478,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B297" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>6</v>
@@ -8402,10 +8492,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B298" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>6</v>
@@ -8416,10 +8506,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B299" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>6</v>
@@ -8430,10 +8520,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B300" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>6</v>
@@ -8444,10 +8534,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B301" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>6</v>
@@ -8458,10 +8548,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B302" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -8472,10 +8562,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B303" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -8486,10 +8576,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B304" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -8500,10 +8590,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B305" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>6</v>
@@ -8514,10 +8604,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B306" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -8528,10 +8618,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B307" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>6</v>
@@ -8542,10 +8632,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B308" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>6</v>
@@ -8556,10 +8646,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B309" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>6</v>
@@ -8570,10 +8660,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B310" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -8584,10 +8674,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B311" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>6</v>
@@ -8598,10 +8688,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B312" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -8612,10 +8702,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B313" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -8626,10 +8716,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B314" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -8640,10 +8730,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B315" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>6</v>
@@ -8654,10 +8744,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="B316" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>6</v>
@@ -8668,10 +8758,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B317" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>6</v>
@@ -8682,10 +8772,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B318" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>6</v>
@@ -8696,10 +8786,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B319" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>6</v>
@@ -8710,10 +8800,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B320" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>6</v>
@@ -8724,10 +8814,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B321" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>6</v>
@@ -8738,10 +8828,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B322" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -8752,10 +8842,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B323" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>6</v>
@@ -8766,10 +8856,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B324" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>6</v>
@@ -8780,10 +8870,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="B325" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>6</v>
@@ -8794,10 +8884,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B326" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>6</v>
@@ -8808,10 +8898,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="B327" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>6</v>
@@ -8822,10 +8912,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B328" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>6</v>
@@ -8836,10 +8926,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="B329" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>6</v>
@@ -8850,10 +8940,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B330" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -8864,10 +8954,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="B331" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>6</v>
@@ -8878,10 +8968,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B332" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>6</v>
@@ -8892,10 +8982,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="B333" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>6</v>
@@ -8906,10 +8996,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="B334" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>6</v>
@@ -8920,10 +9010,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="B335" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>6</v>
@@ -8934,10 +9024,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="B336" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>6</v>
@@ -8948,10 +9038,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="B337" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>6</v>
@@ -8962,10 +9052,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="B338" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>6</v>
@@ -8976,10 +9066,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="B339" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>6</v>
@@ -8990,10 +9080,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="B340" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>6</v>
@@ -9004,10 +9094,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B341" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>6</v>
@@ -9018,10 +9108,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="B342" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>6</v>
@@ -9032,10 +9122,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="B343" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>6</v>
@@ -9046,10 +9136,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B344" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>6</v>
@@ -9060,10 +9150,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B345" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>6</v>
@@ -9074,10 +9164,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B346" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>6</v>
@@ -9088,10 +9178,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B347" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>6</v>
@@ -9102,10 +9192,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B348" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>6</v>
@@ -9116,10 +9206,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B349" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>6</v>
@@ -9130,10 +9220,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B350" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>6</v>
@@ -9144,10 +9234,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B351" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>6</v>
@@ -9158,10 +9248,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B352" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>6</v>
@@ -9172,10 +9262,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B353" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>6</v>
@@ -9186,10 +9276,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B354" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>6</v>
@@ -9200,10 +9290,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B355" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>6</v>
@@ -9214,10 +9304,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B356" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>6</v>
@@ -9228,10 +9318,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B357" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>6</v>
@@ -9242,10 +9332,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B358" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>6</v>
@@ -9256,10 +9346,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B359" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>6</v>
@@ -9270,10 +9360,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B360" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>6</v>
@@ -9284,10 +9374,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B361" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>6</v>
@@ -9298,10 +9388,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B362" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -9312,10 +9402,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B363" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>6</v>
@@ -9326,10 +9416,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B364" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>6</v>
@@ -9340,10 +9430,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B365" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>6</v>
@@ -9354,10 +9444,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="B366" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>6</v>
@@ -9368,10 +9458,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="B367" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>6</v>
@@ -9382,10 +9472,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="B368" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>6</v>
@@ -9396,10 +9486,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="B369" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>6</v>
@@ -9410,10 +9500,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="B370" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>6</v>
@@ -9424,10 +9514,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="B371" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>6</v>
@@ -9438,10 +9528,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="B372" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>6</v>
@@ -9452,10 +9542,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="B373" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>6</v>
@@ -9466,10 +9556,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="B374" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>6</v>
@@ -9480,10 +9570,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="B375" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>6</v>
@@ -9494,10 +9584,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="B376" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>6</v>
@@ -9508,10 +9598,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="B377" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>6</v>
@@ -9522,10 +9612,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="B378" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>6</v>
@@ -9536,10 +9626,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="B379" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>6</v>
@@ -9550,10 +9640,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="B380" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>6</v>
@@ -9564,10 +9654,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="B381" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>6</v>
@@ -9578,10 +9668,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="B382" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>6</v>
@@ -9592,10 +9682,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="B383" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>6</v>
@@ -9606,10 +9696,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="B384" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>6</v>
@@ -9620,10 +9710,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="B385" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>6</v>
@@ -9634,10 +9724,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="B386" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>6</v>
@@ -9648,10 +9738,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="B387" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>6</v>
@@ -9662,10 +9752,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="B388" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>6</v>
@@ -9676,10 +9766,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B389" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>6</v>
@@ -9690,10 +9780,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="B390" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>6</v>
@@ -9704,10 +9794,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="B391" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>6</v>
@@ -9718,10 +9808,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="B392" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>6</v>
@@ -9732,10 +9822,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="B393" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>6</v>
@@ -9746,10 +9836,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="B394" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>6</v>
@@ -9760,10 +9850,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>873</v>
+        <v>859</v>
       </c>
       <c r="B395" t="s">
-        <v>874</v>
+        <v>860</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>6</v>
@@ -9774,10 +9864,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="B396" t="s">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>6</v>
@@ -9788,10 +9878,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="B397" t="s">
-        <v>878</v>
+        <v>864</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>6</v>
@@ -9802,10 +9892,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>879</v>
+        <v>865</v>
       </c>
       <c r="B398" t="s">
-        <v>880</v>
+        <v>866</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>6</v>
@@ -9816,10 +9906,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
       <c r="B399" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>6</v>
@@ -9830,10 +9920,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
       <c r="B400" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>6</v>
@@ -9844,10 +9934,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="B401" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>6</v>
@@ -9858,10 +9948,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
       <c r="B402" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>6</v>
@@ -9872,10 +9962,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>889</v>
+        <v>877</v>
       </c>
       <c r="B403" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>6</v>
@@ -9886,10 +9976,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
       <c r="B404" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>6</v>
@@ -9900,10 +9990,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="B405" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>6</v>
@@ -9914,10 +10004,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="B406" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>6</v>
@@ -9928,10 +10018,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>899</v>
+        <v>885</v>
       </c>
       <c r="B407" t="s">
-        <v>900</v>
+        <v>886</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>6</v>
@@ -9942,10 +10032,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>901</v>
+        <v>887</v>
       </c>
       <c r="B408" t="s">
-        <v>902</v>
+        <v>888</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>6</v>
@@ -9956,10 +10046,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>903</v>
+        <v>889</v>
       </c>
       <c r="B409" t="s">
-        <v>904</v>
+        <v>890</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>6</v>
@@ -9970,10 +10060,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>905</v>
+        <v>891</v>
       </c>
       <c r="B410" t="s">
-        <v>906</v>
+        <v>892</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>6</v>
@@ -9984,10 +10074,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>907</v>
+        <v>893</v>
       </c>
       <c r="B411" t="s">
-        <v>908</v>
+        <v>894</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>6</v>
@@ -9998,10 +10088,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>909</v>
+        <v>895</v>
       </c>
       <c r="B412" t="s">
-        <v>910</v>
+        <v>896</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>6</v>
@@ -10012,10 +10102,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>911</v>
+        <v>897</v>
       </c>
       <c r="B413" t="s">
-        <v>912</v>
+        <v>898</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>6</v>
@@ -10026,10 +10116,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
       <c r="B414" t="s">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>6</v>
@@ -10040,10 +10130,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>915</v>
+        <v>901</v>
       </c>
       <c r="B415" t="s">
-        <v>916</v>
+        <v>902</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>6</v>
@@ -10054,10 +10144,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>917</v>
+        <v>903</v>
       </c>
       <c r="B416" t="s">
-        <v>918</v>
+        <v>904</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>6</v>
@@ -10068,10 +10158,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>919</v>
+        <v>905</v>
       </c>
       <c r="B417" t="s">
-        <v>920</v>
+        <v>906</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>6</v>
@@ -10082,10 +10172,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>921</v>
+        <v>907</v>
       </c>
       <c r="B418" t="s">
-        <v>922</v>
+        <v>908</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>6</v>
@@ -10096,10 +10186,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="B419" t="s">
-        <v>924</v>
+        <v>910</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -10110,10 +10200,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>925</v>
+        <v>911</v>
       </c>
       <c r="B420" t="s">
-        <v>926</v>
+        <v>912</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>6</v>
@@ -10124,10 +10214,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>927</v>
+        <v>913</v>
       </c>
       <c r="B421" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>6</v>
@@ -10138,10 +10228,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>929</v>
+        <v>915</v>
       </c>
       <c r="B422" t="s">
-        <v>930</v>
+        <v>916</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>6</v>
@@ -10152,10 +10242,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>931</v>
+        <v>917</v>
       </c>
       <c r="B423" t="s">
-        <v>932</v>
+        <v>918</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>6</v>
@@ -10166,10 +10256,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>933</v>
+        <v>919</v>
       </c>
       <c r="B424" t="s">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>6</v>
@@ -10180,10 +10270,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>935</v>
+        <v>921</v>
       </c>
       <c r="B425" t="s">
-        <v>936</v>
+        <v>922</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>6</v>
@@ -10194,10 +10284,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>937</v>
+        <v>923</v>
       </c>
       <c r="B426" t="s">
-        <v>938</v>
+        <v>924</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>6</v>
@@ -10208,10 +10298,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>939</v>
+        <v>925</v>
       </c>
       <c r="B427" t="s">
-        <v>940</v>
+        <v>926</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>6</v>
@@ -10222,10 +10312,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="B428" t="s">
-        <v>942</v>
+        <v>928</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -10236,10 +10326,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>943</v>
+        <v>929</v>
       </c>
       <c r="B429" t="s">
-        <v>944</v>
+        <v>930</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>6</v>
@@ -10250,10 +10340,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>945</v>
+        <v>931</v>
       </c>
       <c r="B430" t="s">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>6</v>
@@ -10264,10 +10354,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="B431" t="s">
-        <v>948</v>
+        <v>934</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>6</v>
@@ -10278,10 +10368,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B432" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>6</v>
@@ -10292,10 +10382,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>951</v>
+        <v>937</v>
       </c>
       <c r="B433" t="s">
-        <v>952</v>
+        <v>938</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>6</v>
@@ -10306,10 +10396,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>953</v>
+        <v>939</v>
       </c>
       <c r="B434" t="s">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>6</v>
@@ -10320,10 +10410,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>955</v>
+        <v>941</v>
       </c>
       <c r="B435" t="s">
-        <v>956</v>
+        <v>942</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>6</v>
@@ -10334,10 +10424,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="B436" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>6</v>
@@ -10348,10 +10438,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>959</v>
+        <v>945</v>
       </c>
       <c r="B437" t="s">
-        <v>960</v>
+        <v>946</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>6</v>
@@ -10362,10 +10452,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
       <c r="B438" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>6</v>
@@ -10376,10 +10466,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="B439" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>6</v>
@@ -10390,10 +10480,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>967</v>
+        <v>951</v>
       </c>
       <c r="B440" t="s">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>6</v>
@@ -10404,10 +10494,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="B441" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>6</v>
@@ -10418,10 +10508,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="B442" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>6</v>
@@ -10432,10 +10522,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="B443" t="s">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>6</v>
@@ -10446,10 +10536,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="B444" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>6</v>
@@ -10460,10 +10550,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="B445" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>6</v>
@@ -10474,10 +10564,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>981</v>
+        <v>963</v>
       </c>
       <c r="B446" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>6</v>
@@ -10488,10 +10578,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="B447" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>6</v>
@@ -10502,10 +10592,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>989</v>
+        <v>967</v>
       </c>
       <c r="B448" t="s">
-        <v>990</v>
+        <v>968</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>6</v>
@@ -10516,10 +10606,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>991</v>
+        <v>969</v>
       </c>
       <c r="B449" t="s">
-        <v>992</v>
+        <v>970</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>6</v>
@@ -10530,10 +10620,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>993</v>
+        <v>971</v>
       </c>
       <c r="B450" t="s">
-        <v>994</v>
+        <v>972</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>6</v>
@@ -10544,10 +10634,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>995</v>
+        <v>973</v>
       </c>
       <c r="B451" t="s">
-        <v>996</v>
+        <v>974</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>6</v>
@@ -10558,10 +10648,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>997</v>
+        <v>975</v>
       </c>
       <c r="B452" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>6</v>
@@ -10572,10 +10662,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>999</v>
+        <v>977</v>
       </c>
       <c r="B453" t="s">
-        <v>1000</v>
+        <v>978</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>6</v>
@@ -10586,10 +10676,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1001</v>
+        <v>979</v>
       </c>
       <c r="B454" t="s">
-        <v>1002</v>
+        <v>980</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>6</v>
@@ -10600,10 +10690,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>1003</v>
+        <v>983</v>
       </c>
       <c r="B455" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>6</v>
@@ -10614,10 +10704,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1005</v>
+        <v>985</v>
       </c>
       <c r="B456" t="s">
-        <v>1006</v>
+        <v>986</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>6</v>
@@ -10628,10 +10718,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1007</v>
+        <v>987</v>
       </c>
       <c r="B457" t="s">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>6</v>
@@ -10642,10 +10732,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1009</v>
+        <v>989</v>
       </c>
       <c r="B458" t="s">
-        <v>1010</v>
+        <v>990</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>6</v>
@@ -10656,10 +10746,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1011</v>
+        <v>991</v>
       </c>
       <c r="B459" t="s">
-        <v>1012</v>
+        <v>992</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>6</v>
@@ -10670,10 +10760,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1015</v>
+        <v>993</v>
       </c>
       <c r="B460" t="s">
-        <v>1016</v>
+        <v>994</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>6</v>
@@ -10684,10 +10774,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="B461" t="s">
-        <v>1018</v>
+        <v>996</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>6</v>
@@ -10698,10 +10788,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1021</v>
+        <v>997</v>
       </c>
       <c r="B462" t="s">
-        <v>1022</v>
+        <v>998</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>6</v>
@@ -10712,10 +10802,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1023</v>
+        <v>999</v>
       </c>
       <c r="B463" t="s">
-        <v>1024</v>
+        <v>1000</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>6</v>
@@ -10726,10 +10816,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>1025</v>
+        <v>1001</v>
       </c>
       <c r="B464" t="s">
-        <v>1026</v>
+        <v>1002</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>6</v>
@@ -10740,10 +10830,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>1029</v>
+        <v>1003</v>
       </c>
       <c r="B465" t="s">
-        <v>1030</v>
+        <v>1004</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>6</v>
@@ -10754,10 +10844,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1031</v>
+        <v>1005</v>
       </c>
       <c r="B466" t="s">
-        <v>1032</v>
+        <v>1006</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>6</v>
@@ -10768,10 +10858,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1035</v>
+        <v>1009</v>
       </c>
       <c r="B467" t="s">
-        <v>1036</v>
+        <v>1010</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>6</v>
@@ -10782,10 +10872,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1039</v>
+        <v>1011</v>
       </c>
       <c r="B468" t="s">
-        <v>1040</v>
+        <v>1012</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>6</v>
@@ -10796,10 +10886,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1041</v>
+        <v>1013</v>
       </c>
       <c r="B469" t="s">
-        <v>1042</v>
+        <v>1014</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>6</v>
@@ -10810,10 +10900,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1043</v>
+        <v>1015</v>
       </c>
       <c r="B470" t="s">
-        <v>1044</v>
+        <v>1016</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>6</v>
@@ -10824,10 +10914,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1045</v>
+        <v>1017</v>
       </c>
       <c r="B471" t="s">
-        <v>1046</v>
+        <v>1018</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>6</v>
@@ -10838,10 +10928,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1047</v>
+        <v>1019</v>
       </c>
       <c r="B472" t="s">
-        <v>1048</v>
+        <v>1020</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>6</v>
@@ -10852,10 +10942,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1049</v>
+        <v>1021</v>
       </c>
       <c r="B473" t="s">
-        <v>1050</v>
+        <v>1022</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>6</v>
@@ -10866,10 +10956,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>1051</v>
+        <v>1023</v>
       </c>
       <c r="B474" t="s">
-        <v>1052</v>
+        <v>1024</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>6</v>
@@ -10880,10 +10970,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1053</v>
+        <v>1025</v>
       </c>
       <c r="B475" t="s">
-        <v>1054</v>
+        <v>1026</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>6</v>
@@ -10894,10 +10984,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1059</v>
+        <v>1027</v>
       </c>
       <c r="B476" t="s">
-        <v>1060</v>
+        <v>1028</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>6</v>
@@ -10908,10 +10998,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1061</v>
+        <v>1029</v>
       </c>
       <c r="B477" t="s">
-        <v>1062</v>
+        <v>1030</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>6</v>
@@ -10922,10 +11012,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>1063</v>
+        <v>1031</v>
       </c>
       <c r="B478" t="s">
-        <v>1064</v>
+        <v>1032</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -10936,10 +11026,10 @@
     </row>
     <row r="479" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1065</v>
+        <v>1035</v>
       </c>
       <c r="B479" t="s">
-        <v>1066</v>
+        <v>1036</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>6</v>
@@ -10950,10 +11040,10 @@
     </row>
     <row r="480" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1067</v>
+        <v>1037</v>
       </c>
       <c r="B480" t="s">
-        <v>1068</v>
+        <v>1038</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>6</v>
@@ -10964,10 +11054,10 @@
     </row>
     <row r="481" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1069</v>
+        <v>1041</v>
       </c>
       <c r="B481" t="s">
-        <v>1070</v>
+        <v>1042</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>6</v>
@@ -10978,10 +11068,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1071</v>
+        <v>1043</v>
       </c>
       <c r="B482" t="s">
-        <v>1072</v>
+        <v>1044</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>6</v>
@@ -10992,10 +11082,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>1073</v>
+        <v>1045</v>
       </c>
       <c r="B483" t="s">
-        <v>1074</v>
+        <v>1046</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>6</v>
@@ -11006,10 +11096,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>1075</v>
+        <v>1047</v>
       </c>
       <c r="B484" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>6</v>
@@ -11020,10 +11110,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1077</v>
+        <v>1049</v>
       </c>
       <c r="B485" t="s">
-        <v>1078</v>
+        <v>1050</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>6</v>
@@ -11034,10 +11124,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1079</v>
+        <v>1051</v>
       </c>
       <c r="B486" t="s">
-        <v>1080</v>
+        <v>1052</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>6</v>
@@ -11048,10 +11138,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>1081</v>
+        <v>1055</v>
       </c>
       <c r="B487" t="s">
-        <v>1082</v>
+        <v>1056</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>6</v>
@@ -11062,10 +11152,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1083</v>
+        <v>1059</v>
       </c>
       <c r="B488" t="s">
-        <v>1084</v>
+        <v>1060</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>6</v>
@@ -11076,10 +11166,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1085</v>
+        <v>1061</v>
       </c>
       <c r="B489" t="s">
-        <v>1086</v>
+        <v>1062</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>6</v>
@@ -11090,10 +11180,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>1087</v>
+        <v>1063</v>
       </c>
       <c r="B490" t="s">
-        <v>1088</v>
+        <v>1064</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>6</v>
@@ -11104,10 +11194,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1089</v>
+        <v>1065</v>
       </c>
       <c r="B491" t="s">
-        <v>1090</v>
+        <v>1066</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>6</v>
@@ -11118,10 +11208,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1091</v>
+        <v>1067</v>
       </c>
       <c r="B492" t="s">
-        <v>1092</v>
+        <v>1068</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>6</v>
@@ -11132,10 +11222,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1093</v>
+        <v>1069</v>
       </c>
       <c r="B493" t="s">
-        <v>1094</v>
+        <v>1070</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>6</v>
@@ -11146,10 +11236,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>1095</v>
+        <v>1071</v>
       </c>
       <c r="B494" t="s">
-        <v>1096</v>
+        <v>1072</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>6</v>
@@ -11160,10 +11250,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>1097</v>
+        <v>1073</v>
       </c>
       <c r="B495" t="s">
-        <v>1098</v>
+        <v>1074</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>6</v>
@@ -11174,10 +11264,10 @@
     </row>
     <row r="496" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1099</v>
+        <v>1075</v>
       </c>
       <c r="B496" t="s">
-        <v>1100</v>
+        <v>1076</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>6</v>
@@ -11188,10 +11278,10 @@
     </row>
     <row r="497" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1101</v>
+        <v>1077</v>
       </c>
       <c r="B497" t="s">
-        <v>1102</v>
+        <v>1078</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>6</v>
@@ -11202,10 +11292,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>1103</v>
+        <v>1079</v>
       </c>
       <c r="B498" t="s">
-        <v>1104</v>
+        <v>1080</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>6</v>
@@ -11216,10 +11306,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>1105</v>
+        <v>1081</v>
       </c>
       <c r="B499" t="s">
-        <v>1106</v>
+        <v>1082</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>6</v>
@@ -11230,10 +11320,10 @@
     </row>
     <row r="500" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1107</v>
+        <v>1083</v>
       </c>
       <c r="B500" t="s">
-        <v>1108</v>
+        <v>1084</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>6</v>
@@ -11244,10 +11334,10 @@
     </row>
     <row r="501" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1111</v>
+        <v>1085</v>
       </c>
       <c r="B501" t="s">
-        <v>1112</v>
+        <v>1086</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>6</v>
@@ -11258,10 +11348,10 @@
     </row>
     <row r="502" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>1113</v>
+        <v>1087</v>
       </c>
       <c r="B502" t="s">
-        <v>1114</v>
+        <v>1088</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>6</v>
@@ -11272,10 +11362,10 @@
     </row>
     <row r="503" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1115</v>
+        <v>1089</v>
       </c>
       <c r="B503" t="s">
-        <v>1116</v>
+        <v>1090</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>6</v>
@@ -11286,10 +11376,10 @@
     </row>
     <row r="504" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1117</v>
+        <v>1091</v>
       </c>
       <c r="B504" t="s">
-        <v>1118</v>
+        <v>1092</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>6</v>
@@ -11300,10 +11390,10 @@
     </row>
     <row r="505" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1119</v>
+        <v>1093</v>
       </c>
       <c r="B505" t="s">
-        <v>1120</v>
+        <v>1094</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>6</v>
@@ -11314,10 +11404,10 @@
     </row>
     <row r="506" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>1121</v>
+        <v>1095</v>
       </c>
       <c r="B506" t="s">
-        <v>1122</v>
+        <v>1096</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>6</v>
@@ -11328,10 +11418,10 @@
     </row>
     <row r="507" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1123</v>
+        <v>1097</v>
       </c>
       <c r="B507" t="s">
-        <v>1124</v>
+        <v>1098</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>6</v>
@@ -11342,10 +11432,10 @@
     </row>
     <row r="508" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1125</v>
+        <v>1099</v>
       </c>
       <c r="B508" t="s">
-        <v>1126</v>
+        <v>1100</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>6</v>
@@ -11356,10 +11446,10 @@
     </row>
     <row r="509" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1127</v>
+        <v>1101</v>
       </c>
       <c r="B509" t="s">
-        <v>1128</v>
+        <v>1102</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>6</v>
@@ -11370,10 +11460,10 @@
     </row>
     <row r="510" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1129</v>
+        <v>1103</v>
       </c>
       <c r="B510" t="s">
-        <v>1130</v>
+        <v>1104</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>6</v>
@@ -11384,10 +11474,10 @@
     </row>
     <row r="511" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1131</v>
+        <v>1105</v>
       </c>
       <c r="B511" t="s">
-        <v>1132</v>
+        <v>1106</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>6</v>
@@ -11398,10 +11488,10 @@
     </row>
     <row r="512" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1133</v>
+        <v>1107</v>
       </c>
       <c r="B512" t="s">
-        <v>1134</v>
+        <v>1108</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>6</v>
@@ -11412,10 +11502,10 @@
     </row>
     <row r="513" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1135</v>
+        <v>1109</v>
       </c>
       <c r="B513" t="s">
-        <v>1136</v>
+        <v>1110</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>6</v>
@@ -11426,10 +11516,10 @@
     </row>
     <row r="514" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1137</v>
+        <v>1111</v>
       </c>
       <c r="B514" t="s">
-        <v>1138</v>
+        <v>1112</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>6</v>
@@ -11440,10 +11530,10 @@
     </row>
     <row r="515" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1139</v>
+        <v>1113</v>
       </c>
       <c r="B515" t="s">
-        <v>1140</v>
+        <v>1114</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>6</v>
@@ -11454,10 +11544,10 @@
     </row>
     <row r="516" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1141</v>
+        <v>1115</v>
       </c>
       <c r="B516" t="s">
-        <v>1142</v>
+        <v>1116</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>6</v>
@@ -11468,10 +11558,10 @@
     </row>
     <row r="517" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>1145</v>
+        <v>1117</v>
       </c>
       <c r="B517" t="s">
-        <v>1146</v>
+        <v>1118</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>6</v>
@@ -11482,10 +11572,10 @@
     </row>
     <row r="518" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1147</v>
+        <v>1119</v>
       </c>
       <c r="B518" t="s">
-        <v>1148</v>
+        <v>1120</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>6</v>
@@ -11496,10 +11586,10 @@
     </row>
     <row r="519" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1149</v>
+        <v>1121</v>
       </c>
       <c r="B519" t="s">
-        <v>1150</v>
+        <v>1122</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>6</v>
@@ -11510,10 +11600,10 @@
     </row>
     <row r="520" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1151</v>
+        <v>1123</v>
       </c>
       <c r="B520" t="s">
-        <v>1152</v>
+        <v>1124</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>6</v>
@@ -11524,10 +11614,10 @@
     </row>
     <row r="521" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1153</v>
+        <v>1125</v>
       </c>
       <c r="B521" t="s">
-        <v>1154</v>
+        <v>1126</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>6</v>
@@ -11538,10 +11628,10 @@
     </row>
     <row r="522" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1155</v>
+        <v>1127</v>
       </c>
       <c r="B522" t="s">
-        <v>1156</v>
+        <v>1128</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>6</v>
@@ -11552,10 +11642,10 @@
     </row>
     <row r="523" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1157</v>
+        <v>1131</v>
       </c>
       <c r="B523" t="s">
-        <v>1158</v>
+        <v>1132</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>6</v>
@@ -11566,10 +11656,10 @@
     </row>
     <row r="524" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1159</v>
+        <v>1133</v>
       </c>
       <c r="B524" t="s">
-        <v>1160</v>
+        <v>1134</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>6</v>
@@ -11580,10 +11670,10 @@
     </row>
     <row r="525" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1161</v>
+        <v>1135</v>
       </c>
       <c r="B525" t="s">
-        <v>1162</v>
+        <v>1136</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>6</v>
@@ -11594,10 +11684,10 @@
     </row>
     <row r="526" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>1163</v>
+        <v>1137</v>
       </c>
       <c r="B526" t="s">
-        <v>1164</v>
+        <v>1138</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>6</v>
@@ -11608,10 +11698,10 @@
     </row>
     <row r="527" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>1165</v>
+        <v>1139</v>
       </c>
       <c r="B527" t="s">
-        <v>1166</v>
+        <v>1140</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>6</v>
@@ -11622,10 +11712,10 @@
     </row>
     <row r="528" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1167</v>
+        <v>1141</v>
       </c>
       <c r="B528" t="s">
-        <v>1168</v>
+        <v>1142</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>6</v>
@@ -11636,10 +11726,10 @@
     </row>
     <row r="529" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>1169</v>
+        <v>1143</v>
       </c>
       <c r="B529" t="s">
-        <v>1170</v>
+        <v>1144</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>6</v>
@@ -11650,10 +11740,10 @@
     </row>
     <row r="530" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>1171</v>
+        <v>1145</v>
       </c>
       <c r="B530" t="s">
-        <v>1172</v>
+        <v>1146</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>6</v>
@@ -11664,10 +11754,10 @@
     </row>
     <row r="531" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>1173</v>
+        <v>1147</v>
       </c>
       <c r="B531" t="s">
-        <v>1174</v>
+        <v>1148</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>6</v>
@@ -11678,10 +11768,10 @@
     </row>
     <row r="532" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1175</v>
+        <v>1149</v>
       </c>
       <c r="B532" t="s">
-        <v>1176</v>
+        <v>1150</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>6</v>
@@ -11692,10 +11782,10 @@
     </row>
     <row r="533" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1177</v>
+        <v>1151</v>
       </c>
       <c r="B533" t="s">
-        <v>1178</v>
+        <v>1152</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>6</v>
@@ -11706,10 +11796,10 @@
     </row>
     <row r="534" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>1179</v>
+        <v>1153</v>
       </c>
       <c r="B534" t="s">
-        <v>1180</v>
+        <v>1154</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>6</v>
@@ -11720,10 +11810,10 @@
     </row>
     <row r="535" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>1181</v>
+        <v>1155</v>
       </c>
       <c r="B535" t="s">
-        <v>1182</v>
+        <v>1156</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>6</v>
@@ -11734,10 +11824,10 @@
     </row>
     <row r="536" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>1185</v>
+        <v>1157</v>
       </c>
       <c r="B536" t="s">
-        <v>1186</v>
+        <v>1158</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>6</v>
@@ -11748,10 +11838,10 @@
     </row>
     <row r="537" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1187</v>
+        <v>1159</v>
       </c>
       <c r="B537" t="s">
-        <v>1188</v>
+        <v>1160</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -11762,10 +11852,10 @@
     </row>
     <row r="538" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>1189</v>
+        <v>1161</v>
       </c>
       <c r="B538" t="s">
-        <v>1190</v>
+        <v>1162</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>6</v>
@@ -11776,10 +11866,10 @@
     </row>
     <row r="539" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>1191</v>
+        <v>1163</v>
       </c>
       <c r="B539" t="s">
-        <v>1192</v>
+        <v>1164</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>6</v>
@@ -11790,10 +11880,10 @@
     </row>
     <row r="540" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1193</v>
+        <v>1165</v>
       </c>
       <c r="B540" t="s">
-        <v>1194</v>
+        <v>1166</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>6</v>
@@ -11804,10 +11894,10 @@
     </row>
     <row r="541" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1195</v>
+        <v>1167</v>
       </c>
       <c r="B541" t="s">
-        <v>1196</v>
+        <v>1168</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -11818,10 +11908,10 @@
     </row>
     <row r="542" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1197</v>
+        <v>1173</v>
       </c>
       <c r="B542" t="s">
-        <v>1198</v>
+        <v>1174</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>6</v>
@@ -11832,10 +11922,10 @@
     </row>
     <row r="543" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1201</v>
+        <v>1175</v>
       </c>
       <c r="B543" t="s">
-        <v>1202</v>
+        <v>1176</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>6</v>
@@ -11846,10 +11936,10 @@
     </row>
     <row r="544" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>1203</v>
+        <v>1177</v>
       </c>
       <c r="B544" t="s">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>6</v>
@@ -11860,10 +11950,10 @@
     </row>
     <row r="545" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1205</v>
+        <v>1179</v>
       </c>
       <c r="B545" t="s">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>6</v>
@@ -11874,10 +11964,10 @@
     </row>
     <row r="546" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>1207</v>
+        <v>1181</v>
       </c>
       <c r="B546" t="s">
-        <v>1208</v>
+        <v>1182</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>6</v>
@@ -11888,10 +11978,10 @@
     </row>
     <row r="547" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1209</v>
+        <v>1183</v>
       </c>
       <c r="B547" t="s">
-        <v>1210</v>
+        <v>1184</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>6</v>
@@ -11902,10 +11992,10 @@
     </row>
     <row r="548" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1211</v>
+        <v>1185</v>
       </c>
       <c r="B548" t="s">
-        <v>1212</v>
+        <v>1186</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>6</v>
@@ -11916,10 +12006,10 @@
     </row>
     <row r="549" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>1213</v>
+        <v>1187</v>
       </c>
       <c r="B549" t="s">
-        <v>1214</v>
+        <v>1188</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>6</v>
@@ -11930,10 +12020,10 @@
     </row>
     <row r="550" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1215</v>
+        <v>1189</v>
       </c>
       <c r="B550" t="s">
-        <v>1216</v>
+        <v>1190</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>6</v>
@@ -11944,10 +12034,10 @@
     </row>
     <row r="551" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1217</v>
+        <v>1191</v>
       </c>
       <c r="B551" t="s">
-        <v>1218</v>
+        <v>1192</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>6</v>
@@ -11958,10 +12048,10 @@
     </row>
     <row r="552" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>1219</v>
+        <v>1193</v>
       </c>
       <c r="B552" t="s">
-        <v>1220</v>
+        <v>1194</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>6</v>
@@ -11972,10 +12062,10 @@
     </row>
     <row r="553" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>1221</v>
+        <v>1195</v>
       </c>
       <c r="B553" t="s">
-        <v>1222</v>
+        <v>1196</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>6</v>
@@ -11986,10 +12076,10 @@
     </row>
     <row r="554" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1223</v>
+        <v>1197</v>
       </c>
       <c r="B554" t="s">
-        <v>1224</v>
+        <v>1198</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>6</v>
@@ -12000,10 +12090,10 @@
     </row>
     <row r="555" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1225</v>
+        <v>1199</v>
       </c>
       <c r="B555" t="s">
-        <v>1226</v>
+        <v>1200</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>6</v>
@@ -12014,10 +12104,10 @@
     </row>
     <row r="556" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1227</v>
+        <v>1201</v>
       </c>
       <c r="B556" t="s">
-        <v>1228</v>
+        <v>1202</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>6</v>
@@ -12028,10 +12118,10 @@
     </row>
     <row r="557" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1229</v>
+        <v>1203</v>
       </c>
       <c r="B557" t="s">
-        <v>1230</v>
+        <v>1204</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>6</v>
@@ -12042,10 +12132,10 @@
     </row>
     <row r="558" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1231</v>
+        <v>1205</v>
       </c>
       <c r="B558" t="s">
-        <v>1232</v>
+        <v>1206</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>6</v>
@@ -12056,10 +12146,10 @@
     </row>
     <row r="559" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1233</v>
+        <v>1209</v>
       </c>
       <c r="B559" t="s">
-        <v>1234</v>
+        <v>1210</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>6</v>
@@ -12070,10 +12160,10 @@
     </row>
     <row r="560" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1235</v>
+        <v>1211</v>
       </c>
       <c r="B560" t="s">
-        <v>1236</v>
+        <v>1212</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>6</v>
@@ -12084,10 +12174,10 @@
     </row>
     <row r="561" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>1239</v>
+        <v>1213</v>
       </c>
       <c r="B561" t="s">
-        <v>1240</v>
+        <v>1214</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>6</v>
@@ -12098,10 +12188,10 @@
     </row>
     <row r="562" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>1241</v>
+        <v>1215</v>
       </c>
       <c r="B562" t="s">
-        <v>1242</v>
+        <v>1216</v>
       </c>
       <c r="C562" s="2" t="s">
         <v>6</v>
@@ -12112,10 +12202,10 @@
     </row>
     <row r="563" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1243</v>
+        <v>1217</v>
       </c>
       <c r="B563" t="s">
-        <v>1244</v>
+        <v>1218</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>6</v>
@@ -12126,10 +12216,10 @@
     </row>
     <row r="564" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1245</v>
+        <v>1219</v>
       </c>
       <c r="B564" t="s">
-        <v>1246</v>
+        <v>1220</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>6</v>
@@ -12140,10 +12230,10 @@
     </row>
     <row r="565" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1247</v>
+        <v>1221</v>
       </c>
       <c r="B565" t="s">
-        <v>1248</v>
+        <v>1222</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>6</v>
@@ -12154,10 +12244,10 @@
     </row>
     <row r="566" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1249</v>
+        <v>1225</v>
       </c>
       <c r="B566" t="s">
-        <v>1250</v>
+        <v>1226</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>6</v>
@@ -12168,10 +12258,10 @@
     </row>
     <row r="567" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1251</v>
+        <v>1227</v>
       </c>
       <c r="B567" t="s">
-        <v>1252</v>
+        <v>1228</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>6</v>
@@ -12182,10 +12272,10 @@
     </row>
     <row r="568" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>1253</v>
+        <v>1229</v>
       </c>
       <c r="B568" t="s">
-        <v>1254</v>
+        <v>1230</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>6</v>
@@ -12196,10 +12286,10 @@
     </row>
     <row r="569" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>1255</v>
+        <v>1231</v>
       </c>
       <c r="B569" t="s">
-        <v>1256</v>
+        <v>1232</v>
       </c>
       <c r="C569" s="2" t="s">
         <v>6</v>
@@ -12210,10 +12300,10 @@
     </row>
     <row r="570" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1257</v>
+        <v>1233</v>
       </c>
       <c r="B570" t="s">
-        <v>1258</v>
+        <v>1234</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>6</v>
@@ -12224,10 +12314,10 @@
     </row>
     <row r="571" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>1259</v>
+        <v>1235</v>
       </c>
       <c r="B571" t="s">
-        <v>1260</v>
+        <v>1236</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>6</v>
@@ -12238,10 +12328,10 @@
     </row>
     <row r="572" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>1261</v>
+        <v>1237</v>
       </c>
       <c r="B572" t="s">
-        <v>1262</v>
+        <v>1238</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>6</v>
@@ -12252,10 +12342,10 @@
     </row>
     <row r="573" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>1263</v>
+        <v>1239</v>
       </c>
       <c r="B573" t="s">
-        <v>1264</v>
+        <v>1240</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>6</v>
@@ -12266,10 +12356,10 @@
     </row>
     <row r="574" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>1265</v>
+        <v>1241</v>
       </c>
       <c r="B574" t="s">
-        <v>1266</v>
+        <v>1242</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>6</v>
@@ -12280,10 +12370,10 @@
     </row>
     <row r="575" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>1267</v>
+        <v>1243</v>
       </c>
       <c r="B575" t="s">
-        <v>1268</v>
+        <v>1244</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>6</v>
@@ -12294,221 +12384,221 @@
     </row>
     <row r="576" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C576" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D576" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A577" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D577" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A578" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C578" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D578" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A579" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D579" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A580" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C580" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D580" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A581" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D581" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A582" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C582" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D582" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A583" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C583" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D583" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A584" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C584" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D584" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A585" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C585" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D585" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A586" t="s">
         <v>1269</v>
       </c>
-      <c r="B576" t="s">
+      <c r="B586" t="s">
         <v>1270</v>
       </c>
-      <c r="C576" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D576" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="577" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A577" t="s">
+      <c r="C586" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D586" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A587" t="s">
         <v>1271</v>
       </c>
-      <c r="B577" t="s">
+      <c r="B587" t="s">
         <v>1272</v>
       </c>
-      <c r="C577" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D577" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="578" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A578" t="s">
+      <c r="C587" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D587" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A588" t="s">
         <v>1273</v>
       </c>
-      <c r="B578" t="s">
+      <c r="B588" t="s">
         <v>1274</v>
       </c>
-      <c r="C578" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D578" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="579" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A579" t="s">
+      <c r="C588" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D588" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A589" t="s">
         <v>1275</v>
       </c>
-      <c r="B579" t="s">
+      <c r="B589" t="s">
         <v>1276</v>
       </c>
-      <c r="C579" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D579" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="580" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A580" t="s">
+      <c r="C589" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D589" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A590" t="s">
         <v>1277</v>
       </c>
-      <c r="B580" t="s">
+      <c r="B590" t="s">
         <v>1278</v>
       </c>
-      <c r="C580" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D580" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="581" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A581" t="s">
+      <c r="C590" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D590" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A591" t="s">
         <v>1279</v>
       </c>
-      <c r="B581" t="s">
+      <c r="B591" t="s">
         <v>1280</v>
       </c>
-      <c r="C581" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D581" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="582" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A582" t="s">
-        <v>5</v>
-      </c>
-      <c r="B582" t="s">
-        <v>5</v>
-      </c>
-      <c r="C582" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E582" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="583" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A583" t="s">
-        <v>57</v>
-      </c>
-      <c r="B583" t="s">
-        <v>58</v>
-      </c>
-      <c r="C583" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E583" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="584" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A584" t="s">
-        <v>121</v>
-      </c>
-      <c r="B584" t="s">
-        <v>122</v>
-      </c>
-      <c r="C584" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E584" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="585" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A585" t="s">
-        <v>123</v>
-      </c>
-      <c r="B585" t="s">
-        <v>124</v>
-      </c>
-      <c r="C585" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E585" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="586" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A586" t="s">
-        <v>143</v>
-      </c>
-      <c r="B586" t="s">
-        <v>144</v>
-      </c>
-      <c r="C586" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E586" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="587" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A587" t="s">
-        <v>145</v>
-      </c>
-      <c r="B587" t="s">
-        <v>146</v>
-      </c>
-      <c r="C587" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D587" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="588" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A588" t="s">
-        <v>147</v>
-      </c>
-      <c r="B588" t="s">
-        <v>148</v>
-      </c>
-      <c r="C588" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D588" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="589" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A589" t="s">
-        <v>149</v>
-      </c>
-      <c r="B589" t="s">
-        <v>150</v>
-      </c>
-      <c r="C589" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E589" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="590" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A590" t="s">
-        <v>201</v>
-      </c>
-      <c r="B590" t="s">
-        <v>202</v>
-      </c>
-      <c r="C590" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D590" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="591" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A591" t="s">
-        <v>209</v>
-      </c>
-      <c r="B591" t="s">
-        <v>210</v>
-      </c>
       <c r="C591" s="2" t="s">
         <v>6</v>
       </c>
@@ -12516,68 +12606,68 @@
         <v>10</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>217</v>
+        <v>1281</v>
       </c>
       <c r="B592" t="s">
-        <v>218</v>
+        <v>1282</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E592" t="s">
-        <v>7</v>
+      <c r="D592" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="593" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>221</v>
+        <v>1283</v>
       </c>
       <c r="B593" t="s">
-        <v>222</v>
+        <v>1284</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E593" t="s">
-        <v>7</v>
+      <c r="D593" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="594" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>243</v>
+        <v>1285</v>
       </c>
       <c r="B594" t="s">
-        <v>244</v>
+        <v>1286</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E594" t="s">
-        <v>7</v>
+      <c r="D594" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="595" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>269</v>
+        <v>1287</v>
       </c>
       <c r="B595" t="s">
-        <v>270</v>
+        <v>1288</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E595" t="s">
-        <v>7</v>
+      <c r="D595" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="596" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>281</v>
+        <v>1289</v>
       </c>
       <c r="B596" t="s">
-        <v>282</v>
+        <v>1290</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>6</v>
@@ -12588,10 +12678,10 @@
     </row>
     <row r="597" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>295</v>
+        <v>1291</v>
       </c>
       <c r="B597" t="s">
-        <v>296</v>
+        <v>1292</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>6</v>
@@ -12602,108 +12692,108 @@
     </row>
     <row r="598" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>297</v>
+        <v>1293</v>
       </c>
       <c r="B598" t="s">
-        <v>298</v>
+        <v>1294</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E598" t="s">
-        <v>7</v>
+      <c r="D598" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="599" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>305</v>
+        <v>1295</v>
       </c>
       <c r="B599" t="s">
-        <v>306</v>
+        <v>1296</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E599" t="s">
-        <v>7</v>
+      <c r="D599" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="600" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>315</v>
+        <v>1297</v>
       </c>
       <c r="B600" t="s">
-        <v>316</v>
+        <v>1298</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E600" t="s">
-        <v>7</v>
+      <c r="D600" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="601" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>339</v>
+        <v>1299</v>
       </c>
       <c r="B601" t="s">
-        <v>340</v>
+        <v>1300</v>
       </c>
       <c r="C601" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E601" t="s">
-        <v>7</v>
+      <c r="D601" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="602" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>383</v>
+        <v>1301</v>
       </c>
       <c r="B602" t="s">
-        <v>384</v>
+        <v>1302</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E602" t="s">
-        <v>7</v>
+      <c r="D602" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="603" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>389</v>
+        <v>1303</v>
       </c>
       <c r="B603" t="s">
-        <v>390</v>
+        <v>1304</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E603" t="s">
-        <v>7</v>
+      <c r="D603" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="604" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>435</v>
+        <v>1309</v>
       </c>
       <c r="B604" t="s">
-        <v>436</v>
+        <v>1310</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E604" t="s">
-        <v>7</v>
+      <c r="D604" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="605" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>455</v>
+        <v>5</v>
       </c>
       <c r="B605" t="s">
-        <v>456</v>
+        <v>5</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>6</v>
@@ -12714,52 +12804,52 @@
     </row>
     <row r="606" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>527</v>
+        <v>57</v>
       </c>
       <c r="B606" t="s">
-        <v>528</v>
+        <v>58</v>
       </c>
       <c r="C606" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D606" t="s">
-        <v>10</v>
+      <c r="E606" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="607" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>529</v>
+        <v>89</v>
       </c>
       <c r="B607" t="s">
-        <v>530</v>
+        <v>90</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D607" t="s">
-        <v>10</v>
+      <c r="E607" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="608" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>599</v>
+        <v>91</v>
       </c>
       <c r="B608" t="s">
-        <v>600</v>
+        <v>92</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D608" t="s">
-        <v>10</v>
+      <c r="E608" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="609" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>641</v>
+        <v>119</v>
       </c>
       <c r="B609" t="s">
-        <v>642</v>
+        <v>120</v>
       </c>
       <c r="C609" s="2" t="s">
         <v>6</v>
@@ -12770,10 +12860,10 @@
     </row>
     <row r="610" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>643</v>
+        <v>127</v>
       </c>
       <c r="B610" t="s">
-        <v>644</v>
+        <v>128</v>
       </c>
       <c r="C610" s="2" t="s">
         <v>6</v>
@@ -12784,10 +12874,10 @@
     </row>
     <row r="611" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>693</v>
+        <v>129</v>
       </c>
       <c r="B611" t="s">
-        <v>694</v>
+        <v>130</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>6</v>
@@ -12798,10 +12888,10 @@
     </row>
     <row r="612" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>717</v>
+        <v>149</v>
       </c>
       <c r="B612" t="s">
-        <v>718</v>
+        <v>150</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>6</v>
@@ -12812,38 +12902,38 @@
     </row>
     <row r="613" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>727</v>
+        <v>155</v>
       </c>
       <c r="B613" t="s">
-        <v>728</v>
+        <v>156</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D613" t="s">
-        <v>10</v>
+      <c r="E613" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="614" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>733</v>
+        <v>201</v>
       </c>
       <c r="B614" t="s">
-        <v>734</v>
+        <v>202</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E614" t="s">
-        <v>7</v>
+      <c r="D614" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="615" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>799</v>
+        <v>203</v>
       </c>
       <c r="B615" t="s">
-        <v>800</v>
+        <v>204</v>
       </c>
       <c r="C615" s="2" t="s">
         <v>6</v>
@@ -12854,10 +12944,10 @@
     </row>
     <row r="616" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>801</v>
+        <v>227</v>
       </c>
       <c r="B616" t="s">
-        <v>802</v>
+        <v>228</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>6</v>
@@ -12868,52 +12958,52 @@
     </row>
     <row r="617" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>819</v>
+        <v>231</v>
       </c>
       <c r="B617" t="s">
-        <v>820</v>
+        <v>232</v>
       </c>
       <c r="C617" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D617" t="s">
-        <v>10</v>
+      <c r="E617" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="618" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>821</v>
+        <v>253</v>
       </c>
       <c r="B618" t="s">
-        <v>822</v>
+        <v>254</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D618" t="s">
-        <v>10</v>
+      <c r="E618" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="619" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>845</v>
+        <v>279</v>
       </c>
       <c r="B619" t="s">
-        <v>846</v>
+        <v>280</v>
       </c>
       <c r="C619" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D619" t="s">
-        <v>10</v>
+      <c r="E619" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="620" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>851</v>
+        <v>307</v>
       </c>
       <c r="B620" t="s">
-        <v>852</v>
+        <v>308</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>6</v>
@@ -12924,38 +13014,38 @@
     </row>
     <row r="621" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>869</v>
+        <v>315</v>
       </c>
       <c r="B621" t="s">
-        <v>870</v>
+        <v>316</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D621" t="s">
-        <v>10</v>
+      <c r="E621" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="622" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>897</v>
+        <v>325</v>
       </c>
       <c r="B622" t="s">
-        <v>898</v>
+        <v>326</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D622" t="s">
-        <v>10</v>
+      <c r="E622" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="623" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>961</v>
+        <v>349</v>
       </c>
       <c r="B623" t="s">
-        <v>962</v>
+        <v>350</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>6</v>
@@ -12966,38 +13056,38 @@
     </row>
     <row r="624" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>979</v>
+        <v>393</v>
       </c>
       <c r="B624" t="s">
-        <v>980</v>
+        <v>394</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D624" t="s">
-        <v>10</v>
+      <c r="E624" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="625" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>985</v>
+        <v>399</v>
       </c>
       <c r="B625" t="s">
-        <v>986</v>
+        <v>400</v>
       </c>
       <c r="C625" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D625" t="s">
-        <v>10</v>
+      <c r="E625" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="626" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>987</v>
+        <v>419</v>
       </c>
       <c r="B626" t="s">
-        <v>988</v>
+        <v>420</v>
       </c>
       <c r="C626" s="2" t="s">
         <v>6</v>
@@ -13008,10 +13098,10 @@
     </row>
     <row r="627" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1013</v>
+        <v>447</v>
       </c>
       <c r="B627" t="s">
-        <v>1014</v>
+        <v>448</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>6</v>
@@ -13022,10 +13112,10 @@
     </row>
     <row r="628" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1019</v>
+        <v>467</v>
       </c>
       <c r="B628" t="s">
-        <v>1020</v>
+        <v>468</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>6</v>
@@ -13036,10 +13126,10 @@
     </row>
     <row r="629" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1027</v>
+        <v>495</v>
       </c>
       <c r="B629" t="s">
-        <v>1028</v>
+        <v>496</v>
       </c>
       <c r="C629" s="2" t="s">
         <v>6</v>
@@ -13050,24 +13140,24 @@
     </row>
     <row r="630" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1033</v>
+        <v>497</v>
       </c>
       <c r="B630" t="s">
-        <v>1034</v>
+        <v>498</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E630" t="s">
-        <v>7</v>
+      <c r="D630" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="631" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1037</v>
+        <v>659</v>
       </c>
       <c r="B631" t="s">
-        <v>1038</v>
+        <v>660</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>6</v>
@@ -13078,38 +13168,38 @@
     </row>
     <row r="632" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1055</v>
+        <v>709</v>
       </c>
       <c r="B632" t="s">
-        <v>1056</v>
+        <v>710</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D632" t="s">
-        <v>10</v>
+      <c r="E632" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="633" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1057</v>
+        <v>733</v>
       </c>
       <c r="B633" t="s">
-        <v>1058</v>
+        <v>734</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D633" t="s">
-        <v>10</v>
+      <c r="E633" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="634" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>1109</v>
+        <v>749</v>
       </c>
       <c r="B634" t="s">
-        <v>1110</v>
+        <v>750</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>6</v>
@@ -13120,10 +13210,10 @@
     </row>
     <row r="635" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1143</v>
+        <v>751</v>
       </c>
       <c r="B635" t="s">
-        <v>1144</v>
+        <v>752</v>
       </c>
       <c r="C635" s="2" t="s">
         <v>6</v>
@@ -13134,24 +13224,24 @@
     </row>
     <row r="636" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>1183</v>
+        <v>769</v>
       </c>
       <c r="B636" t="s">
-        <v>1184</v>
+        <v>770</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E636" t="s">
-        <v>7</v>
+      <c r="D636" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="637" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1199</v>
+        <v>821</v>
       </c>
       <c r="B637" t="s">
-        <v>1200</v>
+        <v>822</v>
       </c>
       <c r="C637" s="2" t="s">
         <v>6</v>
@@ -13162,10 +13252,10 @@
     </row>
     <row r="638" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>1237</v>
+        <v>871</v>
       </c>
       <c r="B638" t="s">
-        <v>1238</v>
+        <v>872</v>
       </c>
       <c r="C638" s="2" t="s">
         <v>6</v>
@@ -13174,19 +13264,229 @@
         <v>7</v>
       </c>
     </row>
+    <row r="639" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A639" t="s">
+        <v>981</v>
+      </c>
+      <c r="B639" t="s">
+        <v>982</v>
+      </c>
+      <c r="C639" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E639" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A640" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B640" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C640" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E640" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A641" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C641" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E641" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A642" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B642" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C642" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E642" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A643" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C643" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E643" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A644" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B644" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C644" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E644" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A645" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B645" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C645" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E645" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A646" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C646" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E646" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A647" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C647" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E647" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A648" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C648" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E648" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A649" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B649" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C649" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E649" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A650" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C650" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D650" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A651" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C651" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E651" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A652" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C652" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D652" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A653" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B653" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C653" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D653" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E638">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E653">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D638" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D653" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C582" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C605" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
@@ -13211,7 +13511,7 @@
     <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
     <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
     <hyperlink ref="C25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C583" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C606" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
     <hyperlink ref="C26" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
     <hyperlink ref="C27" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
     <hyperlink ref="C28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
@@ -13227,172 +13527,172 @@
     <hyperlink ref="C38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
     <hyperlink ref="C39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
     <hyperlink ref="C40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C48" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C49" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C50" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C51" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C52" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C53" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C54" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C55" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C56" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C584" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C585" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C57" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C58" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C59" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C60" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C61" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C62" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C63" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C64" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C65" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C586" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C587" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C588" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C589" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C607" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C608" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C41" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C42" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C43" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C44" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C45" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C46" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C47" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C48" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C49" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C50" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C51" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C52" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C53" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C609" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C54" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C55" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C56" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C610" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="C611" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C57" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C58" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C59" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C60" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C61" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C62" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C63" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C64" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C65" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C612" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
     <hyperlink ref="C66" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
     <hyperlink ref="C67" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C68" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C69" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C70" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C71" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C72" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C73" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C74" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C75" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C76" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C77" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C78" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C79" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C80" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C81" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C82" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C83" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C84" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C85" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C86" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C87" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C88" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C89" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C90" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C590" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C91" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C92" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C93" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C591" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C94" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C95" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C96" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="C592" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="C613" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C68" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C69" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C70" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C71" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C72" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C73" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C74" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C75" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C76" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C77" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C78" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C79" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C80" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C81" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C82" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C83" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C84" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C85" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C86" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C87" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C88" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C89" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C614" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C615" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C90" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C91" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C92" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C93" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C94" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C95" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C96" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
     <hyperlink ref="C97" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="C593" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C98" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="C99" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C100" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C98" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="C99" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C100" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C616" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
     <hyperlink ref="C101" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C102" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C103" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C104" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="C105" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C106" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="C107" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C594" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C617" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C102" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C103" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C104" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="C105" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C106" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="C107" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
     <hyperlink ref="C108" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
     <hyperlink ref="C109" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
     <hyperlink ref="C110" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
     <hyperlink ref="C111" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="C112" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C113" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C114" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C115" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="C116" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C117" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="C118" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C119" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="C595" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="C618" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="C112" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C113" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C114" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C115" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="C116" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C117" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C118" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C119" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
     <hyperlink ref="C120" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
     <hyperlink ref="C121" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
     <hyperlink ref="C122" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
     <hyperlink ref="C123" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C124" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="C596" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C619" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="C124" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
     <hyperlink ref="C125" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
     <hyperlink ref="C126" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
     <hyperlink ref="C127" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
     <hyperlink ref="C128" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
     <hyperlink ref="C129" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
     <hyperlink ref="C130" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C597" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C598" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C131" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C132" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C133" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C599" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C134" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C135" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C136" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C137" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C600" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C138" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C139" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C140" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C141" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C142" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C143" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C144" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C145" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C146" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C147" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C148" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C601" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C149" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C150" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C151" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C152" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C153" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C154" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C155" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C156" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C157" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C158" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C159" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C160" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C161" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C162" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C163" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C164" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C165" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C166" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C167" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C168" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C169" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C602" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C170" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C171" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C603" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C172" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C173" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C174" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C175" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C176" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C177" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C178" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C179" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C180" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C181" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C182" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C183" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C184" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="C185" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C186" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C131" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C132" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C133" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C134" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C135" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C136" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C620" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C137" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C138" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C139" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C621" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C140" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C141" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C142" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C143" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C622" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C144" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C145" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C146" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C147" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C148" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C149" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C150" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C151" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="C152" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C153" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C154" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C623" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C155" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C156" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C157" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C158" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C159" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C160" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C161" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C162" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C163" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C164" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C165" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C166" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C167" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C168" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C169" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C170" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C171" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C172" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C173" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C174" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C175" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C624" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C176" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C177" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C625" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C178" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C179" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C180" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C181" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C182" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C183" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C184" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C185" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C186" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C626" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
     <hyperlink ref="C187" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
     <hyperlink ref="C188" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
     <hyperlink ref="C189" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
@@ -13400,23 +13700,23 @@
     <hyperlink ref="C191" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
     <hyperlink ref="C192" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
     <hyperlink ref="C193" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C604" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C194" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C195" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C196" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C197" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C198" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C199" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C194" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C195" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C196" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C197" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C198" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C199" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C627" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
     <hyperlink ref="C200" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
     <hyperlink ref="C201" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
     <hyperlink ref="C202" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C605" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C203" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C204" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C205" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C206" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C207" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C208" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C203" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C204" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C205" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C206" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C207" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C208" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C628" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
     <hyperlink ref="C209" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
     <hyperlink ref="C210" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
     <hyperlink ref="C211" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
@@ -13430,24 +13730,24 @@
     <hyperlink ref="C219" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
     <hyperlink ref="C220" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
     <hyperlink ref="C221" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="C222" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="C223" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="C224" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="C225" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="C226" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="C227" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="C228" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="C229" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="C230" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="C231" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="C232" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="C233" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="C234" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="C235" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="C236" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="C237" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="C606" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="C607" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="C629" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C630" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="C222" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="C223" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="C224" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="C225" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="C226" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="C227" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="C228" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="C229" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="C230" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C231" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="C232" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="C233" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="C234" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="C235" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C236" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="C237" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
     <hyperlink ref="C238" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
     <hyperlink ref="C239" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
     <hyperlink ref="C240" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
@@ -13482,347 +13782,362 @@
     <hyperlink ref="C269" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
     <hyperlink ref="C270" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
     <hyperlink ref="C271" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C608" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C272" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="C273" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="C274" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="C275" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="C276" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C277" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C278" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C279" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C280" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C281" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C282" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C283" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C284" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="C285" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="C286" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="C287" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="C288" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C289" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C290" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C291" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C609" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C610" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C292" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="C293" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C294" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C295" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C296" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C297" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C298" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C299" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C300" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C301" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C302" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C303" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C304" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C305" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C306" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C307" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C308" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C309" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C310" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C311" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C312" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C313" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C314" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C315" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C611" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C316" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C317" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C318" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C319" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C320" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C321" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C322" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="C323" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="C324" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C325" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C326" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C612" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C327" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C328" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="C329" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C330" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C613" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C331" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C332" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C614" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C333" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C334" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C335" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C336" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C337" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C338" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C339" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C340" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C341" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C342" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C343" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C344" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C345" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C346" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C347" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C348" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C349" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C350" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C351" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C352" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C353" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C354" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C355" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C356" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C357" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C358" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C359" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C360" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C361" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C362" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C363" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C364" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C615" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C616" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C365" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C366" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C367" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C368" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C369" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C370" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C371" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C372" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C617" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C618" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C373" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C374" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C375" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C376" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C377" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C378" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C379" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C380" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C381" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C382" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C383" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C619" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C384" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C385" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C620" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C386" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C387" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C388" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C389" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C390" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C391" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C392" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C393" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C621" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C394" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C395" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C396" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C397" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C398" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C399" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C400" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C401" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C402" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C403" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C404" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C405" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C406" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C622" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C407" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C408" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C409" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C410" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C411" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C412" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C413" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C414" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C415" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C416" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C417" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C418" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C419" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C420" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C421" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C422" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C423" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C424" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C425" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C426" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C427" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C428" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C429" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C430" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C431" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C432" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C433" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C434" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C435" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C436" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C437" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C623" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C438" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C439" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C440" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C441" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C442" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C443" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C444" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C445" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C624" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C446" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C447" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C625" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C626" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C448" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C449" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C450" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C451" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C452" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C453" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C454" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C455" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C456" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C457" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C458" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C459" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C627" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C460" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C461" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C628" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="C462" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C463" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="C464" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="C629" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C465" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="C466" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C630" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C467" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C631" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C468" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="C469" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="C470" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="C471" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="C472" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="C473" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="C474" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="C475" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="C632" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="C633" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C476" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C477" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="C478" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="C479" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="C480" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="C481" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="C482" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="C483" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="C484" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="C485" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="C486" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="C487" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="C488" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="C489" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="C490" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C491" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C492" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C493" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C494" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="C495" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="C496" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="C497" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
-    <hyperlink ref="C498" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
-    <hyperlink ref="C499" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
-    <hyperlink ref="C500" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
-    <hyperlink ref="C634" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
-    <hyperlink ref="C501" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
-    <hyperlink ref="C502" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
-    <hyperlink ref="C503" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
-    <hyperlink ref="C504" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
-    <hyperlink ref="C505" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
-    <hyperlink ref="C506" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
-    <hyperlink ref="C507" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
-    <hyperlink ref="C508" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
-    <hyperlink ref="C509" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
-    <hyperlink ref="C510" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
-    <hyperlink ref="C511" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
-    <hyperlink ref="C512" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
-    <hyperlink ref="C513" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
-    <hyperlink ref="C514" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
-    <hyperlink ref="C515" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
-    <hyperlink ref="C516" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
-    <hyperlink ref="C635" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
-    <hyperlink ref="C517" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
-    <hyperlink ref="C518" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
-    <hyperlink ref="C519" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
-    <hyperlink ref="C520" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
-    <hyperlink ref="C521" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
-    <hyperlink ref="C522" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
-    <hyperlink ref="C523" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
-    <hyperlink ref="C524" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
-    <hyperlink ref="C525" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
-    <hyperlink ref="C526" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
-    <hyperlink ref="C527" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
-    <hyperlink ref="C528" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
-    <hyperlink ref="C529" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
-    <hyperlink ref="C530" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
-    <hyperlink ref="C531" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
-    <hyperlink ref="C532" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
-    <hyperlink ref="C533" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
-    <hyperlink ref="C534" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
-    <hyperlink ref="C535" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
-    <hyperlink ref="C636" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
-    <hyperlink ref="C536" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
-    <hyperlink ref="C537" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
-    <hyperlink ref="C538" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
-    <hyperlink ref="C539" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
-    <hyperlink ref="C540" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
-    <hyperlink ref="C541" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
-    <hyperlink ref="C542" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
-    <hyperlink ref="C637" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
-    <hyperlink ref="C543" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
-    <hyperlink ref="C544" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
-    <hyperlink ref="C545" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
-    <hyperlink ref="C546" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
-    <hyperlink ref="C547" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
-    <hyperlink ref="C548" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
-    <hyperlink ref="C549" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
-    <hyperlink ref="C550" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
-    <hyperlink ref="C551" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
-    <hyperlink ref="C552" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
-    <hyperlink ref="C553" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
-    <hyperlink ref="C554" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
-    <hyperlink ref="C555" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
-    <hyperlink ref="C556" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
-    <hyperlink ref="C557" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
-    <hyperlink ref="C558" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
-    <hyperlink ref="C559" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
-    <hyperlink ref="C560" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
-    <hyperlink ref="C638" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
-    <hyperlink ref="C561" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
-    <hyperlink ref="C562" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
-    <hyperlink ref="C563" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
-    <hyperlink ref="C564" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
-    <hyperlink ref="C565" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
-    <hyperlink ref="C566" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
-    <hyperlink ref="C567" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
-    <hyperlink ref="C568" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
-    <hyperlink ref="C569" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
-    <hyperlink ref="C570" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
-    <hyperlink ref="C571" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
-    <hyperlink ref="C572" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
-    <hyperlink ref="C573" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
-    <hyperlink ref="C574" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
-    <hyperlink ref="C575" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
-    <hyperlink ref="C576" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
-    <hyperlink ref="C577" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
-    <hyperlink ref="C578" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
-    <hyperlink ref="C579" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
-    <hyperlink ref="C580" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
-    <hyperlink ref="C581" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
+    <hyperlink ref="C272" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C273" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C274" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="C275" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C276" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="C277" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="C278" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C279" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C280" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C281" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C282" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C283" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C284" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C285" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C286" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="C287" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="C288" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="C289" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C290" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C291" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C292" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C293" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C294" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C295" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C296" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="C297" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C298" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C299" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C300" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C301" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C631" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C302" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C303" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C304" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C305" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C306" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C307" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C308" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C309" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C310" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C311" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C312" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C313" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C314" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C315" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C316" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C317" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C318" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C319" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C320" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C321" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C322" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C323" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C324" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C325" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C632" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C326" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C327" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C328" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C329" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C330" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C331" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C332" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C333" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C334" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C335" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C336" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C633" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C337" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C338" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C339" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C340" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C341" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C342" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C343" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C634" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C635" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C344" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C345" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C346" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C347" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C348" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C349" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C350" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C351" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C636" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C352" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C353" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C354" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C355" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C356" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C357" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C358" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C359" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C360" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C361" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C362" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C363" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C364" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C365" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C366" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C367" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C368" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C369" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C370" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C371" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C372" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C373" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C374" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C375" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C376" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C637" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C377" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C378" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C379" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C380" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C381" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C382" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C383" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C384" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C385" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C386" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C387" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C388" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C389" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C390" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C391" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C392" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C393" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C394" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C395" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C396" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C397" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C398" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C399" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C400" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C638" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C401" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C402" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C403" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C404" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C405" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C406" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C407" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C408" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C409" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C410" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C411" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C412" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C413" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C414" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C415" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C416" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C417" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C418" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C419" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C420" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C421" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C422" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C423" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C424" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C425" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C426" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C427" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C428" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C429" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C430" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C431" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C432" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C433" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C434" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C435" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C436" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C437" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C438" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C439" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C440" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C441" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C442" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C443" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C444" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C445" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C446" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C447" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C448" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C449" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C450" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C451" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C452" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C453" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C454" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C639" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C455" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C456" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C457" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C458" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C459" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C460" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C461" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C462" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C463" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C464" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C465" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C466" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C640" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C467" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C468" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C469" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C470" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C471" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C472" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C473" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C474" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C475" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C476" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C477" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C478" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C641" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C479" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C480" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C642" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C481" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="C482" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="C483" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="C484" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="C485" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="C486" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="C643" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="C487" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="C644" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C488" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C489" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="C490" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="C491" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="C492" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="C493" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="C494" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="C495" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="C496" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="C497" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="C498" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="C499" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="C500" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="C501" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="C502" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C503" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C504" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C505" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C506" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C507" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="C508" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="C509" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C510" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="C511" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="C512" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C513" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="C514" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C515" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="C516" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="C517" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="C518" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C519" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="C520" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="C521" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="C522" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="C645" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="C523" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="C524" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C525" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="C526" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C527" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="C528" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="C529" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="C530" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="C531" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="C532" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="C533" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="C534" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="C535" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="C536" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="C537" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="C538" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="C539" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="C540" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="C541" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="C646" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="C647" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="C542" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="C543" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="C544" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="C545" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="C546" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="C547" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="C548" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="C549" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="C550" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="C551" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="C552" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="C553" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="C554" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="C555" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="C556" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="C557" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="C558" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="C648" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="C559" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="C560" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C561" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="C562" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="C563" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="C564" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="C565" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
+    <hyperlink ref="C649" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
+    <hyperlink ref="C566" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
+    <hyperlink ref="C567" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
+    <hyperlink ref="C568" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
+    <hyperlink ref="C569" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
+    <hyperlink ref="C570" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
+    <hyperlink ref="C571" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
+    <hyperlink ref="C572" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
+    <hyperlink ref="C573" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
+    <hyperlink ref="C574" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
+    <hyperlink ref="C575" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
+    <hyperlink ref="C576" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
+    <hyperlink ref="C577" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
+    <hyperlink ref="C578" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
+    <hyperlink ref="C579" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
+    <hyperlink ref="C650" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
+    <hyperlink ref="C580" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
+    <hyperlink ref="C581" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
+    <hyperlink ref="C582" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
+    <hyperlink ref="C583" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
+    <hyperlink ref="C651" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
+    <hyperlink ref="C584" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
+    <hyperlink ref="C585" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
+    <hyperlink ref="C586" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
+    <hyperlink ref="C587" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
+    <hyperlink ref="C588" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
+    <hyperlink ref="C589" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
+    <hyperlink ref="C590" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
+    <hyperlink ref="C591" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
+    <hyperlink ref="C592" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
+    <hyperlink ref="C593" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
+    <hyperlink ref="C594" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
+    <hyperlink ref="C595" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
+    <hyperlink ref="C596" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
+    <hyperlink ref="C597" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
+    <hyperlink ref="C598" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
+    <hyperlink ref="C599" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
+    <hyperlink ref="C600" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
+    <hyperlink ref="C601" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
+    <hyperlink ref="C602" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
+    <hyperlink ref="C603" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
+    <hyperlink ref="C652" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
+    <hyperlink ref="C653" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
+    <hyperlink ref="C604" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F10D4F-4BB2-4C9F-958E-D92DBEF029EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFACFB6C-AC35-4660-AD39-3F6940265F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2773" uniqueCount="1391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="1403">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -430,6 +430,12 @@
     <t>Bennys badekar</t>
   </si>
   <si>
+    <t>beredskabet</t>
+  </si>
+  <si>
+    <t>Beredskabet</t>
+  </si>
+  <si>
     <t>bering sea gold</t>
   </si>
   <si>
@@ -1114,6 +1120,12 @@
     <t>En bedrager uden nåde</t>
   </si>
   <si>
+    <t>en ganske rar mand</t>
+  </si>
+  <si>
+    <t>En ganske rar mand</t>
+  </si>
+  <si>
     <t>et hus af ler</t>
   </si>
   <si>
@@ -1456,6 +1468,12 @@
     <t>Geniale hverdagsobjekter</t>
   </si>
   <si>
+    <t>genopbygningen af notre-dame</t>
+  </si>
+  <si>
+    <t>Genopbygningen af Notre-Dame</t>
+  </si>
+  <si>
     <t>gigantosaurus</t>
   </si>
   <si>
@@ -2488,6 +2506,12 @@
     <t>Mayafolkets tabte verden</t>
   </si>
   <si>
+    <t>me &amp; mickey</t>
+  </si>
+  <si>
+    <t>Me &amp; Mickey</t>
+  </si>
+  <si>
     <t>med kniven for struben</t>
   </si>
   <si>
@@ -2776,6 +2800,12 @@
     <t>Mysteriet om den danske nazidonor</t>
   </si>
   <si>
+    <t>mysteriet om den forsvundne svindlerdronning (2:3)</t>
+  </si>
+  <si>
+    <t>Mysteriet om den forsvundne svindlerdronning (2:3)</t>
+  </si>
+  <si>
     <t>måneskin i bakkekøbing</t>
   </si>
   <si>
@@ -3776,6 +3806,12 @@
   </si>
   <si>
     <t>Til Døden Skiller Os Ad</t>
+  </si>
+  <si>
+    <t>til middag hos</t>
+  </si>
+  <si>
+    <t>Til Middag Hos</t>
   </si>
   <si>
     <t>til salg i 100 år</t>
@@ -4559,7 +4595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E693"/>
+  <dimension ref="A1:E699"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -5148,10 +5184,10 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -5162,10 +5198,10 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6</v>
@@ -5176,10 +5212,10 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -5190,10 +5226,10 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
@@ -5204,10 +5240,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>6</v>
@@ -5218,10 +5254,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6</v>
@@ -5232,10 +5268,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6</v>
@@ -5246,10 +5282,10 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -5260,10 +5296,10 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>6</v>
@@ -5274,10 +5310,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>6</v>
@@ -5288,10 +5324,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B52" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
@@ -5302,10 +5338,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
@@ -5316,10 +5352,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
@@ -5330,10 +5366,10 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>6</v>
@@ -